--- a/Sales_Report actualizado 16 abr.xlsx
+++ b/Sales_Report actualizado 16 abr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eduardobazua/bza-reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D5EF8DE-2FB0-FB4F-B77E-F22E5158F655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35E3E45-1F7C-9241-AFB6-137E98A69B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="820" windowWidth="30240" windowHeight="17480" xr2:uid="{A69E99B4-FD75-534F-A443-AF5D6F49D11E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="421">
   <si>
     <t>ORDEN DE COMPRA</t>
   </si>
@@ -1314,10 +1314,10 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$$-80A]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="178" formatCode="0.0%"/>
-    <numFmt numFmtId="181" formatCode="mm/dd/yy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="mm/dd/yy;@"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1710,7 +1710,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1831,25 +1831,7 @@
     <xf numFmtId="8" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1866,14 +1848,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1902,12 +1881,10 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1918,16 +1895,21 @@
     <xf numFmtId="8" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1937,16 +1919,27 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -3408,7 +3401,7 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="59">
+      <c r="K19" s="115">
         <v>1135</v>
       </c>
       <c r="L19" s="26">
@@ -3488,7 +3481,7 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="59"/>
+      <c r="K20" s="115"/>
       <c r="L20" s="26">
         <v>1113002292</v>
       </c>
@@ -3566,7 +3559,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="59"/>
+      <c r="K21" s="115"/>
       <c r="L21" s="26">
         <v>1113002292</v>
       </c>
@@ -3644,7 +3637,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="59"/>
+      <c r="K22" s="115"/>
       <c r="L22" s="26">
         <v>1113002292</v>
       </c>
@@ -3766,7 +3759,7 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="59">
+      <c r="K24" s="115">
         <v>1175</v>
       </c>
       <c r="L24" s="26">
@@ -3792,7 +3785,7 @@
       <c r="U24" s="23"/>
       <c r="V24" s="23"/>
       <c r="W24" s="23">
-        <f>R24*O24</f>
+        <f t="shared" ref="W24:W30" si="6">R24*O24</f>
         <v>107157.18000000001</v>
       </c>
       <c r="X24" s="23">
@@ -3804,11 +3797,11 @@
       <c r="AA24" s="23"/>
       <c r="AB24" s="23"/>
       <c r="AC24" s="23">
-        <f>X24*O24</f>
+        <f t="shared" ref="AC24:AC30" si="7">X24*O24</f>
         <v>96441.462</v>
       </c>
       <c r="AD24" s="23">
-        <f t="shared" ref="AD24:AD30" si="6">+W24-AC24</f>
+        <f t="shared" ref="AD24:AD30" si="8">+W24-AC24</f>
         <v>10715.718000000008</v>
       </c>
       <c r="AE24" s="3"/>
@@ -3849,7 +3842,7 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="59"/>
+      <c r="K25" s="115"/>
       <c r="L25" s="26">
         <v>1113002305</v>
       </c>
@@ -3865,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="R25" s="23">
-        <f t="shared" ref="R25:R30" si="7">$K$24*0.6</f>
+        <f t="shared" ref="R25:R30" si="9">$K$24*0.6</f>
         <v>705</v>
       </c>
       <c r="S25" s="23"/>
@@ -3873,11 +3866,11 @@
       <c r="U25" s="23"/>
       <c r="V25" s="23"/>
       <c r="W25" s="23">
-        <f>R25*O25</f>
+        <f t="shared" si="6"/>
         <v>212797.19999999998</v>
       </c>
       <c r="X25" s="23">
-        <f t="shared" ref="X25:X30" si="8">$K$24*0.54</f>
+        <f t="shared" ref="X25:X30" si="10">$K$24*0.54</f>
         <v>634.5</v>
       </c>
       <c r="Y25" s="23"/>
@@ -3885,11 +3878,11 @@
       <c r="AA25" s="23"/>
       <c r="AB25" s="23"/>
       <c r="AC25" s="23">
-        <f>X25*O25</f>
+        <f t="shared" si="7"/>
         <v>191517.47999999998</v>
       </c>
       <c r="AD25" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>21279.72</v>
       </c>
       <c r="AE25" s="14"/>
@@ -3930,7 +3923,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="59"/>
+      <c r="K26" s="115"/>
       <c r="L26" s="26">
         <v>1113002305</v>
       </c>
@@ -3946,7 +3939,7 @@
         <v>16</v>
       </c>
       <c r="R26" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>705</v>
       </c>
       <c r="S26" s="23"/>
@@ -3954,11 +3947,11 @@
       <c r="U26" s="23"/>
       <c r="V26" s="23"/>
       <c r="W26" s="23">
-        <f>R26*O26</f>
+        <f t="shared" si="6"/>
         <v>353039.32500000001</v>
       </c>
       <c r="X26" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>634.5</v>
       </c>
       <c r="Y26" s="23"/>
@@ -3966,11 +3959,11 @@
       <c r="AA26" s="23"/>
       <c r="AB26" s="23"/>
       <c r="AC26" s="23">
-        <f>X26*O26</f>
+        <f t="shared" si="7"/>
         <v>317735.39250000002</v>
       </c>
       <c r="AD26" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>35303.932499999995</v>
       </c>
       <c r="AE26" s="3"/>
@@ -4011,7 +4004,7 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="59"/>
+      <c r="K27" s="115"/>
       <c r="L27" s="26">
         <v>1113002305</v>
       </c>
@@ -4027,7 +4020,7 @@
         <v>16</v>
       </c>
       <c r="R27" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>705</v>
       </c>
       <c r="S27" s="23"/>
@@ -4035,11 +4028,11 @@
       <c r="U27" s="23"/>
       <c r="V27" s="23"/>
       <c r="W27" s="23">
-        <f>R27*O27</f>
+        <f t="shared" si="6"/>
         <v>353039.32500000001</v>
       </c>
       <c r="X27" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>634.5</v>
       </c>
       <c r="Y27" s="23"/>
@@ -4047,11 +4040,11 @@
       <c r="AA27" s="23"/>
       <c r="AB27" s="23"/>
       <c r="AC27" s="23">
-        <f>X27*O27</f>
+        <f t="shared" si="7"/>
         <v>317735.39250000002</v>
       </c>
       <c r="AD27" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>35303.932499999995</v>
       </c>
       <c r="AE27" s="3"/>
@@ -4092,7 +4085,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="59"/>
+      <c r="K28" s="115"/>
       <c r="L28" s="26">
         <v>1113002305</v>
       </c>
@@ -4116,11 +4109,11 @@
       <c r="U28" s="23"/>
       <c r="V28" s="23"/>
       <c r="W28" s="23">
-        <f>R28*O28</f>
+        <f t="shared" si="6"/>
         <v>351878.19</v>
       </c>
       <c r="X28" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>634.5</v>
       </c>
       <c r="Y28" s="23"/>
@@ -4128,11 +4121,11 @@
       <c r="AA28" s="23"/>
       <c r="AB28" s="23"/>
       <c r="AC28" s="23">
-        <f>X28*O28</f>
+        <f t="shared" si="7"/>
         <v>316690.37099999998</v>
       </c>
       <c r="AD28" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>35187.819000000018</v>
       </c>
       <c r="AE28" s="3"/>
@@ -4173,7 +4166,7 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="59"/>
+      <c r="K29" s="115"/>
       <c r="L29" s="26">
         <v>1113002305</v>
       </c>
@@ -4196,11 +4189,11 @@
       <c r="U29" s="23"/>
       <c r="V29" s="23"/>
       <c r="W29" s="23">
-        <f>R29*O29</f>
+        <f t="shared" si="6"/>
         <v>351885.24</v>
       </c>
       <c r="X29" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>634.5</v>
       </c>
       <c r="Y29" s="23"/>
@@ -4208,11 +4201,11 @@
       <c r="AA29" s="23"/>
       <c r="AB29" s="23"/>
       <c r="AC29" s="23">
-        <f>X29*O29</f>
+        <f t="shared" si="7"/>
         <v>316696.71600000001</v>
       </c>
       <c r="AD29" s="23">
-        <f t="shared" ref="AD29" si="9">+W29-AC29</f>
+        <f t="shared" ref="AD29" si="11">+W29-AC29</f>
         <v>35188.523999999976</v>
       </c>
       <c r="AE29" s="3"/>
@@ -4253,7 +4246,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="59"/>
+      <c r="K30" s="115"/>
       <c r="L30" s="26">
         <v>1113002305</v>
       </c>
@@ -4269,7 +4262,7 @@
         <v>16</v>
       </c>
       <c r="R30" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>705</v>
       </c>
       <c r="S30" s="23"/>
@@ -4277,11 +4270,11 @@
       <c r="U30" s="23"/>
       <c r="V30" s="23"/>
       <c r="W30" s="23">
-        <f>R30*O30</f>
+        <f t="shared" si="6"/>
         <v>351807.69</v>
       </c>
       <c r="X30" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>634.5</v>
       </c>
       <c r="Y30" s="23"/>
@@ -4289,11 +4282,11 @@
       <c r="AA30" s="23"/>
       <c r="AB30" s="23"/>
       <c r="AC30" s="23">
-        <f>X30*O30</f>
+        <f t="shared" si="7"/>
         <v>316626.92099999997</v>
       </c>
       <c r="AD30" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>35180.769000000029</v>
       </c>
       <c r="AE30" s="3"/>
@@ -4338,7 +4331,7 @@
       <c r="U31" s="24"/>
       <c r="V31" s="24"/>
       <c r="W31" s="25">
-        <f t="shared" ref="W31:AD31" si="10">+SUM(W24:W30)</f>
+        <f t="shared" ref="W31:AD31" si="12">+SUM(W24:W30)</f>
         <v>2081604.15</v>
       </c>
       <c r="X31" s="24"/>
@@ -4347,11 +4340,11 @@
       <c r="AA31" s="24"/>
       <c r="AB31" s="24"/>
       <c r="AC31" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1873443.7349999999</v>
       </c>
       <c r="AD31" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>208160.41500000004</v>
       </c>
     </row>
@@ -4378,7 +4371,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="59">
+      <c r="K32" s="115">
         <v>1415</v>
       </c>
       <c r="L32" s="26"/>
@@ -4403,11 +4396,11 @@
       <c r="T32" s="23"/>
       <c r="U32" s="23"/>
       <c r="V32" s="23">
-        <f>SUM(R32:S32)</f>
+        <f t="shared" ref="V32:V37" si="13">SUM(R32:S32)</f>
         <v>834</v>
       </c>
       <c r="W32" s="23">
-        <f>O32*V32</f>
+        <f t="shared" ref="W32:W37" si="14">O32*V32</f>
         <v>416234.38799999998</v>
       </c>
       <c r="X32" s="23">
@@ -4424,7 +4417,7 @@
         <v>749.1</v>
       </c>
       <c r="AC32" s="23">
-        <f>AB32*O32</f>
+        <f t="shared" ref="AC32:AC37" si="15">AB32*O32</f>
         <v>373862.32620000001</v>
       </c>
       <c r="AD32" s="23">
@@ -4469,7 +4462,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="59"/>
+      <c r="K33" s="115"/>
       <c r="L33" s="26"/>
       <c r="M33" s="26"/>
       <c r="N33" s="26"/>
@@ -4483,7 +4476,7 @@
         <v>16</v>
       </c>
       <c r="R33" s="23">
-        <f t="shared" ref="R33:R37" si="11">$K$32*0.6</f>
+        <f t="shared" ref="R33:R37" si="16">$K$32*0.6</f>
         <v>849</v>
       </c>
       <c r="S33" s="23">
@@ -4492,15 +4485,15 @@
       <c r="T33" s="23"/>
       <c r="U33" s="23"/>
       <c r="V33" s="23">
-        <f>SUM(R33:S33)</f>
+        <f t="shared" si="13"/>
         <v>834</v>
       </c>
       <c r="W33" s="23">
-        <f>O33*V33</f>
+        <f t="shared" si="14"/>
         <v>416181.01199999999</v>
       </c>
       <c r="X33" s="23">
-        <f t="shared" ref="X33:X37" si="12">($K$32*0.54)</f>
+        <f t="shared" ref="X33:X37" si="17">($K$32*0.54)</f>
         <v>764.1</v>
       </c>
       <c r="Y33" s="23">
@@ -4509,15 +4502,15 @@
       <c r="Z33" s="23"/>
       <c r="AA33" s="23"/>
       <c r="AB33" s="23">
-        <f t="shared" ref="AB33:AB37" si="13">SUM(X33:Z33)</f>
+        <f t="shared" ref="AB33:AB37" si="18">SUM(X33:Z33)</f>
         <v>749.1</v>
       </c>
       <c r="AC33" s="23">
-        <f>AB33*O33</f>
+        <f t="shared" si="15"/>
         <v>373814.38380000001</v>
       </c>
       <c r="AD33" s="23">
-        <f t="shared" ref="AD33:AD37" si="14">+W33-AC33</f>
+        <f t="shared" ref="AD33:AD37" si="19">+W33-AC33</f>
         <v>42366.628199999977</v>
       </c>
       <c r="AE33" s="3"/>
@@ -4558,7 +4551,7 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="59"/>
+      <c r="K34" s="115"/>
       <c r="L34" s="26"/>
       <c r="M34" s="26"/>
       <c r="N34" s="26"/>
@@ -4572,7 +4565,7 @@
         <v>16</v>
       </c>
       <c r="R34" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>849</v>
       </c>
       <c r="S34" s="23">
@@ -4581,15 +4574,15 @@
       <c r="T34" s="23"/>
       <c r="U34" s="23"/>
       <c r="V34" s="23">
-        <f>SUM(R34:S34)</f>
+        <f t="shared" si="13"/>
         <v>834</v>
       </c>
       <c r="W34" s="23">
-        <f>O34*V34</f>
+        <f t="shared" si="14"/>
         <v>416272.75199999998</v>
       </c>
       <c r="X34" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>764.1</v>
       </c>
       <c r="Y34" s="23">
@@ -4598,15 +4591,15 @@
       <c r="Z34" s="23"/>
       <c r="AA34" s="23"/>
       <c r="AB34" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>749.1</v>
       </c>
       <c r="AC34" s="23">
-        <f>AB34*O34</f>
+        <f t="shared" si="15"/>
         <v>373896.78480000002</v>
       </c>
       <c r="AD34" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>42375.967199999955</v>
       </c>
       <c r="AE34" s="3"/>
@@ -4647,7 +4640,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="59"/>
+      <c r="K35" s="115"/>
       <c r="L35" s="21"/>
       <c r="M35" s="21"/>
       <c r="N35" s="21"/>
@@ -4661,7 +4654,7 @@
         <v>16</v>
       </c>
       <c r="R35" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>849</v>
       </c>
       <c r="S35" s="23">
@@ -4670,15 +4663,15 @@
       <c r="T35" s="23"/>
       <c r="U35" s="23"/>
       <c r="V35" s="23">
-        <f>SUM(R35:S35)</f>
+        <f t="shared" si="13"/>
         <v>834</v>
       </c>
       <c r="W35" s="23">
-        <f>O35*V35</f>
+        <f t="shared" si="14"/>
         <v>426957.96</v>
       </c>
       <c r="X35" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>764.1</v>
       </c>
       <c r="Y35" s="23">
@@ -4687,15 +4680,15 @@
       <c r="Z35" s="23"/>
       <c r="AA35" s="23"/>
       <c r="AB35" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>749.1</v>
       </c>
       <c r="AC35" s="23">
-        <f>AB35*O35</f>
+        <f t="shared" si="15"/>
         <v>383494.25400000002</v>
       </c>
       <c r="AD35" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>43463.706000000006</v>
       </c>
       <c r="AE35" s="33"/>
@@ -4736,7 +4729,7 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="59"/>
+      <c r="K36" s="115"/>
       <c r="L36" s="21"/>
       <c r="M36" s="21"/>
       <c r="N36" s="21"/>
@@ -4750,7 +4743,7 @@
         <v>16</v>
       </c>
       <c r="R36" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>849</v>
       </c>
       <c r="S36" s="23">
@@ -4759,15 +4752,15 @@
       <c r="T36" s="23"/>
       <c r="U36" s="23"/>
       <c r="V36" s="23">
-        <f>SUM(R36:S36)</f>
+        <f t="shared" si="13"/>
         <v>834</v>
       </c>
       <c r="W36" s="23">
-        <f>O36*V36</f>
+        <f t="shared" si="14"/>
         <v>425315.81400000001</v>
       </c>
       <c r="X36" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>764.1</v>
       </c>
       <c r="Y36" s="23">
@@ -4776,15 +4769,15 @@
       <c r="Z36" s="23"/>
       <c r="AA36" s="23"/>
       <c r="AB36" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>749.1</v>
       </c>
       <c r="AC36" s="23">
-        <f>AB36*O36</f>
+        <f t="shared" si="15"/>
         <v>382019.27610000002</v>
       </c>
       <c r="AD36" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>43296.537899999996</v>
       </c>
       <c r="AE36" s="33"/>
@@ -4825,7 +4818,7 @@
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="59"/>
+      <c r="K37" s="115"/>
       <c r="L37" s="27"/>
       <c r="M37" s="27"/>
       <c r="N37" s="27"/>
@@ -4839,7 +4832,7 @@
         <v>16</v>
       </c>
       <c r="R37" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>849</v>
       </c>
       <c r="S37" s="28">
@@ -4848,15 +4841,15 @@
       <c r="T37" s="28"/>
       <c r="U37" s="28"/>
       <c r="V37" s="28">
-        <f>SUM(R37:S37)</f>
+        <f t="shared" si="13"/>
         <v>834</v>
       </c>
       <c r="W37" s="28">
-        <f>O37*V37</f>
+        <f t="shared" si="14"/>
         <v>426524.28</v>
       </c>
       <c r="X37" s="28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>764.1</v>
       </c>
       <c r="Y37" s="28">
@@ -4865,15 +4858,15 @@
       <c r="Z37" s="28"/>
       <c r="AA37" s="28"/>
       <c r="AB37" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>749.1</v>
       </c>
       <c r="AC37" s="28">
-        <f>AB37*O37</f>
+        <f t="shared" si="15"/>
         <v>383104.72200000001</v>
       </c>
       <c r="AD37" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>43419.558000000019</v>
       </c>
       <c r="AE37" s="33"/>
@@ -4927,7 +4920,7 @@
       <c r="AA38" s="24"/>
       <c r="AB38" s="24"/>
       <c r="AC38" s="25">
-        <f t="shared" ref="AC38" si="15">+SUM(AC32:AC37)</f>
+        <f t="shared" ref="AC38" si="20">+SUM(AC32:AC37)</f>
         <v>2270191.7469000001</v>
       </c>
       <c r="AD38" s="25">
@@ -4960,7 +4953,7 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="59">
+      <c r="K39" s="115">
         <v>1495</v>
       </c>
       <c r="L39" s="27"/>
@@ -4985,11 +4978,11 @@
       <c r="T39" s="28"/>
       <c r="U39" s="28"/>
       <c r="V39" s="28">
-        <f>SUM(R39:T39)</f>
+        <f t="shared" ref="V39:V45" si="21">SUM(R39:T39)</f>
         <v>882</v>
       </c>
       <c r="W39" s="28">
-        <f>O39*V39</f>
+        <f t="shared" ref="W39:W45" si="22">O39*V39</f>
         <v>449696.52</v>
       </c>
       <c r="X39" s="28">
@@ -5006,11 +4999,11 @@
         <v>792.30000000000007</v>
       </c>
       <c r="AC39" s="28">
-        <f>AB39*O39</f>
+        <f t="shared" ref="AC39:AC45" si="23">AB39*O39</f>
         <v>403962.07800000004</v>
       </c>
       <c r="AD39" s="28">
-        <f t="shared" ref="AD39:AD45" si="16">+W39-AC39</f>
+        <f t="shared" ref="AD39:AD45" si="24">+W39-AC39</f>
         <v>45734.441999999981</v>
       </c>
       <c r="AE39" s="33"/>
@@ -5050,7 +5043,7 @@
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="59"/>
+      <c r="K40" s="115"/>
       <c r="L40" s="27"/>
       <c r="M40" s="27"/>
       <c r="N40" s="27"/>
@@ -5064,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="R40" s="28">
-        <f t="shared" ref="R40:R45" si="17">$K$39*0.6</f>
+        <f t="shared" ref="R40:R45" si="25">$K$39*0.6</f>
         <v>897</v>
       </c>
       <c r="S40" s="28">
@@ -5075,11 +5068,11 @@
       </c>
       <c r="U40" s="28"/>
       <c r="V40" s="28">
-        <f>SUM(R40:T40)</f>
+        <f t="shared" si="21"/>
         <v>867</v>
       </c>
       <c r="W40" s="28">
-        <f>O40*V40</f>
+        <f t="shared" si="22"/>
         <v>442048.62</v>
       </c>
       <c r="X40" s="28">
@@ -5094,15 +5087,15 @@
       </c>
       <c r="AA40" s="28"/>
       <c r="AB40" s="28">
-        <f t="shared" ref="AB40:AB45" si="18">SUM(X40:Z40)</f>
+        <f t="shared" ref="AB40:AB45" si="26">SUM(X40:Z40)</f>
         <v>772.30000000000007</v>
       </c>
       <c r="AC40" s="28">
-        <f>AB40*O40</f>
+        <f t="shared" si="23"/>
         <v>393764.87800000003</v>
       </c>
       <c r="AD40" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>48283.741999999969</v>
       </c>
       <c r="AE40" s="33"/>
@@ -5143,7 +5136,7 @@
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="59"/>
+      <c r="K41" s="115"/>
       <c r="L41" s="27"/>
       <c r="M41" s="27"/>
       <c r="N41" s="27"/>
@@ -5157,7 +5150,7 @@
         <v>16</v>
       </c>
       <c r="R41" s="28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>897</v>
       </c>
       <c r="S41" s="28">
@@ -5168,11 +5161,11 @@
       </c>
       <c r="U41" s="28"/>
       <c r="V41" s="28">
-        <f>SUM(R41:T41)</f>
+        <f t="shared" si="21"/>
         <v>867</v>
       </c>
       <c r="W41" s="28">
-        <f>O41*V41</f>
+        <f t="shared" si="22"/>
         <v>443401.14</v>
       </c>
       <c r="X41" s="28">
@@ -5187,15 +5180,15 @@
       </c>
       <c r="AA41" s="28"/>
       <c r="AB41" s="28">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>772.30000000000007</v>
       </c>
       <c r="AC41" s="28">
-        <f>AB41*O41</f>
+        <f t="shared" si="23"/>
         <v>394969.66600000003</v>
       </c>
       <c r="AD41" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>48431.473999999987</v>
       </c>
       <c r="AE41" s="33"/>
@@ -5236,7 +5229,7 @@
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="59"/>
+      <c r="K42" s="115"/>
       <c r="L42" s="27"/>
       <c r="M42" s="27"/>
       <c r="N42" s="27"/>
@@ -5250,7 +5243,7 @@
         <v>16</v>
       </c>
       <c r="R42" s="28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>897</v>
       </c>
       <c r="S42" s="28">
@@ -5259,15 +5252,15 @@
       <c r="T42" s="28"/>
       <c r="U42" s="28"/>
       <c r="V42" s="28">
-        <f>SUM(R42:T42)</f>
+        <f t="shared" si="21"/>
         <v>882</v>
       </c>
       <c r="W42" s="28">
-        <f>O42*V42</f>
+        <f t="shared" si="22"/>
         <v>336068.45999999996</v>
       </c>
       <c r="X42" s="28">
-        <f t="shared" ref="X42:X45" si="19">($K$39*0.54)</f>
+        <f t="shared" ref="X42:X45" si="27">($K$39*0.54)</f>
         <v>807.30000000000007</v>
       </c>
       <c r="Y42" s="28">
@@ -5276,15 +5269,15 @@
       <c r="Z42" s="28"/>
       <c r="AA42" s="28"/>
       <c r="AB42" s="28">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>792.30000000000007</v>
       </c>
       <c r="AC42" s="28">
-        <f>AB42*O42</f>
+        <f t="shared" si="23"/>
         <v>301890.06900000002</v>
       </c>
       <c r="AD42" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>34178.390999999945</v>
       </c>
       <c r="AE42" s="33"/>
@@ -5325,7 +5318,7 @@
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="59"/>
+      <c r="K43" s="115"/>
       <c r="L43" s="29"/>
       <c r="M43" s="29"/>
       <c r="N43" s="29"/>
@@ -5339,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="R43" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>897</v>
       </c>
       <c r="S43" s="31">
@@ -5348,15 +5341,15 @@
       <c r="T43" s="31"/>
       <c r="U43" s="31"/>
       <c r="V43" s="31">
-        <f>SUM(R43:T43)</f>
+        <f t="shared" si="21"/>
         <v>882</v>
       </c>
       <c r="W43" s="31">
-        <f>O43*V43</f>
+        <f t="shared" si="22"/>
         <v>441000</v>
       </c>
       <c r="X43" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>807.30000000000007</v>
       </c>
       <c r="Y43" s="31">
@@ -5365,15 +5358,15 @@
       <c r="Z43" s="31"/>
       <c r="AA43" s="31"/>
       <c r="AB43" s="31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>792.30000000000007</v>
       </c>
       <c r="AC43" s="31">
-        <f>AB43*O43</f>
+        <f t="shared" si="23"/>
         <v>396150.00000000006</v>
       </c>
       <c r="AD43" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>44849.999999999942</v>
       </c>
       <c r="AE43" s="33"/>
@@ -5414,7 +5407,7 @@
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="59"/>
+      <c r="K44" s="115"/>
       <c r="L44" s="29"/>
       <c r="M44" s="29"/>
       <c r="N44" s="29"/>
@@ -5436,11 +5429,11 @@
       <c r="T44" s="31"/>
       <c r="U44" s="31"/>
       <c r="V44" s="31">
-        <f>SUM(R44:T44)</f>
+        <f t="shared" si="21"/>
         <v>882</v>
       </c>
       <c r="W44" s="31">
-        <f>O44*V44</f>
+        <f t="shared" si="22"/>
         <v>110250</v>
       </c>
       <c r="X44" s="31">
@@ -5455,11 +5448,11 @@
         <v>792.3</v>
       </c>
       <c r="AC44" s="31">
-        <f>AB44*O44</f>
+        <f t="shared" si="23"/>
         <v>99037.5</v>
       </c>
       <c r="AD44" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>11212.5</v>
       </c>
       <c r="AE44" s="33"/>
@@ -5500,7 +5493,7 @@
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="59"/>
+      <c r="K45" s="115"/>
       <c r="L45" s="29"/>
       <c r="M45" s="29"/>
       <c r="N45" s="29"/>
@@ -5514,7 +5507,7 @@
         <v>16</v>
       </c>
       <c r="R45" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>897</v>
       </c>
       <c r="S45" s="31">
@@ -5523,15 +5516,15 @@
       <c r="T45" s="31"/>
       <c r="U45" s="31"/>
       <c r="V45" s="31">
-        <f>SUM(R45:T45)</f>
+        <f t="shared" si="21"/>
         <v>882</v>
       </c>
       <c r="W45" s="31">
-        <f>O45*V45</f>
+        <f t="shared" si="22"/>
         <v>441000</v>
       </c>
       <c r="X45" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>807.30000000000007</v>
       </c>
       <c r="Y45" s="31">
@@ -5540,15 +5533,15 @@
       <c r="Z45" s="31"/>
       <c r="AA45" s="31"/>
       <c r="AB45" s="31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>792.30000000000007</v>
       </c>
       <c r="AC45" s="31">
-        <f>AB45*O45</f>
+        <f t="shared" si="23"/>
         <v>396150.00000000006</v>
       </c>
       <c r="AD45" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>44849.999999999942</v>
       </c>
       <c r="AE45" s="33"/>
@@ -5602,7 +5595,7 @@
       <c r="AA46" s="24"/>
       <c r="AB46" s="24"/>
       <c r="AC46" s="25">
-        <f t="shared" ref="AC46" si="20">+SUM(AC39:AC45)</f>
+        <f t="shared" ref="AC46" si="28">+SUM(AC39:AC45)</f>
         <v>2385924.1910000001</v>
       </c>
       <c r="AD46" s="25">
@@ -5633,7 +5626,7 @@
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="59">
+      <c r="K47" s="115">
         <v>1495</v>
       </c>
       <c r="L47" s="29"/>
@@ -5656,11 +5649,11 @@
       <c r="T47" s="31"/>
       <c r="U47" s="31"/>
       <c r="V47" s="31">
-        <f>SUM(R47:T47)</f>
+        <f t="shared" ref="V47:V52" si="29">SUM(R47:T47)</f>
         <v>897</v>
       </c>
       <c r="W47" s="31">
-        <f>O47*V47</f>
+        <f t="shared" ref="W47:W52" si="30">O47*V47</f>
         <v>448500</v>
       </c>
       <c r="X47" s="31">
@@ -5675,11 +5668,11 @@
         <v>807.30000000000007</v>
       </c>
       <c r="AC47" s="31">
-        <f>AB47*O47</f>
+        <f t="shared" ref="AC47:AC52" si="31">AB47*O47</f>
         <v>403650.00000000006</v>
       </c>
       <c r="AD47" s="31">
-        <f t="shared" ref="AD47:AD52" si="21">+W47-AC47</f>
+        <f t="shared" ref="AD47:AD52" si="32">+W47-AC47</f>
         <v>44849.999999999942</v>
       </c>
       <c r="AE47" s="3" t="s">
@@ -5725,7 +5718,7 @@
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="59"/>
+      <c r="K48" s="115"/>
       <c r="L48" s="29"/>
       <c r="M48" s="29"/>
       <c r="N48" s="29"/>
@@ -5739,18 +5732,18 @@
         <v>16</v>
       </c>
       <c r="R48" s="31">
-        <f t="shared" ref="R48:R52" si="22">$K$39*0.6</f>
+        <f t="shared" ref="R48:R52" si="33">$K$39*0.6</f>
         <v>897</v>
       </c>
       <c r="S48" s="31"/>
       <c r="T48" s="31"/>
       <c r="U48" s="31"/>
       <c r="V48" s="31">
-        <f>SUM(R48:T48)</f>
+        <f t="shared" si="29"/>
         <v>897</v>
       </c>
       <c r="W48" s="31">
-        <f>O48*V48</f>
+        <f t="shared" si="30"/>
         <v>448500</v>
       </c>
       <c r="X48" s="31">
@@ -5761,15 +5754,15 @@
       <c r="Z48" s="31"/>
       <c r="AA48" s="31"/>
       <c r="AB48" s="31">
-        <f t="shared" ref="AB48:AB52" si="23">SUM(X48:Z48)</f>
+        <f t="shared" ref="AB48:AB52" si="34">SUM(X48:Z48)</f>
         <v>807.30000000000007</v>
       </c>
       <c r="AC48" s="31">
-        <f>AB48*O48</f>
+        <f t="shared" si="31"/>
         <v>403650.00000000006</v>
       </c>
       <c r="AD48" s="31">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>44849.999999999942</v>
       </c>
       <c r="AE48" s="3" t="s">
@@ -5812,7 +5805,7 @@
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="59"/>
+      <c r="K49" s="115"/>
       <c r="L49" s="29"/>
       <c r="M49" s="29"/>
       <c r="N49" s="29"/>
@@ -5826,18 +5819,18 @@
         <v>16</v>
       </c>
       <c r="R49" s="31">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>897</v>
       </c>
       <c r="S49" s="31"/>
       <c r="T49" s="31"/>
       <c r="U49" s="31"/>
       <c r="V49" s="31">
-        <f>SUM(R49:T49)</f>
+        <f t="shared" si="29"/>
         <v>897</v>
       </c>
       <c r="W49" s="31">
-        <f>O49*V49</f>
+        <f t="shared" si="30"/>
         <v>448500</v>
       </c>
       <c r="X49" s="31">
@@ -5848,15 +5841,15 @@
       <c r="Z49" s="31"/>
       <c r="AA49" s="31"/>
       <c r="AB49" s="31">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>807.30000000000007</v>
       </c>
       <c r="AC49" s="31">
-        <f>AB49*O49</f>
+        <f t="shared" si="31"/>
         <v>403650.00000000006</v>
       </c>
       <c r="AD49" s="31">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>44849.999999999942</v>
       </c>
       <c r="AE49" s="3" t="s">
@@ -5899,7 +5892,7 @@
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
-      <c r="K50" s="59"/>
+      <c r="K50" s="115"/>
       <c r="L50" s="29"/>
       <c r="M50" s="29"/>
       <c r="N50" s="29"/>
@@ -5913,37 +5906,37 @@
         <v>16</v>
       </c>
       <c r="R50" s="31">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>897</v>
       </c>
       <c r="S50" s="31"/>
       <c r="T50" s="31"/>
       <c r="U50" s="31"/>
       <c r="V50" s="31">
-        <f>SUM(R50:T50)</f>
+        <f t="shared" si="29"/>
         <v>897</v>
       </c>
       <c r="W50" s="31">
-        <f>O50*V50</f>
+        <f t="shared" si="30"/>
         <v>448500</v>
       </c>
       <c r="X50" s="31">
-        <f t="shared" ref="X50:X52" si="24">($K$39*0.54)</f>
+        <f t="shared" ref="X50:X52" si="35">($K$39*0.54)</f>
         <v>807.30000000000007</v>
       </c>
       <c r="Y50" s="31"/>
       <c r="Z50" s="31"/>
       <c r="AA50" s="31"/>
       <c r="AB50" s="31">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>807.30000000000007</v>
       </c>
       <c r="AC50" s="31">
-        <f>AB50*O50</f>
+        <f t="shared" si="31"/>
         <v>403650.00000000006</v>
       </c>
       <c r="AD50" s="31">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>44849.999999999942</v>
       </c>
       <c r="AE50" s="3" t="s">
@@ -5986,7 +5979,7 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
-      <c r="K51" s="59"/>
+      <c r="K51" s="115"/>
       <c r="L51" s="29"/>
       <c r="M51" s="29"/>
       <c r="N51" s="29"/>
@@ -6000,37 +5993,37 @@
         <v>16</v>
       </c>
       <c r="R51" s="31">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>897</v>
       </c>
       <c r="S51" s="31"/>
       <c r="T51" s="31"/>
       <c r="U51" s="31"/>
       <c r="V51" s="31">
-        <f>SUM(R51:T51)</f>
+        <f t="shared" si="29"/>
         <v>897</v>
       </c>
       <c r="W51" s="31">
-        <f>O51*V51</f>
+        <f t="shared" si="30"/>
         <v>448500</v>
       </c>
       <c r="X51" s="31">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>807.30000000000007</v>
       </c>
       <c r="Y51" s="31"/>
       <c r="Z51" s="31"/>
       <c r="AA51" s="31"/>
       <c r="AB51" s="31">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>807.30000000000007</v>
       </c>
       <c r="AC51" s="31">
-        <f>AB51*O51</f>
+        <f t="shared" si="31"/>
         <v>403650.00000000006</v>
       </c>
       <c r="AD51" s="31">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>44849.999999999942</v>
       </c>
       <c r="AE51" s="3" t="s">
@@ -6073,7 +6066,7 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
-      <c r="K52" s="59"/>
+      <c r="K52" s="115"/>
       <c r="L52" s="29"/>
       <c r="M52" s="29"/>
       <c r="N52" s="29"/>
@@ -6087,37 +6080,37 @@
         <v>16</v>
       </c>
       <c r="R52" s="31">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>897</v>
       </c>
       <c r="S52" s="31"/>
       <c r="T52" s="31"/>
       <c r="U52" s="31"/>
       <c r="V52" s="31">
-        <f>SUM(R52:T52)</f>
+        <f t="shared" si="29"/>
         <v>897</v>
       </c>
       <c r="W52" s="31">
-        <f>O52*V52</f>
+        <f t="shared" si="30"/>
         <v>448500</v>
       </c>
       <c r="X52" s="31">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>807.30000000000007</v>
       </c>
       <c r="Y52" s="31"/>
       <c r="Z52" s="31"/>
       <c r="AA52" s="31"/>
       <c r="AB52" s="31">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>807.30000000000007</v>
       </c>
       <c r="AC52" s="31">
-        <f>AB52*O52</f>
+        <f t="shared" si="31"/>
         <v>403650.00000000006</v>
       </c>
       <c r="AD52" s="31">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>44849.999999999942</v>
       </c>
       <c r="AE52" s="3" t="s">
@@ -6173,7 +6166,7 @@
       <c r="AA53" s="24"/>
       <c r="AB53" s="24"/>
       <c r="AC53" s="25">
-        <f t="shared" ref="AC53" si="25">+SUM(AC47:AC52)</f>
+        <f t="shared" ref="AC53" si="36">+SUM(AC47:AC52)</f>
         <v>2421900.0000000005</v>
       </c>
       <c r="AD53" s="25">
@@ -6341,27 +6334,27 @@
       <c r="I58" s="39"/>
       <c r="J58" s="39"/>
       <c r="K58" s="39"/>
-      <c r="L58" s="117">
+      <c r="L58" s="111">
         <v>2025</v>
       </c>
-      <c r="M58" s="118"/>
-      <c r="N58" s="118"/>
-      <c r="O58" s="118"/>
-      <c r="P58" s="118"/>
-      <c r="Q58" s="118"/>
-      <c r="R58" s="118"/>
-      <c r="S58" s="118"/>
-      <c r="T58" s="118"/>
-      <c r="U58" s="118"/>
-      <c r="V58" s="118"/>
-      <c r="W58" s="118"/>
-      <c r="X58" s="118"/>
-      <c r="Y58" s="118"/>
-      <c r="Z58" s="118"/>
-      <c r="AA58" s="118"/>
-      <c r="AB58" s="118"/>
-      <c r="AC58" s="118"/>
-      <c r="AD58" s="119"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="112"/>
+      <c r="R58" s="112"/>
+      <c r="S58" s="112"/>
+      <c r="T58" s="112"/>
+      <c r="U58" s="112"/>
+      <c r="V58" s="112"/>
+      <c r="W58" s="112"/>
+      <c r="X58" s="112"/>
+      <c r="Y58" s="112"/>
+      <c r="Z58" s="112"/>
+      <c r="AA58" s="112"/>
+      <c r="AB58" s="112"/>
+      <c r="AC58" s="112"/>
+      <c r="AD58" s="113"/>
       <c r="AF58" s="3"/>
       <c r="AG58" s="3"/>
       <c r="AH58" s="3"/>
@@ -6430,7 +6423,7 @@
         <v>679</v>
       </c>
       <c r="W59" s="28">
-        <f>O59*V59</f>
+        <f t="shared" ref="W59:W65" si="37">O59*V59</f>
         <v>346808.75599999999</v>
       </c>
       <c r="X59" s="28">
@@ -6448,7 +6441,7 @@
         <v>755</v>
       </c>
       <c r="AC59" s="28">
-        <f>AB59*O59</f>
+        <f t="shared" ref="AC59:AC65" si="38">AB59*O59</f>
         <v>385626.82</v>
       </c>
       <c r="AD59" s="28">
@@ -6525,7 +6518,7 @@
         <v>679</v>
       </c>
       <c r="W60" s="28">
-        <f>O60*V60</f>
+        <f t="shared" si="37"/>
         <v>346520.18099999998</v>
       </c>
       <c r="X60" s="28">
@@ -6543,7 +6536,7 @@
         <v>755</v>
       </c>
       <c r="AC60" s="28">
-        <f>AB60*O60</f>
+        <f t="shared" si="38"/>
         <v>385305.94500000001</v>
       </c>
       <c r="AD60" s="28">
@@ -6603,7 +6596,7 @@
         <v>16</v>
       </c>
       <c r="R61" s="28">
-        <f t="shared" ref="R61" si="26">649+30</f>
+        <f t="shared" ref="R61" si="39">649+30</f>
         <v>679</v>
       </c>
       <c r="S61" s="28">
@@ -6618,7 +6611,7 @@
         <v>679</v>
       </c>
       <c r="W61" s="28">
-        <f>O61*V61</f>
+        <f t="shared" si="37"/>
         <v>346078.152</v>
       </c>
       <c r="X61" s="28">
@@ -6632,21 +6625,21 @@
       </c>
       <c r="AA61" s="28"/>
       <c r="AB61" s="28">
-        <f t="shared" ref="AB61:AB63" si="27">SUM(X61:Z61)</f>
+        <f t="shared" ref="AB61:AB63" si="40">SUM(X61:Z61)</f>
         <v>755</v>
       </c>
       <c r="AC61" s="28">
-        <f>AB61*O61</f>
+        <f t="shared" si="38"/>
         <v>384814.44</v>
       </c>
       <c r="AD61" s="28">
-        <f t="shared" ref="AD61:AD65" si="28">AC61-W61</f>
+        <f t="shared" ref="AD61:AD65" si="41">AC61-W61</f>
         <v>38736.288</v>
       </c>
-      <c r="AE61" s="64"/>
-      <c r="AF61" s="58"/>
-      <c r="AG61" s="58"/>
-      <c r="AH61" s="58"/>
+      <c r="AE61" s="58"/>
+      <c r="AF61" s="114"/>
+      <c r="AG61" s="114"/>
+      <c r="AH61" s="114"/>
       <c r="AI61" s="3"/>
       <c r="AJ61" s="3"/>
       <c r="AK61" s="3"/>
@@ -6710,7 +6703,7 @@
         <v>664</v>
       </c>
       <c r="W62" s="28">
-        <f>O62*V62</f>
+        <f t="shared" si="37"/>
         <v>339237.6</v>
       </c>
       <c r="X62" s="28">
@@ -6724,18 +6717,18 @@
       </c>
       <c r="AA62" s="28"/>
       <c r="AB62" s="28">
-        <f t="shared" si="27"/>
+        <f t="shared" si="40"/>
         <v>755</v>
       </c>
       <c r="AC62" s="28">
-        <f>AB62*O62</f>
+        <f t="shared" si="38"/>
         <v>385729.5</v>
       </c>
       <c r="AD62" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>46491.900000000023</v>
       </c>
-      <c r="AE62" s="64"/>
+      <c r="AE62" s="58"/>
       <c r="AF62" s="14"/>
       <c r="AG62" s="3"/>
       <c r="AH62" s="14"/>
@@ -6789,7 +6782,7 @@
         <v>16</v>
       </c>
       <c r="R63" s="28">
-        <f t="shared" ref="R63:R65" si="29">634+30</f>
+        <f t="shared" ref="R63:R65" si="42">634+30</f>
         <v>664</v>
       </c>
       <c r="S63" s="28">
@@ -6803,7 +6796,7 @@
         <v>664</v>
       </c>
       <c r="W63" s="28">
-        <f>O63*V63</f>
+        <f t="shared" si="37"/>
         <v>339237.6</v>
       </c>
       <c r="X63" s="28">
@@ -6817,15 +6810,15 @@
       </c>
       <c r="AA63" s="28"/>
       <c r="AB63" s="28">
-        <f t="shared" si="27"/>
+        <f t="shared" si="40"/>
         <v>755</v>
       </c>
       <c r="AC63" s="28">
-        <f>AB63*O63</f>
+        <f t="shared" si="38"/>
         <v>385729.5</v>
       </c>
       <c r="AD63" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>46491.900000000023</v>
       </c>
       <c r="AE63" s="33"/>
@@ -6882,7 +6875,7 @@
         <v>16</v>
       </c>
       <c r="R64" s="28">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>664</v>
       </c>
       <c r="S64" s="28">
@@ -6896,7 +6889,7 @@
         <v>664</v>
       </c>
       <c r="W64" s="28">
-        <f>O64*V64</f>
+        <f t="shared" si="37"/>
         <v>339237.6</v>
       </c>
       <c r="X64" s="28">
@@ -6913,11 +6906,11 @@
         <v>755</v>
       </c>
       <c r="AC64" s="28">
-        <f>AB64*O64</f>
+        <f t="shared" si="38"/>
         <v>385729.5</v>
       </c>
       <c r="AD64" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>46491.900000000023</v>
       </c>
       <c r="AE64" s="33"/>
@@ -6974,7 +6967,7 @@
         <v>16</v>
       </c>
       <c r="R65" s="28">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>664</v>
       </c>
       <c r="S65" s="28">
@@ -6988,7 +6981,7 @@
         <v>664</v>
       </c>
       <c r="W65" s="28">
-        <f>O65*V65</f>
+        <f t="shared" si="37"/>
         <v>203542.56000000003</v>
       </c>
       <c r="X65" s="28">
@@ -7002,15 +6995,15 @@
       </c>
       <c r="AA65" s="28"/>
       <c r="AB65" s="28">
-        <f t="shared" ref="AB65" si="30">SUM(X65:Z65)</f>
+        <f t="shared" ref="AB65" si="43">SUM(X65:Z65)</f>
         <v>755</v>
       </c>
       <c r="AC65" s="28">
-        <f>AB65*O65</f>
+        <f t="shared" si="38"/>
         <v>231437.7</v>
       </c>
       <c r="AD65" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>27895.139999999985</v>
       </c>
       <c r="AE65" s="33"/>
@@ -7114,7 +7107,7 @@
         <v>16</v>
       </c>
       <c r="R67" s="42">
-        <f>K67+30</f>
+        <f t="shared" ref="R67:R75" si="44">K67+30</f>
         <v>664</v>
       </c>
       <c r="S67" s="28">
@@ -7128,7 +7121,7 @@
         <v>632</v>
       </c>
       <c r="W67" s="28">
-        <f>O67*V67</f>
+        <f t="shared" ref="W67:W75" si="45">O67*V67</f>
         <v>323053.12</v>
       </c>
       <c r="X67" s="28">
@@ -7145,7 +7138,7 @@
         <v>705</v>
       </c>
       <c r="AC67" s="28">
-        <f>AB67*O67</f>
+        <f t="shared" ref="AC67:AC75" si="46">AB67*O67</f>
         <v>360367.80000000005</v>
       </c>
       <c r="AD67" s="28">
@@ -7197,7 +7190,7 @@
         <v>16</v>
       </c>
       <c r="R68" s="42">
-        <f>K68+30</f>
+        <f t="shared" si="44"/>
         <v>664</v>
       </c>
       <c r="S68" s="28">
@@ -7211,7 +7204,7 @@
         <v>632</v>
       </c>
       <c r="W68" s="28">
-        <f>O68*V68</f>
+        <f t="shared" si="45"/>
         <v>321810.60800000001</v>
       </c>
       <c r="X68" s="28">
@@ -7228,7 +7221,7 @@
         <v>705</v>
       </c>
       <c r="AC68" s="28">
-        <f>AB68*O68</f>
+        <f t="shared" si="46"/>
         <v>358981.77</v>
       </c>
       <c r="AD68" s="28">
@@ -7278,7 +7271,7 @@
         <v>16</v>
       </c>
       <c r="R69" s="42">
-        <f>K69+30</f>
+        <f t="shared" si="44"/>
         <v>664</v>
       </c>
       <c r="S69" s="28">
@@ -7292,7 +7285,7 @@
         <v>632</v>
       </c>
       <c r="W69" s="28">
-        <f>O69*V69</f>
+        <f t="shared" si="45"/>
         <v>306540.85600000003</v>
       </c>
       <c r="X69" s="28">
@@ -7309,11 +7302,11 @@
         <v>705</v>
       </c>
       <c r="AC69" s="28">
-        <f>AB69*O69</f>
+        <f t="shared" si="46"/>
         <v>341948.26500000001</v>
       </c>
       <c r="AD69" s="28">
-        <f t="shared" ref="AD69:AD73" si="31">AC69-W69</f>
+        <f t="shared" ref="AD69:AD73" si="47">AC69-W69</f>
         <v>35407.408999999985</v>
       </c>
     </row>
@@ -7358,7 +7351,7 @@
         <v>16</v>
       </c>
       <c r="R70" s="42">
-        <f>K70+30</f>
+        <f t="shared" si="44"/>
         <v>664</v>
       </c>
       <c r="S70" s="28">
@@ -7372,7 +7365,7 @@
         <v>632</v>
       </c>
       <c r="W70" s="28">
-        <f>O70*V70</f>
+        <f t="shared" si="45"/>
         <v>322560.15999999997</v>
       </c>
       <c r="X70" s="28">
@@ -7389,11 +7382,11 @@
         <v>705</v>
       </c>
       <c r="AC70" s="28">
-        <f>AB70*O70</f>
+        <f t="shared" si="46"/>
         <v>359817.9</v>
       </c>
       <c r="AD70" s="28">
-        <f t="shared" si="31"/>
+        <f t="shared" si="47"/>
         <v>37257.740000000049</v>
       </c>
     </row>
@@ -7438,7 +7431,7 @@
         <v>16</v>
       </c>
       <c r="R71" s="42">
-        <f>K71+30</f>
+        <f t="shared" si="44"/>
         <v>664</v>
       </c>
       <c r="S71" s="28">
@@ -7452,7 +7445,7 @@
         <v>634</v>
       </c>
       <c r="W71" s="28">
-        <f>O71*V71</f>
+        <f t="shared" si="45"/>
         <v>306894.674</v>
       </c>
       <c r="X71" s="28">
@@ -7469,11 +7462,11 @@
         <v>705</v>
       </c>
       <c r="AC71" s="28">
-        <f>AB71*O71</f>
+        <f t="shared" si="46"/>
         <v>341263.005</v>
       </c>
       <c r="AD71" s="28">
-        <f t="shared" si="31"/>
+        <f t="shared" si="47"/>
         <v>34368.331000000006</v>
       </c>
     </row>
@@ -7518,7 +7511,7 @@
         <v>16</v>
       </c>
       <c r="R72" s="42">
-        <f>K72+30</f>
+        <f t="shared" si="44"/>
         <v>664</v>
       </c>
       <c r="S72" s="28">
@@ -7532,7 +7525,7 @@
         <v>634</v>
       </c>
       <c r="W72" s="28">
-        <f>O72*V72</f>
+        <f t="shared" si="45"/>
         <v>307245.27600000001</v>
       </c>
       <c r="X72" s="28">
@@ -7549,11 +7542,11 @@
         <v>705</v>
       </c>
       <c r="AC72" s="28">
-        <f>AB72*O72</f>
+        <f t="shared" si="46"/>
         <v>341652.87</v>
       </c>
       <c r="AD72" s="28">
-        <f t="shared" si="31"/>
+        <f t="shared" si="47"/>
         <v>34407.593999999983</v>
       </c>
     </row>
@@ -7598,7 +7591,7 @@
         <v>16</v>
       </c>
       <c r="R73" s="42">
-        <f>K73+30</f>
+        <f t="shared" si="44"/>
         <v>664</v>
       </c>
       <c r="S73" s="28">
@@ -7612,7 +7605,7 @@
         <v>634</v>
       </c>
       <c r="W73" s="28">
-        <f>O73*V73</f>
+        <f t="shared" si="45"/>
         <v>306775.48200000002</v>
       </c>
       <c r="X73" s="28">
@@ -7629,11 +7622,11 @@
         <v>705</v>
       </c>
       <c r="AC73" s="28">
-        <f>AB73*O73</f>
+        <f t="shared" si="46"/>
         <v>341130.46499999997</v>
       </c>
       <c r="AD73" s="28">
-        <f t="shared" si="31"/>
+        <f t="shared" si="47"/>
         <v>34354.982999999949</v>
       </c>
       <c r="AE73" t="s">
@@ -7681,7 +7674,7 @@
         <v>16</v>
       </c>
       <c r="R74" s="42">
-        <f>K74+30</f>
+        <f t="shared" si="44"/>
         <v>664</v>
       </c>
       <c r="S74" s="28">
@@ -7695,7 +7688,7 @@
         <v>634</v>
       </c>
       <c r="W74" s="28">
-        <f>O74*V74</f>
+        <f t="shared" si="45"/>
         <v>305639.35399999999</v>
       </c>
       <c r="X74" s="28">
@@ -7712,11 +7705,11 @@
         <v>705</v>
       </c>
       <c r="AC74" s="28">
-        <f>AB74*O74</f>
+        <f t="shared" si="46"/>
         <v>339867.10500000004</v>
       </c>
       <c r="AD74" s="28">
-        <f t="shared" ref="AD74" si="32">AC74-W74</f>
+        <f t="shared" ref="AD74" si="48">AC74-W74</f>
         <v>34227.751000000047</v>
       </c>
       <c r="AE74" t="s">
@@ -7764,7 +7757,7 @@
         <v>16</v>
       </c>
       <c r="R75" s="42">
-        <f>K75+30</f>
+        <f t="shared" si="44"/>
         <v>664</v>
       </c>
       <c r="S75" s="28">
@@ -7778,7 +7771,7 @@
         <v>634</v>
       </c>
       <c r="W75" s="28">
-        <f>O75*V75</f>
+        <f t="shared" si="45"/>
         <v>189158.97200000001</v>
       </c>
       <c r="X75" s="28">
@@ -7795,11 +7788,11 @@
         <v>705</v>
       </c>
       <c r="AC75" s="28">
-        <f>AB75*O75</f>
+        <f t="shared" si="46"/>
         <v>210342.39</v>
       </c>
       <c r="AD75" s="28">
-        <f t="shared" ref="AD75" si="33">AC75-W75</f>
+        <f t="shared" ref="AD75" si="49">AC75-W75</f>
         <v>21183.418000000005</v>
       </c>
       <c r="AE75" t="s">
@@ -7807,9 +7800,9 @@
       </c>
     </row>
     <row r="76" spans="1:44" ht="20" x14ac:dyDescent="0.25">
-      <c r="A76" s="61">
+      <c r="A76" s="55">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46139</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="7"/>
@@ -7873,16 +7866,16 @@
       <c r="G77" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H77" s="60">
+      <c r="H77" s="54">
         <v>45768</v>
       </c>
-      <c r="I77" s="60">
+      <c r="I77" s="54">
         <f>H77+60</f>
         <v>45828</v>
       </c>
-      <c r="J77" s="62">
+      <c r="J77" s="56">
         <f ca="1">I77-$A$76</f>
-        <v>-300</v>
+        <v>-311</v>
       </c>
       <c r="K77" s="37"/>
       <c r="L77" s="27" t="s">
@@ -7914,11 +7907,11 @@
       </c>
       <c r="U77" s="28"/>
       <c r="V77" s="28">
-        <f>SUM(R77:T77)</f>
+        <f t="shared" ref="V77:V82" si="50">SUM(R77:T77)</f>
         <v>650</v>
       </c>
       <c r="W77" s="28">
-        <f>O77*V77</f>
+        <f t="shared" ref="W77:W82" si="51">O77*V77</f>
         <v>57835.05</v>
       </c>
       <c r="X77" s="28">
@@ -7935,7 +7928,7 @@
         <v>800</v>
       </c>
       <c r="AC77" s="28">
-        <f>AB77*O77</f>
+        <f t="shared" ref="AC77:AC82" si="52">AB77*O77</f>
         <v>71181.600000000006</v>
       </c>
       <c r="AD77" s="28">
@@ -7976,16 +7969,16 @@
       <c r="G78" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H78" s="60">
+      <c r="H78" s="54">
         <v>45768</v>
       </c>
-      <c r="I78" s="60">
-        <f t="shared" ref="I78:I82" si="34">H78+60</f>
+      <c r="I78" s="54">
+        <f t="shared" ref="I78:I82" si="53">H78+60</f>
         <v>45828</v>
       </c>
-      <c r="J78" s="62">
-        <f t="shared" ref="J78:J97" ca="1" si="35">I78-$A$76</f>
-        <v>-300</v>
+      <c r="J78" s="56">
+        <f t="shared" ref="J78:J97" ca="1" si="54">I78-$A$76</f>
+        <v>-311</v>
       </c>
       <c r="K78" s="37"/>
       <c r="L78" s="27" t="s">
@@ -8017,11 +8010,11 @@
       </c>
       <c r="U78" s="28"/>
       <c r="V78" s="28">
-        <f>SUM(R78:T78)</f>
+        <f t="shared" si="50"/>
         <v>650</v>
       </c>
       <c r="W78" s="28">
-        <f>O78*V78</f>
+        <f t="shared" si="51"/>
         <v>60561.15</v>
       </c>
       <c r="X78" s="28">
@@ -8038,11 +8031,11 @@
         <v>800</v>
       </c>
       <c r="AC78" s="28">
-        <f>AB78*O78</f>
+        <f t="shared" si="52"/>
         <v>74536.800000000003</v>
       </c>
       <c r="AD78" s="28">
-        <f t="shared" ref="AD78:AD82" si="36">AC78-W78</f>
+        <f t="shared" ref="AD78:AD82" si="55">AC78-W78</f>
         <v>13975.650000000001</v>
       </c>
       <c r="AE78" s="38" t="s">
@@ -8079,16 +8072,16 @@
       <c r="G79" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H79" s="60">
+      <c r="H79" s="54">
         <v>45768</v>
       </c>
-      <c r="I79" s="60">
-        <f t="shared" si="34"/>
+      <c r="I79" s="54">
+        <f t="shared" si="53"/>
         <v>45828</v>
       </c>
-      <c r="J79" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-300</v>
+      <c r="J79" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-311</v>
       </c>
       <c r="K79" s="37"/>
       <c r="L79" s="27" t="s">
@@ -8120,11 +8113,11 @@
       </c>
       <c r="U79" s="28"/>
       <c r="V79" s="28">
-        <f>SUM(R79:T79)</f>
+        <f t="shared" si="50"/>
         <v>650</v>
       </c>
       <c r="W79" s="28">
-        <f>O79*V79</f>
+        <f t="shared" si="51"/>
         <v>60416.85</v>
       </c>
       <c r="X79" s="28">
@@ -8141,11 +8134,11 @@
         <v>800</v>
       </c>
       <c r="AC79" s="28">
-        <f>AB79*O79</f>
+        <f t="shared" si="52"/>
         <v>74359.199999999997</v>
       </c>
       <c r="AD79" s="28">
-        <f t="shared" si="36"/>
+        <f t="shared" si="55"/>
         <v>13942.349999999999</v>
       </c>
       <c r="AE79" s="38" t="s">
@@ -8182,16 +8175,16 @@
       <c r="G80" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H80" s="60">
+      <c r="H80" s="54">
         <v>45768</v>
       </c>
-      <c r="I80" s="60">
-        <f t="shared" si="34"/>
+      <c r="I80" s="54">
+        <f t="shared" si="53"/>
         <v>45828</v>
       </c>
-      <c r="J80" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-300</v>
+      <c r="J80" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-311</v>
       </c>
       <c r="K80" s="37"/>
       <c r="L80" s="27" t="s">
@@ -8223,11 +8216,11 @@
       </c>
       <c r="U80" s="28"/>
       <c r="V80" s="28">
-        <f>SUM(R80:T80)</f>
+        <f t="shared" si="50"/>
         <v>650</v>
       </c>
       <c r="W80" s="28">
-        <f>O80*V80</f>
+        <f t="shared" si="51"/>
         <v>58788.6</v>
       </c>
       <c r="X80" s="28">
@@ -8244,11 +8237,11 @@
         <v>800</v>
       </c>
       <c r="AC80" s="28">
-        <f>AB80*O80</f>
+        <f t="shared" si="52"/>
         <v>72355.199999999997</v>
       </c>
       <c r="AD80" s="28">
-        <f t="shared" si="36"/>
+        <f t="shared" si="55"/>
         <v>13566.599999999999</v>
       </c>
       <c r="AE80" s="38" t="s">
@@ -8285,16 +8278,16 @@
       <c r="G81" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H81" s="60">
+      <c r="H81" s="54">
         <v>45768</v>
       </c>
-      <c r="I81" s="60">
-        <f t="shared" si="34"/>
+      <c r="I81" s="54">
+        <f t="shared" si="53"/>
         <v>45828</v>
       </c>
-      <c r="J81" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-300</v>
+      <c r="J81" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-311</v>
       </c>
       <c r="K81" s="37"/>
       <c r="L81" s="27" t="s">
@@ -8326,11 +8319,11 @@
       </c>
       <c r="U81" s="28"/>
       <c r="V81" s="28">
-        <f>SUM(R81:T81)</f>
+        <f t="shared" si="50"/>
         <v>650</v>
       </c>
       <c r="W81" s="28">
-        <f>O81*V81</f>
+        <f t="shared" si="51"/>
         <v>58579.950000000004</v>
       </c>
       <c r="X81" s="28">
@@ -8347,11 +8340,11 @@
         <v>800</v>
       </c>
       <c r="AC81" s="28">
-        <f>AB81*O81</f>
+        <f t="shared" si="52"/>
         <v>72098.400000000009</v>
       </c>
       <c r="AD81" s="28">
-        <f t="shared" si="36"/>
+        <f t="shared" si="55"/>
         <v>13518.450000000004</v>
       </c>
       <c r="AE81" s="38" t="s">
@@ -8388,16 +8381,16 @@
       <c r="G82" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H82" s="60">
+      <c r="H82" s="54">
         <v>45768</v>
       </c>
-      <c r="I82" s="60">
-        <f t="shared" si="34"/>
+      <c r="I82" s="54">
+        <f t="shared" si="53"/>
         <v>45828</v>
       </c>
-      <c r="J82" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-300</v>
+      <c r="J82" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-311</v>
       </c>
       <c r="K82" s="37"/>
       <c r="L82" s="27" t="s">
@@ -8429,11 +8422,11 @@
       </c>
       <c r="U82" s="28"/>
       <c r="V82" s="28">
-        <f>SUM(R82:T82)</f>
+        <f t="shared" si="50"/>
         <v>650</v>
       </c>
       <c r="W82" s="28">
-        <f>O82*V82</f>
+        <f t="shared" si="51"/>
         <v>60598.85</v>
       </c>
       <c r="X82" s="28">
@@ -8450,11 +8443,11 @@
         <v>800</v>
       </c>
       <c r="AC82" s="28">
-        <f>AB82*O82</f>
+        <f t="shared" si="52"/>
         <v>74583.199999999997</v>
       </c>
       <c r="AD82" s="28">
-        <f t="shared" si="36"/>
+        <f t="shared" si="55"/>
         <v>13984.349999999999</v>
       </c>
       <c r="AE82" s="38" t="s">
@@ -8479,7 +8472,7 @@
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="7"/>
-      <c r="J83" s="62"/>
+      <c r="J83" s="56"/>
       <c r="K83" s="7"/>
       <c r="L83" s="24" t="s">
         <v>17</v>
@@ -8533,16 +8526,16 @@
       <c r="G84" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H84" s="60">
+      <c r="H84" s="54">
         <v>45788</v>
       </c>
-      <c r="I84" s="60">
+      <c r="I84" s="54">
         <f>H84+60</f>
         <v>45848</v>
       </c>
-      <c r="J84" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-280</v>
+      <c r="J84" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-291</v>
       </c>
       <c r="K84" s="37"/>
       <c r="L84" s="27" t="s">
@@ -8622,16 +8615,16 @@
       <c r="G85" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H85" s="60">
+      <c r="H85" s="54">
         <v>45796</v>
       </c>
-      <c r="I85" s="60">
-        <f t="shared" ref="I85:I90" si="37">H85+60</f>
+      <c r="I85" s="54">
+        <f t="shared" ref="I85:I90" si="56">H85+60</f>
         <v>45856</v>
       </c>
-      <c r="J85" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-272</v>
+      <c r="J85" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-283</v>
       </c>
       <c r="K85" s="37"/>
       <c r="L85" s="27" t="s">
@@ -8686,7 +8679,7 @@
         <v>369615.2</v>
       </c>
       <c r="AD85" s="28">
-        <f t="shared" ref="AD85:AD86" si="38">AC85-W85</f>
+        <f t="shared" ref="AD85:AD86" si="57">AC85-W85</f>
         <v>45952.159999999974</v>
       </c>
       <c r="AE85" s="38" t="s">
@@ -8711,16 +8704,16 @@
       <c r="G86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H86" s="60">
+      <c r="H86" s="54">
         <v>45799</v>
       </c>
-      <c r="I86" s="60">
-        <f t="shared" si="37"/>
+      <c r="I86" s="54">
+        <f t="shared" si="56"/>
         <v>45859</v>
       </c>
-      <c r="J86" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-269</v>
+      <c r="J86" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-280</v>
       </c>
       <c r="K86" s="37"/>
       <c r="L86" s="27" t="s">
@@ -8775,7 +8768,7 @@
         <v>368884.08</v>
       </c>
       <c r="AD86" s="28">
-        <f t="shared" si="38"/>
+        <f t="shared" si="57"/>
         <v>45861.264000000025</v>
       </c>
       <c r="AE86" s="38" t="s">
@@ -8791,8 +8784,8 @@
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
-      <c r="I87" s="60"/>
-      <c r="J87" s="62"/>
+      <c r="I87" s="54"/>
+      <c r="J87" s="56"/>
       <c r="K87" s="7">
         <f>SUM(O87,O91)</f>
         <v>2993.2339999999999</v>
@@ -8849,16 +8842,16 @@
       <c r="G88" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H88" s="60">
+      <c r="H88" s="54">
         <v>45814</v>
       </c>
-      <c r="I88" s="60">
-        <f t="shared" si="37"/>
+      <c r="I88" s="54">
+        <f t="shared" si="56"/>
         <v>45874</v>
       </c>
-      <c r="J88" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-254</v>
+      <c r="J88" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-265</v>
       </c>
       <c r="K88" s="37">
         <f>O101</f>
@@ -8916,7 +8909,7 @@
         <v>369345.83999999997</v>
       </c>
       <c r="AD88" s="28">
-        <f t="shared" ref="AD88:AD90" si="39">AC88-W88</f>
+        <f t="shared" ref="AD88:AD90" si="58">AC88-W88</f>
         <v>42424.859999999986</v>
       </c>
       <c r="AE88" s="38" t="s">
@@ -8941,16 +8934,16 @@
       <c r="G89" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H89" s="60">
+      <c r="H89" s="54">
         <v>45814</v>
       </c>
-      <c r="I89" s="60">
-        <f t="shared" si="37"/>
+      <c r="I89" s="54">
+        <f t="shared" si="56"/>
         <v>45874</v>
       </c>
-      <c r="J89" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-254</v>
+      <c r="J89" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-265</v>
       </c>
       <c r="K89" s="37"/>
       <c r="L89" s="27" t="s">
@@ -9005,7 +8998,7 @@
         <v>368719.8</v>
       </c>
       <c r="AD89" s="28">
-        <f t="shared" si="39"/>
+        <f t="shared" si="58"/>
         <v>42352.950000000012</v>
       </c>
       <c r="AE89" s="38" t="s">
@@ -9030,16 +9023,16 @@
       <c r="G90" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H90" s="60">
+      <c r="H90" s="54">
         <v>45822</v>
       </c>
-      <c r="I90" s="60">
-        <f t="shared" si="37"/>
+      <c r="I90" s="54">
+        <f t="shared" si="56"/>
         <v>45882</v>
       </c>
-      <c r="J90" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-246</v>
+      <c r="J90" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-257</v>
       </c>
       <c r="K90" s="37"/>
       <c r="L90" s="27" t="s">
@@ -9094,7 +9087,7 @@
         <v>369717.32</v>
       </c>
       <c r="AD90" s="28">
-        <f t="shared" si="39"/>
+        <f t="shared" si="58"/>
         <v>42467.530000000028</v>
       </c>
       <c r="AE90" s="38" t="s">
@@ -9111,7 +9104,7 @@
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
-      <c r="J91" s="62"/>
+      <c r="J91" s="56"/>
       <c r="K91" s="7"/>
       <c r="L91" s="24" t="s">
         <v>17</v>
@@ -9165,16 +9158,16 @@
       <c r="G92" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H92" s="60">
+      <c r="H92" s="54">
         <v>45807</v>
       </c>
-      <c r="I92" s="60">
+      <c r="I92" s="54">
         <f>H92+60</f>
         <v>45867</v>
       </c>
-      <c r="J92" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-261</v>
+      <c r="J92" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-272</v>
       </c>
       <c r="K92" s="37"/>
       <c r="L92" s="27" t="s">
@@ -9206,11 +9199,11 @@
       </c>
       <c r="U92" s="28"/>
       <c r="V92" s="28">
-        <f>SUM(R92:T92)</f>
+        <f t="shared" ref="V92:V97" si="59">SUM(R92:T92)</f>
         <v>650</v>
       </c>
       <c r="W92" s="28">
-        <f>O92*V92</f>
+        <f t="shared" ref="W92:W97" si="60">O92*V92</f>
         <v>60354.45</v>
       </c>
       <c r="X92" s="28">
@@ -9227,7 +9220,7 @@
         <v>800</v>
       </c>
       <c r="AC92" s="28">
-        <f>AB92*O92</f>
+        <f t="shared" ref="AC92:AC97" si="61">AB92*O92</f>
         <v>74282.399999999994</v>
       </c>
       <c r="AD92" s="28">
@@ -9269,16 +9262,16 @@
       <c r="G93" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H93" s="60">
+      <c r="H93" s="54">
         <v>45807</v>
       </c>
-      <c r="I93" s="60">
-        <f t="shared" ref="I93:I97" si="40">H93+60</f>
+      <c r="I93" s="54">
+        <f t="shared" ref="I93:I97" si="62">H93+60</f>
         <v>45867</v>
       </c>
-      <c r="J93" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-261</v>
+      <c r="J93" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-272</v>
       </c>
       <c r="K93" s="37"/>
       <c r="L93" s="27" t="s">
@@ -9310,11 +9303,11 @@
       </c>
       <c r="U93" s="28"/>
       <c r="V93" s="28">
-        <f>SUM(R93:T93)</f>
+        <f t="shared" si="59"/>
         <v>650</v>
       </c>
       <c r="W93" s="28">
-        <f>O93*V93</f>
+        <f t="shared" si="60"/>
         <v>60401.25</v>
       </c>
       <c r="X93" s="28">
@@ -9331,11 +9324,11 @@
         <v>800</v>
       </c>
       <c r="AC93" s="28">
-        <f>AB93*O93</f>
+        <f t="shared" si="61"/>
         <v>74340</v>
       </c>
       <c r="AD93" s="28">
-        <f t="shared" ref="AD93:AD97" si="41">AC93-W93</f>
+        <f t="shared" ref="AD93:AD97" si="63">AC93-W93</f>
         <v>13938.75</v>
       </c>
       <c r="AE93" s="38" t="s">
@@ -9372,16 +9365,16 @@
       <c r="G94" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H94" s="60">
+      <c r="H94" s="54">
         <v>45807</v>
       </c>
-      <c r="I94" s="60">
-        <f t="shared" si="40"/>
+      <c r="I94" s="54">
+        <f t="shared" si="62"/>
         <v>45867</v>
       </c>
-      <c r="J94" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-261</v>
+      <c r="J94" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-272</v>
       </c>
       <c r="K94" s="37"/>
       <c r="L94" s="27" t="s">
@@ -9413,11 +9406,11 @@
       </c>
       <c r="U94" s="28"/>
       <c r="V94" s="28">
-        <f>SUM(R94:T94)</f>
+        <f t="shared" si="59"/>
         <v>650</v>
       </c>
       <c r="W94" s="28">
-        <f>O94*V94</f>
+        <f t="shared" si="60"/>
         <v>59306.65</v>
       </c>
       <c r="X94" s="28">
@@ -9434,11 +9427,11 @@
         <v>800</v>
       </c>
       <c r="AC94" s="28">
-        <f>AB94*O94</f>
+        <f t="shared" si="61"/>
         <v>72992.800000000003</v>
       </c>
       <c r="AD94" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="63"/>
         <v>13686.150000000001</v>
       </c>
       <c r="AE94" s="38" t="s">
@@ -9475,16 +9468,16 @@
       <c r="G95" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H95" s="60">
+      <c r="H95" s="54">
         <v>45807</v>
       </c>
-      <c r="I95" s="60">
-        <f t="shared" si="40"/>
+      <c r="I95" s="54">
+        <f t="shared" si="62"/>
         <v>45867</v>
       </c>
-      <c r="J95" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-261</v>
+      <c r="J95" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-272</v>
       </c>
       <c r="K95" s="37"/>
       <c r="L95" s="27" t="s">
@@ -9516,11 +9509,11 @@
       </c>
       <c r="U95" s="28"/>
       <c r="V95" s="28">
-        <f>SUM(R95:T95)</f>
+        <f t="shared" si="59"/>
         <v>650</v>
       </c>
       <c r="W95" s="28">
-        <f>O95*V95</f>
+        <f t="shared" si="60"/>
         <v>59598.5</v>
       </c>
       <c r="X95" s="28">
@@ -9537,11 +9530,11 @@
         <v>800</v>
       </c>
       <c r="AC95" s="28">
-        <f>AB95*O95</f>
+        <f t="shared" si="61"/>
         <v>73352</v>
       </c>
       <c r="AD95" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="63"/>
         <v>13753.5</v>
       </c>
       <c r="AE95" s="38" t="s">
@@ -9578,16 +9571,16 @@
       <c r="G96" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H96" s="60">
+      <c r="H96" s="54">
         <v>45808</v>
       </c>
-      <c r="I96" s="60">
-        <f t="shared" si="40"/>
+      <c r="I96" s="54">
+        <f t="shared" si="62"/>
         <v>45868</v>
       </c>
-      <c r="J96" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-260</v>
+      <c r="J96" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-271</v>
       </c>
       <c r="K96" s="37"/>
       <c r="L96" s="27" t="s">
@@ -9619,11 +9612,11 @@
       </c>
       <c r="U96" s="28"/>
       <c r="V96" s="28">
-        <f>SUM(R96:T96)</f>
+        <f t="shared" si="59"/>
         <v>650</v>
       </c>
       <c r="W96" s="28">
-        <f>O96*V96</f>
+        <f t="shared" si="60"/>
         <v>58297.200000000004</v>
       </c>
       <c r="X96" s="28">
@@ -9640,11 +9633,11 @@
         <v>800</v>
       </c>
       <c r="AC96" s="28">
-        <f>AB96*O96</f>
+        <f t="shared" si="61"/>
         <v>71750.400000000009</v>
       </c>
       <c r="AD96" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="63"/>
         <v>13453.200000000004</v>
       </c>
       <c r="AE96" s="38" t="s">
@@ -9681,16 +9674,16 @@
       <c r="G97" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H97" s="60">
+      <c r="H97" s="54">
         <v>45814</v>
       </c>
-      <c r="I97" s="60">
-        <f t="shared" si="40"/>
+      <c r="I97" s="54">
+        <f t="shared" si="62"/>
         <v>45874</v>
       </c>
-      <c r="J97" s="62">
-        <f t="shared" ca="1" si="35"/>
-        <v>-254</v>
+      <c r="J97" s="56">
+        <f t="shared" ca="1" si="54"/>
+        <v>-265</v>
       </c>
       <c r="K97" s="37"/>
       <c r="L97" s="27" t="s">
@@ -9722,11 +9715,11 @@
       </c>
       <c r="U97" s="28"/>
       <c r="V97" s="28">
-        <f>SUM(R97:T97)</f>
+        <f t="shared" si="59"/>
         <v>650</v>
       </c>
       <c r="W97" s="28">
-        <f>O97*V97</f>
+        <f t="shared" si="60"/>
         <v>58471.4</v>
       </c>
       <c r="X97" s="28">
@@ -9743,11 +9736,11 @@
         <v>800</v>
       </c>
       <c r="AC97" s="28">
-        <f>AB97*O97</f>
+        <f t="shared" si="61"/>
         <v>71964.800000000003</v>
       </c>
       <c r="AD97" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="63"/>
         <v>13493.400000000001</v>
       </c>
       <c r="AE97" s="38" t="s">
@@ -9830,11 +9823,11 @@
       <c r="G99" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H99" s="60" t="s">
+      <c r="H99" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="I99" s="60"/>
-      <c r="J99" s="62"/>
+      <c r="I99" s="54"/>
+      <c r="J99" s="56"/>
       <c r="K99" s="37"/>
       <c r="L99" s="27" t="s">
         <v>377</v>
@@ -9888,7 +9881,7 @@
         <v>356431.35999999999</v>
       </c>
       <c r="AD99" s="28">
-        <f t="shared" ref="AD99:AD100" si="42">AC99-W99</f>
+        <f t="shared" ref="AD99:AD100" si="64">AC99-W99</f>
         <v>62249.983999999997</v>
       </c>
       <c r="AE99" s="38" t="s">
@@ -9914,11 +9907,11 @@
       <c r="G100" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="60" t="s">
+      <c r="H100" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="I100" s="60"/>
-      <c r="J100" s="62"/>
+      <c r="I100" s="54"/>
+      <c r="J100" s="56"/>
       <c r="K100" s="37"/>
       <c r="L100" s="27" t="s">
         <v>377</v>
@@ -9972,7 +9965,7 @@
         <v>355039.05</v>
       </c>
       <c r="AD100" s="28">
-        <f t="shared" si="42"/>
+        <f t="shared" si="64"/>
         <v>62006.820000000007</v>
       </c>
       <c r="AE100" s="38" t="s">
@@ -9989,8 +9982,8 @@
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
-      <c r="I101" s="60"/>
-      <c r="J101" s="62"/>
+      <c r="I101" s="54"/>
+      <c r="J101" s="56"/>
       <c r="K101" s="7"/>
       <c r="L101" s="24" t="s">
         <v>17</v>
@@ -10044,14 +10037,14 @@
       <c r="G102" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H102" s="60">
+      <c r="H102" s="54">
         <v>45859</v>
       </c>
-      <c r="I102" s="60">
+      <c r="I102" s="54">
         <f>H102+60</f>
         <v>45919</v>
       </c>
-      <c r="J102" s="62"/>
+      <c r="J102" s="56"/>
       <c r="K102" s="37"/>
       <c r="L102" s="27" t="s">
         <v>123</v>
@@ -10080,11 +10073,11 @@
       </c>
       <c r="U102" s="28"/>
       <c r="V102" s="28">
-        <f>SUM(R102:T102)</f>
+        <f t="shared" ref="V102:V108" si="65">SUM(R102:T102)</f>
         <v>590</v>
       </c>
       <c r="W102" s="28">
-        <f>O102*V102</f>
+        <f t="shared" ref="W102:W108" si="66">O102*V102</f>
         <v>56634.1</v>
       </c>
       <c r="X102" s="28">
@@ -10102,7 +10095,7 @@
         <v>780</v>
       </c>
       <c r="AC102" s="28">
-        <f>AB102*O102</f>
+        <f t="shared" ref="AC102:AC108" si="67">AB102*O102</f>
         <v>74872.2</v>
       </c>
       <c r="AD102" s="28">
@@ -10144,14 +10137,14 @@
       <c r="G103" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H103" s="60">
+      <c r="H103" s="54">
         <v>45859</v>
       </c>
-      <c r="I103" s="60">
-        <f t="shared" ref="I103:I108" si="43">H103+60</f>
+      <c r="I103" s="54">
+        <f t="shared" ref="I103:I108" si="68">H103+60</f>
         <v>45919</v>
       </c>
-      <c r="J103" s="62"/>
+      <c r="J103" s="56"/>
       <c r="K103" s="37"/>
       <c r="L103" s="27" t="s">
         <v>123</v>
@@ -10180,11 +10173,11 @@
       </c>
       <c r="U103" s="28"/>
       <c r="V103" s="28">
-        <f>SUM(R103:T103)</f>
+        <f t="shared" si="65"/>
         <v>590</v>
       </c>
       <c r="W103" s="28">
-        <f>O103*V103</f>
+        <f t="shared" si="66"/>
         <v>55617.53</v>
       </c>
       <c r="X103" s="28">
@@ -10198,15 +10191,15 @@
       </c>
       <c r="AA103" s="28"/>
       <c r="AB103" s="28">
-        <f t="shared" ref="AB103:AB107" si="44">SUM(X103:Z103)</f>
+        <f t="shared" ref="AB103:AB107" si="69">SUM(X103:Z103)</f>
         <v>780</v>
       </c>
       <c r="AC103" s="28">
-        <f>AB103*O103</f>
+        <f t="shared" si="67"/>
         <v>73528.259999999995</v>
       </c>
       <c r="AD103" s="28">
-        <f t="shared" ref="AD103:AD107" si="45">AC103-W103</f>
+        <f t="shared" ref="AD103:AD107" si="70">AC103-W103</f>
         <v>17910.729999999996</v>
       </c>
       <c r="AE103" s="38" t="s">
@@ -10243,14 +10236,14 @@
       <c r="G104" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H104" s="60">
+      <c r="H104" s="54">
         <v>45859</v>
       </c>
-      <c r="I104" s="60">
-        <f t="shared" si="43"/>
+      <c r="I104" s="54">
+        <f t="shared" si="68"/>
         <v>45919</v>
       </c>
-      <c r="J104" s="62"/>
+      <c r="J104" s="56"/>
       <c r="K104" s="37"/>
       <c r="L104" s="27" t="s">
         <v>119</v>
@@ -10279,11 +10272,11 @@
       </c>
       <c r="U104" s="28"/>
       <c r="V104" s="28">
-        <f>SUM(R104:T104)</f>
+        <f t="shared" si="65"/>
         <v>590</v>
       </c>
       <c r="W104" s="28">
-        <f>O104*V104</f>
+        <f t="shared" si="66"/>
         <v>54534.29</v>
       </c>
       <c r="X104" s="28">
@@ -10297,15 +10290,15 @@
       </c>
       <c r="AA104" s="28"/>
       <c r="AB104" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="69"/>
         <v>780</v>
       </c>
       <c r="AC104" s="28">
-        <f>AB104*O104</f>
+        <f t="shared" si="67"/>
         <v>72096.179999999993</v>
       </c>
       <c r="AD104" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="70"/>
         <v>17561.889999999992</v>
       </c>
       <c r="AE104" s="38" t="s">
@@ -10342,14 +10335,14 @@
       <c r="G105" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H105" s="60">
+      <c r="H105" s="54">
         <v>45862</v>
       </c>
-      <c r="I105" s="60">
-        <f t="shared" si="43"/>
+      <c r="I105" s="54">
+        <f t="shared" si="68"/>
         <v>45922</v>
       </c>
-      <c r="J105" s="62"/>
+      <c r="J105" s="56"/>
       <c r="K105" s="37"/>
       <c r="L105" s="27" t="s">
         <v>119</v>
@@ -10378,11 +10371,11 @@
       </c>
       <c r="U105" s="28"/>
       <c r="V105" s="28">
-        <f>SUM(R105:T105)</f>
+        <f t="shared" si="65"/>
         <v>590</v>
       </c>
       <c r="W105" s="28">
-        <f>O105*V105</f>
+        <f t="shared" si="66"/>
         <v>54009.189999999995</v>
       </c>
       <c r="X105" s="28">
@@ -10396,15 +10389,15 @@
       </c>
       <c r="AA105" s="28"/>
       <c r="AB105" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="69"/>
         <v>780</v>
       </c>
       <c r="AC105" s="28">
-        <f>AB105*O105</f>
+        <f t="shared" si="67"/>
         <v>71401.98</v>
       </c>
       <c r="AD105" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="70"/>
         <v>17392.79</v>
       </c>
       <c r="AE105" s="38" t="s">
@@ -10441,14 +10434,14 @@
       <c r="G106" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H106" s="60">
+      <c r="H106" s="54">
         <v>45862</v>
       </c>
-      <c r="I106" s="60">
-        <f t="shared" si="43"/>
+      <c r="I106" s="54">
+        <f t="shared" si="68"/>
         <v>45922</v>
       </c>
-      <c r="J106" s="62"/>
+      <c r="J106" s="56"/>
       <c r="K106" s="37"/>
       <c r="L106" s="27" t="s">
         <v>119</v>
@@ -10457,7 +10450,7 @@
         <v>375</v>
       </c>
       <c r="N106" s="27"/>
-      <c r="O106" s="63">
+      <c r="O106" s="57">
         <v>91.376999999999995</v>
       </c>
       <c r="P106" s="20" t="s">
@@ -10477,11 +10470,11 @@
       </c>
       <c r="U106" s="28"/>
       <c r="V106" s="28">
-        <f>SUM(R106:T106)</f>
+        <f t="shared" si="65"/>
         <v>590</v>
       </c>
       <c r="W106" s="28">
-        <f>O106*V106</f>
+        <f t="shared" si="66"/>
         <v>53912.43</v>
       </c>
       <c r="X106" s="28">
@@ -10495,15 +10488,15 @@
       </c>
       <c r="AA106" s="28"/>
       <c r="AB106" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="69"/>
         <v>780</v>
       </c>
       <c r="AC106" s="28">
-        <f>AB106*O106</f>
+        <f t="shared" si="67"/>
         <v>71274.06</v>
       </c>
       <c r="AD106" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="70"/>
         <v>17361.629999999997</v>
       </c>
       <c r="AE106" s="38" t="s">
@@ -10540,14 +10533,14 @@
       <c r="G107" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H107" s="60">
+      <c r="H107" s="54">
         <v>45868</v>
       </c>
-      <c r="I107" s="60">
-        <f t="shared" si="43"/>
+      <c r="I107" s="54">
+        <f t="shared" si="68"/>
         <v>45928</v>
       </c>
-      <c r="J107" s="62"/>
+      <c r="J107" s="56"/>
       <c r="K107" s="37"/>
       <c r="L107" s="27" t="s">
         <v>199</v>
@@ -10556,7 +10549,7 @@
         <v>375</v>
       </c>
       <c r="N107" s="27"/>
-      <c r="O107" s="63">
+      <c r="O107" s="57">
         <v>91.522999999999996</v>
       </c>
       <c r="P107" s="20" t="s">
@@ -10576,11 +10569,11 @@
       </c>
       <c r="U107" s="28"/>
       <c r="V107" s="28">
-        <f>SUM(R107:T107)</f>
+        <f t="shared" si="65"/>
         <v>590</v>
       </c>
       <c r="W107" s="28">
-        <f>O107*V107</f>
+        <f t="shared" si="66"/>
         <v>53998.57</v>
       </c>
       <c r="X107" s="28">
@@ -10594,15 +10587,15 @@
       </c>
       <c r="AA107" s="28"/>
       <c r="AB107" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="69"/>
         <v>780</v>
       </c>
       <c r="AC107" s="28">
-        <f>AB107*O107</f>
+        <f t="shared" si="67"/>
         <v>71387.94</v>
       </c>
       <c r="AD107" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="70"/>
         <v>17389.370000000003</v>
       </c>
       <c r="AE107" s="38" t="s">
@@ -10639,14 +10632,14 @@
       <c r="G108" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H108" s="60">
+      <c r="H108" s="54">
         <v>45869</v>
       </c>
-      <c r="I108" s="60">
-        <f t="shared" si="43"/>
+      <c r="I108" s="54">
+        <f t="shared" si="68"/>
         <v>45929</v>
       </c>
-      <c r="J108" s="62"/>
+      <c r="J108" s="56"/>
       <c r="K108" s="37"/>
       <c r="L108" s="27" t="s">
         <v>118</v>
@@ -10675,11 +10668,11 @@
       </c>
       <c r="U108" s="28"/>
       <c r="V108" s="28">
-        <f>SUM(R108:T108)</f>
+        <f t="shared" si="65"/>
         <v>590</v>
       </c>
       <c r="W108" s="28">
-        <f>O108*V108</f>
+        <f t="shared" si="66"/>
         <v>54425.14</v>
       </c>
       <c r="X108" s="28">
@@ -10693,15 +10686,15 @@
       </c>
       <c r="AA108" s="28"/>
       <c r="AB108" s="28">
-        <f t="shared" ref="AB108" si="46">SUM(X108:Z108)</f>
+        <f t="shared" ref="AB108" si="71">SUM(X108:Z108)</f>
         <v>780</v>
       </c>
       <c r="AC108" s="28">
-        <f>AB108*O108</f>
+        <f t="shared" si="67"/>
         <v>71951.87999999999</v>
       </c>
       <c r="AD108" s="28">
-        <f t="shared" ref="AD108" si="47">AC108-W108</f>
+        <f t="shared" ref="AD108" si="72">AC108-W108</f>
         <v>17526.739999999991</v>
       </c>
       <c r="AE108" s="38" t="s">
@@ -10729,8 +10722,8 @@
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
-      <c r="I109" s="60"/>
-      <c r="J109" s="62"/>
+      <c r="I109" s="54"/>
+      <c r="J109" s="56"/>
       <c r="K109" s="7"/>
       <c r="L109" s="24" t="s">
         <v>17</v>
@@ -10784,14 +10777,14 @@
       <c r="G110" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H110" s="60">
+      <c r="H110" s="54">
         <v>45891</v>
       </c>
-      <c r="I110" s="60">
-        <f t="shared" ref="I110:I117" si="48">H110+60</f>
+      <c r="I110" s="54">
+        <f t="shared" ref="I110:I117" si="73">H110+60</f>
         <v>45951</v>
       </c>
-      <c r="J110" s="62"/>
+      <c r="J110" s="56"/>
       <c r="K110" s="37"/>
       <c r="L110" s="27" t="s">
         <v>123</v>
@@ -10823,7 +10816,7 @@
         <v>570</v>
       </c>
       <c r="W110" s="28">
-        <f>O110*V110</f>
+        <f t="shared" ref="W110:W115" si="74">O110*V110</f>
         <v>51858.600000000006</v>
       </c>
       <c r="X110" s="28">
@@ -10837,15 +10830,15 @@
       </c>
       <c r="AA110" s="28"/>
       <c r="AB110" s="28">
-        <f t="shared" ref="AB110:AB115" si="49">SUM(X110:Z110)</f>
+        <f t="shared" ref="AB110:AB115" si="75">SUM(X110:Z110)</f>
         <v>770</v>
       </c>
       <c r="AC110" s="28">
-        <f>AB110*O110</f>
+        <f t="shared" ref="AC110:AC115" si="76">AB110*O110</f>
         <v>70054.600000000006</v>
       </c>
       <c r="AD110" s="28">
-        <f t="shared" ref="AD110:AD115" si="50">AC110-W110</f>
+        <f t="shared" ref="AD110:AD115" si="77">AC110-W110</f>
         <v>18196</v>
       </c>
       <c r="AE110" s="38" t="s">
@@ -10882,14 +10875,14 @@
       <c r="G111" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H111" s="60">
+      <c r="H111" s="54">
         <v>45894</v>
       </c>
-      <c r="I111" s="60">
-        <f t="shared" si="48"/>
+      <c r="I111" s="54">
+        <f t="shared" si="73"/>
         <v>45954</v>
       </c>
-      <c r="J111" s="62"/>
+      <c r="J111" s="56"/>
       <c r="K111" s="37"/>
       <c r="L111" s="27" t="s">
         <v>123</v>
@@ -10921,7 +10914,7 @@
         <v>570</v>
       </c>
       <c r="W111" s="28">
-        <f>O111*V111</f>
+        <f t="shared" si="74"/>
         <v>51570.18</v>
       </c>
       <c r="X111" s="28">
@@ -10935,15 +10928,15 @@
       </c>
       <c r="AA111" s="28"/>
       <c r="AB111" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="75"/>
         <v>770</v>
       </c>
       <c r="AC111" s="28">
-        <f>AB111*O111</f>
+        <f t="shared" si="76"/>
         <v>69664.98</v>
       </c>
       <c r="AD111" s="28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="77"/>
         <v>18094.799999999996</v>
       </c>
       <c r="AE111" s="38" t="s">
@@ -10980,14 +10973,14 @@
       <c r="G112" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H112" s="60">
+      <c r="H112" s="54">
         <v>45894</v>
       </c>
-      <c r="I112" s="60">
-        <f t="shared" si="48"/>
+      <c r="I112" s="54">
+        <f t="shared" si="73"/>
         <v>45954</v>
       </c>
-      <c r="J112" s="62"/>
+      <c r="J112" s="56"/>
       <c r="K112" s="37"/>
       <c r="L112" s="27" t="s">
         <v>119</v>
@@ -11019,7 +11012,7 @@
         <v>570</v>
       </c>
       <c r="W112" s="28">
-        <f>O112*V112</f>
+        <f t="shared" si="74"/>
         <v>51980.01</v>
       </c>
       <c r="X112" s="28">
@@ -11033,15 +11026,15 @@
       </c>
       <c r="AA112" s="28"/>
       <c r="AB112" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="75"/>
         <v>770</v>
       </c>
       <c r="AC112" s="28">
-        <f>AB112*O112</f>
+        <f t="shared" si="76"/>
         <v>70218.61</v>
       </c>
       <c r="AD112" s="28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="77"/>
         <v>18238.599999999999</v>
       </c>
       <c r="AE112" s="38" t="s">
@@ -11078,14 +11071,14 @@
       <c r="G113" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H113" s="60">
+      <c r="H113" s="54">
         <v>45894</v>
       </c>
-      <c r="I113" s="60">
-        <f t="shared" si="48"/>
+      <c r="I113" s="54">
+        <f t="shared" si="73"/>
         <v>45954</v>
       </c>
-      <c r="J113" s="62"/>
+      <c r="J113" s="56"/>
       <c r="K113" s="37"/>
       <c r="L113" s="27" t="s">
         <v>119</v>
@@ -11117,7 +11110,7 @@
         <v>570</v>
       </c>
       <c r="W113" s="28">
-        <f>O113*V113</f>
+        <f t="shared" si="74"/>
         <v>51385.5</v>
       </c>
       <c r="X113" s="28">
@@ -11131,15 +11124,15 @@
       </c>
       <c r="AA113" s="28"/>
       <c r="AB113" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="75"/>
         <v>770</v>
       </c>
       <c r="AC113" s="28">
-        <f>AB113*O113</f>
+        <f t="shared" si="76"/>
         <v>69415.5</v>
       </c>
       <c r="AD113" s="28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="77"/>
         <v>18030</v>
       </c>
       <c r="AE113" s="38" t="s">
@@ -11176,14 +11169,14 @@
       <c r="G114" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H114" s="60">
+      <c r="H114" s="54">
         <v>45894</v>
       </c>
-      <c r="I114" s="60">
-        <f t="shared" si="48"/>
+      <c r="I114" s="54">
+        <f t="shared" si="73"/>
         <v>45954</v>
       </c>
-      <c r="J114" s="62"/>
+      <c r="J114" s="56"/>
       <c r="K114" s="37"/>
       <c r="L114" s="27" t="s">
         <v>199</v>
@@ -11215,7 +11208,7 @@
         <v>570</v>
       </c>
       <c r="W114" s="28">
-        <f>O114*V114</f>
+        <f t="shared" si="74"/>
         <v>53059.02</v>
       </c>
       <c r="X114" s="28">
@@ -11229,15 +11222,15 @@
       </c>
       <c r="AA114" s="28"/>
       <c r="AB114" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="75"/>
         <v>770</v>
       </c>
       <c r="AC114" s="28">
-        <f>AB114*O114</f>
+        <f t="shared" si="76"/>
         <v>71676.22</v>
       </c>
       <c r="AD114" s="28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="77"/>
         <v>18617.200000000004</v>
       </c>
       <c r="AE114" s="38" t="s">
@@ -11274,14 +11267,14 @@
       <c r="G115" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H115" s="60">
+      <c r="H115" s="54">
         <v>45894</v>
       </c>
-      <c r="I115" s="60">
-        <f t="shared" si="48"/>
+      <c r="I115" s="54">
+        <f t="shared" si="73"/>
         <v>45954</v>
       </c>
-      <c r="J115" s="62"/>
+      <c r="J115" s="56"/>
       <c r="K115" s="37"/>
       <c r="L115" s="27" t="s">
         <v>118</v>
@@ -11313,7 +11306,7 @@
         <v>570</v>
       </c>
       <c r="W115" s="28">
-        <f>O115*V115</f>
+        <f t="shared" si="74"/>
         <v>52640.639999999999</v>
       </c>
       <c r="X115" s="28">
@@ -11327,15 +11320,15 @@
       </c>
       <c r="AA115" s="28"/>
       <c r="AB115" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="75"/>
         <v>770</v>
       </c>
       <c r="AC115" s="28">
-        <f>AB115*O115</f>
+        <f t="shared" si="76"/>
         <v>71111.040000000008</v>
       </c>
       <c r="AD115" s="28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="77"/>
         <v>18470.400000000009</v>
       </c>
       <c r="AE115" s="38" t="s">
@@ -11363,8 +11356,8 @@
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
-      <c r="I116" s="60"/>
-      <c r="J116" s="62"/>
+      <c r="I116" s="54"/>
+      <c r="J116" s="56"/>
       <c r="K116" s="7"/>
       <c r="L116" s="24" t="s">
         <v>17</v>
@@ -11415,17 +11408,17 @@
       <c r="F117" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G117" s="81" t="s">
+      <c r="G117" s="72" t="s">
         <v>226</v>
       </c>
-      <c r="H117" s="60">
+      <c r="H117" s="54">
         <v>45917</v>
       </c>
-      <c r="I117" s="60">
-        <f t="shared" si="48"/>
+      <c r="I117" s="54">
+        <f t="shared" si="73"/>
         <v>45977</v>
       </c>
-      <c r="J117" s="62"/>
+      <c r="J117" s="56"/>
       <c r="K117" s="37"/>
       <c r="L117" s="27" t="s">
         <v>227</v>
@@ -11471,7 +11464,7 @@
       </c>
       <c r="AA117" s="28"/>
       <c r="AB117" s="28">
-        <f t="shared" ref="AB117" si="51">SUM(X117:Z117)</f>
+        <f t="shared" ref="AB117" si="78">SUM(X117:Z117)</f>
         <v>780</v>
       </c>
       <c r="AC117" s="28">
@@ -11479,7 +11472,7 @@
         <v>73070.400000000009</v>
       </c>
       <c r="AD117" s="28">
-        <f t="shared" ref="AD117" si="52">AC117-W117</f>
+        <f t="shared" ref="AD117" si="79">AC117-W117</f>
         <v>19672.800000000003</v>
       </c>
       <c r="AE117" s="38" t="s">
@@ -11507,8 +11500,8 @@
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
-      <c r="I118" s="60"/>
-      <c r="J118" s="62"/>
+      <c r="I118" s="54"/>
+      <c r="J118" s="56"/>
       <c r="K118" s="7"/>
       <c r="L118" s="24" t="s">
         <v>17</v>
@@ -11563,10 +11556,10 @@
       <c r="G119" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H119" s="60">
+      <c r="H119" s="54">
         <v>45937</v>
       </c>
-      <c r="I119" s="60">
+      <c r="I119" s="54">
         <f>H119+60</f>
         <v>45997</v>
       </c>
@@ -11599,7 +11592,7 @@
       </c>
       <c r="U119" s="28"/>
       <c r="V119" s="28">
-        <f>SUM(R119:T119)</f>
+        <f t="shared" ref="V119:V130" si="80">SUM(R119:T119)</f>
         <v>544</v>
       </c>
       <c r="W119" s="28">
@@ -11633,7 +11626,7 @@
       </c>
       <c r="AF119" s="14"/>
       <c r="AG119" s="14"/>
-      <c r="AI119" s="89"/>
+      <c r="AI119" s="80"/>
       <c r="AJ119" s="3"/>
       <c r="AK119" s="3"/>
       <c r="AL119" s="3"/>
@@ -11662,10 +11655,10 @@
       <c r="G120" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H120" s="60">
+      <c r="H120" s="54">
         <v>45937</v>
       </c>
-      <c r="I120" s="60">
+      <c r="I120" s="54">
         <f>H120+60</f>
         <v>45997</v>
       </c>
@@ -11698,7 +11691,7 @@
       </c>
       <c r="U120" s="28"/>
       <c r="V120" s="28">
-        <f>SUM(R120:T120)</f>
+        <f t="shared" si="80"/>
         <v>544</v>
       </c>
       <c r="W120" s="28">
@@ -11716,7 +11709,7 @@
       </c>
       <c r="AA120" s="28"/>
       <c r="AB120" s="28">
-        <f t="shared" ref="AB120:AB121" si="53">SUM(X120:Z120)</f>
+        <f t="shared" ref="AB120:AB121" si="81">SUM(X120:Z120)</f>
         <v>620</v>
       </c>
       <c r="AC120" s="28">
@@ -11724,7 +11717,7 @@
         <v>308927.39999999997</v>
       </c>
       <c r="AD120" s="28">
-        <f t="shared" ref="AD120:AD121" si="54">AC120-W120</f>
+        <f t="shared" ref="AD120:AD121" si="82">AC120-W120</f>
         <v>37868.51999999996</v>
       </c>
       <c r="AE120" s="33" t="s">
@@ -11733,7 +11726,7 @@
       <c r="AF120" s="15"/>
       <c r="AG120" s="17"/>
       <c r="AH120" s="17"/>
-      <c r="AI120" s="90"/>
+      <c r="AI120" s="81"/>
       <c r="AJ120" s="3"/>
       <c r="AK120" s="3"/>
       <c r="AL120" s="3"/>
@@ -11762,10 +11755,10 @@
       <c r="G121" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H121" s="60">
+      <c r="H121" s="54">
         <v>45937</v>
       </c>
-      <c r="I121" s="60">
+      <c r="I121" s="54">
         <f>H121+60</f>
         <v>45997</v>
       </c>
@@ -11798,7 +11791,7 @@
       </c>
       <c r="U121" s="28"/>
       <c r="V121" s="28">
-        <f>SUM(R121:T121)</f>
+        <f t="shared" si="80"/>
         <v>544</v>
       </c>
       <c r="W121" s="28">
@@ -11816,7 +11809,7 @@
       </c>
       <c r="AA121" s="28"/>
       <c r="AB121" s="28">
-        <f t="shared" si="53"/>
+        <f t="shared" si="81"/>
         <v>620</v>
       </c>
       <c r="AC121" s="28">
@@ -11824,7 +11817,7 @@
         <v>617539.22</v>
       </c>
       <c r="AD121" s="28">
-        <f t="shared" si="54"/>
+        <f t="shared" si="82"/>
         <v>75698.356000000029</v>
       </c>
       <c r="AE121" s="33" t="s">
@@ -11850,7 +11843,7 @@
       <c r="F122" s="7"/>
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
-      <c r="I122" s="60"/>
+      <c r="I122" s="54"/>
       <c r="J122" s="7"/>
       <c r="K122" s="7"/>
       <c r="L122" s="24" t="s">
@@ -11869,7 +11862,7 @@
       <c r="T122" s="24"/>
       <c r="U122" s="24"/>
       <c r="V122" s="24">
-        <f>SUM(R122:T122)</f>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="W122" s="25">
@@ -11911,14 +11904,14 @@
       <c r="G123" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H123" s="60">
+      <c r="H123" s="54">
         <v>45917</v>
       </c>
-      <c r="I123" s="60">
+      <c r="I123" s="54">
         <f>H123+60</f>
         <v>45977</v>
       </c>
-      <c r="J123" s="62"/>
+      <c r="J123" s="56"/>
       <c r="K123" s="37"/>
       <c r="L123" s="27" t="s">
         <v>239</v>
@@ -11947,11 +11940,11 @@
       </c>
       <c r="U123" s="28"/>
       <c r="V123" s="28">
-        <f>SUM(R123:T123)</f>
+        <f t="shared" si="80"/>
         <v>560</v>
       </c>
       <c r="W123" s="28">
-        <f>O123*V123</f>
+        <f t="shared" ref="W123:W130" si="83">O123*V123</f>
         <v>50696.800000000003</v>
       </c>
       <c r="X123" s="28">
@@ -11965,15 +11958,15 @@
       </c>
       <c r="AA123" s="28"/>
       <c r="AB123" s="28">
-        <f t="shared" ref="AB123:AB130" si="55">SUM(X123:Z123)</f>
+        <f t="shared" ref="AB123:AB130" si="84">SUM(X123:Z123)</f>
         <v>755</v>
       </c>
       <c r="AC123" s="28">
-        <f>AB123*O123</f>
+        <f t="shared" ref="AC123:AC130" si="85">AB123*O123</f>
         <v>68350.149999999994</v>
       </c>
       <c r="AD123" s="28">
-        <f t="shared" ref="AD123:AD130" si="56">AC123-W123</f>
+        <f t="shared" ref="AD123:AD130" si="86">AC123-W123</f>
         <v>17653.349999999991</v>
       </c>
       <c r="AE123" s="38" t="s">
@@ -12010,14 +12003,14 @@
       <c r="G124" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H124" s="60">
+      <c r="H124" s="54">
         <v>45917</v>
       </c>
-      <c r="I124" s="60">
-        <f t="shared" ref="I124:I130" si="57">H124+60</f>
+      <c r="I124" s="54">
+        <f t="shared" ref="I124:I130" si="87">H124+60</f>
         <v>45977</v>
       </c>
-      <c r="J124" s="62"/>
+      <c r="J124" s="56"/>
       <c r="K124" s="37"/>
       <c r="L124" s="27" t="s">
         <v>239</v>
@@ -12046,11 +12039,11 @@
       </c>
       <c r="U124" s="28"/>
       <c r="V124" s="28">
-        <f>SUM(R124:T124)</f>
+        <f t="shared" si="80"/>
         <v>560</v>
       </c>
       <c r="W124" s="28">
-        <f>O124*V124</f>
+        <f t="shared" si="83"/>
         <v>50952.719999999994</v>
       </c>
       <c r="X124" s="28">
@@ -12064,15 +12057,15 @@
       </c>
       <c r="AA124" s="28"/>
       <c r="AB124" s="28">
-        <f t="shared" ref="AB124" si="58">SUM(X124:Z124)</f>
+        <f t="shared" ref="AB124" si="88">SUM(X124:Z124)</f>
         <v>755</v>
       </c>
       <c r="AC124" s="28">
-        <f>AB124*O124</f>
+        <f t="shared" si="85"/>
         <v>68695.184999999998</v>
       </c>
       <c r="AD124" s="28">
-        <f t="shared" ref="AD124" si="59">AC124-W124</f>
+        <f t="shared" ref="AD124" si="89">AC124-W124</f>
         <v>17742.465000000004</v>
       </c>
       <c r="AE124" s="38" t="s">
@@ -12109,14 +12102,14 @@
       <c r="G125" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H125" s="60">
+      <c r="H125" s="54">
         <v>45919</v>
       </c>
-      <c r="I125" s="60">
-        <f t="shared" si="57"/>
+      <c r="I125" s="54">
+        <f t="shared" si="87"/>
         <v>45979</v>
       </c>
-      <c r="J125" s="62"/>
+      <c r="J125" s="56"/>
       <c r="K125" s="37"/>
       <c r="L125" s="27" t="s">
         <v>118</v>
@@ -12145,11 +12138,11 @@
       </c>
       <c r="U125" s="28"/>
       <c r="V125" s="28">
-        <f>SUM(R125:T125)</f>
+        <f t="shared" si="80"/>
         <v>560</v>
       </c>
       <c r="W125" s="28">
-        <f>O125*V125</f>
+        <f t="shared" si="83"/>
         <v>50799.839999999997</v>
       </c>
       <c r="X125" s="28">
@@ -12163,15 +12156,15 @@
       </c>
       <c r="AA125" s="28"/>
       <c r="AB125" s="28">
-        <f t="shared" ref="AB125" si="60">SUM(X125:Z125)</f>
+        <f t="shared" ref="AB125" si="90">SUM(X125:Z125)</f>
         <v>755</v>
       </c>
       <c r="AC125" s="28">
-        <f>AB125*O125</f>
+        <f t="shared" si="85"/>
         <v>68489.069999999992</v>
       </c>
       <c r="AD125" s="28">
-        <f t="shared" ref="AD125" si="61">AC125-W125</f>
+        <f t="shared" ref="AD125" si="91">AC125-W125</f>
         <v>17689.229999999996</v>
       </c>
       <c r="AE125" s="38" t="s">
@@ -12208,14 +12201,14 @@
       <c r="G126" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H126" s="60">
+      <c r="H126" s="54">
         <v>45919</v>
       </c>
-      <c r="I126" s="60">
-        <f t="shared" si="57"/>
+      <c r="I126" s="54">
+        <f t="shared" si="87"/>
         <v>45979</v>
       </c>
-      <c r="J126" s="62"/>
+      <c r="J126" s="56"/>
       <c r="K126" s="37"/>
       <c r="L126" s="27" t="s">
         <v>246</v>
@@ -12244,11 +12237,11 @@
       </c>
       <c r="U126" s="28"/>
       <c r="V126" s="28">
-        <f>SUM(R126:T126)</f>
+        <f t="shared" si="80"/>
         <v>560</v>
       </c>
       <c r="W126" s="28">
-        <f>O126*V126</f>
+        <f t="shared" si="83"/>
         <v>52150</v>
       </c>
       <c r="X126" s="28">
@@ -12262,15 +12255,15 @@
       </c>
       <c r="AA126" s="28"/>
       <c r="AB126" s="28">
-        <f t="shared" ref="AB126" si="62">SUM(X126:Z126)</f>
+        <f t="shared" ref="AB126" si="92">SUM(X126:Z126)</f>
         <v>755</v>
       </c>
       <c r="AC126" s="28">
-        <f>AB126*O126</f>
+        <f t="shared" si="85"/>
         <v>70309.375</v>
       </c>
       <c r="AD126" s="28">
-        <f t="shared" ref="AD126" si="63">AC126-W126</f>
+        <f t="shared" ref="AD126" si="93">AC126-W126</f>
         <v>18159.375</v>
       </c>
       <c r="AE126" s="38" t="s">
@@ -12307,14 +12300,14 @@
       <c r="G127" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H127" s="60">
+      <c r="H127" s="54">
         <v>45919</v>
       </c>
-      <c r="I127" s="60">
-        <f t="shared" si="57"/>
+      <c r="I127" s="54">
+        <f t="shared" si="87"/>
         <v>45979</v>
       </c>
-      <c r="J127" s="62"/>
+      <c r="J127" s="56"/>
       <c r="K127" s="37"/>
       <c r="L127" s="27" t="s">
         <v>119</v>
@@ -12343,11 +12336,11 @@
       </c>
       <c r="U127" s="28"/>
       <c r="V127" s="28">
-        <f>SUM(R127:T127)</f>
+        <f t="shared" si="80"/>
         <v>560</v>
       </c>
       <c r="W127" s="28">
-        <f>O127*V127</f>
+        <f t="shared" si="83"/>
         <v>50621.2</v>
       </c>
       <c r="X127" s="28">
@@ -12361,15 +12354,15 @@
       </c>
       <c r="AA127" s="28"/>
       <c r="AB127" s="28">
-        <f t="shared" si="55"/>
+        <f t="shared" si="84"/>
         <v>755</v>
       </c>
       <c r="AC127" s="28">
-        <f>AB127*O127</f>
+        <f t="shared" si="85"/>
         <v>68248.224999999991</v>
       </c>
       <c r="AD127" s="28">
-        <f t="shared" si="56"/>
+        <f t="shared" si="86"/>
         <v>17627.024999999994</v>
       </c>
       <c r="AE127" s="38" t="s">
@@ -12406,14 +12399,14 @@
       <c r="G128" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H128" s="60">
+      <c r="H128" s="54">
         <v>45919</v>
       </c>
-      <c r="I128" s="60">
-        <f t="shared" si="57"/>
+      <c r="I128" s="54">
+        <f t="shared" si="87"/>
         <v>45979</v>
       </c>
-      <c r="J128" s="62"/>
+      <c r="J128" s="56"/>
       <c r="K128" s="37"/>
       <c r="L128" s="27" t="s">
         <v>239</v>
@@ -12442,11 +12435,11 @@
       </c>
       <c r="U128" s="28"/>
       <c r="V128" s="28">
-        <f>SUM(R128:T128)</f>
+        <f t="shared" si="80"/>
         <v>560</v>
       </c>
       <c r="W128" s="28">
-        <f>O128*V128</f>
+        <f t="shared" si="83"/>
         <v>49003.360000000001</v>
       </c>
       <c r="X128" s="28">
@@ -12460,15 +12453,15 @@
       </c>
       <c r="AA128" s="28"/>
       <c r="AB128" s="28">
-        <f t="shared" si="55"/>
+        <f t="shared" si="84"/>
         <v>755</v>
       </c>
       <c r="AC128" s="28">
-        <f>AB128*O128</f>
+        <f t="shared" si="85"/>
         <v>66067.03</v>
       </c>
       <c r="AD128" s="28">
-        <f t="shared" si="56"/>
+        <f t="shared" si="86"/>
         <v>17063.669999999998</v>
       </c>
       <c r="AE128" s="38" t="s">
@@ -12505,14 +12498,14 @@
       <c r="G129" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H129" s="60">
+      <c r="H129" s="54">
         <v>45919</v>
       </c>
-      <c r="I129" s="60">
-        <f t="shared" si="57"/>
+      <c r="I129" s="54">
+        <f t="shared" si="87"/>
         <v>45979</v>
       </c>
-      <c r="J129" s="62"/>
+      <c r="J129" s="56"/>
       <c r="K129" s="37"/>
       <c r="L129" s="27" t="s">
         <v>246</v>
@@ -12541,11 +12534,11 @@
       </c>
       <c r="U129" s="28"/>
       <c r="V129" s="28">
-        <f>SUM(R129:T129)</f>
+        <f t="shared" si="80"/>
         <v>560</v>
       </c>
       <c r="W129" s="28">
-        <f>O129*V129</f>
+        <f t="shared" si="83"/>
         <v>51252.32</v>
       </c>
       <c r="X129" s="28">
@@ -12559,15 +12552,15 @@
       </c>
       <c r="AA129" s="28"/>
       <c r="AB129" s="28">
-        <f t="shared" si="55"/>
+        <f t="shared" si="84"/>
         <v>755</v>
       </c>
       <c r="AC129" s="28">
-        <f>AB129*O129</f>
+        <f t="shared" si="85"/>
         <v>69099.11</v>
       </c>
       <c r="AD129" s="28">
-        <f t="shared" si="56"/>
+        <f t="shared" si="86"/>
         <v>17846.79</v>
       </c>
       <c r="AE129" s="38" t="s">
@@ -12604,14 +12597,14 @@
       <c r="G130" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H130" s="60">
+      <c r="H130" s="54">
         <v>45919</v>
       </c>
-      <c r="I130" s="60">
-        <f t="shared" si="57"/>
+      <c r="I130" s="54">
+        <f t="shared" si="87"/>
         <v>45979</v>
       </c>
-      <c r="J130" s="62"/>
+      <c r="J130" s="56"/>
       <c r="K130" s="37"/>
       <c r="L130" s="27" t="s">
         <v>241</v>
@@ -12640,11 +12633,11 @@
       </c>
       <c r="U130" s="28"/>
       <c r="V130" s="28">
-        <f>SUM(R130:T130)</f>
+        <f t="shared" si="80"/>
         <v>560</v>
       </c>
       <c r="W130" s="28">
-        <f>O130*V130</f>
+        <f t="shared" si="83"/>
         <v>49687.12</v>
       </c>
       <c r="X130" s="28">
@@ -12658,15 +12651,15 @@
       </c>
       <c r="AA130" s="28"/>
       <c r="AB130" s="28">
-        <f t="shared" si="55"/>
+        <f t="shared" si="84"/>
         <v>755</v>
       </c>
       <c r="AC130" s="28">
-        <f>AB130*O130</f>
+        <f t="shared" si="85"/>
         <v>66988.885000000009</v>
       </c>
       <c r="AD130" s="28">
-        <f t="shared" si="56"/>
+        <f t="shared" si="86"/>
         <v>17301.765000000007</v>
       </c>
       <c r="AE130" s="38" t="s">
@@ -12694,8 +12687,8 @@
       <c r="F131" s="7"/>
       <c r="G131" s="7"/>
       <c r="H131" s="7"/>
-      <c r="I131" s="60"/>
-      <c r="J131" s="62"/>
+      <c r="I131" s="54"/>
+      <c r="J131" s="56"/>
       <c r="K131" s="7"/>
       <c r="L131" s="24" t="s">
         <v>17</v>
@@ -12749,14 +12742,14 @@
       <c r="G132" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H132" s="60">
+      <c r="H132" s="54">
         <v>45947</v>
       </c>
-      <c r="I132" s="60">
+      <c r="I132" s="54">
         <f>H132+60</f>
         <v>46007</v>
       </c>
-      <c r="J132" s="62"/>
+      <c r="J132" s="56"/>
       <c r="K132" s="3"/>
       <c r="L132" s="27" t="s">
         <v>239</v>
@@ -12785,11 +12778,11 @@
       </c>
       <c r="U132" s="28"/>
       <c r="V132" s="28">
-        <f>SUM(R132:T132)</f>
+        <f t="shared" ref="V132:V142" si="94">SUM(R132:T132)</f>
         <v>540</v>
       </c>
       <c r="W132" s="28">
-        <f>O132*V132</f>
+        <f t="shared" ref="W132:W142" si="95">O132*V132</f>
         <v>51020.82</v>
       </c>
       <c r="X132" s="28">
@@ -12803,15 +12796,15 @@
       </c>
       <c r="AA132" s="28"/>
       <c r="AB132" s="28">
-        <f t="shared" ref="AB132:AB139" si="64">SUM(X132:Z132)</f>
+        <f t="shared" ref="AB132:AB139" si="96">SUM(X132:Z132)</f>
         <v>740</v>
       </c>
       <c r="AC132" s="28">
-        <f>AB132*O132</f>
+        <f t="shared" ref="AC132:AC142" si="97">AB132*O132</f>
         <v>69917.42</v>
       </c>
       <c r="AD132" s="28">
-        <f t="shared" ref="AD132:AD139" si="65">AC132-W132</f>
+        <f t="shared" ref="AD132:AD139" si="98">AC132-W132</f>
         <v>18896.599999999999</v>
       </c>
       <c r="AE132" s="38" t="s">
@@ -12848,14 +12841,14 @@
       <c r="G133" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H133" s="60">
+      <c r="H133" s="54">
         <v>45947</v>
       </c>
-      <c r="I133" s="60">
-        <f t="shared" ref="I133:I145" si="66">H133+60</f>
+      <c r="I133" s="54">
+        <f t="shared" ref="I133:I145" si="99">H133+60</f>
         <v>46007</v>
       </c>
-      <c r="J133" s="62"/>
+      <c r="J133" s="56"/>
       <c r="K133" s="3"/>
       <c r="L133" s="27" t="s">
         <v>119</v>
@@ -12884,11 +12877,11 @@
       </c>
       <c r="U133" s="28"/>
       <c r="V133" s="28">
-        <f>SUM(R133:T133)</f>
+        <f t="shared" si="94"/>
         <v>540</v>
       </c>
       <c r="W133" s="28">
-        <f>O133*V133</f>
+        <f t="shared" si="95"/>
         <v>49630.86</v>
       </c>
       <c r="X133" s="28">
@@ -12902,15 +12895,15 @@
       </c>
       <c r="AA133" s="28"/>
       <c r="AB133" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="96"/>
         <v>740</v>
       </c>
       <c r="AC133" s="28">
-        <f>AB133*O133</f>
+        <f t="shared" si="97"/>
         <v>68012.66</v>
       </c>
       <c r="AD133" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="98"/>
         <v>18381.800000000003</v>
       </c>
       <c r="AE133" s="38" t="s">
@@ -12947,14 +12940,14 @@
       <c r="G134" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H134" s="60">
+      <c r="H134" s="54">
         <v>45947</v>
       </c>
-      <c r="I134" s="60">
-        <f t="shared" si="66"/>
+      <c r="I134" s="54">
+        <f t="shared" si="99"/>
         <v>46007</v>
       </c>
-      <c r="J134" s="62"/>
+      <c r="J134" s="56"/>
       <c r="K134" s="3"/>
       <c r="L134" s="27" t="s">
         <v>239</v>
@@ -12983,11 +12976,11 @@
       </c>
       <c r="U134" s="28"/>
       <c r="V134" s="28">
-        <f>SUM(R134:T134)</f>
+        <f t="shared" si="94"/>
         <v>540</v>
       </c>
       <c r="W134" s="28">
-        <f>O134*V134</f>
+        <f t="shared" si="95"/>
         <v>47287.26</v>
       </c>
       <c r="X134" s="28">
@@ -13001,15 +12994,15 @@
       </c>
       <c r="AA134" s="28"/>
       <c r="AB134" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="96"/>
         <v>740</v>
       </c>
       <c r="AC134" s="28">
-        <f>AB134*O134</f>
+        <f t="shared" si="97"/>
         <v>64801.060000000005</v>
       </c>
       <c r="AD134" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="98"/>
         <v>17513.800000000003</v>
       </c>
       <c r="AE134" s="38" t="s">
@@ -13046,14 +13039,14 @@
       <c r="G135" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H135" s="60">
+      <c r="H135" s="54">
         <v>45947</v>
       </c>
-      <c r="I135" s="60">
-        <f t="shared" si="66"/>
+      <c r="I135" s="54">
+        <f t="shared" si="99"/>
         <v>46007</v>
       </c>
-      <c r="J135" s="62"/>
+      <c r="J135" s="56"/>
       <c r="K135" s="3"/>
       <c r="L135" s="27" t="s">
         <v>119</v>
@@ -13082,11 +13075,11 @@
       </c>
       <c r="U135" s="28"/>
       <c r="V135" s="28">
-        <f>SUM(R135:T135)</f>
+        <f t="shared" si="94"/>
         <v>540</v>
       </c>
       <c r="W135" s="28">
-        <f>O135*V135</f>
+        <f t="shared" si="95"/>
         <v>50018.04</v>
       </c>
       <c r="X135" s="28">
@@ -13100,15 +13093,15 @@
       </c>
       <c r="AA135" s="28"/>
       <c r="AB135" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="96"/>
         <v>740</v>
       </c>
       <c r="AC135" s="28">
-        <f>AB135*O135</f>
+        <f t="shared" si="97"/>
         <v>68543.240000000005</v>
       </c>
       <c r="AD135" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="98"/>
         <v>18525.200000000004</v>
       </c>
       <c r="AE135" s="38" t="s">
@@ -13145,14 +13138,14 @@
       <c r="G136" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H136" s="60">
+      <c r="H136" s="54">
         <v>45950</v>
       </c>
-      <c r="I136" s="60">
-        <f t="shared" si="66"/>
+      <c r="I136" s="54">
+        <f t="shared" si="99"/>
         <v>46010</v>
       </c>
-      <c r="J136" s="62"/>
+      <c r="J136" s="56"/>
       <c r="K136" s="3"/>
       <c r="L136" s="27" t="s">
         <v>239</v>
@@ -13181,11 +13174,11 @@
       </c>
       <c r="U136" s="28"/>
       <c r="V136" s="28">
-        <f>SUM(R136:T136)</f>
+        <f t="shared" si="94"/>
         <v>540</v>
       </c>
       <c r="W136" s="28">
-        <f>O136*V136</f>
+        <f t="shared" si="95"/>
         <v>49562.28</v>
       </c>
       <c r="X136" s="28">
@@ -13199,15 +13192,15 @@
       </c>
       <c r="AA136" s="28"/>
       <c r="AB136" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="96"/>
         <v>740</v>
       </c>
       <c r="AC136" s="28">
-        <f>AB136*O136</f>
+        <f t="shared" si="97"/>
         <v>67918.679999999993</v>
       </c>
       <c r="AD136" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="98"/>
         <v>18356.399999999994</v>
       </c>
       <c r="AE136" s="38" t="s">
@@ -13244,14 +13237,14 @@
       <c r="G137" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H137" s="60">
+      <c r="H137" s="54">
         <v>45950</v>
       </c>
-      <c r="I137" s="60">
-        <f t="shared" si="66"/>
+      <c r="I137" s="54">
+        <f t="shared" si="99"/>
         <v>46010</v>
       </c>
-      <c r="J137" s="62"/>
+      <c r="J137" s="56"/>
       <c r="K137" s="3"/>
       <c r="L137" s="27" t="s">
         <v>119</v>
@@ -13280,11 +13273,11 @@
       </c>
       <c r="U137" s="28"/>
       <c r="V137" s="28">
-        <f>SUM(R137:T137)</f>
+        <f t="shared" si="94"/>
         <v>540</v>
       </c>
       <c r="W137" s="28">
-        <f>O137*V137</f>
+        <f t="shared" si="95"/>
         <v>49337.1</v>
       </c>
       <c r="X137" s="28">
@@ -13298,15 +13291,15 @@
       </c>
       <c r="AA137" s="28"/>
       <c r="AB137" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="96"/>
         <v>740</v>
       </c>
       <c r="AC137" s="28">
-        <f>AB137*O137</f>
+        <f t="shared" si="97"/>
         <v>67610.099999999991</v>
       </c>
       <c r="AD137" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="98"/>
         <v>18272.999999999993</v>
       </c>
       <c r="AE137" s="38" t="s">
@@ -13343,14 +13336,14 @@
       <c r="G138" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H138" s="60">
+      <c r="H138" s="54">
         <v>45950</v>
       </c>
-      <c r="I138" s="60">
-        <f t="shared" si="66"/>
+      <c r="I138" s="54">
+        <f t="shared" si="99"/>
         <v>46010</v>
       </c>
-      <c r="J138" s="62"/>
+      <c r="J138" s="56"/>
       <c r="K138" s="3"/>
       <c r="L138" s="27" t="s">
         <v>241</v>
@@ -13379,11 +13372,11 @@
       </c>
       <c r="U138" s="28"/>
       <c r="V138" s="28">
-        <f>SUM(R138:T138)</f>
+        <f t="shared" si="94"/>
         <v>540</v>
       </c>
       <c r="W138" s="28">
-        <f>O138*V138</f>
+        <f t="shared" si="95"/>
         <v>49400.28</v>
       </c>
       <c r="X138" s="28">
@@ -13397,15 +13390,15 @@
       </c>
       <c r="AA138" s="28"/>
       <c r="AB138" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="96"/>
         <v>740</v>
       </c>
       <c r="AC138" s="28">
-        <f>AB138*O138</f>
+        <f t="shared" si="97"/>
         <v>67696.679999999993</v>
       </c>
       <c r="AD138" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="98"/>
         <v>18296.399999999994</v>
       </c>
       <c r="AE138" s="38" t="s">
@@ -13442,14 +13435,14 @@
       <c r="G139" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H139" s="60">
+      <c r="H139" s="54">
         <v>45950</v>
       </c>
-      <c r="I139" s="60">
-        <f t="shared" si="66"/>
+      <c r="I139" s="54">
+        <f t="shared" si="99"/>
         <v>46010</v>
       </c>
-      <c r="J139" s="62"/>
+      <c r="J139" s="56"/>
       <c r="K139" s="3"/>
       <c r="L139" s="27" t="s">
         <v>241</v>
@@ -13478,11 +13471,11 @@
       </c>
       <c r="U139" s="28"/>
       <c r="V139" s="28">
-        <f>SUM(R139:T139)</f>
+        <f t="shared" si="94"/>
         <v>540</v>
       </c>
       <c r="W139" s="28">
-        <f>O139*V139</f>
+        <f t="shared" si="95"/>
         <v>50186.520000000004</v>
       </c>
       <c r="X139" s="28">
@@ -13496,15 +13489,15 @@
       </c>
       <c r="AA139" s="28"/>
       <c r="AB139" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="96"/>
         <v>740</v>
       </c>
       <c r="AC139" s="28">
-        <f>AB139*O139</f>
+        <f t="shared" si="97"/>
         <v>68774.12</v>
       </c>
       <c r="AD139" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="98"/>
         <v>18587.599999999991</v>
       </c>
       <c r="AE139" s="38" t="s">
@@ -13541,14 +13534,14 @@
       <c r="G140" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H140" s="60">
+      <c r="H140" s="54">
         <v>45950</v>
       </c>
-      <c r="I140" s="60">
-        <f t="shared" si="66"/>
+      <c r="I140" s="54">
+        <f t="shared" si="99"/>
         <v>46010</v>
       </c>
-      <c r="J140" s="62"/>
+      <c r="J140" s="56"/>
       <c r="K140" s="3"/>
       <c r="L140" s="27" t="s">
         <v>123</v>
@@ -13577,11 +13570,11 @@
       </c>
       <c r="U140" s="28"/>
       <c r="V140" s="28">
-        <f>SUM(R140:T140)</f>
+        <f t="shared" si="94"/>
         <v>540</v>
       </c>
       <c r="W140" s="28">
-        <f>O140*V140</f>
+        <f t="shared" si="95"/>
         <v>48387.24</v>
       </c>
       <c r="X140" s="28">
@@ -13595,15 +13588,15 @@
       </c>
       <c r="AA140" s="28"/>
       <c r="AB140" s="28">
-        <f t="shared" ref="AB140:AB142" si="67">SUM(X140:Z140)</f>
+        <f t="shared" ref="AB140:AB142" si="100">SUM(X140:Z140)</f>
         <v>740</v>
       </c>
       <c r="AC140" s="28">
-        <f>AB140*O140</f>
+        <f t="shared" si="97"/>
         <v>66308.44</v>
       </c>
       <c r="AD140" s="28">
-        <f t="shared" ref="AD140:AD142" si="68">AC140-W140</f>
+        <f t="shared" ref="AD140:AD142" si="101">AC140-W140</f>
         <v>17921.200000000004</v>
       </c>
       <c r="AE140" s="38" t="s">
@@ -13640,14 +13633,14 @@
       <c r="G141" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H141" s="60">
+      <c r="H141" s="54">
         <v>45950</v>
       </c>
-      <c r="I141" s="60">
-        <f t="shared" si="66"/>
+      <c r="I141" s="54">
+        <f t="shared" si="99"/>
         <v>46010</v>
       </c>
-      <c r="J141" s="62"/>
+      <c r="J141" s="56"/>
       <c r="K141" s="3"/>
       <c r="L141" s="27" t="s">
         <v>119</v>
@@ -13676,11 +13669,11 @@
       </c>
       <c r="U141" s="28"/>
       <c r="V141" s="28">
-        <f>SUM(R141:T141)</f>
+        <f t="shared" si="94"/>
         <v>540</v>
       </c>
       <c r="W141" s="28">
-        <f>O141*V141</f>
+        <f t="shared" si="95"/>
         <v>49942.979999999996</v>
       </c>
       <c r="X141" s="28">
@@ -13694,15 +13687,15 @@
       </c>
       <c r="AA141" s="28"/>
       <c r="AB141" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="100"/>
         <v>740</v>
       </c>
       <c r="AC141" s="28">
-        <f>AB141*O141</f>
+        <f t="shared" si="97"/>
         <v>68440.37999999999</v>
       </c>
       <c r="AD141" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="101"/>
         <v>18497.399999999994</v>
       </c>
       <c r="AE141" s="38" t="s">
@@ -13739,14 +13732,14 @@
       <c r="G142" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H142" s="60">
+      <c r="H142" s="54">
         <v>45958</v>
       </c>
-      <c r="I142" s="60">
-        <f t="shared" si="66"/>
+      <c r="I142" s="54">
+        <f t="shared" si="99"/>
         <v>46018</v>
       </c>
-      <c r="J142" s="62"/>
+      <c r="J142" s="56"/>
       <c r="K142" s="3"/>
       <c r="L142" s="27" t="s">
         <v>242</v>
@@ -13775,11 +13768,11 @@
       </c>
       <c r="U142" s="28"/>
       <c r="V142" s="28">
-        <f>SUM(R142:T142)</f>
+        <f t="shared" si="94"/>
         <v>540</v>
       </c>
       <c r="W142" s="28">
-        <f>O142*V142</f>
+        <f t="shared" si="95"/>
         <v>49624.380000000005</v>
       </c>
       <c r="X142" s="28">
@@ -13793,15 +13786,15 @@
       </c>
       <c r="AA142" s="28"/>
       <c r="AB142" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="100"/>
         <v>740</v>
       </c>
       <c r="AC142" s="28">
-        <f>AB142*O142</f>
+        <f t="shared" si="97"/>
         <v>68003.78</v>
       </c>
       <c r="AD142" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="101"/>
         <v>18379.399999999994</v>
       </c>
       <c r="AE142" s="38" t="s">
@@ -13829,8 +13822,8 @@
       <c r="F143" s="7"/>
       <c r="G143" s="7"/>
       <c r="H143" s="7"/>
-      <c r="I143" s="60"/>
-      <c r="J143" s="62"/>
+      <c r="I143" s="54"/>
+      <c r="J143" s="56"/>
       <c r="K143" s="7"/>
       <c r="L143" s="24" t="s">
         <v>17</v>
@@ -13881,17 +13874,17 @@
       <c r="F144" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G144" s="81" t="s">
+      <c r="G144" s="72" t="s">
         <v>226</v>
       </c>
-      <c r="H144" s="60">
+      <c r="H144" s="54">
         <v>45952</v>
       </c>
-      <c r="I144" s="60">
-        <f t="shared" si="66"/>
+      <c r="I144" s="54">
+        <f t="shared" si="99"/>
         <v>46012</v>
       </c>
-      <c r="J144" s="62"/>
+      <c r="J144" s="56"/>
       <c r="K144" s="37"/>
       <c r="L144" s="27" t="s">
         <v>227</v>
@@ -13937,7 +13930,7 @@
       </c>
       <c r="AA144" s="28"/>
       <c r="AB144" s="28">
-        <f t="shared" ref="AB144" si="69">SUM(X144:Z144)</f>
+        <f t="shared" ref="AB144" si="102">SUM(X144:Z144)</f>
         <v>745</v>
       </c>
       <c r="AC144" s="28">
@@ -13945,7 +13938,7 @@
         <v>67508.92</v>
       </c>
       <c r="AD144" s="28">
-        <f t="shared" ref="AD144" si="70">AC144-W144</f>
+        <f t="shared" ref="AD144" si="103">AC144-W144</f>
         <v>17670.119999999995</v>
       </c>
       <c r="AE144" s="38" t="s">
@@ -13978,17 +13971,17 @@
       <c r="F145" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G145" s="81" t="s">
+      <c r="G145" s="72" t="s">
         <v>226</v>
       </c>
-      <c r="H145" s="60">
+      <c r="H145" s="54">
         <v>45952</v>
       </c>
-      <c r="I145" s="60">
-        <f t="shared" si="66"/>
+      <c r="I145" s="54">
+        <f t="shared" si="99"/>
         <v>46012</v>
       </c>
-      <c r="J145" s="62"/>
+      <c r="J145" s="56"/>
       <c r="K145" s="37"/>
       <c r="L145" s="27" t="s">
         <v>227</v>
@@ -14034,7 +14027,7 @@
       </c>
       <c r="AA145" s="28"/>
       <c r="AB145" s="28">
-        <f t="shared" ref="AB145" si="71">SUM(X145:Z145)</f>
+        <f t="shared" ref="AB145" si="104">SUM(X145:Z145)</f>
         <v>745</v>
       </c>
       <c r="AC145" s="28">
@@ -14042,7 +14035,7 @@
         <v>68131.740000000005</v>
       </c>
       <c r="AD145" s="28">
-        <f t="shared" ref="AD145" si="72">AC145-W145</f>
+        <f t="shared" ref="AD145" si="105">AC145-W145</f>
         <v>17833.140000000007</v>
       </c>
       <c r="AE145" s="38" t="s">
@@ -14069,8 +14062,8 @@
       <c r="F146" s="7"/>
       <c r="G146" s="7"/>
       <c r="H146" s="7"/>
-      <c r="I146" s="60"/>
-      <c r="J146" s="62"/>
+      <c r="I146" s="54"/>
+      <c r="J146" s="56"/>
       <c r="K146" s="7"/>
       <c r="L146" s="24" t="s">
         <v>17</v>
@@ -14125,9 +14118,9 @@
       <c r="G147" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H147" s="60"/>
-      <c r="I147" s="60"/>
-      <c r="J147" s="62"/>
+      <c r="H147" s="54"/>
+      <c r="I147" s="54"/>
+      <c r="J147" s="56"/>
       <c r="K147" s="37"/>
       <c r="L147" s="27"/>
       <c r="M147" s="27"/>
@@ -14177,7 +14170,7 @@
         <v>302500</v>
       </c>
       <c r="AD147" s="28">
-        <f t="shared" ref="AD147:AD148" si="73">AC147-W147</f>
+        <f t="shared" ref="AD147:AD148" si="106">AC147-W147</f>
         <v>49500</v>
       </c>
       <c r="AE147" s="38" t="s">
@@ -14202,9 +14195,9 @@
       <c r="G148" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H148" s="60"/>
-      <c r="I148" s="60"/>
-      <c r="J148" s="62"/>
+      <c r="H148" s="54"/>
+      <c r="I148" s="54"/>
+      <c r="J148" s="56"/>
       <c r="K148" s="37"/>
       <c r="L148" s="27"/>
       <c r="M148" s="27"/>
@@ -14254,7 +14247,7 @@
         <v>302500</v>
       </c>
       <c r="AD148" s="28">
-        <f t="shared" si="73"/>
+        <f t="shared" si="106"/>
         <v>49500</v>
       </c>
       <c r="AE148" s="38" t="s">
@@ -14270,8 +14263,8 @@
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
       <c r="H149" s="7"/>
-      <c r="I149" s="60"/>
-      <c r="J149" s="62"/>
+      <c r="I149" s="54"/>
+      <c r="J149" s="56"/>
       <c r="K149" s="7"/>
       <c r="L149" s="24" t="s">
         <v>17</v>
@@ -14322,15 +14315,15 @@
       <c r="F150" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G150" s="81" t="s">
+      <c r="G150" s="72" t="s">
         <v>226</v>
       </c>
-      <c r="H150" s="60"/>
-      <c r="I150" s="60">
-        <f t="shared" ref="I150:I152" si="74">H150+60</f>
+      <c r="H150" s="54"/>
+      <c r="I150" s="54">
+        <f t="shared" ref="I150:I152" si="107">H150+60</f>
         <v>60</v>
       </c>
-      <c r="J150" s="62"/>
+      <c r="J150" s="56"/>
       <c r="K150" s="37"/>
       <c r="L150" s="27" t="s">
         <v>227</v>
@@ -14376,7 +14369,7 @@
       </c>
       <c r="AA150" s="28"/>
       <c r="AB150" s="28">
-        <f t="shared" ref="AB150:AB152" si="75">SUM(X150:Z150)</f>
+        <f t="shared" ref="AB150:AB152" si="108">SUM(X150:Z150)</f>
         <v>730</v>
       </c>
       <c r="AC150" s="28">
@@ -14384,7 +14377,7 @@
         <v>66333.64</v>
       </c>
       <c r="AD150" s="28">
-        <f t="shared" ref="AD150:AD152" si="76">AC150-W150</f>
+        <f t="shared" ref="AD150:AD152" si="109">AC150-W150</f>
         <v>17264.920000000006</v>
       </c>
       <c r="AE150" s="38" t="s">
@@ -14417,15 +14410,15 @@
       <c r="F151" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G151" s="81" t="s">
+      <c r="G151" s="72" t="s">
         <v>226</v>
       </c>
-      <c r="H151" s="60"/>
-      <c r="I151" s="60">
-        <f t="shared" si="74"/>
+      <c r="H151" s="54"/>
+      <c r="I151" s="54">
+        <f t="shared" si="107"/>
         <v>60</v>
       </c>
-      <c r="J151" s="62"/>
+      <c r="J151" s="56"/>
       <c r="K151" s="37"/>
       <c r="L151" s="27" t="s">
         <v>227</v>
@@ -14471,7 +14464,7 @@
       </c>
       <c r="AA151" s="28"/>
       <c r="AB151" s="28">
-        <f t="shared" ref="AB151" si="77">SUM(X151:Z151)</f>
+        <f t="shared" ref="AB151" si="110">SUM(X151:Z151)</f>
         <v>730</v>
       </c>
       <c r="AC151" s="28">
@@ -14479,7 +14472,7 @@
         <v>68015.56</v>
       </c>
       <c r="AD151" s="28">
-        <f t="shared" ref="AD151" si="78">AC151-W151</f>
+        <f t="shared" ref="AD151" si="111">AC151-W151</f>
         <v>17702.68</v>
       </c>
       <c r="AE151" s="38" t="s">
@@ -14512,15 +14505,15 @@
       <c r="F152" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G152" s="81" t="s">
+      <c r="G152" s="72" t="s">
         <v>226</v>
       </c>
-      <c r="H152" s="60"/>
-      <c r="I152" s="60">
-        <f t="shared" si="74"/>
+      <c r="H152" s="54"/>
+      <c r="I152" s="54">
+        <f t="shared" si="107"/>
         <v>60</v>
       </c>
-      <c r="J152" s="62"/>
+      <c r="J152" s="56"/>
       <c r="K152" s="37"/>
       <c r="L152" s="27" t="s">
         <v>227</v>
@@ -14566,7 +14559,7 @@
       </c>
       <c r="AA152" s="28"/>
       <c r="AB152" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="108"/>
         <v>730</v>
       </c>
       <c r="AC152" s="28">
@@ -14574,7 +14567,7 @@
         <v>68344.06</v>
       </c>
       <c r="AD152" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="109"/>
         <v>17788.18</v>
       </c>
       <c r="AE152" s="38" t="s">
@@ -14601,8 +14594,8 @@
       <c r="F153" s="7"/>
       <c r="G153" s="7"/>
       <c r="H153" s="7"/>
-      <c r="I153" s="60"/>
-      <c r="J153" s="62"/>
+      <c r="I153" s="54"/>
+      <c r="J153" s="56"/>
       <c r="K153" s="7"/>
       <c r="L153" s="24" t="s">
         <v>17</v>
@@ -14657,12 +14650,12 @@
       <c r="G154" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H154" s="60"/>
-      <c r="I154" s="60">
-        <f t="shared" ref="I154:I160" si="79">H154+60</f>
+      <c r="H154" s="54"/>
+      <c r="I154" s="54">
+        <f t="shared" ref="I154:I160" si="112">H154+60</f>
         <v>60</v>
       </c>
-      <c r="J154" s="62"/>
+      <c r="J154" s="56"/>
       <c r="K154" s="3"/>
       <c r="L154" s="27" t="s">
         <v>239</v>
@@ -14694,7 +14687,7 @@
         <v>530</v>
       </c>
       <c r="W154" s="28">
-        <f>O154*V154</f>
+        <f t="shared" ref="W154:W160" si="113">O154*V154</f>
         <v>47439.24</v>
       </c>
       <c r="X154" s="28">
@@ -14708,15 +14701,15 @@
       </c>
       <c r="AA154" s="28"/>
       <c r="AB154" s="28">
-        <f t="shared" ref="AB154:AB158" si="80">SUM(X154:Z154)</f>
+        <f t="shared" ref="AB154:AB158" si="114">SUM(X154:Z154)</f>
         <v>720</v>
       </c>
       <c r="AC154" s="28">
-        <f>AB154*O154</f>
+        <f t="shared" ref="AC154:AC160" si="115">AB154*O154</f>
         <v>64445.759999999995</v>
       </c>
       <c r="AD154" s="28">
-        <f t="shared" ref="AD154:AD158" si="81">AC154-W154</f>
+        <f t="shared" ref="AD154:AD158" si="116">AC154-W154</f>
         <v>17006.519999999997</v>
       </c>
       <c r="AE154" s="38" t="s">
@@ -14753,12 +14746,12 @@
       <c r="G155" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H155" s="60"/>
-      <c r="I155" s="60">
-        <f t="shared" si="79"/>
+      <c r="H155" s="54"/>
+      <c r="I155" s="54">
+        <f t="shared" si="112"/>
         <v>60</v>
       </c>
-      <c r="J155" s="62"/>
+      <c r="J155" s="56"/>
       <c r="K155" s="3"/>
       <c r="L155" s="27" t="s">
         <v>239</v>
@@ -14790,7 +14783,7 @@
         <v>530</v>
       </c>
       <c r="W155" s="28">
-        <f>O155*V155</f>
+        <f t="shared" si="113"/>
         <v>48506.66</v>
       </c>
       <c r="X155" s="28">
@@ -14804,15 +14797,15 @@
       </c>
       <c r="AA155" s="28"/>
       <c r="AB155" s="28">
-        <f t="shared" si="80"/>
+        <f t="shared" si="114"/>
         <v>720</v>
       </c>
       <c r="AC155" s="28">
-        <f>AB155*O155</f>
+        <f t="shared" si="115"/>
         <v>65895.840000000011</v>
       </c>
       <c r="AD155" s="28">
-        <f t="shared" si="81"/>
+        <f t="shared" si="116"/>
         <v>17389.180000000008</v>
       </c>
       <c r="AE155" s="38" t="s">
@@ -14849,12 +14842,12 @@
       <c r="G156" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H156" s="60"/>
-      <c r="I156" s="60">
-        <f t="shared" si="79"/>
+      <c r="H156" s="54"/>
+      <c r="I156" s="54">
+        <f t="shared" si="112"/>
         <v>60</v>
       </c>
-      <c r="J156" s="62"/>
+      <c r="J156" s="56"/>
       <c r="K156" s="3"/>
       <c r="L156" s="27" t="s">
         <v>119</v>
@@ -14886,7 +14879,7 @@
         <v>530</v>
       </c>
       <c r="W156" s="28">
-        <f>O156*V156</f>
+        <f t="shared" si="113"/>
         <v>48006.340000000004</v>
       </c>
       <c r="X156" s="28">
@@ -14900,15 +14893,15 @@
       </c>
       <c r="AA156" s="28"/>
       <c r="AB156" s="28">
-        <f t="shared" si="80"/>
+        <f t="shared" si="114"/>
         <v>720</v>
       </c>
       <c r="AC156" s="28">
-        <f>AB156*O156</f>
+        <f t="shared" si="115"/>
         <v>65216.160000000003</v>
       </c>
       <c r="AD156" s="28">
-        <f t="shared" si="81"/>
+        <f t="shared" si="116"/>
         <v>17209.82</v>
       </c>
       <c r="AE156" s="38" t="s">
@@ -14945,12 +14938,12 @@
       <c r="G157" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H157" s="60"/>
-      <c r="I157" s="60">
-        <f t="shared" si="79"/>
+      <c r="H157" s="54"/>
+      <c r="I157" s="54">
+        <f t="shared" si="112"/>
         <v>60</v>
       </c>
-      <c r="J157" s="62"/>
+      <c r="J157" s="56"/>
       <c r="K157" s="3"/>
       <c r="L157" s="27" t="s">
         <v>119</v>
@@ -14982,7 +14975,7 @@
         <v>530</v>
       </c>
       <c r="W157" s="28">
-        <f>O157*V157</f>
+        <f t="shared" si="113"/>
         <v>49106.619999999995</v>
       </c>
       <c r="X157" s="28">
@@ -14996,15 +14989,15 @@
       </c>
       <c r="AA157" s="28"/>
       <c r="AB157" s="28">
-        <f t="shared" si="80"/>
+        <f t="shared" si="114"/>
         <v>720</v>
       </c>
       <c r="AC157" s="28">
-        <f>AB157*O157</f>
+        <f t="shared" si="115"/>
         <v>66710.880000000005</v>
       </c>
       <c r="AD157" s="28">
-        <f t="shared" si="81"/>
+        <f t="shared" si="116"/>
         <v>17604.260000000009</v>
       </c>
       <c r="AE157" s="38" t="s">
@@ -15041,12 +15034,12 @@
       <c r="G158" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H158" s="60"/>
-      <c r="I158" s="60">
-        <f t="shared" si="79"/>
+      <c r="H158" s="54"/>
+      <c r="I158" s="54">
+        <f t="shared" si="112"/>
         <v>60</v>
       </c>
-      <c r="J158" s="62"/>
+      <c r="J158" s="56"/>
       <c r="K158" s="3"/>
       <c r="L158" s="27" t="s">
         <v>242</v>
@@ -15078,7 +15071,7 @@
         <v>530</v>
       </c>
       <c r="W158" s="28">
-        <f>O158*V158</f>
+        <f t="shared" si="113"/>
         <v>49185.060000000005</v>
       </c>
       <c r="X158" s="28">
@@ -15092,15 +15085,15 @@
       </c>
       <c r="AA158" s="28"/>
       <c r="AB158" s="28">
-        <f t="shared" si="80"/>
+        <f t="shared" si="114"/>
         <v>720</v>
       </c>
       <c r="AC158" s="28">
-        <f>AB158*O158</f>
+        <f t="shared" si="115"/>
         <v>66817.440000000002</v>
       </c>
       <c r="AD158" s="28">
-        <f t="shared" si="81"/>
+        <f t="shared" si="116"/>
         <v>17632.379999999997</v>
       </c>
       <c r="AE158" s="38" t="s">
@@ -15137,12 +15130,12 @@
       <c r="G159" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H159" s="60"/>
-      <c r="I159" s="60">
-        <f t="shared" si="79"/>
+      <c r="H159" s="54"/>
+      <c r="I159" s="54">
+        <f t="shared" si="112"/>
         <v>60</v>
       </c>
-      <c r="J159" s="62"/>
+      <c r="J159" s="56"/>
       <c r="K159" s="3"/>
       <c r="L159" s="27" t="s">
         <v>242</v>
@@ -15174,7 +15167,7 @@
         <v>530</v>
       </c>
       <c r="W159" s="28">
-        <f>O159*V159</f>
+        <f t="shared" si="113"/>
         <v>49325.509999999995</v>
       </c>
       <c r="X159" s="28">
@@ -15188,15 +15181,15 @@
       </c>
       <c r="AA159" s="28"/>
       <c r="AB159" s="28">
-        <f t="shared" ref="AB159" si="82">SUM(X159:Z159)</f>
+        <f t="shared" ref="AB159" si="117">SUM(X159:Z159)</f>
         <v>720</v>
       </c>
       <c r="AC159" s="28">
-        <f>AB159*O159</f>
+        <f t="shared" si="115"/>
         <v>67008.239999999991</v>
       </c>
       <c r="AD159" s="28">
-        <f t="shared" ref="AD159" si="83">AC159-W159</f>
+        <f t="shared" ref="AD159" si="118">AC159-W159</f>
         <v>17682.729999999996</v>
       </c>
       <c r="AE159" s="38" t="s">
@@ -15233,12 +15226,12 @@
       <c r="G160" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H160" s="60"/>
-      <c r="I160" s="60">
-        <f t="shared" si="79"/>
+      <c r="H160" s="54"/>
+      <c r="I160" s="54">
+        <f t="shared" si="112"/>
         <v>60</v>
       </c>
-      <c r="J160" s="62"/>
+      <c r="J160" s="56"/>
       <c r="K160" s="3"/>
       <c r="L160" s="27"/>
       <c r="M160" s="27" t="s">
@@ -15268,7 +15261,7 @@
         <v>530</v>
       </c>
       <c r="W160" s="28">
-        <f>O160*V160</f>
+        <f t="shared" si="113"/>
         <v>48025.420000000006</v>
       </c>
       <c r="X160" s="28">
@@ -15282,15 +15275,15 @@
       </c>
       <c r="AA160" s="28"/>
       <c r="AB160" s="28">
-        <f t="shared" ref="AB160" si="84">SUM(X160:Z160)</f>
+        <f t="shared" ref="AB160" si="119">SUM(X160:Z160)</f>
         <v>720</v>
       </c>
       <c r="AC160" s="28">
-        <f>AB160*O160</f>
+        <f t="shared" si="115"/>
         <v>65242.080000000002</v>
       </c>
       <c r="AD160" s="28">
-        <f t="shared" ref="AD160" si="85">AC160-W160</f>
+        <f t="shared" ref="AD160" si="120">AC160-W160</f>
         <v>17216.659999999996</v>
       </c>
       <c r="AE160" s="38" t="s">
@@ -15318,8 +15311,8 @@
       <c r="F161" s="7"/>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
-      <c r="I161" s="60"/>
-      <c r="J161" s="62"/>
+      <c r="I161" s="54"/>
+      <c r="J161" s="56"/>
       <c r="K161" s="7"/>
       <c r="L161" s="24" t="s">
         <v>17</v>
@@ -15373,11 +15366,11 @@
       <c r="G162" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H162" s="60"/>
-      <c r="I162" s="60">
+      <c r="H162" s="54"/>
+      <c r="I162" s="54">
         <v>46010</v>
       </c>
-      <c r="J162" s="62"/>
+      <c r="J162" s="56"/>
       <c r="K162" s="3"/>
       <c r="L162" s="27" t="s">
         <v>241</v>
@@ -15409,7 +15402,7 @@
         <v>540</v>
       </c>
       <c r="W162" s="28">
-        <f>O162*V162</f>
+        <f t="shared" ref="W162:W168" si="121">O162*V162</f>
         <v>48450.42</v>
       </c>
       <c r="X162" s="28">
@@ -15423,15 +15416,15 @@
       </c>
       <c r="AA162" s="28"/>
       <c r="AB162" s="28">
-        <f t="shared" ref="AB162:AB168" si="86">SUM(X162:Z162)</f>
+        <f t="shared" ref="AB162:AB168" si="122">SUM(X162:Z162)</f>
         <v>705</v>
       </c>
       <c r="AC162" s="28">
-        <f>AB162*O162</f>
+        <f t="shared" ref="AC162:AC168" si="123">AB162*O162</f>
         <v>63254.714999999997</v>
       </c>
       <c r="AD162" s="28">
-        <f t="shared" ref="AD162:AD168" si="87">AC162-W162</f>
+        <f t="shared" ref="AD162:AD168" si="124">AC162-W162</f>
         <v>14804.294999999998</v>
       </c>
       <c r="AE162" s="38" t="s">
@@ -15468,11 +15461,11 @@
       <c r="G163" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H163" s="60"/>
-      <c r="I163" s="60">
+      <c r="H163" s="54"/>
+      <c r="I163" s="54">
         <v>46010</v>
       </c>
-      <c r="J163" s="62"/>
+      <c r="J163" s="56"/>
       <c r="K163" s="3"/>
       <c r="L163" s="27" t="s">
         <v>241</v>
@@ -15504,7 +15497,7 @@
         <v>540</v>
       </c>
       <c r="W163" s="28">
-        <f>O163*V163</f>
+        <f t="shared" si="121"/>
         <v>50385.24</v>
       </c>
       <c r="X163" s="28">
@@ -15518,15 +15511,15 @@
       </c>
       <c r="AA163" s="28"/>
       <c r="AB163" s="28">
-        <f t="shared" si="86"/>
+        <f t="shared" si="122"/>
         <v>705</v>
       </c>
       <c r="AC163" s="28">
-        <f>AB163*O163</f>
+        <f t="shared" si="123"/>
         <v>65780.73</v>
       </c>
       <c r="AD163" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="124"/>
         <v>15395.489999999998</v>
       </c>
       <c r="AE163" s="38" t="s">
@@ -15563,11 +15556,11 @@
       <c r="G164" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H164" s="60"/>
-      <c r="I164" s="60">
+      <c r="H164" s="54"/>
+      <c r="I164" s="54">
         <v>46010</v>
       </c>
-      <c r="J164" s="62"/>
+      <c r="J164" s="56"/>
       <c r="K164" s="3"/>
       <c r="L164" s="27" t="s">
         <v>241</v>
@@ -15599,7 +15592,7 @@
         <v>540</v>
       </c>
       <c r="W164" s="28">
-        <f>O164*V164</f>
+        <f t="shared" si="121"/>
         <v>49955.939999999995</v>
       </c>
       <c r="X164" s="28">
@@ -15613,15 +15606,15 @@
       </c>
       <c r="AA164" s="28"/>
       <c r="AB164" s="28">
-        <f t="shared" si="86"/>
+        <f t="shared" si="122"/>
         <v>705</v>
       </c>
       <c r="AC164" s="28">
-        <f>AB164*O164</f>
+        <f t="shared" si="123"/>
         <v>65220.254999999997</v>
       </c>
       <c r="AD164" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="124"/>
         <v>15264.315000000002</v>
       </c>
       <c r="AE164" s="38" t="s">
@@ -15658,11 +15651,11 @@
       <c r="G165" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H165" s="60"/>
-      <c r="I165" s="60">
+      <c r="H165" s="54"/>
+      <c r="I165" s="54">
         <v>46013</v>
       </c>
-      <c r="J165" s="62"/>
+      <c r="J165" s="56"/>
       <c r="K165" s="3"/>
       <c r="L165" s="27" t="s">
         <v>241</v>
@@ -15694,7 +15687,7 @@
         <v>540</v>
       </c>
       <c r="W165" s="28">
-        <f>O165*V165</f>
+        <f t="shared" si="121"/>
         <v>48357.54</v>
       </c>
       <c r="X165" s="28">
@@ -15708,15 +15701,15 @@
       </c>
       <c r="AA165" s="28"/>
       <c r="AB165" s="28">
-        <f t="shared" si="86"/>
+        <f t="shared" si="122"/>
         <v>705</v>
       </c>
       <c r="AC165" s="28">
-        <f>AB165*O165</f>
+        <f t="shared" si="123"/>
         <v>63133.455000000002</v>
       </c>
       <c r="AD165" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="124"/>
         <v>14775.915000000001</v>
       </c>
       <c r="AE165" s="38" t="s">
@@ -15753,11 +15746,11 @@
       <c r="G166" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H166" s="60"/>
-      <c r="I166" s="60">
+      <c r="H166" s="54"/>
+      <c r="I166" s="54">
         <v>46013</v>
       </c>
-      <c r="J166" s="62"/>
+      <c r="J166" s="56"/>
       <c r="K166" s="3"/>
       <c r="L166" s="27" t="s">
         <v>239</v>
@@ -15789,7 +15782,7 @@
         <v>540</v>
       </c>
       <c r="W166" s="28">
-        <f>O166*V166</f>
+        <f t="shared" si="121"/>
         <v>48729.060000000005</v>
       </c>
       <c r="X166" s="28">
@@ -15803,15 +15796,15 @@
       </c>
       <c r="AA166" s="28"/>
       <c r="AB166" s="28">
-        <f t="shared" si="86"/>
+        <f t="shared" si="122"/>
         <v>705</v>
       </c>
       <c r="AC166" s="28">
-        <f>AB166*O166</f>
+        <f t="shared" si="123"/>
         <v>63618.495000000003</v>
       </c>
       <c r="AD166" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="124"/>
         <v>14889.434999999998</v>
       </c>
       <c r="AE166" s="38" t="s">
@@ -15848,11 +15841,11 @@
       <c r="G167" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H167" s="60"/>
-      <c r="I167" s="60">
+      <c r="H167" s="54"/>
+      <c r="I167" s="54">
         <v>46013</v>
       </c>
-      <c r="J167" s="62"/>
+      <c r="J167" s="56"/>
       <c r="K167" s="3"/>
       <c r="L167" s="27" t="s">
         <v>239</v>
@@ -15884,7 +15877,7 @@
         <v>540</v>
       </c>
       <c r="W167" s="28">
-        <f>O167*V167</f>
+        <f t="shared" si="121"/>
         <v>46769.94</v>
       </c>
       <c r="X167" s="28">
@@ -15898,15 +15891,15 @@
       </c>
       <c r="AA167" s="28"/>
       <c r="AB167" s="28">
-        <f t="shared" si="86"/>
+        <f t="shared" si="122"/>
         <v>705</v>
       </c>
       <c r="AC167" s="28">
-        <f>AB167*O167</f>
+        <f t="shared" si="123"/>
         <v>61060.755000000005</v>
       </c>
       <c r="AD167" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="124"/>
         <v>14290.815000000002</v>
       </c>
       <c r="AE167" s="38" t="s">
@@ -15943,11 +15936,11 @@
       <c r="G168" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H168" s="60"/>
-      <c r="I168" s="60">
+      <c r="H168" s="54"/>
+      <c r="I168" s="54">
         <v>46013</v>
       </c>
-      <c r="J168" s="62"/>
+      <c r="J168" s="56"/>
       <c r="K168" s="3"/>
       <c r="L168" s="27" t="s">
         <v>239</v>
@@ -15979,7 +15972,7 @@
         <v>540</v>
       </c>
       <c r="W168" s="28">
-        <f>O168*V168</f>
+        <f t="shared" si="121"/>
         <v>48591.9</v>
       </c>
       <c r="X168" s="28">
@@ -15993,15 +15986,15 @@
       </c>
       <c r="AA168" s="28"/>
       <c r="AB168" s="28">
-        <f t="shared" si="86"/>
+        <f t="shared" si="122"/>
         <v>705</v>
       </c>
       <c r="AC168" s="28">
-        <f>AB168*O168</f>
+        <f t="shared" si="123"/>
         <v>63439.425000000003</v>
       </c>
       <c r="AD168" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="124"/>
         <v>14847.525000000001</v>
       </c>
       <c r="AE168" s="38" t="s">
@@ -16029,8 +16022,8 @@
       <c r="F169" s="7"/>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
-      <c r="I169" s="60"/>
-      <c r="J169" s="62"/>
+      <c r="I169" s="54"/>
+      <c r="J169" s="56"/>
       <c r="K169" s="7"/>
       <c r="L169" s="24" t="s">
         <v>17</v>
@@ -16084,11 +16077,11 @@
       <c r="G170" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H170" s="60"/>
-      <c r="I170" s="60">
+      <c r="H170" s="54"/>
+      <c r="I170" s="54">
         <v>46010</v>
       </c>
-      <c r="J170" s="62"/>
+      <c r="J170" s="56"/>
       <c r="K170" s="3"/>
       <c r="L170" s="27" t="s">
         <v>239</v>
@@ -16120,7 +16113,7 @@
         <v>545</v>
       </c>
       <c r="W170" s="28">
-        <f>O170*V170</f>
+        <f t="shared" ref="W170:W175" si="125">O170*V170</f>
         <v>51854.025000000001</v>
       </c>
       <c r="X170" s="28">
@@ -16134,15 +16127,15 @@
       </c>
       <c r="AA170" s="28"/>
       <c r="AB170" s="28">
-        <f>SUM(X170:Z170)</f>
+        <f t="shared" ref="AB170:AB175" si="126">SUM(X170:Z170)</f>
         <v>675</v>
       </c>
       <c r="AC170" s="28">
-        <f>AB170*O170</f>
+        <f t="shared" ref="AC170:AC175" si="127">AB170*O170</f>
         <v>64222.875</v>
       </c>
       <c r="AD170" s="28">
-        <f>AC170-W170</f>
+        <f t="shared" ref="AD170:AD175" si="128">AC170-W170</f>
         <v>12368.849999999999</v>
       </c>
       <c r="AE170" s="38"/>
@@ -16177,11 +16170,11 @@
       <c r="G171" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H171" s="60"/>
-      <c r="I171" s="60">
+      <c r="H171" s="54"/>
+      <c r="I171" s="54">
         <v>46010</v>
       </c>
-      <c r="J171" s="62"/>
+      <c r="J171" s="56"/>
       <c r="K171" s="3"/>
       <c r="L171" s="27" t="s">
         <v>239</v>
@@ -16213,7 +16206,7 @@
         <v>545</v>
       </c>
       <c r="W171" s="28">
-        <f>O171*V171</f>
+        <f t="shared" si="125"/>
         <v>50367.264999999999</v>
       </c>
       <c r="X171" s="28">
@@ -16227,15 +16220,15 @@
       </c>
       <c r="AA171" s="28"/>
       <c r="AB171" s="28">
-        <f>SUM(X171:Z171)</f>
+        <f t="shared" si="126"/>
         <v>675</v>
       </c>
       <c r="AC171" s="28">
-        <f>AB171*O171</f>
+        <f t="shared" si="127"/>
         <v>62381.474999999999</v>
       </c>
       <c r="AD171" s="28">
-        <f>AC171-W171</f>
+        <f t="shared" si="128"/>
         <v>12014.21</v>
       </c>
       <c r="AE171" s="38"/>
@@ -16270,11 +16263,11 @@
       <c r="G172" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H172" s="60"/>
-      <c r="I172" s="60">
+      <c r="H172" s="54"/>
+      <c r="I172" s="54">
         <v>46010</v>
       </c>
-      <c r="J172" s="62"/>
+      <c r="J172" s="56"/>
       <c r="K172" s="3"/>
       <c r="L172" s="27" t="s">
         <v>285</v>
@@ -16306,7 +16299,7 @@
         <v>545</v>
       </c>
       <c r="W172" s="28">
-        <f>O172*V172</f>
+        <f t="shared" si="125"/>
         <v>51559.18</v>
       </c>
       <c r="X172" s="28">
@@ -16320,15 +16313,15 @@
       </c>
       <c r="AA172" s="28"/>
       <c r="AB172" s="28">
-        <f>SUM(X172:Z172)</f>
+        <f t="shared" si="126"/>
         <v>675</v>
       </c>
       <c r="AC172" s="28">
-        <f>AB172*O172</f>
+        <f t="shared" si="127"/>
         <v>63857.7</v>
       </c>
       <c r="AD172" s="28">
-        <f>AC172-W172</f>
+        <f t="shared" si="128"/>
         <v>12298.519999999997</v>
       </c>
       <c r="AE172" s="38"/>
@@ -16363,11 +16356,11 @@
       <c r="G173" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H173" s="60"/>
-      <c r="I173" s="60">
+      <c r="H173" s="54"/>
+      <c r="I173" s="54">
         <v>46013</v>
       </c>
-      <c r="J173" s="62"/>
+      <c r="J173" s="56"/>
       <c r="K173" s="3"/>
       <c r="L173" s="27" t="s">
         <v>285</v>
@@ -16399,7 +16392,7 @@
         <v>545</v>
       </c>
       <c r="W173" s="28">
-        <f>O173*V173</f>
+        <f t="shared" si="125"/>
         <v>50544.39</v>
       </c>
       <c r="X173" s="28">
@@ -16413,15 +16406,15 @@
       </c>
       <c r="AA173" s="28"/>
       <c r="AB173" s="28">
-        <f>SUM(X173:Z173)</f>
+        <f t="shared" si="126"/>
         <v>675</v>
       </c>
       <c r="AC173" s="28">
-        <f>AB173*O173</f>
+        <f t="shared" si="127"/>
         <v>62600.850000000006</v>
       </c>
       <c r="AD173" s="28">
-        <f>AC173-W173</f>
+        <f t="shared" si="128"/>
         <v>12056.460000000006</v>
       </c>
       <c r="AE173" s="38"/>
@@ -16456,11 +16449,11 @@
       <c r="G174" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H174" s="60"/>
-      <c r="I174" s="60">
+      <c r="H174" s="54"/>
+      <c r="I174" s="54">
         <v>46013</v>
       </c>
-      <c r="J174" s="62"/>
+      <c r="J174" s="56"/>
       <c r="K174" s="3"/>
       <c r="L174" s="27" t="s">
         <v>241</v>
@@ -16492,7 +16485,7 @@
         <v>545</v>
       </c>
       <c r="W174" s="28">
-        <f>O174*V174</f>
+        <f t="shared" si="125"/>
         <v>49967.235000000001</v>
       </c>
       <c r="X174" s="28">
@@ -16506,15 +16499,15 @@
       </c>
       <c r="AA174" s="28"/>
       <c r="AB174" s="28">
-        <f>SUM(X174:Z174)</f>
+        <f t="shared" si="126"/>
         <v>675</v>
       </c>
       <c r="AC174" s="28">
-        <f>AB174*O174</f>
+        <f t="shared" si="127"/>
         <v>61886.025000000001</v>
       </c>
       <c r="AD174" s="28">
-        <f>AC174-W174</f>
+        <f t="shared" si="128"/>
         <v>11918.79</v>
       </c>
       <c r="AE174" s="38"/>
@@ -16549,11 +16542,11 @@
       <c r="G175" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H175" s="60"/>
-      <c r="I175" s="60">
+      <c r="H175" s="54"/>
+      <c r="I175" s="54">
         <v>46013</v>
       </c>
-      <c r="J175" s="62"/>
+      <c r="J175" s="56"/>
       <c r="K175" s="3"/>
       <c r="L175" s="27" t="s">
         <v>241</v>
@@ -16585,7 +16578,7 @@
         <v>545</v>
       </c>
       <c r="W175" s="28">
-        <f>O175*V175</f>
+        <f t="shared" si="125"/>
         <v>49883.85</v>
       </c>
       <c r="X175" s="28">
@@ -16599,15 +16592,15 @@
       </c>
       <c r="AA175" s="28"/>
       <c r="AB175" s="28">
-        <f>SUM(X175:Z175)</f>
+        <f t="shared" si="126"/>
         <v>675</v>
       </c>
       <c r="AC175" s="28">
-        <f>AB175*O175</f>
+        <f t="shared" si="127"/>
         <v>61782.75</v>
       </c>
       <c r="AD175" s="28">
-        <f>AC175-W175</f>
+        <f t="shared" si="128"/>
         <v>11898.900000000001</v>
       </c>
       <c r="AE175" s="38"/>
@@ -16633,8 +16626,8 @@
       <c r="F176" s="7"/>
       <c r="G176" s="7"/>
       <c r="H176" s="7"/>
-      <c r="I176" s="60"/>
-      <c r="J176" s="62"/>
+      <c r="I176" s="54"/>
+      <c r="J176" s="56"/>
       <c r="K176" s="7"/>
       <c r="L176" s="24" t="s">
         <v>17</v>
@@ -16688,11 +16681,11 @@
       <c r="G177" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H177" s="60"/>
-      <c r="I177" s="60">
+      <c r="H177" s="54"/>
+      <c r="I177" s="54">
         <v>46010</v>
       </c>
-      <c r="J177" s="62"/>
+      <c r="J177" s="56"/>
       <c r="K177" s="3"/>
       <c r="L177" s="27" t="s">
         <v>199</v>
@@ -16724,7 +16717,7 @@
         <v>550</v>
       </c>
       <c r="W177" s="28">
-        <f>O177*V177</f>
+        <f t="shared" ref="W177:W182" si="129">O177*V177</f>
         <v>50502.1</v>
       </c>
       <c r="X177" s="28">
@@ -16738,15 +16731,15 @@
       </c>
       <c r="AA177" s="28"/>
       <c r="AB177" s="28">
-        <f>SUM(X177:Z177)</f>
+        <f t="shared" ref="AB177:AB182" si="130">SUM(X177:Z177)</f>
         <v>665</v>
       </c>
       <c r="AC177" s="28">
-        <f>AB177*O177</f>
+        <f t="shared" ref="AC177:AC182" si="131">AB177*O177</f>
         <v>61061.630000000005</v>
       </c>
       <c r="AD177" s="28">
-        <f>AC177-W177</f>
+        <f t="shared" ref="AD177:AD182" si="132">AC177-W177</f>
         <v>10559.530000000006</v>
       </c>
       <c r="AE177" s="38"/>
@@ -16781,11 +16774,11 @@
       <c r="G178" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H178" s="60"/>
-      <c r="I178" s="60">
+      <c r="H178" s="54"/>
+      <c r="I178" s="54">
         <v>46010</v>
       </c>
-      <c r="J178" s="62"/>
+      <c r="J178" s="56"/>
       <c r="K178" s="3"/>
       <c r="L178" s="27" t="s">
         <v>241</v>
@@ -16817,7 +16810,7 @@
         <v>550</v>
       </c>
       <c r="W178" s="28">
-        <f>O178*V178</f>
+        <f t="shared" si="129"/>
         <v>51762.700000000004</v>
       </c>
       <c r="X178" s="28">
@@ -16831,15 +16824,15 @@
       </c>
       <c r="AA178" s="28"/>
       <c r="AB178" s="28">
-        <f>SUM(X178:Z178)</f>
+        <f t="shared" si="130"/>
         <v>665</v>
       </c>
       <c r="AC178" s="28">
-        <f>AB178*O178</f>
+        <f t="shared" si="131"/>
         <v>62585.810000000005</v>
       </c>
       <c r="AD178" s="28">
-        <f>AC178-W178</f>
+        <f t="shared" si="132"/>
         <v>10823.11</v>
       </c>
       <c r="AE178" s="38"/>
@@ -16874,11 +16867,11 @@
       <c r="G179" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H179" s="60"/>
-      <c r="I179" s="60">
+      <c r="H179" s="54"/>
+      <c r="I179" s="54">
         <v>46010</v>
       </c>
-      <c r="J179" s="62"/>
+      <c r="J179" s="56"/>
       <c r="K179" s="3"/>
       <c r="L179" s="27" t="s">
         <v>241</v>
@@ -16910,7 +16903,7 @@
         <v>550</v>
       </c>
       <c r="W179" s="28">
-        <f>O179*V179</f>
+        <f t="shared" si="129"/>
         <v>49014.899999999994</v>
       </c>
       <c r="X179" s="28">
@@ -16924,15 +16917,15 @@
       </c>
       <c r="AA179" s="28"/>
       <c r="AB179" s="28">
-        <f>SUM(X179:Z179)</f>
+        <f t="shared" si="130"/>
         <v>665</v>
       </c>
       <c r="AC179" s="28">
-        <f>AB179*O179</f>
+        <f t="shared" si="131"/>
         <v>59263.469999999994</v>
       </c>
       <c r="AD179" s="28">
-        <f>AC179-W179</f>
+        <f t="shared" si="132"/>
         <v>10248.57</v>
       </c>
       <c r="AE179" s="38"/>
@@ -16967,11 +16960,11 @@
       <c r="G180" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H180" s="60"/>
-      <c r="I180" s="60">
+      <c r="H180" s="54"/>
+      <c r="I180" s="54">
         <v>46013</v>
       </c>
-      <c r="J180" s="62"/>
+      <c r="J180" s="56"/>
       <c r="K180" s="3"/>
       <c r="L180" s="27" t="s">
         <v>241</v>
@@ -17003,7 +16996,7 @@
         <v>550</v>
       </c>
       <c r="W180" s="28">
-        <f>O180*V180</f>
+        <f t="shared" si="129"/>
         <v>49608.35</v>
       </c>
       <c r="X180" s="28">
@@ -17017,15 +17010,15 @@
       </c>
       <c r="AA180" s="28"/>
       <c r="AB180" s="28">
-        <f>SUM(X180:Z180)</f>
+        <f t="shared" si="130"/>
         <v>665</v>
       </c>
       <c r="AC180" s="28">
-        <f>AB180*O180</f>
+        <f t="shared" si="131"/>
         <v>59981.005000000005</v>
       </c>
       <c r="AD180" s="28">
-        <f>AC180-W180</f>
+        <f t="shared" si="132"/>
         <v>10372.655000000006</v>
       </c>
       <c r="AE180" s="38"/>
@@ -17060,11 +17053,11 @@
       <c r="G181" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H181" s="60"/>
-      <c r="I181" s="60">
+      <c r="H181" s="54"/>
+      <c r="I181" s="54">
         <v>46013</v>
       </c>
-      <c r="J181" s="62"/>
+      <c r="J181" s="56"/>
       <c r="K181" s="3"/>
       <c r="L181" s="27" t="s">
         <v>240</v>
@@ -17096,7 +17089,7 @@
         <v>550</v>
       </c>
       <c r="W181" s="28">
-        <f>O181*V181</f>
+        <f t="shared" si="129"/>
         <v>49747.5</v>
       </c>
       <c r="X181" s="28">
@@ -17110,15 +17103,15 @@
       </c>
       <c r="AA181" s="28"/>
       <c r="AB181" s="28">
-        <f>SUM(X181:Z181)</f>
+        <f t="shared" si="130"/>
         <v>665</v>
       </c>
       <c r="AC181" s="28">
-        <f>AB181*O181</f>
+        <f t="shared" si="131"/>
         <v>60149.25</v>
       </c>
       <c r="AD181" s="28">
-        <f>AC181-W181</f>
+        <f t="shared" si="132"/>
         <v>10401.75</v>
       </c>
       <c r="AE181" s="38"/>
@@ -17153,11 +17146,11 @@
       <c r="G182" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H182" s="60"/>
-      <c r="I182" s="60">
+      <c r="H182" s="54"/>
+      <c r="I182" s="54">
         <v>46013</v>
       </c>
-      <c r="J182" s="62"/>
+      <c r="J182" s="56"/>
       <c r="K182" s="3"/>
       <c r="L182" s="27" t="s">
         <v>119</v>
@@ -17189,7 +17182,7 @@
         <v>550</v>
       </c>
       <c r="W182" s="28">
-        <f>O182*V182</f>
+        <f t="shared" si="129"/>
         <v>49924.600000000006</v>
       </c>
       <c r="X182" s="28">
@@ -17203,15 +17196,15 @@
       </c>
       <c r="AA182" s="28"/>
       <c r="AB182" s="28">
-        <f>SUM(X182:Z182)</f>
+        <f t="shared" si="130"/>
         <v>665</v>
       </c>
       <c r="AC182" s="28">
-        <f>AB182*O182</f>
+        <f t="shared" si="131"/>
         <v>60363.380000000005</v>
       </c>
       <c r="AD182" s="28">
-        <f>AC182-W182</f>
+        <f t="shared" si="132"/>
         <v>10438.779999999999</v>
       </c>
       <c r="AE182" s="38"/>
@@ -17237,8 +17230,8 @@
       <c r="F183" s="7"/>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
-      <c r="I183" s="60"/>
-      <c r="J183" s="62"/>
+      <c r="I183" s="54"/>
+      <c r="J183" s="56"/>
       <c r="K183" s="7"/>
       <c r="L183" s="24" t="s">
         <v>17</v>
@@ -17292,9 +17285,9 @@
       <c r="G184" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H184" s="60"/>
-      <c r="I184" s="60"/>
-      <c r="J184" s="62"/>
+      <c r="H184" s="54"/>
+      <c r="I184" s="54"/>
+      <c r="J184" s="56"/>
       <c r="K184" s="3"/>
       <c r="L184" s="27" t="s">
         <v>239</v>
@@ -17340,15 +17333,15 @@
       </c>
       <c r="AA184" s="28"/>
       <c r="AB184" s="28">
-        <f>SUM(X184:Z184)</f>
+        <f t="shared" ref="AB184:AB192" si="133">SUM(X184:Z184)</f>
         <v>660</v>
       </c>
       <c r="AC184" s="28">
-        <f>AB184*O184</f>
+        <f t="shared" ref="AC184:AC192" si="134">AB184*O184</f>
         <v>59592.72</v>
       </c>
       <c r="AD184" s="28">
-        <f>AC184-W184</f>
+        <f t="shared" ref="AD184:AD192" si="135">AC184-W184</f>
         <v>9932.1200000000026</v>
       </c>
       <c r="AE184" s="38"/>
@@ -17383,9 +17376,9 @@
       <c r="G185" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H185" s="60"/>
-      <c r="I185" s="60"/>
-      <c r="J185" s="62"/>
+      <c r="H185" s="54"/>
+      <c r="I185" s="54"/>
+      <c r="J185" s="56"/>
       <c r="K185" s="3"/>
       <c r="L185" s="27" t="s">
         <v>239</v>
@@ -17431,15 +17424,15 @@
       </c>
       <c r="AA185" s="28"/>
       <c r="AB185" s="28">
-        <f>SUM(X185:Z185)</f>
+        <f t="shared" si="133"/>
         <v>660</v>
       </c>
       <c r="AC185" s="28">
-        <f>AB185*O185</f>
+        <f t="shared" si="134"/>
         <v>60899.520000000004</v>
       </c>
       <c r="AD185" s="28">
-        <f>AC185-W185</f>
+        <f t="shared" si="135"/>
         <v>10149.919999999998</v>
       </c>
       <c r="AE185" s="38"/>
@@ -17474,9 +17467,9 @@
       <c r="G186" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H186" s="60"/>
-      <c r="I186" s="60"/>
-      <c r="J186" s="62"/>
+      <c r="H186" s="54"/>
+      <c r="I186" s="54"/>
+      <c r="J186" s="56"/>
       <c r="K186" s="3"/>
       <c r="L186" s="27" t="s">
         <v>239</v>
@@ -17522,15 +17515,15 @@
       </c>
       <c r="AA186" s="28"/>
       <c r="AB186" s="28">
-        <f>SUM(X186:Z186)</f>
+        <f t="shared" si="133"/>
         <v>660</v>
       </c>
       <c r="AC186" s="28">
-        <f>AB186*O186</f>
+        <f t="shared" si="134"/>
         <v>59444.88</v>
       </c>
       <c r="AD186" s="28">
-        <f>AC186-W186</f>
+        <f t="shared" si="135"/>
         <v>9907.4799999999959</v>
       </c>
       <c r="AE186" s="38"/>
@@ -17565,9 +17558,9 @@
       <c r="G187" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H187" s="60"/>
-      <c r="I187" s="60"/>
-      <c r="J187" s="62"/>
+      <c r="H187" s="54"/>
+      <c r="I187" s="54"/>
+      <c r="J187" s="56"/>
       <c r="K187" s="3"/>
       <c r="L187" s="27" t="s">
         <v>241</v>
@@ -17613,15 +17606,15 @@
       </c>
       <c r="AA187" s="28"/>
       <c r="AB187" s="28">
-        <f>SUM(X187:Z187)</f>
+        <f t="shared" si="133"/>
         <v>660</v>
       </c>
       <c r="AC187" s="28">
-        <f>AB187*O187</f>
+        <f t="shared" si="134"/>
         <v>59821.08</v>
       </c>
       <c r="AD187" s="28">
-        <f>AC187-W187</f>
+        <f t="shared" si="135"/>
         <v>9970.18</v>
       </c>
       <c r="AE187" s="38"/>
@@ -17656,9 +17649,9 @@
       <c r="G188" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H188" s="60"/>
-      <c r="I188" s="60"/>
-      <c r="J188" s="62"/>
+      <c r="H188" s="54"/>
+      <c r="I188" s="54"/>
+      <c r="J188" s="56"/>
       <c r="K188" s="3"/>
       <c r="L188" s="27" t="s">
         <v>241</v>
@@ -17690,7 +17683,7 @@
         <v>550</v>
       </c>
       <c r="W188" s="28">
-        <f t="shared" ref="W188:W190" si="88">O188*V188</f>
+        <f t="shared" ref="W188:W190" si="136">O188*V188</f>
         <v>49788.2</v>
       </c>
       <c r="X188" s="28">
@@ -17704,15 +17697,15 @@
       </c>
       <c r="AA188" s="28"/>
       <c r="AB188" s="28">
-        <f>SUM(X188:Z188)</f>
+        <f t="shared" si="133"/>
         <v>660</v>
       </c>
       <c r="AC188" s="28">
-        <f>AB188*O188</f>
+        <f t="shared" si="134"/>
         <v>59745.840000000004</v>
       </c>
       <c r="AD188" s="28">
-        <f>AC188-W188</f>
+        <f t="shared" si="135"/>
         <v>9957.6400000000067</v>
       </c>
       <c r="AE188" s="38"/>
@@ -17747,9 +17740,9 @@
       <c r="G189" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H189" s="60"/>
-      <c r="I189" s="60"/>
-      <c r="J189" s="62"/>
+      <c r="H189" s="54"/>
+      <c r="I189" s="54"/>
+      <c r="J189" s="56"/>
       <c r="K189" s="3"/>
       <c r="L189" s="27" t="s">
         <v>241</v>
@@ -17781,7 +17774,7 @@
         <v>550</v>
       </c>
       <c r="W189" s="28">
-        <f t="shared" si="88"/>
+        <f t="shared" si="136"/>
         <v>50460.299999999996</v>
       </c>
       <c r="X189" s="28">
@@ -17795,15 +17788,15 @@
       </c>
       <c r="AA189" s="28"/>
       <c r="AB189" s="28">
-        <f>SUM(X189:Z189)</f>
+        <f t="shared" si="133"/>
         <v>660</v>
       </c>
       <c r="AC189" s="28">
-        <f>AB189*O189</f>
+        <f t="shared" si="134"/>
         <v>60552.359999999993</v>
       </c>
       <c r="AD189" s="28">
-        <f>AC189-W189</f>
+        <f t="shared" si="135"/>
         <v>10092.059999999998</v>
       </c>
       <c r="AE189" s="38"/>
@@ -17838,9 +17831,9 @@
       <c r="G190" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H190" s="60"/>
-      <c r="I190" s="60"/>
-      <c r="J190" s="62"/>
+      <c r="H190" s="54"/>
+      <c r="I190" s="54"/>
+      <c r="J190" s="56"/>
       <c r="K190" s="3"/>
       <c r="L190" s="27" t="s">
         <v>242</v>
@@ -17872,7 +17865,7 @@
         <v>550</v>
       </c>
       <c r="W190" s="28">
-        <f t="shared" si="88"/>
+        <f t="shared" si="136"/>
         <v>49489.549999999996</v>
       </c>
       <c r="X190" s="28">
@@ -17886,15 +17879,15 @@
       </c>
       <c r="AA190" s="28"/>
       <c r="AB190" s="28">
-        <f>SUM(X190:Z190)</f>
+        <f t="shared" si="133"/>
         <v>660</v>
       </c>
       <c r="AC190" s="28">
-        <f>AB190*O190</f>
+        <f t="shared" si="134"/>
         <v>59387.46</v>
       </c>
       <c r="AD190" s="28">
-        <f>AC190-W190</f>
+        <f t="shared" si="135"/>
         <v>9897.9100000000035</v>
       </c>
       <c r="AE190" s="38"/>
@@ -17929,9 +17922,9 @@
       <c r="G191" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H191" s="60"/>
-      <c r="I191" s="60"/>
-      <c r="J191" s="62"/>
+      <c r="H191" s="54"/>
+      <c r="I191" s="54"/>
+      <c r="J191" s="56"/>
       <c r="K191" s="3"/>
       <c r="L191" s="27" t="s">
         <v>242</v>
@@ -17963,7 +17956,7 @@
         <v>550</v>
       </c>
       <c r="W191" s="28">
-        <f t="shared" ref="W191" si="89">O191*V191</f>
+        <f t="shared" ref="W191" si="137">O191*V191</f>
         <v>48554.55</v>
       </c>
       <c r="X191" s="28">
@@ -17977,15 +17970,15 @@
       </c>
       <c r="AA191" s="28"/>
       <c r="AB191" s="28">
-        <f>SUM(X191:Z191)</f>
+        <f t="shared" si="133"/>
         <v>660</v>
       </c>
       <c r="AC191" s="28">
-        <f>AB191*O191</f>
+        <f t="shared" si="134"/>
         <v>58265.460000000006</v>
       </c>
       <c r="AD191" s="28">
-        <f>AC191-W191</f>
+        <f t="shared" si="135"/>
         <v>9710.9100000000035</v>
       </c>
       <c r="AE191" s="38"/>
@@ -18020,9 +18013,9 @@
       <c r="G192" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H192" s="60"/>
-      <c r="I192" s="60"/>
-      <c r="J192" s="62"/>
+      <c r="H192" s="54"/>
+      <c r="I192" s="54"/>
+      <c r="J192" s="56"/>
       <c r="K192" s="3"/>
       <c r="L192" s="27" t="s">
         <v>242</v>
@@ -18068,15 +18061,15 @@
       </c>
       <c r="AA192" s="28"/>
       <c r="AB192" s="28">
-        <f>SUM(X192:Z192)</f>
+        <f t="shared" si="133"/>
         <v>660</v>
       </c>
       <c r="AC192" s="28">
-        <f>AB192*O192</f>
+        <f t="shared" si="134"/>
         <v>60786.659999999996</v>
       </c>
       <c r="AD192" s="28">
-        <f>AC192-W192</f>
+        <f t="shared" si="135"/>
         <v>10131.109999999993</v>
       </c>
       <c r="AE192" s="38"/>
@@ -18102,8 +18095,8 @@
       <c r="F193" s="7"/>
       <c r="G193" s="7"/>
       <c r="H193" s="7"/>
-      <c r="I193" s="60"/>
-      <c r="J193" s="62"/>
+      <c r="I193" s="54"/>
+      <c r="J193" s="56"/>
       <c r="K193" s="7"/>
       <c r="L193" s="24" t="s">
         <v>17</v>
@@ -18157,9 +18150,9 @@
       <c r="G194" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H194" s="60"/>
-      <c r="I194" s="60"/>
-      <c r="J194" s="62"/>
+      <c r="H194" s="54"/>
+      <c r="I194" s="54"/>
+      <c r="J194" s="56"/>
       <c r="K194" s="3"/>
       <c r="L194" s="27" t="s">
         <v>241</v>
@@ -18205,15 +18198,15 @@
       </c>
       <c r="AA194" s="28"/>
       <c r="AB194" s="28">
-        <f>SUM(X194:Z194)</f>
+        <f t="shared" ref="AB194:AB205" si="138">SUM(X194:Z194)</f>
         <v>660</v>
       </c>
       <c r="AC194" s="28">
-        <f>AB194*O194</f>
+        <f t="shared" ref="AC194:AC205" si="139">AB194*O194</f>
         <v>59651.46</v>
       </c>
       <c r="AD194" s="28">
-        <f>AC194-W194</f>
+        <f t="shared" ref="AD194:AD205" si="140">AC194-W194</f>
         <v>9941.9099999999962</v>
       </c>
       <c r="AE194" s="38"/>
@@ -18248,9 +18241,9 @@
       <c r="G195" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H195" s="60"/>
-      <c r="I195" s="60"/>
-      <c r="J195" s="62"/>
+      <c r="H195" s="54"/>
+      <c r="I195" s="54"/>
+      <c r="J195" s="56"/>
       <c r="K195" s="3"/>
       <c r="L195" s="27" t="s">
         <v>241</v>
@@ -18296,15 +18289,15 @@
       </c>
       <c r="AA195" s="28"/>
       <c r="AB195" s="28">
-        <f>SUM(X195:Z195)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC195" s="28">
-        <f>AB195*O195</f>
+        <f t="shared" si="139"/>
         <v>60455.999999999993</v>
       </c>
       <c r="AD195" s="28">
-        <f>AC195-W195</f>
+        <f t="shared" si="140"/>
         <v>10075.999999999993</v>
       </c>
       <c r="AE195" s="38"/>
@@ -18339,9 +18332,9 @@
       <c r="G196" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H196" s="60"/>
-      <c r="I196" s="60"/>
-      <c r="J196" s="62"/>
+      <c r="H196" s="54"/>
+      <c r="I196" s="54"/>
+      <c r="J196" s="56"/>
       <c r="K196" s="3"/>
       <c r="L196" s="27" t="s">
         <v>241</v>
@@ -18387,15 +18380,15 @@
       </c>
       <c r="AA196" s="28"/>
       <c r="AB196" s="28">
-        <f>SUM(X196:Z196)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC196" s="28">
-        <f>AB196*O196</f>
+        <f t="shared" si="139"/>
         <v>60318.719999999994</v>
       </c>
       <c r="AD196" s="28">
-        <f>AC196-W196</f>
+        <f t="shared" si="140"/>
         <v>10053.119999999995</v>
       </c>
       <c r="AE196" s="38"/>
@@ -18430,9 +18423,9 @@
       <c r="G197" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H197" s="60"/>
-      <c r="I197" s="60"/>
-      <c r="J197" s="62"/>
+      <c r="H197" s="54"/>
+      <c r="I197" s="54"/>
+      <c r="J197" s="56"/>
       <c r="K197" s="3"/>
       <c r="L197" s="27" t="s">
         <v>239</v>
@@ -18478,15 +18471,15 @@
       </c>
       <c r="AA197" s="28"/>
       <c r="AB197" s="28">
-        <f>SUM(X197:Z197)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC197" s="28">
-        <f>AB197*O197</f>
+        <f t="shared" si="139"/>
         <v>60535.86</v>
       </c>
       <c r="AD197" s="28">
-        <f>AC197-W197</f>
+        <f t="shared" si="140"/>
         <v>10089.309999999998</v>
       </c>
       <c r="AE197" s="38"/>
@@ -18521,9 +18514,9 @@
       <c r="G198" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H198" s="60"/>
-      <c r="I198" s="60"/>
-      <c r="J198" s="62"/>
+      <c r="H198" s="54"/>
+      <c r="I198" s="54"/>
+      <c r="J198" s="56"/>
       <c r="K198" s="3"/>
       <c r="L198" s="27" t="s">
         <v>239</v>
@@ -18555,7 +18548,7 @@
         <v>550</v>
       </c>
       <c r="W198" s="28">
-        <f t="shared" ref="W198:W201" si="90">O198*V198</f>
+        <f t="shared" ref="W198:W201" si="141">O198*V198</f>
         <v>51025.15</v>
       </c>
       <c r="X198" s="28">
@@ -18569,15 +18562,15 @@
       </c>
       <c r="AA198" s="28"/>
       <c r="AB198" s="28">
-        <f>SUM(X198:Z198)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC198" s="28">
-        <f>AB198*O198</f>
+        <f t="shared" si="139"/>
         <v>61230.18</v>
       </c>
       <c r="AD198" s="28">
-        <f>AC198-W198</f>
+        <f t="shared" si="140"/>
         <v>10205.029999999999</v>
       </c>
       <c r="AE198" s="38"/>
@@ -18612,9 +18605,9 @@
       <c r="G199" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H199" s="60"/>
-      <c r="I199" s="60"/>
-      <c r="J199" s="62"/>
+      <c r="H199" s="54"/>
+      <c r="I199" s="54"/>
+      <c r="J199" s="56"/>
       <c r="K199" s="3"/>
       <c r="L199" s="27" t="s">
         <v>420</v>
@@ -18646,7 +18639,7 @@
         <v>550</v>
       </c>
       <c r="W199" s="28">
-        <f t="shared" si="90"/>
+        <f t="shared" si="141"/>
         <v>49856.4</v>
       </c>
       <c r="X199" s="28">
@@ -18660,15 +18653,15 @@
       </c>
       <c r="AA199" s="28"/>
       <c r="AB199" s="28">
-        <f>SUM(X199:Z199)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC199" s="28">
-        <f>AB199*O199</f>
+        <f t="shared" si="139"/>
         <v>59827.68</v>
       </c>
       <c r="AD199" s="28">
-        <f>AC199-W199</f>
+        <f t="shared" si="140"/>
         <v>9971.2799999999988</v>
       </c>
       <c r="AE199" s="38"/>
@@ -18703,17 +18696,19 @@
       <c r="G200" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H200" s="60"/>
-      <c r="I200" s="60"/>
-      <c r="J200" s="62"/>
+      <c r="H200" s="54"/>
+      <c r="I200" s="54"/>
+      <c r="J200" s="56"/>
       <c r="K200" s="3"/>
-      <c r="L200" s="27"/>
+      <c r="L200" s="27" t="s">
+        <v>241</v>
+      </c>
       <c r="M200" s="27" t="s">
         <v>375</v>
       </c>
       <c r="N200" s="27"/>
       <c r="O200" s="27">
-        <v>90</v>
+        <v>93.665000000000006</v>
       </c>
       <c r="P200" s="20" t="s">
         <v>15</v>
@@ -18735,8 +18730,8 @@
         <v>550</v>
       </c>
       <c r="W200" s="28">
-        <f t="shared" si="90"/>
-        <v>49500</v>
+        <f t="shared" si="141"/>
+        <v>51515.75</v>
       </c>
       <c r="X200" s="28">
         <v>660</v>
@@ -18749,16 +18744,16 @@
       </c>
       <c r="AA200" s="28"/>
       <c r="AB200" s="28">
-        <f>SUM(X200:Z200)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC200" s="28">
-        <f>AB200*O200</f>
-        <v>59400</v>
+        <f t="shared" si="139"/>
+        <v>61818.9</v>
       </c>
       <c r="AD200" s="28">
-        <f>AC200-W200</f>
-        <v>9900</v>
+        <f t="shared" si="140"/>
+        <v>10303.150000000001</v>
       </c>
       <c r="AE200" s="38"/>
       <c r="AF200" s="3"/>
@@ -18792,17 +18787,19 @@
       <c r="G201" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H201" s="60"/>
-      <c r="I201" s="60"/>
-      <c r="J201" s="62"/>
+      <c r="H201" s="54"/>
+      <c r="I201" s="54"/>
+      <c r="J201" s="56"/>
       <c r="K201" s="3"/>
-      <c r="L201" s="27"/>
+      <c r="L201" s="27" t="s">
+        <v>241</v>
+      </c>
       <c r="M201" s="27" t="s">
         <v>375</v>
       </c>
       <c r="N201" s="27"/>
       <c r="O201" s="27">
-        <v>90</v>
+        <v>91.561999999999998</v>
       </c>
       <c r="P201" s="20" t="s">
         <v>15</v>
@@ -18824,8 +18821,8 @@
         <v>550</v>
       </c>
       <c r="W201" s="28">
-        <f t="shared" si="90"/>
-        <v>49500</v>
+        <f t="shared" si="141"/>
+        <v>50359.1</v>
       </c>
       <c r="X201" s="28">
         <v>660</v>
@@ -18838,16 +18835,16 @@
       </c>
       <c r="AA201" s="28"/>
       <c r="AB201" s="28">
-        <f>SUM(X201:Z201)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC201" s="28">
-        <f>AB201*O201</f>
-        <v>59400</v>
+        <f t="shared" si="139"/>
+        <v>60430.92</v>
       </c>
       <c r="AD201" s="28">
-        <f>AC201-W201</f>
-        <v>9900</v>
+        <f t="shared" si="140"/>
+        <v>10071.82</v>
       </c>
       <c r="AE201" s="38"/>
       <c r="AF201" s="3"/>
@@ -18881,17 +18878,19 @@
       <c r="G202" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H202" s="60"/>
-      <c r="I202" s="60"/>
-      <c r="J202" s="62"/>
+      <c r="H202" s="54"/>
+      <c r="I202" s="54"/>
+      <c r="J202" s="56"/>
       <c r="K202" s="3"/>
-      <c r="L202" s="27"/>
+      <c r="L202" s="27" t="s">
+        <v>241</v>
+      </c>
       <c r="M202" s="27" t="s">
         <v>375</v>
       </c>
       <c r="N202" s="27"/>
       <c r="O202" s="27">
-        <v>90</v>
+        <v>90.658000000000001</v>
       </c>
       <c r="P202" s="20" t="s">
         <v>15</v>
@@ -18914,7 +18913,7 @@
       </c>
       <c r="W202" s="28">
         <f>O202*V202</f>
-        <v>49500</v>
+        <v>49861.9</v>
       </c>
       <c r="X202" s="28">
         <v>660</v>
@@ -18927,16 +18926,16 @@
       </c>
       <c r="AA202" s="28"/>
       <c r="AB202" s="28">
-        <f>SUM(X202:Z202)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC202" s="28">
-        <f>AB202*O202</f>
-        <v>59400</v>
+        <f t="shared" si="139"/>
+        <v>59834.28</v>
       </c>
       <c r="AD202" s="28">
-        <f>AC202-W202</f>
-        <v>9900</v>
+        <f t="shared" si="140"/>
+        <v>9972.3799999999974</v>
       </c>
       <c r="AE202" s="38"/>
       <c r="AF202" s="3"/>
@@ -18970,17 +18969,19 @@
       <c r="G203" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H203" s="60"/>
-      <c r="I203" s="60"/>
-      <c r="J203" s="62"/>
+      <c r="H203" s="54"/>
+      <c r="I203" s="54"/>
+      <c r="J203" s="56"/>
       <c r="K203" s="3"/>
-      <c r="L203" s="27"/>
+      <c r="L203" s="27" t="s">
+        <v>241</v>
+      </c>
       <c r="M203" s="27" t="s">
         <v>375</v>
       </c>
       <c r="N203" s="27"/>
       <c r="O203" s="27">
-        <v>90</v>
+        <v>92.525999999999996</v>
       </c>
       <c r="P203" s="20" t="s">
         <v>15</v>
@@ -19003,7 +19004,7 @@
       </c>
       <c r="W203" s="28">
         <f>O203*V203</f>
-        <v>49500</v>
+        <v>50889.299999999996</v>
       </c>
       <c r="X203" s="28">
         <v>660</v>
@@ -19016,16 +19017,16 @@
       </c>
       <c r="AA203" s="28"/>
       <c r="AB203" s="28">
-        <f>SUM(X203:Z203)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC203" s="28">
-        <f>AB203*O203</f>
-        <v>59400</v>
+        <f t="shared" si="139"/>
+        <v>61067.159999999996</v>
       </c>
       <c r="AD203" s="28">
-        <f>AC203-W203</f>
-        <v>9900</v>
+        <f t="shared" si="140"/>
+        <v>10177.86</v>
       </c>
       <c r="AE203" s="38"/>
       <c r="AF203" s="3"/>
@@ -19059,17 +19060,19 @@
       <c r="G204" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H204" s="60"/>
-      <c r="I204" s="60"/>
-      <c r="J204" s="62"/>
+      <c r="H204" s="54"/>
+      <c r="I204" s="54"/>
+      <c r="J204" s="56"/>
       <c r="K204" s="3"/>
-      <c r="L204" s="27"/>
+      <c r="L204" s="27" t="s">
+        <v>241</v>
+      </c>
       <c r="M204" s="27" t="s">
         <v>375</v>
       </c>
       <c r="N204" s="27"/>
       <c r="O204" s="27">
-        <v>90</v>
+        <v>93.212000000000003</v>
       </c>
       <c r="P204" s="20" t="s">
         <v>15</v>
@@ -19092,7 +19095,7 @@
       </c>
       <c r="W204" s="28">
         <f>O204*V204</f>
-        <v>49500</v>
+        <v>51266.6</v>
       </c>
       <c r="X204" s="28">
         <v>660</v>
@@ -19105,16 +19108,16 @@
       </c>
       <c r="AA204" s="28"/>
       <c r="AB204" s="28">
-        <f>SUM(X204:Z204)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC204" s="28">
-        <f>AB204*O204</f>
-        <v>59400</v>
+        <f t="shared" si="139"/>
+        <v>61519.920000000006</v>
       </c>
       <c r="AD204" s="28">
-        <f>AC204-W204</f>
-        <v>9900</v>
+        <f t="shared" si="140"/>
+        <v>10253.320000000007</v>
       </c>
       <c r="AE204" s="38"/>
       <c r="AF204" s="3"/>
@@ -19148,17 +19151,19 @@
       <c r="G205" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H205" s="60"/>
-      <c r="I205" s="60"/>
-      <c r="J205" s="62"/>
+      <c r="H205" s="54"/>
+      <c r="I205" s="54"/>
+      <c r="J205" s="56"/>
       <c r="K205" s="3"/>
-      <c r="L205" s="27"/>
+      <c r="L205" s="27" t="s">
+        <v>241</v>
+      </c>
       <c r="M205" s="27" t="s">
         <v>375</v>
       </c>
       <c r="N205" s="27"/>
       <c r="O205" s="27">
-        <v>90</v>
+        <v>89.864999999999995</v>
       </c>
       <c r="P205" s="20" t="s">
         <v>15</v>
@@ -19181,7 +19186,7 @@
       </c>
       <c r="W205" s="28">
         <f>O205*V205</f>
-        <v>49500</v>
+        <v>49425.75</v>
       </c>
       <c r="X205" s="28">
         <v>660</v>
@@ -19194,16 +19199,16 @@
       </c>
       <c r="AA205" s="28"/>
       <c r="AB205" s="28">
-        <f>SUM(X205:Z205)</f>
+        <f t="shared" si="138"/>
         <v>660</v>
       </c>
       <c r="AC205" s="28">
-        <f>AB205*O205</f>
-        <v>59400</v>
+        <f t="shared" si="139"/>
+        <v>59310.899999999994</v>
       </c>
       <c r="AD205" s="28">
-        <f>AC205-W205</f>
-        <v>9900</v>
+        <f t="shared" si="140"/>
+        <v>9885.1499999999942</v>
       </c>
       <c r="AE205" s="38"/>
       <c r="AF205" s="3"/>
@@ -19228,8 +19233,8 @@
       <c r="F206" s="7"/>
       <c r="G206" s="7"/>
       <c r="H206" s="7"/>
-      <c r="I206" s="60"/>
-      <c r="J206" s="62"/>
+      <c r="I206" s="54"/>
+      <c r="J206" s="56"/>
       <c r="K206" s="7"/>
       <c r="L206" s="24" t="s">
         <v>17</v>
@@ -19238,7 +19243,7 @@
       <c r="N206" s="24"/>
       <c r="O206" s="24">
         <f>+SUM(O194:O205)</f>
-        <v>1088.5149999999999</v>
+        <v>1100.0029999999999</v>
       </c>
       <c r="P206" s="8"/>
       <c r="Q206" s="24"/>
@@ -19249,7 +19254,7 @@
       <c r="V206" s="24"/>
       <c r="W206" s="25">
         <f>+SUM(W194:W205)</f>
-        <v>598683.25</v>
+        <v>605001.65</v>
       </c>
       <c r="X206" s="24"/>
       <c r="Y206" s="24"/>
@@ -19258,11 +19263,11 @@
       <c r="AB206" s="24"/>
       <c r="AC206" s="25">
         <f>+SUM(AC194:AC205)</f>
-        <v>718419.89999999991</v>
+        <v>726001.9800000001</v>
       </c>
       <c r="AD206" s="25">
         <f>+SUM(AD194:AD205)</f>
-        <v>119736.64999999998</v>
+        <v>121000.33</v>
       </c>
     </row>
     <row r="207" spans="1:44" x14ac:dyDescent="0.2">
@@ -19274,7 +19279,7 @@
         <f>SUM(AD146,AD118,AD153)</f>
         <v>107931.84000000001</v>
       </c>
-      <c r="AE207" s="96">
+      <c r="AE207">
         <f>SUM(O146,O118,O153)</f>
         <v>553.41</v>
       </c>
@@ -19290,12 +19295,12 @@
       <c r="Y209" s="17"/>
       <c r="Z209" s="43"/>
       <c r="AA209" s="43"/>
-      <c r="AB209" s="106"/>
-      <c r="AC209" s="54" t="s">
+      <c r="AB209" s="95"/>
+      <c r="AC209" s="120" t="s">
         <v>372</v>
       </c>
-      <c r="AD209" s="54"/>
-      <c r="AE209" s="96" t="s">
+      <c r="AD209" s="120"/>
+      <c r="AE209" t="s">
         <v>244</v>
       </c>
     </row>
@@ -19316,9 +19321,8 @@
       </c>
       <c r="AD211" s="17">
         <f>SUM(AD176,AD183,AD193,AD206)</f>
-        <v>344886.10499999998</v>
-      </c>
-      <c r="AE211" s="96"/>
+        <v>346149.78500000003</v>
+      </c>
     </row>
     <row r="212" spans="16:36" x14ac:dyDescent="0.2">
       <c r="W212" s="17"/>
@@ -19327,26 +19331,21 @@
         <v>269</v>
       </c>
       <c r="AD212" s="17"/>
-      <c r="AE212" s="96"/>
     </row>
     <row r="213" spans="16:36" x14ac:dyDescent="0.2">
       <c r="W213" s="17"/>
       <c r="AD213" s="17"/>
-      <c r="AE213" s="96"/>
     </row>
     <row r="214" spans="16:36" x14ac:dyDescent="0.2">
       <c r="AD214" s="17"/>
-      <c r="AE214" s="96"/>
     </row>
     <row r="215" spans="16:36" x14ac:dyDescent="0.2">
       <c r="W215" s="17"/>
       <c r="AC215" s="17"/>
-      <c r="AE215" s="96"/>
     </row>
     <row r="216" spans="16:36" x14ac:dyDescent="0.2">
       <c r="AB216" s="17"/>
       <c r="AC216" s="17"/>
-      <c r="AE216" s="96"/>
     </row>
     <row r="217" spans="16:36" x14ac:dyDescent="0.2">
       <c r="P217" s="36"/>
@@ -19369,53 +19368,53 @@
     <row r="221" spans="16:36" x14ac:dyDescent="0.2">
       <c r="Q221" s="17"/>
       <c r="AB221" s="17"/>
-      <c r="AF221" s="88" t="s">
+      <c r="AF221" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="AG221" s="88"/>
-      <c r="AH221" s="88"/>
-      <c r="AI221" s="88"/>
-      <c r="AJ221" s="88"/>
+      <c r="AG221" s="116"/>
+      <c r="AH221" s="116"/>
+      <c r="AI221" s="116"/>
+      <c r="AJ221" s="116"/>
     </row>
     <row r="222" spans="16:36" ht="16" x14ac:dyDescent="0.2">
       <c r="Q222" s="17"/>
       <c r="AB222" s="17"/>
-      <c r="AF222" s="83" t="s">
+      <c r="AF222" s="74" t="s">
         <v>243</v>
       </c>
-      <c r="AG222" s="121" t="s">
+      <c r="AG222" s="105" t="s">
         <v>380</v>
       </c>
-      <c r="AH222" s="122" t="s">
+      <c r="AH222" s="79" t="s">
         <v>244</v>
       </c>
-      <c r="AI222" s="122"/>
-      <c r="AJ222" s="82" t="s">
+      <c r="AI222" s="79"/>
+      <c r="AJ222" s="73" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="223" spans="16:36" x14ac:dyDescent="0.2">
       <c r="Q223" s="17"/>
       <c r="AB223" s="17"/>
-      <c r="AF223" s="80"/>
-      <c r="AG223" s="123"/>
+      <c r="AF223" s="71"/>
+      <c r="AG223" s="106"/>
       <c r="AH223" s="52"/>
-      <c r="AI223" s="122"/>
+      <c r="AI223" s="79"/>
       <c r="AJ223" s="52"/>
     </row>
     <row r="224" spans="16:36" x14ac:dyDescent="0.2">
       <c r="Q224" s="17"/>
       <c r="AB224" s="17"/>
-      <c r="AF224" s="80">
+      <c r="AF224" s="71">
         <v>297000</v>
       </c>
-      <c r="AG224" s="123">
+      <c r="AG224" s="106">
         <v>46121</v>
       </c>
       <c r="AH224" s="52" t="s">
         <v>419</v>
       </c>
-      <c r="AI224" s="122"/>
+      <c r="AI224" s="79"/>
       <c r="AJ224" s="52" t="s">
         <v>99</v>
       </c>
@@ -19423,16 +19422,16 @@
     <row r="225" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q225" s="17"/>
       <c r="AB225" s="17"/>
-      <c r="AF225" s="80">
+      <c r="AF225" s="71">
         <v>297000</v>
       </c>
-      <c r="AG225" s="123" t="s">
+      <c r="AG225" s="106" t="s">
         <v>415</v>
       </c>
       <c r="AH225" s="52">
         <v>540</v>
       </c>
-      <c r="AI225" s="122"/>
+      <c r="AI225" s="79"/>
       <c r="AJ225" s="52" t="s">
         <v>99</v>
       </c>
@@ -19440,16 +19439,16 @@
     <row r="226" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q226" s="17"/>
       <c r="AB226" s="17"/>
-      <c r="AF226" s="80">
+      <c r="AF226" s="71">
         <v>445000</v>
       </c>
-      <c r="AG226" s="124">
+      <c r="AG226" s="107">
         <v>46091</v>
       </c>
       <c r="AH226" s="52">
         <v>810</v>
       </c>
-      <c r="AI226" s="122"/>
+      <c r="AI226" s="79"/>
       <c r="AJ226" s="52" t="s">
         <v>99</v>
       </c>
@@ -19457,16 +19456,16 @@
     <row r="227" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q227" s="17"/>
       <c r="AB227" s="17"/>
-      <c r="AF227" s="80">
+      <c r="AF227" s="71">
         <v>290000</v>
       </c>
-      <c r="AG227" s="124">
+      <c r="AG227" s="107">
         <v>46072</v>
       </c>
       <c r="AH227" s="52">
         <v>540</v>
       </c>
-      <c r="AI227" s="122"/>
+      <c r="AI227" s="79"/>
       <c r="AJ227" s="52" t="s">
         <v>99</v>
       </c>
@@ -19474,10 +19473,10 @@
     <row r="228" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q228" s="17"/>
       <c r="AB228" s="17"/>
-      <c r="AF228" s="80">
+      <c r="AF228" s="71">
         <v>294000</v>
       </c>
-      <c r="AG228" s="124">
+      <c r="AG228" s="107">
         <v>46043</v>
       </c>
       <c r="AH228" s="52">
@@ -19491,10 +19490,10 @@
     <row r="229" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q229" s="17"/>
       <c r="AB229" s="17"/>
-      <c r="AF229" s="80">
+      <c r="AF229" s="71">
         <v>143100</v>
       </c>
-      <c r="AG229" s="124">
+      <c r="AG229" s="107">
         <v>46010</v>
       </c>
       <c r="AH229" s="52">
@@ -19508,10 +19507,10 @@
     <row r="230" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q230" s="17"/>
       <c r="AB230" s="17"/>
-      <c r="AF230" s="80">
+      <c r="AF230" s="71">
         <v>190800</v>
       </c>
-      <c r="AG230" s="124">
+      <c r="AG230" s="107">
         <v>46007</v>
       </c>
       <c r="AH230" s="52">
@@ -19525,10 +19524,10 @@
     <row r="231" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q231" s="17"/>
       <c r="AB231" s="17"/>
-      <c r="AF231" s="80">
+      <c r="AF231" s="71">
         <v>47700</v>
       </c>
-      <c r="AG231" s="124">
+      <c r="AG231" s="107">
         <v>45993</v>
       </c>
       <c r="AH231" s="52">
@@ -19551,10 +19550,10 @@
     <row r="232" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q232" s="17"/>
       <c r="AB232" s="17"/>
-      <c r="AF232" s="80">
+      <c r="AF232" s="71">
         <v>286000</v>
       </c>
-      <c r="AG232" s="124">
+      <c r="AG232" s="107">
         <v>45979</v>
       </c>
       <c r="AH232" s="52">
@@ -19581,10 +19580,10 @@
     <row r="233" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q233" s="17"/>
       <c r="AB233" s="17"/>
-      <c r="AF233" s="80">
+      <c r="AF233" s="71">
         <v>145000</v>
       </c>
-      <c r="AG233" s="124">
+      <c r="AG233" s="107">
         <v>45973</v>
       </c>
       <c r="AH233" s="52">
@@ -19612,10 +19611,10 @@
       <c r="Q234" s="17"/>
       <c r="AB234" s="17"/>
       <c r="AE234" s="43"/>
-      <c r="AF234" s="80">
+      <c r="AF234" s="71">
         <v>541800</v>
       </c>
-      <c r="AG234" s="124">
+      <c r="AG234" s="107">
         <v>45960</v>
       </c>
       <c r="AH234" s="52">
@@ -19642,10 +19641,10 @@
     <row r="235" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q235" s="17"/>
       <c r="AB235" s="17"/>
-      <c r="AF235" s="80">
+      <c r="AF235" s="71">
         <v>2089</v>
       </c>
-      <c r="AG235" s="124">
+      <c r="AG235" s="107">
         <v>45954</v>
       </c>
       <c r="AH235" s="52" t="s">
@@ -19671,10 +19670,10 @@
     </row>
     <row r="236" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q236" s="17"/>
-      <c r="AF236" s="80">
+      <c r="AF236" s="71">
         <v>540000</v>
       </c>
-      <c r="AG236" s="124">
+      <c r="AG236" s="107">
         <v>45951</v>
       </c>
       <c r="AH236" s="52">
@@ -19700,10 +19699,10 @@
     </row>
     <row r="237" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q237" s="17"/>
-      <c r="AF237" s="80">
+      <c r="AF237" s="71">
         <v>99000</v>
       </c>
-      <c r="AG237" s="124">
+      <c r="AG237" s="107">
         <v>45950</v>
       </c>
       <c r="AH237" s="52">
@@ -19717,16 +19716,16 @@
     </row>
     <row r="238" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q238" s="17"/>
-      <c r="AF238" s="80">
+      <c r="AF238" s="71">
         <v>530000</v>
       </c>
-      <c r="AG238" s="124">
+      <c r="AG238" s="107">
         <v>45939</v>
       </c>
       <c r="AH238" s="52">
         <v>990</v>
       </c>
-      <c r="AI238" s="122"/>
+      <c r="AI238" s="79"/>
       <c r="AJ238" s="52" t="s">
         <v>99</v>
       </c>
@@ -19740,32 +19739,32 @@
     </row>
     <row r="239" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q239" s="17"/>
-      <c r="AF239" s="80">
+      <c r="AF239" s="71">
         <v>400000</v>
       </c>
-      <c r="AG239" s="124">
+      <c r="AG239" s="107">
         <v>45915</v>
       </c>
       <c r="AH239" s="52">
         <v>720</v>
       </c>
-      <c r="AI239" s="122"/>
+      <c r="AI239" s="79"/>
       <c r="AJ239" s="52" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="240" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q240" s="17"/>
-      <c r="AF240" s="80">
+      <c r="AF240" s="71">
         <v>1395</v>
       </c>
-      <c r="AG240" s="124">
+      <c r="AG240" s="107">
         <v>45904</v>
       </c>
       <c r="AH240" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="AI240" s="122"/>
+      <c r="AI240" s="79"/>
       <c r="AJ240" s="52" t="s">
         <v>16</v>
       </c>
@@ -19775,16 +19774,16 @@
       <c r="W241" s="17"/>
       <c r="AD241" s="17"/>
       <c r="AE241" s="43"/>
-      <c r="AF241" s="80">
+      <c r="AF241" s="71">
         <v>51300</v>
       </c>
-      <c r="AG241" s="124">
+      <c r="AG241" s="107">
         <v>45904</v>
       </c>
       <c r="AH241" s="52">
         <v>90</v>
       </c>
-      <c r="AI241" s="122"/>
+      <c r="AI241" s="79"/>
       <c r="AJ241" s="52" t="s">
         <v>99</v>
       </c>
@@ -19795,16 +19794,16 @@
       <c r="Z242" t="s">
         <v>223</v>
       </c>
-      <c r="AF242" s="80">
+      <c r="AF242" s="71">
         <v>307760</v>
       </c>
-      <c r="AG242" s="124">
+      <c r="AG242" s="107">
         <v>43313</v>
       </c>
       <c r="AH242" s="52">
         <v>540</v>
       </c>
-      <c r="AI242" s="122"/>
+      <c r="AI242" s="79"/>
       <c r="AJ242" s="52" t="s">
         <v>99</v>
       </c>
@@ -19812,20 +19811,20 @@
     <row r="243" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Q243" s="17"/>
       <c r="W243" s="17"/>
-      <c r="Y243" s="65"/>
-      <c r="Z243" s="66" t="s">
+      <c r="Y243" s="59"/>
+      <c r="Z243" s="60" t="s">
         <v>167</v>
       </c>
-      <c r="AA243" s="66"/>
-      <c r="AB243" s="67" t="s">
+      <c r="AA243" s="60"/>
+      <c r="AB243" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="AC243" s="65"/>
-      <c r="AD243" s="67"/>
-      <c r="AF243" s="80">
+      <c r="AC243" s="59"/>
+      <c r="AD243" s="61"/>
+      <c r="AF243" s="71">
         <v>4561</v>
       </c>
-      <c r="AG243" s="124">
+      <c r="AG243" s="107">
         <v>41487</v>
       </c>
       <c r="AH243" s="52" t="s">
@@ -19840,31 +19839,31 @@
     </row>
     <row r="244" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Q244" s="17"/>
-      <c r="Y244" s="68"/>
-      <c r="Z244" s="69">
+      <c r="Y244" s="62"/>
+      <c r="Z244" s="17">
         <f>X84-R84</f>
         <v>72</v>
       </c>
-      <c r="AA244" s="69"/>
-      <c r="AB244" s="70">
+      <c r="AA244" s="17"/>
+      <c r="AB244" s="63">
         <v>72</v>
       </c>
-      <c r="AC244" s="97">
+      <c r="AC244" s="86">
         <v>73</v>
       </c>
-      <c r="AD244" s="98">
+      <c r="AD244" s="87">
         <v>73</v>
       </c>
-      <c r="AF244" s="80">
+      <c r="AF244" s="71">
         <v>585970</v>
       </c>
-      <c r="AG244" s="124">
+      <c r="AG244" s="107">
         <v>45873</v>
       </c>
       <c r="AH244" s="52">
         <v>1000</v>
       </c>
-      <c r="AI244" s="122"/>
+      <c r="AI244" s="79"/>
       <c r="AJ244" s="52" t="s">
         <v>16</v>
       </c>
@@ -19872,197 +19871,191 @@
     </row>
     <row r="245" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Q245" s="19"/>
-      <c r="Y245" s="68" t="s">
+      <c r="Y245" s="62" t="s">
         <v>244</v>
       </c>
-      <c r="Z245" s="71">
+      <c r="Z245">
         <v>1496.23</v>
       </c>
-      <c r="AA245" s="71"/>
-      <c r="AB245" s="72">
+      <c r="AB245" s="64">
         <v>1497.0039999999999</v>
       </c>
-      <c r="AC245" s="68">
+      <c r="AC245" s="62">
         <f>O101</f>
         <v>1002.071</v>
       </c>
-      <c r="AD245" s="72">
+      <c r="AD245" s="64">
         <f>O122</f>
         <v>1992.5709999999999</v>
       </c>
       <c r="AE245" s="17"/>
-      <c r="AF245" s="80">
+      <c r="AF245" s="71">
         <v>110000</v>
       </c>
-      <c r="AG245" s="124">
+      <c r="AG245" s="107">
         <v>45866</v>
       </c>
       <c r="AH245" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="AI245" s="122"/>
+      <c r="AI245" s="79"/>
       <c r="AJ245" s="52" t="s">
         <v>99</v>
       </c>
       <c r="AP245" s="43"/>
     </row>
     <row r="246" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y246" s="68" t="s">
+      <c r="Y246" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="Z246" s="69">
+      <c r="Z246" s="17">
         <f>Z244*Z245</f>
         <v>107728.56</v>
       </c>
-      <c r="AA246" s="69"/>
-      <c r="AB246" s="70">
+      <c r="AA246" s="17"/>
+      <c r="AB246" s="63">
         <f>AB244*AB245</f>
         <v>107784.288</v>
       </c>
-      <c r="AC246" s="97">
+      <c r="AC246" s="86">
         <f>AC244*AC245</f>
         <v>73151.183000000005</v>
       </c>
-      <c r="AD246" s="98">
+      <c r="AD246" s="87">
         <f>AD244*AD245</f>
         <v>145457.68299999999</v>
       </c>
       <c r="AE246" s="17"/>
-      <c r="AF246" s="80">
+      <c r="AF246" s="71">
         <v>150000</v>
       </c>
-      <c r="AG246" s="124">
+      <c r="AG246" s="107">
         <v>45856</v>
       </c>
       <c r="AH246" s="52">
         <v>270</v>
       </c>
-      <c r="AI246" s="122"/>
+      <c r="AI246" s="79"/>
       <c r="AJ246" s="52" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="247" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y247" s="68" t="s">
+      <c r="Y247" s="62" t="s">
         <v>283</v>
       </c>
-      <c r="Z247" s="71">
+      <c r="Z247">
         <v>0.36</v>
       </c>
-      <c r="AA247" s="71"/>
-      <c r="AB247" s="72">
+      <c r="AB247" s="64">
         <v>0.36</v>
       </c>
-      <c r="AC247" s="68">
+      <c r="AC247" s="62">
         <v>0.36</v>
       </c>
-      <c r="AD247" s="72">
+      <c r="AD247" s="64">
         <v>0.36</v>
       </c>
-      <c r="AF247" s="80">
+      <c r="AF247" s="71">
         <v>150000</v>
       </c>
-      <c r="AG247" s="124">
+      <c r="AG247" s="107">
         <v>45854</v>
       </c>
       <c r="AH247" s="52">
         <v>270</v>
       </c>
-      <c r="AI247" s="122"/>
+      <c r="AI247" s="79"/>
       <c r="AJ247" s="52" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="248" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y248" s="68" t="s">
+      <c r="Y248" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="Z248" s="92">
+      <c r="Z248" s="83">
         <f>Z246*Z247</f>
         <v>38782.281599999995</v>
       </c>
-      <c r="AA248" s="92"/>
-      <c r="AB248" s="93">
+      <c r="AA248" s="83"/>
+      <c r="AB248" s="84">
         <f>AB246*AB247</f>
         <v>38802.343679999998</v>
       </c>
-      <c r="AC248" s="99">
+      <c r="AC248" s="88">
         <f>AC247*AC246</f>
         <v>26334.425879999999</v>
       </c>
-      <c r="AD248" s="100">
+      <c r="AD248" s="89">
         <f>AD247*AD246</f>
         <v>52364.765879999992</v>
       </c>
-      <c r="AF248" s="80">
+      <c r="AF248" s="71">
         <v>1665</v>
       </c>
-      <c r="AG248" s="124">
+      <c r="AG248" s="107">
         <v>45832</v>
       </c>
       <c r="AH248" s="52" t="s">
         <v>195</v>
       </c>
-      <c r="AI248" s="122"/>
+      <c r="AI248" s="79"/>
       <c r="AJ248" s="52" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="249" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y249" s="68"/>
-      <c r="Z249" s="71"/>
-      <c r="AA249" s="71"/>
-      <c r="AB249" s="72"/>
-      <c r="AC249" s="68"/>
-      <c r="AD249" s="72"/>
-      <c r="AF249" s="80">
+      <c r="Y249" s="62"/>
+      <c r="AB249" s="64"/>
+      <c r="AC249" s="62"/>
+      <c r="AD249" s="64"/>
+      <c r="AF249" s="71">
         <v>324000</v>
       </c>
-      <c r="AG249" s="124">
+      <c r="AG249" s="107">
         <v>45831</v>
       </c>
       <c r="AH249" s="52">
         <v>500</v>
       </c>
-      <c r="AI249" s="122"/>
+      <c r="AI249" s="79"/>
       <c r="AJ249" s="52" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="250" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y250" s="68" t="s">
+      <c r="Y250" s="62" t="s">
         <v>274</v>
       </c>
-      <c r="Z250" s="71"/>
-      <c r="AA250" s="71"/>
-      <c r="AB250" s="72"/>
-      <c r="AC250" s="68"/>
-      <c r="AD250" s="72"/>
-      <c r="AF250" s="80">
+      <c r="AB250" s="64"/>
+      <c r="AC250" s="62"/>
+      <c r="AD250" s="64"/>
+      <c r="AF250" s="71">
         <v>324000</v>
       </c>
-      <c r="AG250" s="124">
+      <c r="AG250" s="107">
         <v>45818</v>
       </c>
       <c r="AH250" s="52">
         <v>500</v>
       </c>
-      <c r="AI250" s="122"/>
+      <c r="AI250" s="79"/>
       <c r="AJ250" s="52" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="251" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y251" s="68"/>
-      <c r="Z251" s="69"/>
-      <c r="AA251" s="69"/>
-      <c r="AB251" s="72"/>
-      <c r="AC251" s="68"/>
-      <c r="AD251" s="72"/>
-      <c r="AF251" s="80">
+      <c r="Y251" s="62"/>
+      <c r="Z251" s="17"/>
+      <c r="AA251" s="17"/>
+      <c r="AB251" s="64"/>
+      <c r="AC251" s="62"/>
+      <c r="AD251" s="64"/>
+      <c r="AF251" s="71">
         <v>31780</v>
       </c>
-      <c r="AG251" s="124">
+      <c r="AG251" s="107">
         <v>45810</v>
       </c>
       <c r="AH251" s="52" t="s">
@@ -20074,26 +20067,26 @@
       </c>
     </row>
     <row r="252" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y252" s="68"/>
-      <c r="Z252" s="95" t="s">
+      <c r="Y252" s="62"/>
+      <c r="Z252" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AA252" s="95"/>
-      <c r="AB252" s="93">
+      <c r="AA252" s="85"/>
+      <c r="AB252" s="84">
         <f>AB248+Z248</f>
         <v>77584.625279999993</v>
       </c>
-      <c r="AC252" s="68" t="s">
+      <c r="AC252" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="AD252" s="100">
+      <c r="AD252" s="89">
         <f>AC248+AD248</f>
         <v>78699.191759999987</v>
       </c>
-      <c r="AF252" s="80">
+      <c r="AF252" s="71">
         <v>324000</v>
       </c>
-      <c r="AG252" s="124">
+      <c r="AG252" s="107">
         <v>45807</v>
       </c>
       <c r="AH252" s="52">
@@ -20105,21 +20098,19 @@
       </c>
     </row>
     <row r="253" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y253" s="68"/>
-      <c r="Z253" s="71"/>
-      <c r="AA253" s="71"/>
-      <c r="AB253" s="72"/>
-      <c r="AC253" s="68" t="s">
+      <c r="Y253" s="62"/>
+      <c r="AB253" s="64"/>
+      <c r="AC253" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="AD253" s="70">
+      <c r="AD253" s="63">
         <f>AB263</f>
         <v>11456.374720000007</v>
       </c>
-      <c r="AF253" s="80">
+      <c r="AF253" s="71">
         <v>325000</v>
       </c>
-      <c r="AG253" s="124">
+      <c r="AG253" s="107">
         <v>45806</v>
       </c>
       <c r="AH253" s="52">
@@ -20131,20 +20122,19 @@
       </c>
     </row>
     <row r="254" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y254" s="68"/>
-      <c r="Z254" s="71" t="s">
+      <c r="Y254" s="62"/>
+      <c r="Z254" t="s">
         <v>275</v>
       </c>
-      <c r="AA254" s="71"/>
-      <c r="AB254" s="70">
+      <c r="AB254" s="63">
         <v>15300</v>
       </c>
-      <c r="AC254" s="68"/>
-      <c r="AD254" s="72"/>
-      <c r="AF254" s="80">
+      <c r="AC254" s="62"/>
+      <c r="AD254" s="64"/>
+      <c r="AF254" s="71">
         <v>648000</v>
       </c>
-      <c r="AG254" s="124">
+      <c r="AG254" s="107">
         <v>45786</v>
       </c>
       <c r="AH254" s="52">
@@ -20158,25 +20148,24 @@
       </c>
     </row>
     <row r="255" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y255" s="68"/>
-      <c r="Z255" s="75" t="s">
+      <c r="Y255" s="62"/>
+      <c r="Z255" t="s">
         <v>276</v>
       </c>
-      <c r="AA255" s="75"/>
-      <c r="AB255" s="70">
+      <c r="AB255" s="63">
         <v>1200</v>
       </c>
-      <c r="AC255" s="68" t="s">
+      <c r="AC255" s="62" t="s">
         <v>309</v>
       </c>
-      <c r="AD255" s="100">
+      <c r="AD255" s="89">
         <f>AD252-AD253</f>
         <v>67242.81703999998</v>
       </c>
-      <c r="AF255" s="80">
+      <c r="AF255" s="71">
         <v>514200</v>
       </c>
-      <c r="AG255" s="124">
+      <c r="AG255" s="107">
         <v>45772</v>
       </c>
       <c r="AH255" s="52">
@@ -20190,24 +20179,23 @@
       </c>
     </row>
     <row r="256" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y256" s="68"/>
-      <c r="Z256" s="75" t="s">
+      <c r="Y256" s="62"/>
+      <c r="Z256" t="s">
         <v>277</v>
       </c>
-      <c r="AA256" s="75"/>
-      <c r="AB256" s="70">
+      <c r="AB256" s="63">
         <v>12900</v>
       </c>
-      <c r="AC256" s="68" t="s">
+      <c r="AC256" s="62" t="s">
         <v>342</v>
       </c>
-      <c r="AD256" s="100">
+      <c r="AD256" s="89">
         <v>50000</v>
       </c>
-      <c r="AF256" s="80">
+      <c r="AF256" s="71">
         <v>325000</v>
       </c>
-      <c r="AG256" s="124">
+      <c r="AG256" s="107">
         <v>45762</v>
       </c>
       <c r="AH256" s="52">
@@ -20219,25 +20207,24 @@
       </c>
     </row>
     <row r="257" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="Y257" s="68"/>
-      <c r="Z257" s="75" t="s">
+      <c r="Y257" s="62"/>
+      <c r="Z257" t="s">
         <v>279</v>
       </c>
-      <c r="AA257" s="75"/>
-      <c r="AB257" s="70">
+      <c r="AB257" s="63">
         <v>7000</v>
       </c>
-      <c r="AC257" s="68" t="s">
+      <c r="AC257" s="62" t="s">
         <v>341</v>
       </c>
-      <c r="AD257" s="100">
+      <c r="AD257" s="89">
         <f>AD255-AD256</f>
         <v>17242.81703999998</v>
       </c>
-      <c r="AF257" s="80">
+      <c r="AF257" s="71">
         <v>632000</v>
       </c>
-      <c r="AG257" s="124">
+      <c r="AG257" s="107">
         <v>45749</v>
       </c>
       <c r="AH257" s="52">
@@ -20249,22 +20236,21 @@
       </c>
     </row>
     <row r="258" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="Y258" s="68"/>
-      <c r="Z258" s="75" t="s">
+      <c r="Y258" s="62"/>
+      <c r="Z258" t="s">
         <v>280</v>
       </c>
-      <c r="AA258" s="75"/>
-      <c r="AB258" s="70">
+      <c r="AB258" s="63">
         <v>5000</v>
       </c>
-      <c r="AC258" s="68"/>
-      <c r="AD258" s="72" t="s">
+      <c r="AC258" s="62"/>
+      <c r="AD258" s="64" t="s">
         <v>194</v>
       </c>
-      <c r="AF258" s="80">
+      <c r="AF258" s="71">
         <v>632000</v>
       </c>
-      <c r="AG258" s="124">
+      <c r="AG258" s="107">
         <v>45736</v>
       </c>
       <c r="AH258" s="52">
@@ -20276,20 +20262,19 @@
       </c>
     </row>
     <row r="259" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="Y259" s="68"/>
-      <c r="Z259" s="75" t="s">
+      <c r="Y259" s="62"/>
+      <c r="Z259" t="s">
         <v>281</v>
       </c>
-      <c r="AA259" s="75"/>
-      <c r="AB259" s="94">
+      <c r="AB259" s="63">
         <v>10400</v>
       </c>
-      <c r="AC259" s="68"/>
-      <c r="AD259" s="72"/>
-      <c r="AF259" s="80">
+      <c r="AC259" s="62"/>
+      <c r="AD259" s="64"/>
+      <c r="AF259" s="71">
         <v>632000</v>
       </c>
-      <c r="AG259" s="124">
+      <c r="AG259" s="107">
         <v>45721</v>
       </c>
       <c r="AH259" s="52">
@@ -20301,23 +20286,22 @@
       </c>
     </row>
     <row r="260" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="Y260" s="68"/>
-      <c r="Z260" s="75" t="s">
+      <c r="Y260" s="62"/>
+      <c r="Z260" t="s">
         <v>282</v>
       </c>
-      <c r="AA260" s="75"/>
-      <c r="AB260" s="94">
+      <c r="AB260" s="63">
         <v>5441</v>
       </c>
-      <c r="AC260" s="68"/>
-      <c r="AD260" s="72"/>
-      <c r="AF260" s="80">
+      <c r="AC260" s="62"/>
+      <c r="AD260" s="64"/>
+      <c r="AF260" s="71">
         <v>632000</v>
       </c>
-      <c r="AG260" s="125">
+      <c r="AG260" s="108">
         <v>45706</v>
       </c>
-      <c r="AH260" s="126">
+      <c r="AH260" s="109">
         <v>1000</v>
       </c>
       <c r="AI260" s="52"/>
@@ -20326,21 +20310,21 @@
       </c>
     </row>
     <row r="261" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="Y261" s="68"/>
-      <c r="Z261" s="95" t="s">
+      <c r="Y261" s="62"/>
+      <c r="Z261" s="85" t="s">
         <v>307</v>
       </c>
-      <c r="AA261" s="95"/>
-      <c r="AB261" s="93">
+      <c r="AA261" s="85"/>
+      <c r="AB261" s="84">
         <f>AB252-AB254+AB255-AB256-AB257+AB258+AB259-AB260</f>
         <v>53543.625279999993</v>
       </c>
-      <c r="AC261" s="68"/>
-      <c r="AD261" s="72"/>
-      <c r="AF261" s="80">
+      <c r="AC261" s="62"/>
+      <c r="AD261" s="64"/>
+      <c r="AF261" s="71">
         <v>21610</v>
       </c>
-      <c r="AG261" s="125">
+      <c r="AG261" s="108">
         <v>45692</v>
       </c>
       <c r="AH261" s="52"/>
@@ -20350,23 +20334,23 @@
       </c>
     </row>
     <row r="262" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="Y262" s="68"/>
-      <c r="Z262" s="95" t="s">
+      <c r="Y262" s="62"/>
+      <c r="Z262" s="85" t="s">
         <v>278</v>
       </c>
-      <c r="AA262" s="95"/>
-      <c r="AB262" s="93">
+      <c r="AA262" s="85"/>
+      <c r="AB262" s="84">
         <v>65000</v>
       </c>
-      <c r="AC262" s="68"/>
-      <c r="AD262" s="72"/>
-      <c r="AF262" s="80">
+      <c r="AC262" s="62"/>
+      <c r="AD262" s="64"/>
+      <c r="AF262" s="71">
         <v>200000</v>
       </c>
-      <c r="AG262" s="125">
+      <c r="AG262" s="108">
         <v>45687</v>
       </c>
-      <c r="AH262" s="126">
+      <c r="AH262" s="109">
         <v>300</v>
       </c>
       <c r="AI262" s="52"/>
@@ -20375,47 +20359,46 @@
       </c>
     </row>
     <row r="263" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="Y263" s="68"/>
-      <c r="Z263" s="75" t="s">
+      <c r="Y263" s="62"/>
+      <c r="Z263" t="s">
         <v>68</v>
       </c>
-      <c r="AA263" s="75"/>
-      <c r="AB263" s="102">
+      <c r="AB263" s="91">
         <f>AB262-AB261</f>
         <v>11456.374720000007</v>
       </c>
-      <c r="AC263" s="68"/>
-      <c r="AD263" s="72"/>
-      <c r="AF263" s="80">
+      <c r="AC263" s="62"/>
+      <c r="AD263" s="64"/>
+      <c r="AF263" s="71">
         <v>50000</v>
       </c>
-      <c r="AG263" s="125">
+      <c r="AG263" s="108">
         <v>45680</v>
       </c>
-      <c r="AH263" s="114"/>
+      <c r="AH263" s="101"/>
       <c r="AI263" s="52"/>
       <c r="AJ263" s="52" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="264" spans="18:36" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="R264" s="77"/>
-      <c r="S264" s="78"/>
-      <c r="T264" s="77"/>
-      <c r="U264" s="77"/>
-      <c r="Y264" s="73"/>
-      <c r="Z264" s="76"/>
-      <c r="AA264" s="76"/>
-      <c r="AB264" s="74"/>
-      <c r="AC264" s="73"/>
-      <c r="AD264" s="101"/>
-      <c r="AF264" s="80">
+      <c r="R264" s="68"/>
+      <c r="S264" s="69"/>
+      <c r="T264" s="68"/>
+      <c r="U264" s="68"/>
+      <c r="Y264" s="65"/>
+      <c r="Z264" s="67"/>
+      <c r="AA264" s="67"/>
+      <c r="AB264" s="66"/>
+      <c r="AC264" s="65"/>
+      <c r="AD264" s="90"/>
+      <c r="AF264" s="71">
         <v>300000</v>
       </c>
-      <c r="AG264" s="125">
+      <c r="AG264" s="108">
         <v>45674</v>
       </c>
-      <c r="AH264" s="127">
+      <c r="AH264" s="110">
         <v>500</v>
       </c>
       <c r="AI264" s="52"/>
@@ -20424,20 +20407,18 @@
       </c>
     </row>
     <row r="265" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="R265" s="79"/>
-      <c r="S265" s="79"/>
-      <c r="T265" s="79"/>
-      <c r="U265" s="79"/>
-      <c r="Z265" s="75"/>
-      <c r="AA265" s="75"/>
+      <c r="R265" s="70"/>
+      <c r="S265" s="70"/>
+      <c r="T265" s="70"/>
+      <c r="U265" s="70"/>
       <c r="AB265" s="17"/>
-      <c r="AF265" s="80">
+      <c r="AF265" s="71">
         <v>332000</v>
       </c>
-      <c r="AG265" s="125">
+      <c r="AG265" s="108">
         <v>45664</v>
       </c>
-      <c r="AH265" s="127">
+      <c r="AH265" s="110">
         <v>500</v>
       </c>
       <c r="AI265" s="52"/>
@@ -20446,17 +20427,17 @@
       </c>
     </row>
     <row r="266" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="R266" s="79"/>
-      <c r="S266" s="79"/>
-      <c r="T266" s="79"/>
-      <c r="U266" s="79"/>
-      <c r="AF266" s="80">
+      <c r="R266" s="70"/>
+      <c r="S266" s="70"/>
+      <c r="T266" s="70"/>
+      <c r="U266" s="70"/>
+      <c r="AF266" s="71">
         <v>332000</v>
       </c>
-      <c r="AG266" s="125">
+      <c r="AG266" s="108">
         <v>45656</v>
       </c>
-      <c r="AH266" s="127">
+      <c r="AH266" s="110">
         <v>500</v>
       </c>
       <c r="AI266" s="52"/>
@@ -20480,13 +20461,13 @@
         <f>AC88+AC89+AC90</f>
         <v>1107782.96</v>
       </c>
-      <c r="AF267" s="80">
+      <c r="AF267" s="71">
         <v>339500</v>
       </c>
-      <c r="AG267" s="125">
+      <c r="AG267" s="108">
         <v>45649</v>
       </c>
-      <c r="AH267" s="127">
+      <c r="AH267" s="110">
         <v>500</v>
       </c>
       <c r="AI267" s="52"/>
@@ -20507,10 +20488,10 @@
         <f>72*O91</f>
         <v>107784.288</v>
       </c>
-      <c r="AF268" s="80">
+      <c r="AF268" s="71">
         <v>679000</v>
       </c>
-      <c r="AG268" s="124">
+      <c r="AG268" s="107">
         <v>45643</v>
       </c>
       <c r="AH268" s="52">
@@ -20542,7 +20523,7 @@
       <c r="Z270">
         <v>18.899999999999999</v>
       </c>
-      <c r="AB270" s="91">
+      <c r="AB270" s="82">
         <v>18.309999999999999</v>
       </c>
     </row>
@@ -20558,13 +20539,13 @@
       <c r="AB271" s="17">
         <v>491765.81</v>
       </c>
-      <c r="AD271" s="88" t="s">
+      <c r="AD271" s="116" t="s">
         <v>237</v>
       </c>
-      <c r="AE271" s="88"/>
-      <c r="AF271" s="88"/>
-      <c r="AG271" s="88"/>
-      <c r="AH271" s="88"/>
+      <c r="AE271" s="116"/>
+      <c r="AF271" s="116"/>
+      <c r="AG271" s="116"/>
+      <c r="AH271" s="116"/>
     </row>
     <row r="272" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y272" s="41" t="s">
@@ -20580,14 +20561,14 @@
         <v>24588.290500000003</v>
       </c>
       <c r="AD272" s="52"/>
-      <c r="AE272" s="85" t="s">
+      <c r="AE272" s="76" t="s">
         <v>236</v>
       </c>
-      <c r="AF272" s="85" t="s">
+      <c r="AF272" s="76" t="s">
         <v>234</v>
       </c>
-      <c r="AG272" s="82"/>
-      <c r="AH272" s="82" t="s">
+      <c r="AG272" s="73"/>
+      <c r="AH272" s="73" t="s">
         <v>235</v>
       </c>
     </row>
@@ -20595,16 +20576,16 @@
       <c r="Y273" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="Z273" s="110">
+      <c r="Z273" s="97">
         <f>O87</f>
         <v>1496.23</v>
       </c>
-      <c r="AA273" s="110"/>
-      <c r="AB273" s="110">
+      <c r="AA273" s="97"/>
+      <c r="AB273" s="97">
         <f>O91</f>
         <v>1497.0039999999999</v>
       </c>
-      <c r="AC273" s="111"/>
+      <c r="AC273" s="98"/>
       <c r="AD273" s="52" t="s">
         <v>128</v>
       </c>
@@ -20612,29 +20593,29 @@
         <f>SUM(W66,W76,W87,W91,W101,W122)</f>
         <v>8571607.8409999982</v>
       </c>
-      <c r="AF273" s="86">
+      <c r="AF273" s="77">
         <f>SUMIF(AJ223:AJ268,"Arauco",AF223:AF268)</f>
         <v>8589229</v>
       </c>
       <c r="AG273" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="AH273" s="87">
+      <c r="AH273" s="78">
         <f>AE273-AF273</f>
         <v>-17621.159000001848</v>
       </c>
     </row>
     <row r="274" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="X274" s="111"/>
+      <c r="X274" s="98"/>
       <c r="Y274" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="Z274" s="105">
+      <c r="Z274" s="94">
         <f>Z271-Z272</f>
         <v>483566.57369999995</v>
       </c>
-      <c r="AA274" s="105"/>
-      <c r="AB274" s="104">
+      <c r="AA274" s="94"/>
+      <c r="AB274" s="93">
         <f>AB271-AB272</f>
         <v>467177.51949999999</v>
       </c>
@@ -20643,18 +20624,18 @@
       </c>
       <c r="AE274" s="53">
         <f>SUM(W83,W98,W109,W116,W118,W131,W143,W146,W153,W161,W169,W176,W183,W193,W206)</f>
-        <v>4994869.585</v>
-      </c>
-      <c r="AF274" s="86">
+        <v>5001187.9850000003</v>
+      </c>
+      <c r="AF274" s="77">
         <f>SUMIF(AJ222:AJ268,"CPP",AF222:AF268)</f>
         <v>4920001</v>
       </c>
       <c r="AG274" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="AH274" s="87">
+      <c r="AH274" s="78">
         <f>AE274-AF274</f>
-        <v>74868.584999999963</v>
+        <v>81186.985000000335</v>
       </c>
     </row>
     <row r="275" spans="24:40" x14ac:dyDescent="0.2">
@@ -20670,18 +20651,18 @@
       </c>
       <c r="AE275" s="53">
         <f>SUM(AE273:AE274)</f>
-        <v>13566477.425999999</v>
-      </c>
-      <c r="AF275" s="86">
+        <v>13572795.825999998</v>
+      </c>
+      <c r="AF275" s="77">
         <f>SUM(AF228:AF268)</f>
         <v>12180230</v>
       </c>
       <c r="AG275" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="AH275" s="87">
+      <c r="AH275" s="78">
         <f>SUM(AH273:AH274)</f>
-        <v>57247.425999998115</v>
+        <v>63565.825999998488</v>
       </c>
     </row>
     <row r="276" spans="24:40" x14ac:dyDescent="0.2">
@@ -20711,20 +20692,20 @@
         <f>73*O122</f>
         <v>145457.68299999999</v>
       </c>
-      <c r="AF277" s="56" t="s">
+      <c r="AF277" s="117" t="s">
         <v>142</v>
       </c>
-      <c r="AG277" s="56"/>
-      <c r="AI277" s="57" t="s">
+      <c r="AG277" s="117"/>
+      <c r="AI277" s="119" t="s">
         <v>164</v>
       </c>
-      <c r="AJ277" s="57"/>
-      <c r="AK277" s="57"/>
+      <c r="AJ277" s="119"/>
+      <c r="AK277" s="119"/>
       <c r="AL277" s="36"/>
-      <c r="AM277" s="56" t="s">
+      <c r="AM277" s="117" t="s">
         <v>146</v>
       </c>
-      <c r="AN277" s="56"/>
+      <c r="AN277" s="117"/>
     </row>
     <row r="278" spans="24:40" x14ac:dyDescent="0.2">
       <c r="Y278" s="41" t="s">
@@ -20756,7 +20737,7 @@
       <c r="Z279">
         <v>18.2</v>
       </c>
-      <c r="AB279" s="91">
+      <c r="AB279" s="82">
         <v>17.7</v>
       </c>
       <c r="AF279" t="s">
@@ -20820,7 +20801,7 @@
       </c>
     </row>
     <row r="281" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y281" s="103" t="s">
+      <c r="Y281" s="92" t="s">
         <v>213</v>
       </c>
       <c r="Z281" s="17">
@@ -20847,21 +20828,21 @@
         <v>0</v>
       </c>
       <c r="AK281" s="50">
-        <f t="shared" ref="AK281:AK283" si="91">AI281*AJ281</f>
+        <f t="shared" ref="AK281:AK283" si="142">AI281*AJ281</f>
         <v>0</v>
       </c>
     </row>
     <row r="282" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="X282" s="111"/>
+      <c r="X282" s="98"/>
       <c r="Y282" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="Z282" s="110">
+      <c r="Z282" s="97">
         <f>O101</f>
         <v>1002.071</v>
       </c>
-      <c r="AA282" s="110"/>
-      <c r="AB282" s="110">
+      <c r="AA282" s="97"/>
+      <c r="AB282" s="97">
         <f>O122</f>
         <v>1992.5709999999999</v>
       </c>
@@ -20879,7 +20860,7 @@
         <v>0</v>
       </c>
       <c r="AK282" s="50">
-        <f t="shared" si="91"/>
+        <f t="shared" si="142"/>
         <v>0</v>
       </c>
       <c r="AM282" t="s">
@@ -20894,12 +20875,12 @@
       <c r="Y283" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="Z283" s="104">
+      <c r="Z283" s="93">
         <f>Z280-Z281</f>
         <v>316195.98851749999</v>
       </c>
-      <c r="AA283" s="104"/>
-      <c r="AB283" s="104">
+      <c r="AA283" s="93"/>
+      <c r="AB283" s="93">
         <f>AB280-AB281</f>
         <v>611467.73491124995</v>
       </c>
@@ -20918,7 +20899,7 @@
         <v>0</v>
       </c>
       <c r="AK283" s="50">
-        <f t="shared" si="91"/>
+        <f t="shared" si="142"/>
         <v>0</v>
       </c>
       <c r="AM283" t="s">
@@ -20949,7 +20930,7 @@
     </row>
     <row r="285" spans="24:40" x14ac:dyDescent="0.2">
       <c r="Y285" s="41"/>
-      <c r="AB285" s="111"/>
+      <c r="AB285" s="98"/>
       <c r="AF285" t="s">
         <v>145</v>
       </c>
@@ -21011,7 +20992,7 @@
       </c>
     </row>
     <row r="290" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y290" s="103"/>
+      <c r="Y290" s="92"/>
       <c r="AB290" s="43"/>
       <c r="AF290" t="s">
         <v>155</v>
@@ -21026,11 +21007,11 @@
     <row r="291" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Y291" s="41"/>
       <c r="AF291">
-        <f>O59-500</f>
+        <f t="shared" ref="AF291:AF296" si="143">O59-500</f>
         <v>10.76400000000001</v>
       </c>
       <c r="AG291" s="17">
-        <f>X59-V59</f>
+        <f t="shared" ref="AG291:AG297" si="144">X59-V59</f>
         <v>76</v>
       </c>
       <c r="AH291" s="17">
@@ -21041,29 +21022,29 @@
     <row r="292" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Y292" s="41"/>
       <c r="AF292">
-        <f>O60-500</f>
+        <f t="shared" si="143"/>
         <v>10.338999999999999</v>
       </c>
       <c r="AG292" s="17">
-        <f>X60-V60</f>
+        <f t="shared" si="144"/>
         <v>76</v>
       </c>
       <c r="AH292" s="17">
-        <f t="shared" ref="AH292:AH297" si="92">AG292*AF292</f>
+        <f t="shared" ref="AH292:AH297" si="145">AG292*AF292</f>
         <v>785.7639999999999</v>
       </c>
     </row>
     <row r="293" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AF293">
-        <f>O61-500</f>
+        <f t="shared" si="143"/>
         <v>9.6879999999999882</v>
       </c>
       <c r="AG293" s="17">
-        <f>X61-V61</f>
+        <f t="shared" si="144"/>
         <v>76</v>
       </c>
       <c r="AH293" s="17">
-        <f t="shared" si="92"/>
+        <f t="shared" si="145"/>
         <v>736.2879999999991</v>
       </c>
     </row>
@@ -21072,15 +21053,15 @@
         <v>157</v>
       </c>
       <c r="AF294">
-        <f>O62-500</f>
+        <f t="shared" si="143"/>
         <v>10.899999999999977</v>
       </c>
       <c r="AG294" s="17">
-        <f>X62-V62</f>
+        <f t="shared" si="144"/>
         <v>91</v>
       </c>
       <c r="AH294" s="17">
-        <f t="shared" si="92"/>
+        <f t="shared" si="145"/>
         <v>991.89999999999793</v>
       </c>
     </row>
@@ -21089,15 +21070,15 @@
         <v>157</v>
       </c>
       <c r="AF295">
-        <f>O63-500</f>
+        <f t="shared" si="143"/>
         <v>10.899999999999977</v>
       </c>
       <c r="AG295" s="17">
-        <f>X63-V63</f>
+        <f t="shared" si="144"/>
         <v>91</v>
       </c>
       <c r="AH295" s="17">
-        <f t="shared" si="92"/>
+        <f t="shared" si="145"/>
         <v>991.89999999999793</v>
       </c>
     </row>
@@ -21106,15 +21087,15 @@
         <v>157</v>
       </c>
       <c r="AF296">
-        <f>O64-500</f>
+        <f t="shared" si="143"/>
         <v>10.899999999999977</v>
       </c>
       <c r="AG296" s="17">
-        <f>X64-V64</f>
+        <f t="shared" si="144"/>
         <v>91</v>
       </c>
       <c r="AH296" s="17">
-        <f t="shared" si="92"/>
+        <f t="shared" si="145"/>
         <v>991.89999999999793</v>
       </c>
     </row>
@@ -21127,11 +21108,11 @@
         <v>6.5400000000000205</v>
       </c>
       <c r="AG297" s="17">
-        <f>X65-V65</f>
+        <f t="shared" si="144"/>
         <v>91</v>
       </c>
       <c r="AH297" s="17">
-        <f t="shared" si="92"/>
+        <f t="shared" si="145"/>
         <v>595.14000000000192</v>
       </c>
     </row>
@@ -21154,11 +21135,11 @@
       </c>
     </row>
     <row r="300" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF300" s="55" t="s">
+      <c r="AF300" s="118" t="s">
         <v>158</v>
       </c>
-      <c r="AG300" s="55"/>
-      <c r="AH300" s="55"/>
+      <c r="AG300" s="118"/>
+      <c r="AH300" s="118"/>
     </row>
     <row r="303" spans="25:40" x14ac:dyDescent="0.2">
       <c r="AF303" s="41" t="s">
@@ -21345,11 +21326,11 @@
     </row>
     <row r="321" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF321">
-        <f>O67-500</f>
+        <f t="shared" ref="AF321:AF328" si="146">O67-500</f>
         <v>11.160000000000025</v>
       </c>
       <c r="AG321" s="17">
-        <f>X67-V67</f>
+        <f t="shared" ref="AG321:AG329" si="147">X67-V67</f>
         <v>73</v>
       </c>
       <c r="AH321" s="17">
@@ -21359,99 +21340,99 @@
     </row>
     <row r="322" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF322">
-        <f>O68-500</f>
+        <f t="shared" si="146"/>
         <v>9.1940000000000168</v>
       </c>
       <c r="AG322" s="17">
-        <f>X68-V68</f>
+        <f t="shared" si="147"/>
         <v>73</v>
       </c>
       <c r="AH322" s="17">
-        <f t="shared" ref="AH322:AH329" si="93">AF322*AG322</f>
+        <f t="shared" ref="AH322:AH329" si="148">AF322*AG322</f>
         <v>671.16200000000117</v>
       </c>
     </row>
     <row r="323" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF323">
-        <f>O69-500</f>
+        <f t="shared" si="146"/>
         <v>-14.966999999999985</v>
       </c>
       <c r="AG323" s="17">
-        <f>X69-V69</f>
+        <f t="shared" si="147"/>
         <v>73</v>
       </c>
       <c r="AH323" s="17">
-        <f t="shared" si="93"/>
+        <f t="shared" si="148"/>
         <v>-1092.590999999999</v>
       </c>
     </row>
     <row r="324" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF324">
-        <f>O70-500</f>
+        <f t="shared" si="146"/>
         <v>10.379999999999995</v>
       </c>
       <c r="AG324" s="17">
-        <f>X70-V70</f>
+        <f t="shared" si="147"/>
         <v>73</v>
       </c>
       <c r="AH324" s="17">
-        <f t="shared" si="93"/>
+        <f t="shared" si="148"/>
         <v>757.73999999999967</v>
       </c>
     </row>
     <row r="325" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF325">
-        <f>O71-500</f>
+        <f t="shared" si="146"/>
         <v>-15.939000000000021</v>
       </c>
       <c r="AG325" s="17">
-        <f>X71-V71</f>
+        <f t="shared" si="147"/>
         <v>71</v>
       </c>
       <c r="AH325" s="17">
-        <f t="shared" si="93"/>
+        <f t="shared" si="148"/>
         <v>-1131.6690000000015</v>
       </c>
     </row>
     <row r="326" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF326">
-        <f>O72-500</f>
+        <f t="shared" si="146"/>
         <v>-15.386000000000024</v>
       </c>
       <c r="AG326" s="17">
-        <f>X72-V72</f>
+        <f t="shared" si="147"/>
         <v>71</v>
       </c>
       <c r="AH326" s="17">
-        <f t="shared" si="93"/>
+        <f t="shared" si="148"/>
         <v>-1092.4060000000018</v>
       </c>
     </row>
     <row r="327" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF327">
-        <f>O73-500</f>
+        <f t="shared" si="146"/>
         <v>-16.12700000000001</v>
       </c>
       <c r="AG327" s="17">
-        <f>X73-V73</f>
+        <f t="shared" si="147"/>
         <v>71</v>
       </c>
       <c r="AH327" s="17">
-        <f t="shared" si="93"/>
+        <f t="shared" si="148"/>
         <v>-1145.0170000000007</v>
       </c>
     </row>
     <row r="328" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF328">
-        <f>O74-500</f>
+        <f t="shared" si="146"/>
         <v>-17.918999999999983</v>
       </c>
       <c r="AG328" s="17">
-        <f>X74-V74</f>
+        <f t="shared" si="147"/>
         <v>71</v>
       </c>
       <c r="AH328" s="17">
-        <f t="shared" si="93"/>
+        <f t="shared" si="148"/>
         <v>-1272.2489999999989</v>
       </c>
     </row>
@@ -21461,11 +21442,11 @@
         <v>-1.6419999999999959</v>
       </c>
       <c r="AG329" s="17">
-        <f>X75-V75</f>
+        <f t="shared" si="147"/>
         <v>71</v>
       </c>
       <c r="AH329" s="17">
-        <f t="shared" si="93"/>
+        <f t="shared" si="148"/>
         <v>-116.58199999999971</v>
       </c>
     </row>
@@ -21488,21 +21469,21 @@
       </c>
     </row>
     <row r="332" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF332" s="55" t="s">
+      <c r="AF332" s="118" t="s">
         <v>161</v>
       </c>
-      <c r="AG332" s="55"/>
-      <c r="AH332" s="55"/>
+      <c r="AG332" s="118"/>
+      <c r="AH332" s="118"/>
     </row>
     <row r="336" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF336" s="56" t="s">
+      <c r="AF336" s="117" t="s">
         <v>151</v>
       </c>
-      <c r="AG336" s="56"/>
-      <c r="AI336" s="55" t="s">
+      <c r="AG336" s="117"/>
+      <c r="AI336" s="118" t="s">
         <v>150</v>
       </c>
-      <c r="AJ336" s="55"/>
+      <c r="AJ336" s="118"/>
       <c r="AK336" s="46"/>
       <c r="AL336" s="46"/>
     </row>
@@ -21591,13 +21572,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="L58:AD58"/>
-    <mergeCell ref="AF61:AH61"/>
-    <mergeCell ref="K39:K45"/>
-    <mergeCell ref="K24:K30"/>
-    <mergeCell ref="K19:K22"/>
-    <mergeCell ref="K32:K37"/>
-    <mergeCell ref="K47:K52"/>
+    <mergeCell ref="AC209:AD209"/>
     <mergeCell ref="AF221:AJ221"/>
     <mergeCell ref="AF277:AG277"/>
     <mergeCell ref="AM277:AN277"/>
@@ -21607,7 +21582,13 @@
     <mergeCell ref="AF332:AH332"/>
     <mergeCell ref="AI277:AK277"/>
     <mergeCell ref="AD271:AH271"/>
-    <mergeCell ref="AC209:AD209"/>
+    <mergeCell ref="L58:AD58"/>
+    <mergeCell ref="AF61:AH61"/>
+    <mergeCell ref="K39:K45"/>
+    <mergeCell ref="K24:K30"/>
+    <mergeCell ref="K19:K22"/>
+    <mergeCell ref="K32:K37"/>
+    <mergeCell ref="K47:K52"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21658,7 +21639,7 @@
       <c r="C9" t="s">
         <v>344</v>
       </c>
-      <c r="D9" s="112">
+      <c r="D9" s="99">
         <f>D7-D8</f>
         <v>600</v>
       </c>
@@ -21692,276 +21673,266 @@
       <c r="D15" t="s">
         <v>141</v>
       </c>
-      <c r="E15" s="84">
+      <c r="E15" s="75">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="116" t="s">
         <v>354</v>
       </c>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="88"/>
-      <c r="J18" s="88"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="116"/>
+      <c r="J18" s="116"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="73" t="s">
         <v>349</v>
       </c>
-      <c r="D19" s="115">
+      <c r="D19" s="102">
         <v>0.03</v>
       </c>
-      <c r="E19" s="115">
+      <c r="E19" s="102">
         <v>0.05</v>
       </c>
-      <c r="F19" s="116">
+      <c r="F19" s="103">
         <v>5.5E-2</v>
       </c>
-      <c r="G19" s="115">
+      <c r="G19" s="102">
         <v>0.06</v>
       </c>
-      <c r="H19" s="116">
+      <c r="H19" s="103">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="I19" s="115">
+      <c r="I19" s="102">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J19" s="115">
+      <c r="J19" s="102">
         <v>0.08</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C20" s="82" t="s">
+      <c r="C20" s="73" t="s">
         <v>350</v>
       </c>
-      <c r="D20" s="80">
+      <c r="D20" s="71">
         <v>550</v>
       </c>
-      <c r="E20" s="80">
+      <c r="E20" s="71">
         <v>550</v>
       </c>
-      <c r="F20" s="80">
+      <c r="F20" s="71">
         <v>550</v>
       </c>
-      <c r="G20" s="80">
+      <c r="G20" s="71">
         <v>550</v>
       </c>
-      <c r="H20" s="80">
+      <c r="H20" s="71">
         <v>550</v>
       </c>
-      <c r="I20" s="80">
+      <c r="I20" s="71">
         <v>550</v>
       </c>
-      <c r="J20" s="80">
+      <c r="J20" s="71">
         <v>550</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C21" s="82" t="s">
+      <c r="C21" s="73" t="s">
         <v>361</v>
       </c>
-      <c r="D21" s="80">
+      <c r="D21" s="71">
         <f>D20*0.03</f>
         <v>16.5</v>
       </c>
-      <c r="E21" s="80">
+      <c r="E21" s="71">
         <f>E20*0.05</f>
         <v>27.5</v>
       </c>
-      <c r="F21" s="80">
+      <c r="F21" s="71">
         <f>F20*0.055</f>
         <v>30.25</v>
       </c>
-      <c r="G21" s="80">
+      <c r="G21" s="71">
         <f>G20*0.06</f>
         <v>33</v>
       </c>
-      <c r="H21" s="80">
+      <c r="H21" s="71">
         <f>H20*0.065</f>
         <v>35.75</v>
       </c>
-      <c r="I21" s="80">
+      <c r="I21" s="71">
         <f>I20*0.07</f>
         <v>38.500000000000007</v>
       </c>
-      <c r="J21" s="80">
+      <c r="J21" s="71">
         <f>J20*0.08</f>
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C22" s="82" t="s">
+      <c r="C22" s="73" t="s">
         <v>351</v>
       </c>
-      <c r="D22" s="80">
+      <c r="D22" s="71">
         <f>D20-D21</f>
         <v>533.5</v>
       </c>
-      <c r="E22" s="80">
+      <c r="E22" s="71">
         <f t="shared" ref="E22:J22" si="0">E20-E21</f>
         <v>522.5</v>
       </c>
-      <c r="F22" s="80">
+      <c r="F22" s="71">
         <f t="shared" si="0"/>
         <v>519.75</v>
       </c>
-      <c r="G22" s="80">
+      <c r="G22" s="71">
         <f t="shared" si="0"/>
         <v>517</v>
       </c>
-      <c r="H22" s="80">
+      <c r="H22" s="71">
         <f t="shared" si="0"/>
         <v>514.25</v>
       </c>
-      <c r="I22" s="80">
+      <c r="I22" s="71">
         <f t="shared" si="0"/>
         <v>511.5</v>
       </c>
-      <c r="J22" s="80">
+      <c r="J22" s="71">
         <f t="shared" si="0"/>
         <v>506</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="71"/>
-    </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="116" t="s">
         <v>355</v>
       </c>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="116"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="116"/>
+      <c r="J24" s="116"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C25" s="82" t="s">
+      <c r="C25" s="73" t="s">
         <v>349</v>
       </c>
-      <c r="D25" s="115">
+      <c r="D25" s="102">
         <v>0.03</v>
       </c>
-      <c r="E25" s="115">
+      <c r="E25" s="102">
         <v>0.05</v>
       </c>
-      <c r="F25" s="116">
+      <c r="F25" s="103">
         <v>5.5E-2</v>
       </c>
-      <c r="G25" s="115">
+      <c r="G25" s="102">
         <v>0.06</v>
       </c>
-      <c r="H25" s="116">
+      <c r="H25" s="103">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="I25" s="115">
+      <c r="I25" s="102">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J25" s="115">
+      <c r="J25" s="102">
         <v>0.08</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C26" s="82" t="s">
+      <c r="C26" s="73" t="s">
         <v>350</v>
       </c>
-      <c r="D26" s="80">
+      <c r="D26" s="71">
         <v>530</v>
       </c>
-      <c r="E26" s="80">
+      <c r="E26" s="71">
         <v>530</v>
       </c>
-      <c r="F26" s="80">
+      <c r="F26" s="71">
         <v>530</v>
       </c>
-      <c r="G26" s="80">
+      <c r="G26" s="71">
         <v>530</v>
       </c>
-      <c r="H26" s="80">
+      <c r="H26" s="71">
         <v>530</v>
       </c>
-      <c r="I26" s="80">
+      <c r="I26" s="71">
         <v>530</v>
       </c>
-      <c r="J26" s="80">
+      <c r="J26" s="71">
         <v>530</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C27" s="82" t="s">
+      <c r="C27" s="73" t="s">
         <v>361</v>
       </c>
-      <c r="D27" s="80">
+      <c r="D27" s="71">
         <f>D26*0.03</f>
         <v>15.899999999999999</v>
       </c>
-      <c r="E27" s="80">
+      <c r="E27" s="71">
         <f>E26*0.05</f>
         <v>26.5</v>
       </c>
-      <c r="F27" s="80">
+      <c r="F27" s="71">
         <f>F26*0.055</f>
         <v>29.15</v>
       </c>
-      <c r="G27" s="80">
+      <c r="G27" s="71">
         <f>G26*0.06</f>
         <v>31.799999999999997</v>
       </c>
-      <c r="H27" s="80">
+      <c r="H27" s="71">
         <f>H26*0.065</f>
         <v>34.450000000000003</v>
       </c>
-      <c r="I27" s="80">
+      <c r="I27" s="71">
         <f>I26*0.07</f>
         <v>37.1</v>
       </c>
-      <c r="J27" s="80">
+      <c r="J27" s="71">
         <f>J26*0.08</f>
         <v>42.4</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C28" s="82" t="s">
+      <c r="C28" s="73" t="s">
         <v>351</v>
       </c>
-      <c r="D28" s="80">
+      <c r="D28" s="71">
         <f>D26-D27</f>
         <v>514.1</v>
       </c>
-      <c r="E28" s="80">
+      <c r="E28" s="71">
         <f t="shared" ref="E28:H28" si="1">E26-E27</f>
         <v>503.5</v>
       </c>
-      <c r="F28" s="80">
+      <c r="F28" s="71">
         <f t="shared" si="1"/>
         <v>500.85</v>
       </c>
-      <c r="G28" s="80">
+      <c r="G28" s="71">
         <f t="shared" si="1"/>
         <v>498.2</v>
       </c>
-      <c r="H28" s="80">
+      <c r="H28" s="71">
         <f t="shared" si="1"/>
         <v>495.55</v>
       </c>
-      <c r="I28" s="80">
+      <c r="I28" s="71">
         <f t="shared" ref="I28" si="2">I26-I27</f>
         <v>492.9</v>
       </c>
-      <c r="J28" s="80">
+      <c r="J28" s="71">
         <f t="shared" ref="J28" si="3">J26-J27</f>
         <v>487.6</v>
       </c>
@@ -21972,7 +21943,7 @@
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C32" s="113"/>
+      <c r="C32" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -21994,25 +21965,25 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="73" t="s">
         <v>316</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="73" t="s">
         <v>317</v>
       </c>
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="73" t="s">
         <v>312</v>
       </c>
-      <c r="E4" s="82" t="s">
+      <c r="E4" s="73" t="s">
         <v>314</v>
       </c>
-      <c r="F4" s="82" t="s">
+      <c r="F4" s="73" t="s">
         <v>315</v>
       </c>
-      <c r="G4" s="82" t="s">
+      <c r="G4" s="73" t="s">
         <v>313</v>
       </c>
-      <c r="I4" s="107" t="s">
+      <c r="I4" s="96" t="s">
         <v>330</v>
       </c>
     </row>
@@ -22026,14 +21997,14 @@
       <c r="D5" s="52">
         <v>19</v>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="71">
         <v>80</v>
       </c>
-      <c r="F5" s="80">
+      <c r="F5" s="71">
         <f>700/D5</f>
         <v>36.842105263157897</v>
       </c>
-      <c r="G5" s="80">
+      <c r="G5" s="71">
         <f>SUM(E5:F5)</f>
         <v>116.84210526315789</v>
       </c>
@@ -22048,14 +22019,14 @@
       <c r="D6" s="52">
         <v>19</v>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="71">
         <v>80</v>
       </c>
-      <c r="F6" s="80">
+      <c r="F6" s="71">
         <f>650/D6</f>
         <v>34.210526315789473</v>
       </c>
-      <c r="G6" s="80">
+      <c r="G6" s="71">
         <f t="shared" ref="G6:G8" si="0">SUM(E6:F6)</f>
         <v>114.21052631578948</v>
       </c>
@@ -22070,14 +22041,14 @@
       <c r="D7" s="52">
         <v>19</v>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="71">
         <v>80</v>
       </c>
-      <c r="F7" s="80">
+      <c r="F7" s="71">
         <f>700/D7</f>
         <v>36.842105263157897</v>
       </c>
-      <c r="G7" s="80">
+      <c r="G7" s="71">
         <f t="shared" si="0"/>
         <v>116.84210526315789</v>
       </c>
@@ -22092,48 +22063,48 @@
       <c r="D8" s="52">
         <v>19</v>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="71">
         <v>80</v>
       </c>
-      <c r="F8" s="80">
+      <c r="F8" s="71">
         <f>1000/D8</f>
         <v>52.631578947368418</v>
       </c>
-      <c r="G8" s="80">
+      <c r="G8" s="71">
         <f t="shared" si="0"/>
         <v>132.63157894736841</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B10" s="82" t="s">
+      <c r="B10" s="73" t="s">
         <v>316</v>
       </c>
-      <c r="C10" s="82" t="s">
+      <c r="C10" s="73" t="s">
         <v>317</v>
       </c>
-      <c r="D10" s="82" t="s">
+      <c r="D10" s="73" t="s">
         <v>329</v>
       </c>
-      <c r="E10" s="82" t="s">
+      <c r="E10" s="73" t="s">
         <v>314</v>
       </c>
-      <c r="F10" s="82" t="s">
+      <c r="F10" s="73" t="s">
         <v>315</v>
       </c>
-      <c r="G10" s="82" t="s">
+      <c r="G10" s="73" t="s">
         <v>313</v>
       </c>
-      <c r="H10" s="109" t="s">
+      <c r="H10" s="73" t="s">
         <v>311</v>
       </c>
       <c r="I10" s="43"/>
-      <c r="K10" s="108" t="s">
+      <c r="K10" s="41" t="s">
         <v>331</v>
       </c>
-      <c r="L10" s="108" t="s">
+      <c r="L10" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="M10" s="108" t="s">
+      <c r="M10" s="41" t="s">
         <v>332</v>
       </c>
     </row>
@@ -22147,18 +22118,18 @@
       <c r="D11" s="52">
         <v>19</v>
       </c>
-      <c r="E11" s="80">
+      <c r="E11" s="71">
         <v>80</v>
       </c>
       <c r="F11" s="52">
         <f>(1250/D11)+10</f>
         <v>75.78947368421052</v>
       </c>
-      <c r="G11" s="86">
+      <c r="G11" s="77">
         <f>SUM(E11:F11)</f>
         <v>155.78947368421052</v>
       </c>
-      <c r="H11" s="86">
+      <c r="H11" s="77">
         <v>175</v>
       </c>
       <c r="I11" s="43"/>
@@ -22188,18 +22159,18 @@
       <c r="D12" s="52">
         <v>19</v>
       </c>
-      <c r="E12" s="80">
+      <c r="E12" s="71">
         <v>80</v>
       </c>
       <c r="F12" s="52">
         <f>1250/D12+10</f>
         <v>75.78947368421052</v>
       </c>
-      <c r="G12" s="86">
+      <c r="G12" s="77">
         <f>SUM(E12:F12)</f>
         <v>155.78947368421052</v>
       </c>
-      <c r="H12" s="86">
+      <c r="H12" s="77">
         <f t="shared" ref="H12:H20" si="1">G12+50</f>
         <v>205.78947368421052</v>
       </c>
@@ -22229,18 +22200,18 @@
       <c r="D13" s="52">
         <v>19</v>
       </c>
-      <c r="E13" s="80">
+      <c r="E13" s="71">
         <v>80</v>
       </c>
       <c r="F13" s="52">
         <f>1250/D13+10</f>
         <v>75.78947368421052</v>
       </c>
-      <c r="G13" s="86">
+      <c r="G13" s="77">
         <f>SUM(E13:F13)</f>
         <v>155.78947368421052</v>
       </c>
-      <c r="H13" s="86">
+      <c r="H13" s="77">
         <f t="shared" si="1"/>
         <v>205.78947368421052</v>
       </c>
@@ -22270,18 +22241,18 @@
       <c r="D14" s="52">
         <v>19</v>
       </c>
-      <c r="E14" s="80">
+      <c r="E14" s="71">
         <v>80</v>
       </c>
       <c r="F14" s="52">
         <f>2900/D14+10</f>
         <v>162.63157894736841</v>
       </c>
-      <c r="G14" s="86">
+      <c r="G14" s="77">
         <f>SUM(E14:F14)</f>
         <v>242.63157894736841</v>
       </c>
-      <c r="H14" s="86">
+      <c r="H14" s="77">
         <f t="shared" si="1"/>
         <v>292.63157894736844</v>
       </c>
@@ -22302,30 +22273,30 @@
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H15" s="86"/>
+      <c r="H15" s="77"/>
       <c r="K15" s="43"/>
       <c r="M15" s="43"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B16" s="82" t="s">
+      <c r="B16" s="73" t="s">
         <v>316</v>
       </c>
-      <c r="C16" s="82" t="s">
+      <c r="C16" s="73" t="s">
         <v>317</v>
       </c>
-      <c r="D16" s="82" t="s">
+      <c r="D16" s="73" t="s">
         <v>329</v>
       </c>
-      <c r="E16" s="82" t="s">
+      <c r="E16" s="73" t="s">
         <v>314</v>
       </c>
-      <c r="F16" s="82" t="s">
+      <c r="F16" s="73" t="s">
         <v>315</v>
       </c>
-      <c r="G16" s="82" t="s">
+      <c r="G16" s="73" t="s">
         <v>313</v>
       </c>
-      <c r="H16" s="109" t="s">
+      <c r="H16" s="73" t="s">
         <v>311</v>
       </c>
       <c r="K16" s="43"/>
@@ -22341,18 +22312,18 @@
       <c r="D17" s="52">
         <v>19</v>
       </c>
-      <c r="E17" s="80">
+      <c r="E17" s="71">
         <v>80</v>
       </c>
       <c r="F17" s="52">
         <f>3200/D17+10</f>
         <v>178.42105263157896</v>
       </c>
-      <c r="G17" s="86">
+      <c r="G17" s="77">
         <f>SUM(E17:F17)</f>
         <v>258.42105263157896</v>
       </c>
-      <c r="H17" s="86">
+      <c r="H17" s="77">
         <f t="shared" si="1"/>
         <v>308.42105263157896</v>
       </c>
@@ -22382,18 +22353,18 @@
       <c r="D18" s="52">
         <v>19</v>
       </c>
-      <c r="E18" s="80">
+      <c r="E18" s="71">
         <v>80</v>
       </c>
       <c r="F18" s="52">
         <f>3200/D18+10</f>
         <v>178.42105263157896</v>
       </c>
-      <c r="G18" s="86">
+      <c r="G18" s="77">
         <f>SUM(E18:F18)</f>
         <v>258.42105263157896</v>
       </c>
-      <c r="H18" s="86">
+      <c r="H18" s="77">
         <f t="shared" si="1"/>
         <v>308.42105263157896</v>
       </c>
@@ -22423,18 +22394,18 @@
       <c r="D19" s="52">
         <v>19</v>
       </c>
-      <c r="E19" s="80">
+      <c r="E19" s="71">
         <v>80</v>
       </c>
       <c r="F19" s="52">
         <f>3200/D19+10</f>
         <v>178.42105263157896</v>
       </c>
-      <c r="G19" s="86">
+      <c r="G19" s="77">
         <f>SUM(E19:F19)</f>
         <v>258.42105263157896</v>
       </c>
-      <c r="H19" s="86">
+      <c r="H19" s="77">
         <f t="shared" si="1"/>
         <v>308.42105263157896</v>
       </c>
@@ -22464,18 +22435,18 @@
       <c r="D20" s="52">
         <v>19</v>
       </c>
-      <c r="E20" s="80">
+      <c r="E20" s="71">
         <v>80</v>
       </c>
       <c r="F20" s="52">
         <f>4000/D20+10</f>
         <v>220.52631578947367</v>
       </c>
-      <c r="G20" s="86">
+      <c r="G20" s="77">
         <f>SUM(E20:F20)</f>
         <v>300.52631578947364</v>
       </c>
-      <c r="H20" s="86">
+      <c r="H20" s="77">
         <f t="shared" si="1"/>
         <v>350.52631578947364</v>
       </c>
@@ -22699,7 +22670,7 @@
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B31" s="120" t="s">
+      <c r="B31" s="104" t="s">
         <v>379</v>
       </c>
     </row>

--- a/Sales_Report actualizado 16 abr.xlsx
+++ b/Sales_Report actualizado 16 abr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eduardobazua/bza-reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35E3E45-1F7C-9241-AFB6-137E98A69B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9818A4-BFB0-D940-94CF-469912A5F37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="820" windowWidth="30240" windowHeight="17480" xr2:uid="{A69E99B4-FD75-534F-A443-AF5D6F49D11E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="424">
   <si>
     <t>ORDEN DE COMPRA</t>
   </si>
@@ -833,12 +833,6 @@
     <t>IX0034-8</t>
   </si>
   <si>
-    <t>KCM</t>
-  </si>
-  <si>
-    <t>Scribe</t>
-  </si>
-  <si>
     <t>X0035</t>
   </si>
   <si>
@@ -848,9 +842,6 @@
     <t>IX0035-2</t>
   </si>
   <si>
-    <t>GCP</t>
-  </si>
-  <si>
     <t>IX0034-9</t>
   </si>
   <si>
@@ -1157,9 +1148,6 @@
     <t>IX0041-2</t>
   </si>
   <si>
-    <t>Utilidades 2026</t>
-  </si>
-  <si>
     <t>FLETE</t>
   </si>
   <si>
@@ -1302,6 +1290,27 @@
   </si>
   <si>
     <t>bajo</t>
+  </si>
+  <si>
+    <t>X0044</t>
+  </si>
+  <si>
+    <t>IX0044-1</t>
+  </si>
+  <si>
+    <t>IX0044-2</t>
+  </si>
+  <si>
+    <t>IX0044-3</t>
+  </si>
+  <si>
+    <t>IX0044-4</t>
+  </si>
+  <si>
+    <t>IX0044-5</t>
+  </si>
+  <si>
+    <t>IX0044-6</t>
   </si>
 </sst>
 </file>
@@ -1710,7 +1719,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1894,7 +1903,6 @@
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="8" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1935,9 +1943,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2278,7 +2283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E60E4A7-44BB-EF45-AA03-B01A671D9B12}">
-  <dimension ref="A3:AR342"/>
+  <dimension ref="A3:AR343"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -2347,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
@@ -2369,7 +2374,7 @@
         <v>59</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V3" s="2" t="s">
         <v>60</v>
@@ -2387,7 +2392,7 @@
         <v>59</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>58</v>
@@ -3401,7 +3406,7 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="115">
+      <c r="K19" s="114">
         <v>1135</v>
       </c>
       <c r="L19" s="26">
@@ -3481,7 +3486,7 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="115"/>
+      <c r="K20" s="114"/>
       <c r="L20" s="26">
         <v>1113002292</v>
       </c>
@@ -3559,7 +3564,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="115"/>
+      <c r="K21" s="114"/>
       <c r="L21" s="26">
         <v>1113002292</v>
       </c>
@@ -3637,7 +3642,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="115"/>
+      <c r="K22" s="114"/>
       <c r="L22" s="26">
         <v>1113002292</v>
       </c>
@@ -3759,7 +3764,7 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="115">
+      <c r="K24" s="114">
         <v>1175</v>
       </c>
       <c r="L24" s="26">
@@ -3842,7 +3847,7 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="115"/>
+      <c r="K25" s="114"/>
       <c r="L25" s="26">
         <v>1113002305</v>
       </c>
@@ -3923,7 +3928,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="115"/>
+      <c r="K26" s="114"/>
       <c r="L26" s="26">
         <v>1113002305</v>
       </c>
@@ -4004,7 +4009,7 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="115"/>
+      <c r="K27" s="114"/>
       <c r="L27" s="26">
         <v>1113002305</v>
       </c>
@@ -4085,7 +4090,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="115"/>
+      <c r="K28" s="114"/>
       <c r="L28" s="26">
         <v>1113002305</v>
       </c>
@@ -4166,7 +4171,7 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="115"/>
+      <c r="K29" s="114"/>
       <c r="L29" s="26">
         <v>1113002305</v>
       </c>
@@ -4246,7 +4251,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="115"/>
+      <c r="K30" s="114"/>
       <c r="L30" s="26">
         <v>1113002305</v>
       </c>
@@ -4371,7 +4376,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="115">
+      <c r="K32" s="114">
         <v>1415</v>
       </c>
       <c r="L32" s="26"/>
@@ -4462,7 +4467,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="115"/>
+      <c r="K33" s="114"/>
       <c r="L33" s="26"/>
       <c r="M33" s="26"/>
       <c r="N33" s="26"/>
@@ -4551,7 +4556,7 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="115"/>
+      <c r="K34" s="114"/>
       <c r="L34" s="26"/>
       <c r="M34" s="26"/>
       <c r="N34" s="26"/>
@@ -4640,7 +4645,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="115"/>
+      <c r="K35" s="114"/>
       <c r="L35" s="21"/>
       <c r="M35" s="21"/>
       <c r="N35" s="21"/>
@@ -4729,7 +4734,7 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="115"/>
+      <c r="K36" s="114"/>
       <c r="L36" s="21"/>
       <c r="M36" s="21"/>
       <c r="N36" s="21"/>
@@ -4818,7 +4823,7 @@
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="115"/>
+      <c r="K37" s="114"/>
       <c r="L37" s="27"/>
       <c r="M37" s="27"/>
       <c r="N37" s="27"/>
@@ -4953,7 +4958,7 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="115">
+      <c r="K39" s="114">
         <v>1495</v>
       </c>
       <c r="L39" s="27"/>
@@ -5043,7 +5048,7 @@
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="115"/>
+      <c r="K40" s="114"/>
       <c r="L40" s="27"/>
       <c r="M40" s="27"/>
       <c r="N40" s="27"/>
@@ -5136,7 +5141,7 @@
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="115"/>
+      <c r="K41" s="114"/>
       <c r="L41" s="27"/>
       <c r="M41" s="27"/>
       <c r="N41" s="27"/>
@@ -5229,7 +5234,7 @@
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="115"/>
+      <c r="K42" s="114"/>
       <c r="L42" s="27"/>
       <c r="M42" s="27"/>
       <c r="N42" s="27"/>
@@ -5318,7 +5323,7 @@
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="115"/>
+      <c r="K43" s="114"/>
       <c r="L43" s="29"/>
       <c r="M43" s="29"/>
       <c r="N43" s="29"/>
@@ -5407,7 +5412,7 @@
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="115"/>
+      <c r="K44" s="114"/>
       <c r="L44" s="29"/>
       <c r="M44" s="29"/>
       <c r="N44" s="29"/>
@@ -5493,7 +5498,7 @@
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="115"/>
+      <c r="K45" s="114"/>
       <c r="L45" s="29"/>
       <c r="M45" s="29"/>
       <c r="N45" s="29"/>
@@ -5626,7 +5631,7 @@
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="115">
+      <c r="K47" s="114">
         <v>1495</v>
       </c>
       <c r="L47" s="29"/>
@@ -5718,7 +5723,7 @@
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="115"/>
+      <c r="K48" s="114"/>
       <c r="L48" s="29"/>
       <c r="M48" s="29"/>
       <c r="N48" s="29"/>
@@ -5805,7 +5810,7 @@
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="115"/>
+      <c r="K49" s="114"/>
       <c r="L49" s="29"/>
       <c r="M49" s="29"/>
       <c r="N49" s="29"/>
@@ -5892,7 +5897,7 @@
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
-      <c r="K50" s="115"/>
+      <c r="K50" s="114"/>
       <c r="L50" s="29"/>
       <c r="M50" s="29"/>
       <c r="N50" s="29"/>
@@ -5979,7 +5984,7 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
-      <c r="K51" s="115"/>
+      <c r="K51" s="114"/>
       <c r="L51" s="29"/>
       <c r="M51" s="29"/>
       <c r="N51" s="29"/>
@@ -6066,7 +6071,7 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
-      <c r="K52" s="115"/>
+      <c r="K52" s="114"/>
       <c r="L52" s="29"/>
       <c r="M52" s="29"/>
       <c r="N52" s="29"/>
@@ -6334,27 +6339,27 @@
       <c r="I58" s="39"/>
       <c r="J58" s="39"/>
       <c r="K58" s="39"/>
-      <c r="L58" s="111">
+      <c r="L58" s="110">
         <v>2025</v>
       </c>
-      <c r="M58" s="112"/>
-      <c r="N58" s="112"/>
-      <c r="O58" s="112"/>
-      <c r="P58" s="112"/>
-      <c r="Q58" s="112"/>
-      <c r="R58" s="112"/>
-      <c r="S58" s="112"/>
-      <c r="T58" s="112"/>
-      <c r="U58" s="112"/>
-      <c r="V58" s="112"/>
-      <c r="W58" s="112"/>
-      <c r="X58" s="112"/>
-      <c r="Y58" s="112"/>
-      <c r="Z58" s="112"/>
-      <c r="AA58" s="112"/>
-      <c r="AB58" s="112"/>
-      <c r="AC58" s="112"/>
-      <c r="AD58" s="113"/>
+      <c r="M58" s="111"/>
+      <c r="N58" s="111"/>
+      <c r="O58" s="111"/>
+      <c r="P58" s="111"/>
+      <c r="Q58" s="111"/>
+      <c r="R58" s="111"/>
+      <c r="S58" s="111"/>
+      <c r="T58" s="111"/>
+      <c r="U58" s="111"/>
+      <c r="V58" s="111"/>
+      <c r="W58" s="111"/>
+      <c r="X58" s="111"/>
+      <c r="Y58" s="111"/>
+      <c r="Z58" s="111"/>
+      <c r="AA58" s="111"/>
+      <c r="AB58" s="111"/>
+      <c r="AC58" s="111"/>
+      <c r="AD58" s="112"/>
       <c r="AF58" s="3"/>
       <c r="AG58" s="3"/>
       <c r="AH58" s="3"/>
@@ -6392,10 +6397,10 @@
       <c r="J59" s="11"/>
       <c r="K59" s="37"/>
       <c r="L59" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M59" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N59" s="27"/>
       <c r="O59" s="27">
@@ -6487,10 +6492,10 @@
       <c r="J60" s="11"/>
       <c r="K60" s="37"/>
       <c r="L60" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M60" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N60" s="27"/>
       <c r="O60" s="27">
@@ -6580,10 +6585,10 @@
       <c r="J61" s="11"/>
       <c r="K61" s="37"/>
       <c r="L61" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M61" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N61" s="27"/>
       <c r="O61" s="27">
@@ -6637,9 +6642,9 @@
         <v>38736.288</v>
       </c>
       <c r="AE61" s="58"/>
-      <c r="AF61" s="114"/>
-      <c r="AG61" s="114"/>
-      <c r="AH61" s="114"/>
+      <c r="AF61" s="113"/>
+      <c r="AG61" s="113"/>
+      <c r="AH61" s="113"/>
       <c r="AI61" s="3"/>
       <c r="AJ61" s="3"/>
       <c r="AK61" s="3"/>
@@ -6674,10 +6679,10 @@
       <c r="J62" s="11"/>
       <c r="K62" s="37"/>
       <c r="L62" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M62" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N62" s="27"/>
       <c r="O62" s="27">
@@ -6766,10 +6771,10 @@
       <c r="J63" s="11"/>
       <c r="K63" s="37"/>
       <c r="L63" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M63" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N63" s="27"/>
       <c r="O63" s="27">
@@ -6859,10 +6864,10 @@
       <c r="J64" s="11"/>
       <c r="K64" s="37"/>
       <c r="L64" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M64" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N64" s="27"/>
       <c r="O64" s="27">
@@ -6951,10 +6956,10 @@
       <c r="J65" s="11"/>
       <c r="K65" s="37"/>
       <c r="L65" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M65" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N65" s="27"/>
       <c r="O65" s="27">
@@ -7091,10 +7096,10 @@
         <v>634</v>
       </c>
       <c r="L67" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M67" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N67" s="27"/>
       <c r="O67" s="27">
@@ -7174,10 +7179,10 @@
         <v>634</v>
       </c>
       <c r="L68" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M68" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N68" s="27"/>
       <c r="O68" s="27">
@@ -7255,10 +7260,10 @@
         <v>634</v>
       </c>
       <c r="L69" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M69" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N69" s="27"/>
       <c r="O69" s="27">
@@ -7335,10 +7340,10 @@
         <v>634</v>
       </c>
       <c r="L70" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M70" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N70" s="27"/>
       <c r="O70" s="27">
@@ -7415,10 +7420,10 @@
         <v>634</v>
       </c>
       <c r="L71" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M71" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N71" s="27"/>
       <c r="O71" s="27">
@@ -7495,10 +7500,10 @@
         <v>634</v>
       </c>
       <c r="L72" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M72" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N72" s="27"/>
       <c r="O72" s="27">
@@ -7575,10 +7580,10 @@
         <v>634</v>
       </c>
       <c r="L73" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M73" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N73" s="27"/>
       <c r="O73" s="27">
@@ -7658,10 +7663,10 @@
         <v>634</v>
       </c>
       <c r="L74" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M74" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N74" s="27"/>
       <c r="O74" s="27">
@@ -7741,10 +7746,10 @@
         <v>634</v>
       </c>
       <c r="L75" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M75" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N75" s="27"/>
       <c r="O75" s="27">
@@ -7802,7 +7807,7 @@
     <row r="76" spans="1:44" ht="20" x14ac:dyDescent="0.25">
       <c r="A76" s="55">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="7"/>
@@ -7875,14 +7880,14 @@
       </c>
       <c r="J77" s="56">
         <f ca="1">I77-$A$76</f>
-        <v>-311</v>
+        <v>-332</v>
       </c>
       <c r="K77" s="37"/>
       <c r="L77" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M77" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N77" s="27" t="s">
         <v>122</v>
@@ -7978,14 +7983,14 @@
       </c>
       <c r="J78" s="56">
         <f t="shared" ref="J78:J97" ca="1" si="54">I78-$A$76</f>
-        <v>-311</v>
+        <v>-332</v>
       </c>
       <c r="K78" s="37"/>
       <c r="L78" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M78" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N78" s="27" t="s">
         <v>124</v>
@@ -8081,14 +8086,14 @@
       </c>
       <c r="J79" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-311</v>
+        <v>-332</v>
       </c>
       <c r="K79" s="37"/>
       <c r="L79" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M79" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N79" s="27" t="s">
         <v>125</v>
@@ -8184,14 +8189,14 @@
       </c>
       <c r="J80" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-311</v>
+        <v>-332</v>
       </c>
       <c r="K80" s="37"/>
       <c r="L80" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M80" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N80" s="27" t="s">
         <v>126</v>
@@ -8287,14 +8292,14 @@
       </c>
       <c r="J81" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-311</v>
+        <v>-332</v>
       </c>
       <c r="K81" s="37"/>
       <c r="L81" s="27" t="s">
         <v>119</v>
       </c>
       <c r="M81" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N81" s="27" t="s">
         <v>121</v>
@@ -8390,14 +8395,14 @@
       </c>
       <c r="J82" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-311</v>
+        <v>-332</v>
       </c>
       <c r="K82" s="37"/>
       <c r="L82" s="27" t="s">
         <v>118</v>
       </c>
       <c r="M82" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N82" s="27" t="s">
         <v>120</v>
@@ -8535,14 +8540,14 @@
       </c>
       <c r="J84" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-291</v>
+        <v>-312</v>
       </c>
       <c r="K84" s="37"/>
       <c r="L84" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M84" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N84" s="27"/>
       <c r="O84" s="27">
@@ -8624,14 +8629,14 @@
       </c>
       <c r="J85" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-283</v>
+        <v>-304</v>
       </c>
       <c r="K85" s="37"/>
       <c r="L85" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M85" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N85" s="27"/>
       <c r="O85" s="27">
@@ -8713,14 +8718,14 @@
       </c>
       <c r="J86" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-280</v>
+        <v>-301</v>
       </c>
       <c r="K86" s="37"/>
       <c r="L86" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M86" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N86" s="27"/>
       <c r="O86" s="27">
@@ -8851,17 +8856,17 @@
       </c>
       <c r="J88" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-265</v>
+        <v>-286</v>
       </c>
       <c r="K88" s="37">
         <f>O101</f>
         <v>1002.071</v>
       </c>
       <c r="L88" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M88" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N88" s="27"/>
       <c r="O88" s="27">
@@ -8943,14 +8948,14 @@
       </c>
       <c r="J89" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-265</v>
+        <v>-286</v>
       </c>
       <c r="K89" s="37"/>
       <c r="L89" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M89" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N89" s="27"/>
       <c r="O89" s="27">
@@ -9032,14 +9037,14 @@
       </c>
       <c r="J90" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-257</v>
+        <v>-278</v>
       </c>
       <c r="K90" s="37"/>
       <c r="L90" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M90" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N90" s="27"/>
       <c r="O90" s="27">
@@ -9167,14 +9172,14 @@
       </c>
       <c r="J92" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-272</v>
+        <v>-293</v>
       </c>
       <c r="K92" s="37"/>
       <c r="L92" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M92" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N92" s="27" t="s">
         <v>176</v>
@@ -9271,14 +9276,14 @@
       </c>
       <c r="J93" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-272</v>
+        <v>-293</v>
       </c>
       <c r="K93" s="37"/>
       <c r="L93" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M93" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N93" s="27" t="s">
         <v>177</v>
@@ -9374,14 +9379,14 @@
       </c>
       <c r="J94" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-272</v>
+        <v>-293</v>
       </c>
       <c r="K94" s="37"/>
       <c r="L94" s="27" t="s">
         <v>119</v>
       </c>
       <c r="M94" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N94" s="27" t="s">
         <v>178</v>
@@ -9477,14 +9482,14 @@
       </c>
       <c r="J95" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-272</v>
+        <v>-293</v>
       </c>
       <c r="K95" s="37"/>
       <c r="L95" s="27" t="s">
         <v>119</v>
       </c>
       <c r="M95" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N95" s="27" t="s">
         <v>179</v>
@@ -9580,14 +9585,14 @@
       </c>
       <c r="J96" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-271</v>
+        <v>-292</v>
       </c>
       <c r="K96" s="37"/>
       <c r="L96" s="27" t="s">
         <v>119</v>
       </c>
       <c r="M96" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N96" s="27" t="s">
         <v>180</v>
@@ -9683,14 +9688,14 @@
       </c>
       <c r="J97" s="56">
         <f t="shared" ca="1" si="54"/>
-        <v>-265</v>
+        <v>-286</v>
       </c>
       <c r="K97" s="37"/>
       <c r="L97" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M97" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N97" s="27" t="s">
         <v>184</v>
@@ -9830,10 +9835,10 @@
       <c r="J99" s="56"/>
       <c r="K99" s="37"/>
       <c r="L99" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M99" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N99" s="27"/>
       <c r="O99" s="27">
@@ -9914,10 +9919,10 @@
       <c r="J100" s="56"/>
       <c r="K100" s="37"/>
       <c r="L100" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M100" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N100" s="27"/>
       <c r="O100" s="27">
@@ -10050,7 +10055,7 @@
         <v>123</v>
       </c>
       <c r="M102" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N102" s="27"/>
       <c r="O102" s="27">
@@ -10150,7 +10155,7 @@
         <v>123</v>
       </c>
       <c r="M103" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N103" s="27"/>
       <c r="O103" s="27">
@@ -10249,7 +10254,7 @@
         <v>119</v>
       </c>
       <c r="M104" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N104" s="27"/>
       <c r="O104" s="27">
@@ -10348,7 +10353,7 @@
         <v>119</v>
       </c>
       <c r="M105" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N105" s="27"/>
       <c r="O105" s="27">
@@ -10447,7 +10452,7 @@
         <v>119</v>
       </c>
       <c r="M106" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N106" s="27"/>
       <c r="O106" s="57">
@@ -10546,7 +10551,7 @@
         <v>199</v>
       </c>
       <c r="M107" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N107" s="27"/>
       <c r="O107" s="57">
@@ -10645,7 +10650,7 @@
         <v>118</v>
       </c>
       <c r="M108" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N108" s="27"/>
       <c r="O108" s="27">
@@ -10790,7 +10795,7 @@
         <v>123</v>
       </c>
       <c r="M110" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N110" s="27"/>
       <c r="O110" s="27">
@@ -10888,7 +10893,7 @@
         <v>123</v>
       </c>
       <c r="M111" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N111" s="27"/>
       <c r="O111" s="27">
@@ -10986,7 +10991,7 @@
         <v>119</v>
       </c>
       <c r="M112" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N112" s="27"/>
       <c r="O112" s="27">
@@ -11084,7 +11089,7 @@
         <v>119</v>
       </c>
       <c r="M113" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N113" s="27"/>
       <c r="O113" s="27">
@@ -11182,7 +11187,7 @@
         <v>199</v>
       </c>
       <c r="M114" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N114" s="27"/>
       <c r="O114" s="27">
@@ -11280,7 +11285,7 @@
         <v>118</v>
       </c>
       <c r="M115" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N115" s="27"/>
       <c r="O115" s="27">
@@ -11424,7 +11429,7 @@
         <v>227</v>
       </c>
       <c r="M117" s="27" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N117" s="27"/>
       <c r="O117" s="27">
@@ -11545,7 +11550,7 @@
       </c>
       <c r="C119" s="3"/>
       <c r="D119" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>12</v>
@@ -11566,10 +11571,10 @@
       <c r="J119" s="11"/>
       <c r="K119" s="37"/>
       <c r="L119" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M119" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N119" s="27"/>
       <c r="O119" s="27">
@@ -11622,7 +11627,7 @@
         <v>37868.51999999996</v>
       </c>
       <c r="AE119" s="33" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AF119" s="14"/>
       <c r="AG119" s="14"/>
@@ -11644,7 +11649,7 @@
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>12</v>
@@ -11665,10 +11670,10 @@
       <c r="J120" s="11"/>
       <c r="K120" s="37"/>
       <c r="L120" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M120" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N120" s="27"/>
       <c r="O120" s="27">
@@ -11721,7 +11726,7 @@
         <v>37868.51999999996</v>
       </c>
       <c r="AE120" s="33" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AF120" s="15"/>
       <c r="AG120" s="17"/>
@@ -11744,7 +11749,7 @@
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>12</v>
@@ -11765,10 +11770,10 @@
       <c r="J121" s="11"/>
       <c r="K121" s="37"/>
       <c r="L121" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M121" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N121" s="27"/>
       <c r="O121" s="27">
@@ -11821,7 +11826,7 @@
         <v>75698.356000000029</v>
       </c>
       <c r="AE121" s="33" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AF121" s="17"/>
       <c r="AH121" s="43"/>
@@ -11917,7 +11922,7 @@
         <v>239</v>
       </c>
       <c r="M123" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N123" s="27"/>
       <c r="O123" s="27">
@@ -12016,7 +12021,7 @@
         <v>239</v>
       </c>
       <c r="M124" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N124" s="27"/>
       <c r="O124" s="27">
@@ -12115,7 +12120,7 @@
         <v>118</v>
       </c>
       <c r="M125" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N125" s="27"/>
       <c r="O125" s="27">
@@ -12214,7 +12219,7 @@
         <v>246</v>
       </c>
       <c r="M126" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N126" s="27"/>
       <c r="O126" s="27">
@@ -12313,7 +12318,7 @@
         <v>119</v>
       </c>
       <c r="M127" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N127" s="27"/>
       <c r="O127" s="27">
@@ -12412,7 +12417,7 @@
         <v>239</v>
       </c>
       <c r="M128" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N128" s="27"/>
       <c r="O128" s="27">
@@ -12511,7 +12516,7 @@
         <v>246</v>
       </c>
       <c r="M129" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N129" s="27"/>
       <c r="O129" s="27">
@@ -12610,7 +12615,7 @@
         <v>241</v>
       </c>
       <c r="M130" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N130" s="27"/>
       <c r="O130" s="27">
@@ -12755,7 +12760,7 @@
         <v>239</v>
       </c>
       <c r="M132" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N132" s="27"/>
       <c r="O132" s="27">
@@ -12808,7 +12813,7 @@
         <v>18896.599999999999</v>
       </c>
       <c r="AE132" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF132" s="3"/>
       <c r="AG132" s="14"/>
@@ -12854,7 +12859,7 @@
         <v>119</v>
       </c>
       <c r="M133" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N133" s="27"/>
       <c r="O133" s="27">
@@ -12907,7 +12912,7 @@
         <v>18381.800000000003</v>
       </c>
       <c r="AE133" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF133" s="3"/>
       <c r="AG133" s="14"/>
@@ -12953,7 +12958,7 @@
         <v>239</v>
       </c>
       <c r="M134" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N134" s="27"/>
       <c r="O134" s="27">
@@ -13006,7 +13011,7 @@
         <v>17513.800000000003</v>
       </c>
       <c r="AE134" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF134" s="3"/>
       <c r="AG134" s="14"/>
@@ -13052,7 +13057,7 @@
         <v>119</v>
       </c>
       <c r="M135" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N135" s="27"/>
       <c r="O135" s="27">
@@ -13105,7 +13110,7 @@
         <v>18525.200000000004</v>
       </c>
       <c r="AE135" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF135" s="3"/>
       <c r="AG135" s="14"/>
@@ -13151,7 +13156,7 @@
         <v>239</v>
       </c>
       <c r="M136" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N136" s="27"/>
       <c r="O136" s="27">
@@ -13204,7 +13209,7 @@
         <v>18356.399999999994</v>
       </c>
       <c r="AE136" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF136" s="3"/>
       <c r="AG136" s="14"/>
@@ -13250,7 +13255,7 @@
         <v>119</v>
       </c>
       <c r="M137" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N137" s="27"/>
       <c r="O137" s="27">
@@ -13303,7 +13308,7 @@
         <v>18272.999999999993</v>
       </c>
       <c r="AE137" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF137" s="3"/>
       <c r="AG137" s="14"/>
@@ -13349,7 +13354,7 @@
         <v>241</v>
       </c>
       <c r="M138" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N138" s="27"/>
       <c r="O138" s="27">
@@ -13402,7 +13407,7 @@
         <v>18296.399999999994</v>
       </c>
       <c r="AE138" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF138" s="3"/>
       <c r="AG138" s="14"/>
@@ -13448,7 +13453,7 @@
         <v>241</v>
       </c>
       <c r="M139" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N139" s="27"/>
       <c r="O139" s="27">
@@ -13501,7 +13506,7 @@
         <v>18587.599999999991</v>
       </c>
       <c r="AE139" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF139" s="3"/>
       <c r="AG139" s="14"/>
@@ -13523,7 +13528,7 @@
       </c>
       <c r="C140" s="3"/>
       <c r="D140" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>12</v>
@@ -13547,7 +13552,7 @@
         <v>123</v>
       </c>
       <c r="M140" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N140" s="27"/>
       <c r="O140" s="27">
@@ -13600,7 +13605,7 @@
         <v>17921.200000000004</v>
       </c>
       <c r="AE140" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF140" s="3"/>
       <c r="AG140" s="14"/>
@@ -13622,7 +13627,7 @@
       </c>
       <c r="C141" s="3"/>
       <c r="D141" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>12</v>
@@ -13646,7 +13651,7 @@
         <v>119</v>
       </c>
       <c r="M141" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N141" s="27"/>
       <c r="O141" s="27">
@@ -13699,7 +13704,7 @@
         <v>18497.399999999994</v>
       </c>
       <c r="AE141" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF141" s="3"/>
       <c r="AG141" s="14"/>
@@ -13721,7 +13726,7 @@
       </c>
       <c r="C142" s="3"/>
       <c r="D142" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>12</v>
@@ -13745,7 +13750,7 @@
         <v>242</v>
       </c>
       <c r="M142" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N142" s="27"/>
       <c r="O142" s="27">
@@ -13798,7 +13803,7 @@
         <v>18379.399999999994</v>
       </c>
       <c r="AE142" s="38" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AF142" s="3"/>
       <c r="AG142" s="14"/>
@@ -13862,11 +13867,11 @@
     <row r="144" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A144" s="3"/>
       <c r="B144" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>12</v>
@@ -13890,7 +13895,7 @@
         <v>227</v>
       </c>
       <c r="M144" s="27" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N144" s="27"/>
       <c r="O144" s="27">
@@ -13942,7 +13947,7 @@
         <v>17670.119999999995</v>
       </c>
       <c r="AE144" s="38" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AF144" s="3"/>
       <c r="AI144" s="3"/>
@@ -13959,11 +13964,11 @@
     <row r="145" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A145" s="3"/>
       <c r="B145" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>12</v>
@@ -13987,7 +13992,7 @@
         <v>227</v>
       </c>
       <c r="M145" s="27" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N145" s="27"/>
       <c r="O145" s="27">
@@ -14039,7 +14044,7 @@
         <v>17833.140000000007</v>
       </c>
       <c r="AE145" s="38" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AF145" s="3"/>
       <c r="AI145" s="3"/>
@@ -14103,11 +14108,11 @@
     <row r="147" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A147" s="3"/>
       <c r="B147" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>12</v>
@@ -14180,11 +14185,11 @@
     <row r="148" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A148" s="3"/>
       <c r="B148" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C148" s="3"/>
       <c r="D148" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>12</v>
@@ -14303,11 +14308,11 @@
     <row r="150" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A150" s="3"/>
       <c r="B150" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>12</v>
@@ -14329,7 +14334,7 @@
         <v>227</v>
       </c>
       <c r="M150" s="27" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N150" s="27"/>
       <c r="O150" s="27">
@@ -14381,7 +14386,7 @@
         <v>17264.920000000006</v>
       </c>
       <c r="AE150" s="38" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AF150" s="3"/>
       <c r="AI150" s="3"/>
@@ -14398,11 +14403,11 @@
     <row r="151" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A151" s="3"/>
       <c r="B151" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C151" s="3"/>
       <c r="D151" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>12</v>
@@ -14424,7 +14429,7 @@
         <v>227</v>
       </c>
       <c r="M151" s="27" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N151" s="27"/>
       <c r="O151" s="27">
@@ -14476,7 +14481,7 @@
         <v>17702.68</v>
       </c>
       <c r="AE151" s="38" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AF151" s="3"/>
       <c r="AI151" s="3"/>
@@ -14493,11 +14498,11 @@
     <row r="152" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A152" s="3"/>
       <c r="B152" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C152" s="3"/>
       <c r="D152" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>12</v>
@@ -14519,7 +14524,7 @@
         <v>227</v>
       </c>
       <c r="M152" s="27" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N152" s="27"/>
       <c r="O152" s="27">
@@ -14571,7 +14576,7 @@
         <v>17788.18</v>
       </c>
       <c r="AE152" s="38" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AF152" s="14"/>
       <c r="AI152" s="3"/>
@@ -14635,11 +14640,11 @@
     <row r="154" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A154" s="3"/>
       <c r="B154" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C154" s="3"/>
       <c r="D154" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>12</v>
@@ -14661,7 +14666,7 @@
         <v>239</v>
       </c>
       <c r="M154" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N154" s="27"/>
       <c r="O154" s="27">
@@ -14713,7 +14718,7 @@
         <v>17006.519999999997</v>
       </c>
       <c r="AE154" s="38" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AF154" s="3"/>
       <c r="AG154" s="14"/>
@@ -14731,11 +14736,11 @@
     <row r="155" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A155" s="3"/>
       <c r="B155" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C155" s="3"/>
       <c r="D155" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>12</v>
@@ -14757,7 +14762,7 @@
         <v>239</v>
       </c>
       <c r="M155" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N155" s="27"/>
       <c r="O155" s="27">
@@ -14809,7 +14814,7 @@
         <v>17389.180000000008</v>
       </c>
       <c r="AE155" s="38" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AF155" s="3"/>
       <c r="AG155" s="14"/>
@@ -14827,11 +14832,11 @@
     <row r="156" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A156" s="3"/>
       <c r="B156" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C156" s="3"/>
       <c r="D156" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>12</v>
@@ -14853,7 +14858,7 @@
         <v>119</v>
       </c>
       <c r="M156" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N156" s="27"/>
       <c r="O156" s="27">
@@ -14905,7 +14910,7 @@
         <v>17209.82</v>
       </c>
       <c r="AE156" s="38" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AF156" s="3"/>
       <c r="AG156" s="14"/>
@@ -14923,11 +14928,11 @@
     <row r="157" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A157" s="3"/>
       <c r="B157" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C157" s="3"/>
       <c r="D157" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>12</v>
@@ -14949,7 +14954,7 @@
         <v>119</v>
       </c>
       <c r="M157" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N157" s="27"/>
       <c r="O157" s="27">
@@ -15001,7 +15006,7 @@
         <v>17604.260000000009</v>
       </c>
       <c r="AE157" s="38" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AF157" s="3"/>
       <c r="AG157" s="14"/>
@@ -15019,11 +15024,11 @@
     <row r="158" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A158" s="3"/>
       <c r="B158" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C158" s="3"/>
       <c r="D158" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>12</v>
@@ -15045,7 +15050,7 @@
         <v>242</v>
       </c>
       <c r="M158" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N158" s="27"/>
       <c r="O158" s="27">
@@ -15097,7 +15102,7 @@
         <v>17632.379999999997</v>
       </c>
       <c r="AE158" s="38" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AF158" s="3"/>
       <c r="AG158" s="14"/>
@@ -15115,11 +15120,11 @@
     <row r="159" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A159" s="3"/>
       <c r="B159" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C159" s="3"/>
       <c r="D159" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>12</v>
@@ -15141,7 +15146,7 @@
         <v>242</v>
       </c>
       <c r="M159" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N159" s="27"/>
       <c r="O159" s="27">
@@ -15193,7 +15198,7 @@
         <v>17682.729999999996</v>
       </c>
       <c r="AE159" s="38" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AF159" s="3"/>
       <c r="AG159" s="14"/>
@@ -15211,11 +15216,11 @@
     <row r="160" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A160" s="3"/>
       <c r="B160" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C160" s="3"/>
       <c r="D160" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>12</v>
@@ -15235,7 +15240,7 @@
       <c r="K160" s="3"/>
       <c r="L160" s="27"/>
       <c r="M160" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N160" s="27"/>
       <c r="O160" s="27">
@@ -15287,7 +15292,7 @@
         <v>17216.659999999996</v>
       </c>
       <c r="AE160" s="38" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AF160" s="3"/>
       <c r="AG160" s="14"/>
@@ -15351,11 +15356,11 @@
     <row r="162" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A162" s="3"/>
       <c r="B162" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C162" s="3"/>
       <c r="D162" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>12</v>
@@ -15376,7 +15381,7 @@
         <v>241</v>
       </c>
       <c r="M162" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N162" s="27"/>
       <c r="O162" s="27">
@@ -15428,7 +15433,7 @@
         <v>14804.294999999998</v>
       </c>
       <c r="AE162" s="38" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AF162" s="3"/>
       <c r="AG162" s="14"/>
@@ -15446,11 +15451,11 @@
     <row r="163" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A163" s="3"/>
       <c r="B163" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C163" s="3"/>
       <c r="D163" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>12</v>
@@ -15471,7 +15476,7 @@
         <v>241</v>
       </c>
       <c r="M163" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N163" s="27"/>
       <c r="O163" s="27">
@@ -15523,7 +15528,7 @@
         <v>15395.489999999998</v>
       </c>
       <c r="AE163" s="38" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AF163" s="3"/>
       <c r="AG163" s="14"/>
@@ -15541,11 +15546,11 @@
     <row r="164" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A164" s="3"/>
       <c r="B164" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C164" s="3"/>
       <c r="D164" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>12</v>
@@ -15566,7 +15571,7 @@
         <v>241</v>
       </c>
       <c r="M164" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N164" s="27"/>
       <c r="O164" s="27">
@@ -15618,7 +15623,7 @@
         <v>15264.315000000002</v>
       </c>
       <c r="AE164" s="38" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AF164" s="3"/>
       <c r="AG164" s="14"/>
@@ -15636,11 +15641,11 @@
     <row r="165" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A165" s="3"/>
       <c r="B165" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C165" s="3"/>
       <c r="D165" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>12</v>
@@ -15661,7 +15666,7 @@
         <v>241</v>
       </c>
       <c r="M165" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N165" s="27"/>
       <c r="O165" s="27">
@@ -15713,7 +15718,7 @@
         <v>14775.915000000001</v>
       </c>
       <c r="AE165" s="38" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AF165" s="3"/>
       <c r="AG165" s="14"/>
@@ -15731,11 +15736,11 @@
     <row r="166" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A166" s="3"/>
       <c r="B166" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C166" s="3"/>
       <c r="D166" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>12</v>
@@ -15756,7 +15761,7 @@
         <v>239</v>
       </c>
       <c r="M166" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N166" s="27"/>
       <c r="O166" s="27">
@@ -15808,7 +15813,7 @@
         <v>14889.434999999998</v>
       </c>
       <c r="AE166" s="38" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AF166" s="3"/>
       <c r="AG166" s="14"/>
@@ -15826,11 +15831,11 @@
     <row r="167" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A167" s="3"/>
       <c r="B167" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C167" s="3"/>
       <c r="D167" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>12</v>
@@ -15851,7 +15856,7 @@
         <v>239</v>
       </c>
       <c r="M167" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N167" s="27"/>
       <c r="O167" s="27">
@@ -15903,7 +15908,7 @@
         <v>14290.815000000002</v>
       </c>
       <c r="AE167" s="38" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AF167" s="3"/>
       <c r="AG167" s="14"/>
@@ -15921,11 +15926,11 @@
     <row r="168" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A168" s="3"/>
       <c r="B168" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C168" s="3"/>
       <c r="D168" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>12</v>
@@ -15946,7 +15951,7 @@
         <v>239</v>
       </c>
       <c r="M168" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N168" s="27"/>
       <c r="O168" s="27">
@@ -15998,7 +16003,7 @@
         <v>14847.525000000001</v>
       </c>
       <c r="AE168" s="38" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AF168" s="3"/>
       <c r="AG168" s="14"/>
@@ -16062,11 +16067,11 @@
     <row r="170" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A170" s="3"/>
       <c r="B170" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C170" s="3"/>
       <c r="D170" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>12</v>
@@ -16087,7 +16092,7 @@
         <v>239</v>
       </c>
       <c r="M170" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N170" s="27"/>
       <c r="O170" s="27">
@@ -16155,11 +16160,11 @@
     <row r="171" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A171" s="3"/>
       <c r="B171" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C171" s="3"/>
       <c r="D171" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>12</v>
@@ -16180,7 +16185,7 @@
         <v>239</v>
       </c>
       <c r="M171" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N171" s="27"/>
       <c r="O171" s="27">
@@ -16248,11 +16253,11 @@
     <row r="172" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A172" s="3"/>
       <c r="B172" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C172" s="3"/>
       <c r="D172" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>12</v>
@@ -16270,10 +16275,10 @@
       <c r="J172" s="56"/>
       <c r="K172" s="3"/>
       <c r="L172" s="27" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="M172" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N172" s="27"/>
       <c r="O172" s="27">
@@ -16341,11 +16346,11 @@
     <row r="173" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A173" s="3"/>
       <c r="B173" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C173" s="3"/>
       <c r="D173" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>12</v>
@@ -16363,10 +16368,10 @@
       <c r="J173" s="56"/>
       <c r="K173" s="3"/>
       <c r="L173" s="27" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="M173" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N173" s="27"/>
       <c r="O173" s="27">
@@ -16434,11 +16439,11 @@
     <row r="174" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A174" s="3"/>
       <c r="B174" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C174" s="3"/>
       <c r="D174" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>12</v>
@@ -16459,7 +16464,7 @@
         <v>241</v>
       </c>
       <c r="M174" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N174" s="27"/>
       <c r="O174" s="27">
@@ -16527,11 +16532,11 @@
     <row r="175" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A175" s="3"/>
       <c r="B175" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C175" s="3"/>
       <c r="D175" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>12</v>
@@ -16552,7 +16557,7 @@
         <v>241</v>
       </c>
       <c r="M175" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N175" s="27"/>
       <c r="O175" s="27">
@@ -16666,11 +16671,11 @@
     <row r="177" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A177" s="3"/>
       <c r="B177" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C177" s="3"/>
       <c r="D177" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>12</v>
@@ -16691,7 +16696,7 @@
         <v>199</v>
       </c>
       <c r="M177" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N177" s="27"/>
       <c r="O177" s="27">
@@ -16759,11 +16764,11 @@
     <row r="178" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A178" s="3"/>
       <c r="B178" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C178" s="3"/>
       <c r="D178" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>12</v>
@@ -16784,7 +16789,7 @@
         <v>241</v>
       </c>
       <c r="M178" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N178" s="27"/>
       <c r="O178" s="27">
@@ -16852,11 +16857,11 @@
     <row r="179" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A179" s="3"/>
       <c r="B179" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C179" s="3"/>
       <c r="D179" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>12</v>
@@ -16877,7 +16882,7 @@
         <v>241</v>
       </c>
       <c r="M179" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N179" s="27"/>
       <c r="O179" s="27">
@@ -16945,11 +16950,11 @@
     <row r="180" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A180" s="3"/>
       <c r="B180" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>12</v>
@@ -16970,7 +16975,7 @@
         <v>241</v>
       </c>
       <c r="M180" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N180" s="27"/>
       <c r="O180" s="27">
@@ -17038,11 +17043,11 @@
     <row r="181" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A181" s="3"/>
       <c r="B181" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>12</v>
@@ -17063,7 +17068,7 @@
         <v>240</v>
       </c>
       <c r="M181" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N181" s="27"/>
       <c r="O181" s="27">
@@ -17131,11 +17136,11 @@
     <row r="182" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A182" s="3"/>
       <c r="B182" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>12</v>
@@ -17156,7 +17161,7 @@
         <v>119</v>
       </c>
       <c r="M182" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N182" s="27"/>
       <c r="O182" s="27">
@@ -17270,11 +17275,11 @@
     <row r="184" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A184" s="3"/>
       <c r="B184" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>12</v>
@@ -17293,7 +17298,7 @@
         <v>239</v>
       </c>
       <c r="M184" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N184" s="27"/>
       <c r="O184" s="27">
@@ -17361,11 +17366,11 @@
     <row r="185" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A185" s="3"/>
       <c r="B185" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>12</v>
@@ -17384,7 +17389,7 @@
         <v>239</v>
       </c>
       <c r="M185" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N185" s="27"/>
       <c r="O185" s="27">
@@ -17452,11 +17457,11 @@
     <row r="186" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A186" s="3"/>
       <c r="B186" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>12</v>
@@ -17475,7 +17480,7 @@
         <v>239</v>
       </c>
       <c r="M186" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N186" s="27"/>
       <c r="O186" s="27">
@@ -17543,11 +17548,11 @@
     <row r="187" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A187" s="3"/>
       <c r="B187" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C187" s="3"/>
       <c r="D187" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>12</v>
@@ -17566,7 +17571,7 @@
         <v>241</v>
       </c>
       <c r="M187" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N187" s="27"/>
       <c r="O187" s="27">
@@ -17634,11 +17639,11 @@
     <row r="188" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="3"/>
       <c r="B188" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C188" s="3"/>
       <c r="D188" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>12</v>
@@ -17657,7 +17662,7 @@
         <v>241</v>
       </c>
       <c r="M188" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N188" s="27"/>
       <c r="O188" s="27">
@@ -17725,11 +17730,11 @@
     <row r="189" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A189" s="3"/>
       <c r="B189" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>12</v>
@@ -17748,7 +17753,7 @@
         <v>241</v>
       </c>
       <c r="M189" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N189" s="27"/>
       <c r="O189" s="27">
@@ -17816,11 +17821,11 @@
     <row r="190" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3"/>
       <c r="B190" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>12</v>
@@ -17839,7 +17844,7 @@
         <v>242</v>
       </c>
       <c r="M190" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N190" s="27"/>
       <c r="O190" s="27">
@@ -17907,11 +17912,11 @@
     <row r="191" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="3"/>
       <c r="B191" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C191" s="3"/>
       <c r="D191" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>12</v>
@@ -17930,7 +17935,7 @@
         <v>242</v>
       </c>
       <c r="M191" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N191" s="27"/>
       <c r="O191" s="27">
@@ -17998,11 +18003,11 @@
     <row r="192" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A192" s="3"/>
       <c r="B192" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>12</v>
@@ -18021,7 +18026,7 @@
         <v>242</v>
       </c>
       <c r="M192" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N192" s="27"/>
       <c r="O192" s="27">
@@ -18135,11 +18140,11 @@
     <row r="194" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A194" s="3"/>
       <c r="B194" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>12</v>
@@ -18158,7 +18163,7 @@
         <v>241</v>
       </c>
       <c r="M194" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N194" s="27"/>
       <c r="O194" s="27">
@@ -18226,11 +18231,11 @@
     <row r="195" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A195" s="3"/>
       <c r="B195" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>12</v>
@@ -18249,7 +18254,7 @@
         <v>241</v>
       </c>
       <c r="M195" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N195" s="27"/>
       <c r="O195" s="27">
@@ -18317,11 +18322,11 @@
     <row r="196" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A196" s="3"/>
       <c r="B196" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C196" s="3"/>
       <c r="D196" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>12</v>
@@ -18340,7 +18345,7 @@
         <v>241</v>
       </c>
       <c r="M196" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N196" s="27"/>
       <c r="O196" s="27">
@@ -18408,11 +18413,11 @@
     <row r="197" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A197" s="3"/>
       <c r="B197" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>12</v>
@@ -18431,7 +18436,7 @@
         <v>239</v>
       </c>
       <c r="M197" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N197" s="27"/>
       <c r="O197" s="27">
@@ -18499,11 +18504,11 @@
     <row r="198" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3"/>
       <c r="B198" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>12</v>
@@ -18522,7 +18527,7 @@
         <v>239</v>
       </c>
       <c r="M198" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N198" s="27"/>
       <c r="O198" s="27">
@@ -18590,11 +18595,11 @@
     <row r="199" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A199" s="3"/>
       <c r="B199" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>12</v>
@@ -18610,10 +18615,10 @@
       <c r="J199" s="56"/>
       <c r="K199" s="3"/>
       <c r="L199" s="27" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="M199" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N199" s="27"/>
       <c r="O199" s="27">
@@ -18681,11 +18686,11 @@
     <row r="200" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="3"/>
       <c r="B200" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C200" s="3"/>
       <c r="D200" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>12</v>
@@ -18704,7 +18709,7 @@
         <v>241</v>
       </c>
       <c r="M200" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N200" s="27"/>
       <c r="O200" s="27">
@@ -18772,11 +18777,11 @@
     <row r="201" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="3"/>
       <c r="B201" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C201" s="3"/>
       <c r="D201" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>12</v>
@@ -18795,7 +18800,7 @@
         <v>241</v>
       </c>
       <c r="M201" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N201" s="27"/>
       <c r="O201" s="27">
@@ -18863,11 +18868,11 @@
     <row r="202" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A202" s="3"/>
       <c r="B202" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C202" s="3"/>
       <c r="D202" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>12</v>
@@ -18886,7 +18891,7 @@
         <v>241</v>
       </c>
       <c r="M202" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N202" s="27"/>
       <c r="O202" s="27">
@@ -18954,11 +18959,11 @@
     <row r="203" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A203" s="3"/>
       <c r="B203" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C203" s="3"/>
       <c r="D203" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>12</v>
@@ -18977,7 +18982,7 @@
         <v>241</v>
       </c>
       <c r="M203" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N203" s="27"/>
       <c r="O203" s="27">
@@ -19045,11 +19050,11 @@
     <row r="204" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A204" s="3"/>
       <c r="B204" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C204" s="3"/>
       <c r="D204" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>12</v>
@@ -19068,7 +19073,7 @@
         <v>241</v>
       </c>
       <c r="M204" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N204" s="27"/>
       <c r="O204" s="27">
@@ -19136,11 +19141,11 @@
     <row r="205" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A205" s="3"/>
       <c r="B205" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C205" s="3"/>
       <c r="D205" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>12</v>
@@ -19159,7 +19164,7 @@
         <v>241</v>
       </c>
       <c r="M205" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N205" s="27"/>
       <c r="O205" s="27">
@@ -19270,154 +19275,667 @@
         <v>121000.33</v>
       </c>
     </row>
-    <row r="207" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="W207" s="17"/>
-      <c r="AC207" t="s">
-        <v>269</v>
-      </c>
-      <c r="AD207" s="17">
-        <f>SUM(AD146,AD118,AD153)</f>
-        <v>107931.84000000001</v>
-      </c>
-      <c r="AE207">
-        <f>SUM(O146,O118,O153)</f>
-        <v>553.41</v>
-      </c>
-    </row>
-    <row r="208" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="W208" s="17"/>
-      <c r="Y208" s="15"/>
-      <c r="AD208" s="17"/>
-      <c r="AE208" s="43"/>
-    </row>
-    <row r="209" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="W209" s="17"/>
-      <c r="Y209" s="17"/>
-      <c r="Z209" s="43"/>
-      <c r="AA209" s="43"/>
-      <c r="AB209" s="95"/>
-      <c r="AC209" s="120" t="s">
-        <v>372</v>
-      </c>
-      <c r="AD209" s="120"/>
-      <c r="AE209" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="210" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="W210" s="17"/>
-      <c r="AC210" t="s">
-        <v>265</v>
-      </c>
-      <c r="AD210" s="17"/>
-      <c r="AE210" s="43"/>
-    </row>
-    <row r="211" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="W211" s="17"/>
-      <c r="Z211" s="43"/>
-      <c r="AA211" s="43"/>
-      <c r="AC211" t="s">
-        <v>264</v>
-      </c>
-      <c r="AD211" s="17">
-        <f>SUM(AD176,AD183,AD193,AD206)</f>
-        <v>346149.78500000003</v>
-      </c>
-    </row>
-    <row r="212" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="W212" s="17"/>
-      <c r="Y212" s="17"/>
-      <c r="AC212" t="s">
-        <v>269</v>
-      </c>
-      <c r="AD212" s="17"/>
-    </row>
-    <row r="213" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="W213" s="17"/>
-      <c r="AD213" s="17"/>
-    </row>
-    <row r="214" spans="16:36" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A207" s="3"/>
+      <c r="B207" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H207" s="54"/>
+      <c r="I207" s="54"/>
+      <c r="J207" s="56"/>
+      <c r="K207" s="3"/>
+      <c r="L207" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="M207" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="N207" s="27"/>
+      <c r="O207" s="27">
+        <v>88.072000000000003</v>
+      </c>
+      <c r="P207" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q207" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R207" s="28">
+        <v>550</v>
+      </c>
+      <c r="S207" s="28">
+        <v>0</v>
+      </c>
+      <c r="T207" s="28">
+        <v>0</v>
+      </c>
+      <c r="U207" s="28"/>
+      <c r="V207" s="28">
+        <v>550</v>
+      </c>
+      <c r="W207" s="28">
+        <f>O207*V207</f>
+        <v>48439.6</v>
+      </c>
+      <c r="X207" s="28">
+        <v>665</v>
+      </c>
+      <c r="Y207" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="28"/>
+      <c r="AB207" s="28">
+        <f t="shared" ref="AB207:AB213" si="142">SUM(X207:Z207)</f>
+        <v>665</v>
+      </c>
+      <c r="AC207" s="28">
+        <f t="shared" ref="AC207:AC212" si="143">AB207*O207</f>
+        <v>58567.880000000005</v>
+      </c>
+      <c r="AD207" s="28">
+        <f t="shared" ref="AD207:AD212" si="144">AC207-W207</f>
+        <v>10128.280000000006</v>
+      </c>
+      <c r="AE207" s="38"/>
+      <c r="AF207" s="3"/>
+      <c r="AG207" s="14"/>
+      <c r="AI207" s="3"/>
+      <c r="AJ207" s="3"/>
+      <c r="AK207" s="3"/>
+      <c r="AL207" s="3"/>
+      <c r="AM207" s="3"/>
+      <c r="AN207" s="3"/>
+      <c r="AO207" s="3"/>
+      <c r="AP207" s="3"/>
+      <c r="AQ207" s="3"/>
+      <c r="AR207" s="3"/>
+    </row>
+    <row r="208" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="3"/>
+      <c r="B208" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H208" s="54"/>
+      <c r="I208" s="54"/>
+      <c r="J208" s="56"/>
+      <c r="K208" s="3"/>
+      <c r="L208" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="M208" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="N208" s="27"/>
+      <c r="O208" s="27">
+        <v>92.093999999999994</v>
+      </c>
+      <c r="P208" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q208" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R208" s="28">
+        <v>550</v>
+      </c>
+      <c r="S208" s="28">
+        <v>0</v>
+      </c>
+      <c r="T208" s="28">
+        <v>0</v>
+      </c>
+      <c r="U208" s="28"/>
+      <c r="V208" s="28">
+        <v>550</v>
+      </c>
+      <c r="W208" s="28">
+        <f t="shared" ref="W208:W211" si="145">O208*V208</f>
+        <v>50651.7</v>
+      </c>
+      <c r="X208" s="28">
+        <v>665</v>
+      </c>
+      <c r="Y208" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z208" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA208" s="28"/>
+      <c r="AB208" s="28">
+        <f t="shared" si="142"/>
+        <v>665</v>
+      </c>
+      <c r="AC208" s="28">
+        <f t="shared" si="143"/>
+        <v>61242.509999999995</v>
+      </c>
+      <c r="AD208" s="28">
+        <f t="shared" si="144"/>
+        <v>10590.809999999998</v>
+      </c>
+      <c r="AE208" s="38"/>
+      <c r="AF208" s="3"/>
+      <c r="AG208" s="14"/>
+      <c r="AI208" s="3"/>
+      <c r="AJ208" s="3"/>
+      <c r="AK208" s="3"/>
+      <c r="AL208" s="3"/>
+      <c r="AM208" s="3"/>
+      <c r="AN208" s="3"/>
+      <c r="AO208" s="3"/>
+      <c r="AP208" s="3"/>
+      <c r="AQ208" s="3"/>
+      <c r="AR208" s="3"/>
+    </row>
+    <row r="209" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A209" s="3"/>
+      <c r="B209" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H209" s="54"/>
+      <c r="I209" s="54"/>
+      <c r="J209" s="56"/>
+      <c r="K209" s="3"/>
+      <c r="L209" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="M209" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="N209" s="27"/>
+      <c r="O209" s="27">
+        <v>92.524000000000001</v>
+      </c>
+      <c r="P209" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q209" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R209" s="28">
+        <v>550</v>
+      </c>
+      <c r="S209" s="28">
+        <v>0</v>
+      </c>
+      <c r="T209" s="28">
+        <v>0</v>
+      </c>
+      <c r="U209" s="28"/>
+      <c r="V209" s="28">
+        <v>550</v>
+      </c>
+      <c r="W209" s="28">
+        <f t="shared" si="145"/>
+        <v>50888.2</v>
+      </c>
+      <c r="X209" s="28">
+        <v>665</v>
+      </c>
+      <c r="Y209" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z209" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA209" s="28"/>
+      <c r="AB209" s="28">
+        <f t="shared" si="142"/>
+        <v>665</v>
+      </c>
+      <c r="AC209" s="28">
+        <f t="shared" si="143"/>
+        <v>61528.46</v>
+      </c>
+      <c r="AD209" s="28">
+        <f t="shared" si="144"/>
+        <v>10640.260000000002</v>
+      </c>
+      <c r="AE209" s="38"/>
+      <c r="AF209" s="3"/>
+      <c r="AG209" s="14"/>
+      <c r="AI209" s="3"/>
+      <c r="AJ209" s="3"/>
+      <c r="AK209" s="3"/>
+      <c r="AL209" s="3"/>
+      <c r="AM209" s="3"/>
+      <c r="AN209" s="3"/>
+      <c r="AO209" s="3"/>
+      <c r="AP209" s="3"/>
+      <c r="AQ209" s="3"/>
+      <c r="AR209" s="3"/>
+    </row>
+    <row r="210" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="3"/>
+      <c r="B210" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H210" s="54"/>
+      <c r="I210" s="54"/>
+      <c r="J210" s="56"/>
+      <c r="K210" s="3"/>
+      <c r="L210" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="M210" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="N210" s="27"/>
+      <c r="O210" s="27">
+        <v>90.257000000000005</v>
+      </c>
+      <c r="P210" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q210" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R210" s="28">
+        <v>550</v>
+      </c>
+      <c r="S210" s="28">
+        <v>0</v>
+      </c>
+      <c r="T210" s="28">
+        <v>0</v>
+      </c>
+      <c r="U210" s="28"/>
+      <c r="V210" s="28">
+        <v>550</v>
+      </c>
+      <c r="W210" s="28">
+        <f t="shared" si="145"/>
+        <v>49641.350000000006</v>
+      </c>
+      <c r="X210" s="28">
+        <v>665</v>
+      </c>
+      <c r="Y210" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z210" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA210" s="28"/>
+      <c r="AB210" s="28">
+        <f t="shared" si="142"/>
+        <v>665</v>
+      </c>
+      <c r="AC210" s="28">
+        <f t="shared" si="143"/>
+        <v>60020.905000000006</v>
+      </c>
+      <c r="AD210" s="28">
+        <f t="shared" si="144"/>
+        <v>10379.555</v>
+      </c>
+      <c r="AE210" s="38"/>
+      <c r="AF210" s="3"/>
+      <c r="AG210" s="14"/>
+      <c r="AI210" s="3"/>
+      <c r="AJ210" s="3"/>
+      <c r="AK210" s="3"/>
+      <c r="AL210" s="3"/>
+      <c r="AM210" s="3"/>
+      <c r="AN210" s="3"/>
+      <c r="AO210" s="3"/>
+      <c r="AP210" s="3"/>
+      <c r="AQ210" s="3"/>
+      <c r="AR210" s="3"/>
+    </row>
+    <row r="211" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="3"/>
+      <c r="B211" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H211" s="54"/>
+      <c r="I211" s="54"/>
+      <c r="J211" s="56"/>
+      <c r="K211" s="3"/>
+      <c r="L211" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="M211" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="N211" s="27"/>
+      <c r="O211" s="27">
+        <v>91.072000000000003</v>
+      </c>
+      <c r="P211" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q211" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R211" s="28">
+        <v>550</v>
+      </c>
+      <c r="S211" s="28">
+        <v>0</v>
+      </c>
+      <c r="T211" s="28">
+        <v>0</v>
+      </c>
+      <c r="U211" s="28"/>
+      <c r="V211" s="28">
+        <v>550</v>
+      </c>
+      <c r="W211" s="28">
+        <f t="shared" si="145"/>
+        <v>50089.599999999999</v>
+      </c>
+      <c r="X211" s="28">
+        <v>665</v>
+      </c>
+      <c r="Y211" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z211" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA211" s="28"/>
+      <c r="AB211" s="28">
+        <f t="shared" si="142"/>
+        <v>665</v>
+      </c>
+      <c r="AC211" s="28">
+        <f t="shared" si="143"/>
+        <v>60562.880000000005</v>
+      </c>
+      <c r="AD211" s="28">
+        <f t="shared" si="144"/>
+        <v>10473.280000000006</v>
+      </c>
+      <c r="AE211" s="38"/>
+      <c r="AF211" s="3"/>
+      <c r="AG211" s="14"/>
+      <c r="AI211" s="3"/>
+      <c r="AJ211" s="3"/>
+      <c r="AK211" s="3"/>
+      <c r="AL211" s="3"/>
+      <c r="AM211" s="3"/>
+      <c r="AN211" s="3"/>
+      <c r="AO211" s="3"/>
+      <c r="AP211" s="3"/>
+      <c r="AQ211" s="3"/>
+      <c r="AR211" s="3"/>
+    </row>
+    <row r="212" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A212" s="3"/>
+      <c r="B212" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H212" s="54"/>
+      <c r="I212" s="54"/>
+      <c r="J212" s="56"/>
+      <c r="K212" s="3"/>
+      <c r="L212" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="M212" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="N212" s="27"/>
+      <c r="O212" s="27">
+        <v>91.527000000000001</v>
+      </c>
+      <c r="P212" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q212" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R212" s="28">
+        <v>550</v>
+      </c>
+      <c r="S212" s="28">
+        <v>0</v>
+      </c>
+      <c r="T212" s="28">
+        <v>0</v>
+      </c>
+      <c r="U212" s="28"/>
+      <c r="V212" s="28">
+        <v>550</v>
+      </c>
+      <c r="W212" s="28">
+        <f>O212*V212</f>
+        <v>50339.85</v>
+      </c>
+      <c r="X212" s="28">
+        <v>665</v>
+      </c>
+      <c r="Y212" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z212" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA212" s="28"/>
+      <c r="AB212" s="28">
+        <f t="shared" si="142"/>
+        <v>665</v>
+      </c>
+      <c r="AC212" s="28">
+        <f t="shared" si="143"/>
+        <v>60865.455000000002</v>
+      </c>
+      <c r="AD212" s="28">
+        <f t="shared" si="144"/>
+        <v>10525.605000000003</v>
+      </c>
+      <c r="AE212" s="38"/>
+      <c r="AF212" s="3"/>
+      <c r="AG212" s="14"/>
+      <c r="AI212" s="3"/>
+      <c r="AJ212" s="3"/>
+      <c r="AK212" s="3"/>
+      <c r="AL212" s="3"/>
+      <c r="AM212" s="3"/>
+      <c r="AN212" s="3"/>
+      <c r="AO212" s="3"/>
+      <c r="AP212" s="3"/>
+      <c r="AQ212" s="3"/>
+      <c r="AR212" s="3"/>
+    </row>
+    <row r="213" spans="1:44" ht="20" x14ac:dyDescent="0.25">
+      <c r="A213" s="6"/>
+      <c r="B213" s="6"/>
+      <c r="C213" s="7"/>
+      <c r="D213" s="7"/>
+      <c r="E213" s="7"/>
+      <c r="F213" s="7"/>
+      <c r="G213" s="7"/>
+      <c r="H213" s="7"/>
+      <c r="I213" s="54"/>
+      <c r="J213" s="56"/>
+      <c r="K213" s="7"/>
+      <c r="L213" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="M213" s="24"/>
+      <c r="N213" s="24"/>
+      <c r="O213" s="24">
+        <f>+SUM(O207:O212)</f>
+        <v>545.54600000000005</v>
+      </c>
+      <c r="P213" s="8"/>
+      <c r="Q213" s="24"/>
+      <c r="R213" s="24"/>
+      <c r="S213" s="24"/>
+      <c r="T213" s="24"/>
+      <c r="U213" s="24"/>
+      <c r="V213" s="24"/>
+      <c r="W213" s="25">
+        <f>+SUM(W207:W212)</f>
+        <v>300050.3</v>
+      </c>
+      <c r="X213" s="24"/>
+      <c r="Y213" s="24"/>
+      <c r="Z213" s="24"/>
+      <c r="AA213" s="24"/>
+      <c r="AB213" s="24"/>
+      <c r="AC213" s="25">
+        <f>+SUM(AC207:AC212)</f>
+        <v>362788.09</v>
+      </c>
+      <c r="AD213" s="25">
+        <f>+SUM(AD207:AD212)</f>
+        <v>62737.790000000015</v>
+      </c>
+    </row>
+    <row r="214" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="W214" s="17"/>
       <c r="AD214" s="17"/>
     </row>
-    <row r="215" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="W215" s="17"/>
-      <c r="AC215" s="17"/>
-    </row>
-    <row r="216" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="AB216" s="17"/>
+    <row r="215" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AD215" s="17"/>
+    </row>
+    <row r="216" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="W216" s="17"/>
       <c r="AC216" s="17"/>
     </row>
-    <row r="217" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="P217" s="36"/>
+    <row r="217" spans="1:44" x14ac:dyDescent="0.2">
       <c r="AB217" s="17"/>
-      <c r="AE217" s="43"/>
-    </row>
-    <row r="218" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="W218" s="17"/>
+      <c r="AC217" s="17"/>
+    </row>
+    <row r="218" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="P218" s="36"/>
       <c r="AB218" s="17"/>
       <c r="AE218" s="43"/>
     </row>
-    <row r="219" spans="16:36" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="W219" s="17"/>
       <c r="AB219" s="17"/>
       <c r="AE219" s="43"/>
     </row>
-    <row r="220" spans="16:36" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:44" x14ac:dyDescent="0.2">
       <c r="AB220" s="17"/>
       <c r="AE220" s="43"/>
     </row>
-    <row r="221" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="Q221" s="17"/>
+    <row r="221" spans="1:44" x14ac:dyDescent="0.2">
       <c r="AB221" s="17"/>
-      <c r="AF221" s="116" t="s">
-        <v>188</v>
-      </c>
-      <c r="AG221" s="116"/>
-      <c r="AH221" s="116"/>
-      <c r="AI221" s="116"/>
-      <c r="AJ221" s="116"/>
-    </row>
-    <row r="222" spans="16:36" ht="16" x14ac:dyDescent="0.2">
+      <c r="AE221" s="43"/>
+    </row>
+    <row r="222" spans="1:44" x14ac:dyDescent="0.2">
       <c r="Q222" s="17"/>
       <c r="AB222" s="17"/>
-      <c r="AF222" s="74" t="s">
-        <v>243</v>
-      </c>
-      <c r="AG222" s="105" t="s">
-        <v>380</v>
-      </c>
-      <c r="AH222" s="79" t="s">
-        <v>244</v>
-      </c>
-      <c r="AI222" s="79"/>
-      <c r="AJ222" s="73" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="223" spans="16:36" x14ac:dyDescent="0.2">
+      <c r="AF222" s="115" t="s">
+        <v>188</v>
+      </c>
+      <c r="AG222" s="115"/>
+      <c r="AH222" s="115"/>
+      <c r="AI222" s="115"/>
+      <c r="AJ222" s="115"/>
+    </row>
+    <row r="223" spans="1:44" ht="16" x14ac:dyDescent="0.2">
       <c r="Q223" s="17"/>
       <c r="AB223" s="17"/>
-      <c r="AF223" s="71"/>
-      <c r="AG223" s="106"/>
-      <c r="AH223" s="52"/>
+      <c r="AF223" s="74" t="s">
+        <v>243</v>
+      </c>
+      <c r="AG223" s="104" t="s">
+        <v>376</v>
+      </c>
+      <c r="AH223" s="79" t="s">
+        <v>244</v>
+      </c>
       <c r="AI223" s="79"/>
-      <c r="AJ223" s="52"/>
-    </row>
-    <row r="224" spans="16:36" x14ac:dyDescent="0.2">
+      <c r="AJ223" s="73" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="224" spans="1:44" x14ac:dyDescent="0.2">
       <c r="Q224" s="17"/>
       <c r="AB224" s="17"/>
-      <c r="AF224" s="71">
-        <v>297000</v>
-      </c>
-      <c r="AG224" s="106">
-        <v>46121</v>
-      </c>
-      <c r="AH224" s="52" t="s">
-        <v>419</v>
-      </c>
+      <c r="AF224" s="71"/>
+      <c r="AG224" s="105"/>
+      <c r="AH224" s="52"/>
       <c r="AI224" s="79"/>
-      <c r="AJ224" s="52" t="s">
-        <v>99</v>
-      </c>
+      <c r="AJ224" s="52"/>
     </row>
     <row r="225" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q225" s="17"/>
@@ -19425,11 +19943,11 @@
       <c r="AF225" s="71">
         <v>297000</v>
       </c>
-      <c r="AG225" s="106" t="s">
+      <c r="AG225" s="105">
+        <v>46121</v>
+      </c>
+      <c r="AH225" s="52" t="s">
         <v>415</v>
-      </c>
-      <c r="AH225" s="52">
-        <v>540</v>
       </c>
       <c r="AI225" s="79"/>
       <c r="AJ225" s="52" t="s">
@@ -19440,13 +19958,13 @@
       <c r="Q226" s="17"/>
       <c r="AB226" s="17"/>
       <c r="AF226" s="71">
-        <v>445000</v>
-      </c>
-      <c r="AG226" s="107">
-        <v>46091</v>
+        <v>297000</v>
+      </c>
+      <c r="AG226" s="105" t="s">
+        <v>411</v>
       </c>
       <c r="AH226" s="52">
-        <v>810</v>
+        <v>540</v>
       </c>
       <c r="AI226" s="79"/>
       <c r="AJ226" s="52" t="s">
@@ -19457,13 +19975,13 @@
       <c r="Q227" s="17"/>
       <c r="AB227" s="17"/>
       <c r="AF227" s="71">
-        <v>290000</v>
-      </c>
-      <c r="AG227" s="107">
-        <v>46072</v>
+        <v>445000</v>
+      </c>
+      <c r="AG227" s="106">
+        <v>46091</v>
       </c>
       <c r="AH227" s="52">
-        <v>540</v>
+        <v>810</v>
       </c>
       <c r="AI227" s="79"/>
       <c r="AJ227" s="52" t="s">
@@ -19474,15 +19992,15 @@
       <c r="Q228" s="17"/>
       <c r="AB228" s="17"/>
       <c r="AF228" s="71">
-        <v>294000</v>
-      </c>
-      <c r="AG228" s="107">
-        <v>46043</v>
+        <v>290000</v>
+      </c>
+      <c r="AG228" s="106">
+        <v>46072</v>
       </c>
       <c r="AH228" s="52">
         <v>540</v>
       </c>
-      <c r="AI228" s="52"/>
+      <c r="AI228" s="79"/>
       <c r="AJ228" s="52" t="s">
         <v>99</v>
       </c>
@@ -19491,13 +20009,13 @@
       <c r="Q229" s="17"/>
       <c r="AB229" s="17"/>
       <c r="AF229" s="71">
-        <v>143100</v>
-      </c>
-      <c r="AG229" s="107">
-        <v>46010</v>
+        <v>294000</v>
+      </c>
+      <c r="AG229" s="106">
+        <v>46043</v>
       </c>
       <c r="AH229" s="52">
-        <v>270</v>
+        <v>540</v>
       </c>
       <c r="AI229" s="52"/>
       <c r="AJ229" s="52" t="s">
@@ -19508,13 +20026,13 @@
       <c r="Q230" s="17"/>
       <c r="AB230" s="17"/>
       <c r="AF230" s="71">
-        <v>190800</v>
-      </c>
-      <c r="AG230" s="107">
-        <v>46007</v>
+        <v>143100</v>
+      </c>
+      <c r="AG230" s="106">
+        <v>46010</v>
       </c>
       <c r="AH230" s="52">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="AI230" s="52"/>
       <c r="AJ230" s="52" t="s">
@@ -19525,442 +20043,429 @@
       <c r="Q231" s="17"/>
       <c r="AB231" s="17"/>
       <c r="AF231" s="71">
-        <v>47700</v>
-      </c>
-      <c r="AG231" s="107">
-        <v>45993</v>
+        <v>190800</v>
+      </c>
+      <c r="AG231" s="106">
+        <v>46007</v>
       </c>
       <c r="AH231" s="52">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="AI231" s="52"/>
       <c r="AJ231" s="52" t="s">
         <v>99</v>
-      </c>
-      <c r="AN231" t="s">
-        <v>406</v>
-      </c>
-      <c r="AP231" t="s">
-        <v>408</v>
-      </c>
-      <c r="AQ231" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="232" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q232" s="17"/>
       <c r="AB232" s="17"/>
       <c r="AF232" s="71">
-        <v>286000</v>
-      </c>
-      <c r="AG232" s="107">
-        <v>45979</v>
+        <v>47700</v>
+      </c>
+      <c r="AG232" s="106">
+        <v>45993</v>
       </c>
       <c r="AH232" s="52">
-        <v>540</v>
+        <v>90</v>
       </c>
       <c r="AI232" s="52"/>
       <c r="AJ232" s="52" t="s">
         <v>99</v>
       </c>
       <c r="AN232" t="s">
-        <v>407</v>
-      </c>
-      <c r="AO232">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="AP232" t="s">
-        <v>409</v>
-      </c>
-      <c r="AQ232" s="15">
-        <f>13*150</f>
-        <v>1950</v>
+        <v>404</v>
+      </c>
+      <c r="AQ232" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="233" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q233" s="17"/>
       <c r="AB233" s="17"/>
       <c r="AF233" s="71">
-        <v>145000</v>
-      </c>
-      <c r="AG233" s="107">
-        <v>45973</v>
+        <v>286000</v>
+      </c>
+      <c r="AG233" s="106">
+        <v>45979</v>
       </c>
       <c r="AH233" s="52">
-        <v>270</v>
+        <v>540</v>
       </c>
       <c r="AI233" s="52"/>
       <c r="AJ233" s="52" t="s">
         <v>99</v>
       </c>
       <c r="AN233" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AO233">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="AP233" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AQ233" s="15">
-        <f>330*7</f>
-        <v>2310</v>
+        <f>13*150</f>
+        <v>1950</v>
       </c>
     </row>
     <row r="234" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q234" s="17"/>
       <c r="AB234" s="17"/>
-      <c r="AE234" s="43"/>
       <c r="AF234" s="71">
-        <v>541800</v>
-      </c>
-      <c r="AG234" s="107">
-        <v>45960</v>
+        <v>145000</v>
+      </c>
+      <c r="AG234" s="106">
+        <v>45973</v>
       </c>
       <c r="AH234" s="52">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AI234" s="52"/>
       <c r="AJ234" s="52" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="AN234" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AO234">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP234" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AQ234" s="15">
-        <f>290*6</f>
-        <v>1740</v>
+        <f>330*7</f>
+        <v>2310</v>
       </c>
     </row>
     <row r="235" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q235" s="17"/>
       <c r="AB235" s="17"/>
+      <c r="AE235" s="43"/>
       <c r="AF235" s="71">
-        <v>2089</v>
-      </c>
-      <c r="AG235" s="107">
-        <v>45954</v>
-      </c>
-      <c r="AH235" s="52" t="s">
-        <v>294</v>
+        <v>541800</v>
+      </c>
+      <c r="AG235" s="106">
+        <v>45960</v>
+      </c>
+      <c r="AH235" s="52">
+        <v>1000</v>
       </c>
       <c r="AI235" s="52"/>
       <c r="AJ235" s="52" t="s">
         <v>16</v>
       </c>
       <c r="AN235" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AO235">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP235" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AQ235" s="15">
-        <f>320*5</f>
-        <v>1600</v>
+        <f>290*6</f>
+        <v>1740</v>
       </c>
     </row>
     <row r="236" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q236" s="17"/>
+      <c r="AB236" s="17"/>
       <c r="AF236" s="71">
-        <v>540000</v>
-      </c>
-      <c r="AG236" s="107">
-        <v>45951</v>
-      </c>
-      <c r="AH236" s="52">
-        <v>1000</v>
+        <v>2089</v>
+      </c>
+      <c r="AG236" s="106">
+        <v>45954</v>
+      </c>
+      <c r="AH236" s="52" t="s">
+        <v>291</v>
       </c>
       <c r="AI236" s="52"/>
       <c r="AJ236" s="52" t="s">
         <v>16</v>
       </c>
       <c r="AN236" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="AO236">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AP236" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AQ236" s="15">
-        <f>1650*2</f>
-        <v>3300</v>
+        <f>320*5</f>
+        <v>1600</v>
       </c>
     </row>
     <row r="237" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q237" s="17"/>
       <c r="AF237" s="71">
-        <v>99000</v>
-      </c>
-      <c r="AG237" s="107">
-        <v>45950</v>
+        <v>540000</v>
+      </c>
+      <c r="AG237" s="106">
+        <v>45951</v>
       </c>
       <c r="AH237" s="52">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AI237" s="52"/>
       <c r="AJ237" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="AQ237" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="AN237" t="s">
+        <v>410</v>
+      </c>
+      <c r="AO237">
+        <v>2</v>
+      </c>
+      <c r="AP237" t="s">
+        <v>407</v>
+      </c>
+      <c r="AQ237" s="15">
+        <f>1650*2</f>
+        <v>3300</v>
+      </c>
     </row>
     <row r="238" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q238" s="17"/>
       <c r="AF238" s="71">
-        <v>530000</v>
-      </c>
-      <c r="AG238" s="107">
-        <v>45939</v>
+        <v>99000</v>
+      </c>
+      <c r="AG238" s="106">
+        <v>45950</v>
       </c>
       <c r="AH238" s="52">
-        <v>990</v>
-      </c>
-      <c r="AI238" s="79"/>
+        <v>180</v>
+      </c>
+      <c r="AI238" s="52"/>
       <c r="AJ238" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="AP238" t="s">
-        <v>141</v>
-      </c>
-      <c r="AQ238" s="15">
-        <f>SUM(AQ232:AQ236)</f>
-        <v>10900</v>
-      </c>
+      <c r="AQ238" s="15"/>
     </row>
     <row r="239" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q239" s="17"/>
       <c r="AF239" s="71">
-        <v>400000</v>
-      </c>
-      <c r="AG239" s="107">
-        <v>45915</v>
+        <v>530000</v>
+      </c>
+      <c r="AG239" s="106">
+        <v>45939</v>
       </c>
       <c r="AH239" s="52">
-        <v>720</v>
+        <v>990</v>
       </c>
       <c r="AI239" s="79"/>
       <c r="AJ239" s="52" t="s">
         <v>99</v>
       </c>
+      <c r="AP239" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ239" s="15">
+        <f>SUM(AQ233:AQ237)</f>
+        <v>10900</v>
+      </c>
     </row>
     <row r="240" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q240" s="17"/>
       <c r="AF240" s="71">
-        <v>1395</v>
-      </c>
-      <c r="AG240" s="107">
-        <v>45904</v>
-      </c>
-      <c r="AH240" s="52" t="s">
-        <v>229</v>
+        <v>400000</v>
+      </c>
+      <c r="AG240" s="106">
+        <v>45915</v>
+      </c>
+      <c r="AH240" s="52">
+        <v>720</v>
       </c>
       <c r="AI240" s="79"/>
       <c r="AJ240" s="52" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
     </row>
     <row r="241" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Q241" s="17"/>
-      <c r="W241" s="17"/>
-      <c r="AD241" s="17"/>
-      <c r="AE241" s="43"/>
       <c r="AF241" s="71">
-        <v>51300</v>
-      </c>
-      <c r="AG241" s="107">
+        <v>1395</v>
+      </c>
+      <c r="AG241" s="106">
         <v>45904</v>
       </c>
-      <c r="AH241" s="52">
-        <v>90</v>
+      <c r="AH241" s="52" t="s">
+        <v>229</v>
       </c>
       <c r="AI241" s="79"/>
       <c r="AJ241" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="AP241" s="15"/>
-    </row>
-    <row r="242" spans="17:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="242" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Q242" s="17"/>
-      <c r="Z242" t="s">
-        <v>223</v>
-      </c>
+      <c r="W242" s="17"/>
+      <c r="AD242" s="17"/>
+      <c r="AE242" s="43"/>
       <c r="AF242" s="71">
-        <v>307760</v>
-      </c>
-      <c r="AG242" s="107">
-        <v>43313</v>
+        <v>51300</v>
+      </c>
+      <c r="AG242" s="106">
+        <v>45904</v>
       </c>
       <c r="AH242" s="52">
-        <v>540</v>
+        <v>90</v>
       </c>
       <c r="AI242" s="79"/>
       <c r="AJ242" s="52" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="243" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="AP242" s="15"/>
+    </row>
+    <row r="243" spans="17:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="Q243" s="17"/>
-      <c r="W243" s="17"/>
-      <c r="Y243" s="59"/>
-      <c r="Z243" s="60" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA243" s="60"/>
-      <c r="AB243" s="61" t="s">
-        <v>167</v>
-      </c>
-      <c r="AC243" s="59"/>
-      <c r="AD243" s="61"/>
+      <c r="Z243" t="s">
+        <v>223</v>
+      </c>
       <c r="AF243" s="71">
-        <v>4561</v>
-      </c>
-      <c r="AG243" s="107">
-        <v>41487</v>
-      </c>
-      <c r="AH243" s="52" t="s">
-        <v>228</v>
-      </c>
-      <c r="AI243" s="52"/>
+        <v>307760</v>
+      </c>
+      <c r="AG243" s="106">
+        <v>43313</v>
+      </c>
+      <c r="AH243" s="52">
+        <v>540</v>
+      </c>
+      <c r="AI243" s="79"/>
       <c r="AJ243" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="AP243" s="43"/>
-      <c r="AR243" s="43"/>
     </row>
     <row r="244" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Q244" s="17"/>
-      <c r="Y244" s="62"/>
-      <c r="Z244" s="17">
+      <c r="W244" s="17"/>
+      <c r="Y244" s="59"/>
+      <c r="Z244" s="60" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA244" s="60"/>
+      <c r="AB244" s="61" t="s">
+        <v>167</v>
+      </c>
+      <c r="AC244" s="59"/>
+      <c r="AD244" s="61"/>
+      <c r="AF244" s="71">
+        <v>4561</v>
+      </c>
+      <c r="AG244" s="106">
+        <v>41487</v>
+      </c>
+      <c r="AH244" s="52" t="s">
+        <v>228</v>
+      </c>
+      <c r="AI244" s="52"/>
+      <c r="AJ244" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP244" s="43"/>
+      <c r="AR244" s="43"/>
+    </row>
+    <row r="245" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="Q245" s="17"/>
+      <c r="Y245" s="62"/>
+      <c r="Z245" s="17">
         <f>X84-R84</f>
         <v>72</v>
       </c>
-      <c r="AA244" s="17"/>
-      <c r="AB244" s="63">
+      <c r="AA245" s="17"/>
+      <c r="AB245" s="63">
         <v>72</v>
       </c>
-      <c r="AC244" s="86">
+      <c r="AC245" s="86">
         <v>73</v>
       </c>
-      <c r="AD244" s="87">
+      <c r="AD245" s="87">
         <v>73</v>
       </c>
-      <c r="AF244" s="71">
+      <c r="AF245" s="71">
         <v>585970</v>
       </c>
-      <c r="AG244" s="107">
+      <c r="AG245" s="106">
         <v>45873</v>
       </c>
-      <c r="AH244" s="52">
+      <c r="AH245" s="52">
         <v>1000</v>
       </c>
-      <c r="AI244" s="79"/>
-      <c r="AJ244" s="52" t="s">
+      <c r="AI245" s="79"/>
+      <c r="AJ245" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="AP244" s="43"/>
-    </row>
-    <row r="245" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Q245" s="19"/>
-      <c r="Y245" s="62" t="s">
+      <c r="AP245" s="43"/>
+    </row>
+    <row r="246" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="Q246" s="19"/>
+      <c r="Y246" s="62" t="s">
         <v>244</v>
       </c>
-      <c r="Z245">
+      <c r="Z246">
         <v>1496.23</v>
       </c>
-      <c r="AB245" s="64">
+      <c r="AB246" s="64">
         <v>1497.0039999999999</v>
       </c>
-      <c r="AC245" s="62">
+      <c r="AC246" s="62">
         <f>O101</f>
         <v>1002.071</v>
       </c>
-      <c r="AD245" s="64">
+      <c r="AD246" s="64">
         <f>O122</f>
         <v>1992.5709999999999</v>
       </c>
-      <c r="AE245" s="17"/>
-      <c r="AF245" s="71">
-        <v>110000</v>
-      </c>
-      <c r="AG245" s="107">
-        <v>45866</v>
-      </c>
-      <c r="AH245" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI245" s="79"/>
-      <c r="AJ245" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="AP245" s="43"/>
-    </row>
-    <row r="246" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y246" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z246" s="17">
-        <f>Z244*Z245</f>
-        <v>107728.56</v>
-      </c>
-      <c r="AA246" s="17"/>
-      <c r="AB246" s="63">
-        <f>AB244*AB245</f>
-        <v>107784.288</v>
-      </c>
-      <c r="AC246" s="86">
-        <f>AC244*AC245</f>
-        <v>73151.183000000005</v>
-      </c>
-      <c r="AD246" s="87">
-        <f>AD244*AD245</f>
-        <v>145457.68299999999</v>
-      </c>
       <c r="AE246" s="17"/>
       <c r="AF246" s="71">
-        <v>150000</v>
-      </c>
-      <c r="AG246" s="107">
-        <v>45856</v>
-      </c>
-      <c r="AH246" s="52">
-        <v>270</v>
+        <v>110000</v>
+      </c>
+      <c r="AG246" s="106">
+        <v>45866</v>
+      </c>
+      <c r="AH246" s="52" t="s">
+        <v>208</v>
       </c>
       <c r="AI246" s="79"/>
       <c r="AJ246" s="52" t="s">
         <v>99</v>
       </c>
+      <c r="AP246" s="43"/>
     </row>
     <row r="247" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y247" s="62" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z247">
-        <v>0.36</v>
-      </c>
-      <c r="AB247" s="64">
-        <v>0.36</v>
-      </c>
-      <c r="AC247" s="62">
-        <v>0.36</v>
-      </c>
-      <c r="AD247" s="64">
-        <v>0.36</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="Z247" s="17">
+        <f>Z245*Z246</f>
+        <v>107728.56</v>
+      </c>
+      <c r="AA247" s="17"/>
+      <c r="AB247" s="63">
+        <f>AB245*AB246</f>
+        <v>107784.288</v>
+      </c>
+      <c r="AC247" s="86">
+        <f>AC245*AC246</f>
+        <v>73151.183000000005</v>
+      </c>
+      <c r="AD247" s="87">
+        <f>AD245*AD246</f>
+        <v>145457.68299999999</v>
+      </c>
+      <c r="AE247" s="17"/>
       <c r="AF247" s="71">
         <v>150000</v>
       </c>
-      <c r="AG247" s="107">
-        <v>45854</v>
+      <c r="AG247" s="106">
+        <v>45856</v>
       </c>
       <c r="AH247" s="52">
         <v>270</v>
@@ -19972,52 +20477,63 @@
     </row>
     <row r="248" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y248" s="62" t="s">
-        <v>166</v>
-      </c>
-      <c r="Z248" s="83">
-        <f>Z246*Z247</f>
-        <v>38782.281599999995</v>
-      </c>
-      <c r="AA248" s="83"/>
-      <c r="AB248" s="84">
-        <f>AB246*AB247</f>
-        <v>38802.343679999998</v>
-      </c>
-      <c r="AC248" s="88">
-        <f>AC247*AC246</f>
-        <v>26334.425879999999</v>
-      </c>
-      <c r="AD248" s="89">
-        <f>AD247*AD246</f>
-        <v>52364.765879999992</v>
+        <v>280</v>
+      </c>
+      <c r="Z248">
+        <v>0.36</v>
+      </c>
+      <c r="AB248" s="64">
+        <v>0.36</v>
+      </c>
+      <c r="AC248" s="62">
+        <v>0.36</v>
+      </c>
+      <c r="AD248" s="64">
+        <v>0.36</v>
       </c>
       <c r="AF248" s="71">
-        <v>1665</v>
-      </c>
-      <c r="AG248" s="107">
-        <v>45832</v>
-      </c>
-      <c r="AH248" s="52" t="s">
-        <v>195</v>
+        <v>150000</v>
+      </c>
+      <c r="AG248" s="106">
+        <v>45854</v>
+      </c>
+      <c r="AH248" s="52">
+        <v>270</v>
       </c>
       <c r="AI248" s="79"/>
       <c r="AJ248" s="52" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
     </row>
     <row r="249" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y249" s="62"/>
-      <c r="AB249" s="64"/>
-      <c r="AC249" s="62"/>
-      <c r="AD249" s="64"/>
+      <c r="Y249" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z249" s="83">
+        <f>Z247*Z248</f>
+        <v>38782.281599999995</v>
+      </c>
+      <c r="AA249" s="83"/>
+      <c r="AB249" s="84">
+        <f>AB247*AB248</f>
+        <v>38802.343679999998</v>
+      </c>
+      <c r="AC249" s="88">
+        <f>AC248*AC247</f>
+        <v>26334.425879999999</v>
+      </c>
+      <c r="AD249" s="89">
+        <f>AD248*AD247</f>
+        <v>52364.765879999992</v>
+      </c>
       <c r="AF249" s="71">
-        <v>324000</v>
-      </c>
-      <c r="AG249" s="107">
-        <v>45831</v>
-      </c>
-      <c r="AH249" s="52">
-        <v>500</v>
+        <v>1665</v>
+      </c>
+      <c r="AG249" s="106">
+        <v>45832</v>
+      </c>
+      <c r="AH249" s="52" t="s">
+        <v>195</v>
       </c>
       <c r="AI249" s="79"/>
       <c r="AJ249" s="52" t="s">
@@ -20025,17 +20541,15 @@
       </c>
     </row>
     <row r="250" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y250" s="62" t="s">
-        <v>274</v>
-      </c>
+      <c r="Y250" s="62"/>
       <c r="AB250" s="64"/>
       <c r="AC250" s="62"/>
       <c r="AD250" s="64"/>
       <c r="AF250" s="71">
         <v>324000</v>
       </c>
-      <c r="AG250" s="107">
-        <v>45818</v>
+      <c r="AG250" s="106">
+        <v>45831</v>
       </c>
       <c r="AH250" s="52">
         <v>500</v>
@@ -20046,133 +20560,123 @@
       </c>
     </row>
     <row r="251" spans="17:44" x14ac:dyDescent="0.2">
-      <c r="Y251" s="62"/>
-      <c r="Z251" s="17"/>
-      <c r="AA251" s="17"/>
+      <c r="Y251" s="62" t="s">
+        <v>271</v>
+      </c>
       <c r="AB251" s="64"/>
       <c r="AC251" s="62"/>
       <c r="AD251" s="64"/>
       <c r="AF251" s="71">
-        <v>31780</v>
-      </c>
-      <c r="AG251" s="107">
-        <v>45810</v>
-      </c>
-      <c r="AH251" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="AI251" s="52"/>
+        <v>324000</v>
+      </c>
+      <c r="AG251" s="106">
+        <v>45818</v>
+      </c>
+      <c r="AH251" s="52">
+        <v>500</v>
+      </c>
+      <c r="AI251" s="79"/>
       <c r="AJ251" s="52" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
     </row>
     <row r="252" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y252" s="62"/>
-      <c r="Z252" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA252" s="85"/>
-      <c r="AB252" s="84">
-        <f>AB248+Z248</f>
-        <v>77584.625279999993</v>
-      </c>
-      <c r="AC252" s="62" t="s">
-        <v>308</v>
-      </c>
-      <c r="AD252" s="89">
-        <f>AC248+AD248</f>
-        <v>78699.191759999987</v>
-      </c>
+      <c r="Z252" s="17"/>
+      <c r="AA252" s="17"/>
+      <c r="AB252" s="64"/>
+      <c r="AC252" s="62"/>
+      <c r="AD252" s="64"/>
       <c r="AF252" s="71">
-        <v>324000</v>
-      </c>
-      <c r="AG252" s="107">
-        <v>45807</v>
-      </c>
-      <c r="AH252" s="52">
-        <v>500</v>
+        <v>31780</v>
+      </c>
+      <c r="AG252" s="106">
+        <v>45810</v>
+      </c>
+      <c r="AH252" s="52" t="s">
+        <v>182</v>
       </c>
       <c r="AI252" s="52"/>
       <c r="AJ252" s="52" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
     </row>
     <row r="253" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y253" s="62"/>
-      <c r="AB253" s="64"/>
+      <c r="Z253" s="85" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA253" s="85"/>
+      <c r="AB253" s="84">
+        <f>AB249+Z249</f>
+        <v>77584.625279999993</v>
+      </c>
       <c r="AC253" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD253" s="63">
-        <f>AB263</f>
-        <v>11456.374720000007</v>
+        <v>305</v>
+      </c>
+      <c r="AD253" s="89">
+        <f>AC249+AD249</f>
+        <v>78699.191759999987</v>
       </c>
       <c r="AF253" s="71">
-        <v>325000</v>
-      </c>
-      <c r="AG253" s="107">
-        <v>45806</v>
+        <v>324000</v>
+      </c>
+      <c r="AG253" s="106">
+        <v>45807</v>
       </c>
       <c r="AH253" s="52">
         <v>500</v>
       </c>
       <c r="AI253" s="52"/>
       <c r="AJ253" s="52" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
     </row>
     <row r="254" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y254" s="62"/>
-      <c r="Z254" t="s">
-        <v>275</v>
-      </c>
-      <c r="AB254" s="63">
-        <v>15300</v>
-      </c>
-      <c r="AC254" s="62"/>
-      <c r="AD254" s="64"/>
+      <c r="AB254" s="64"/>
+      <c r="AC254" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD254" s="63">
+        <f>AB264</f>
+        <v>11456.374720000007</v>
+      </c>
       <c r="AF254" s="71">
-        <v>648000</v>
-      </c>
-      <c r="AG254" s="107">
-        <v>45786</v>
+        <v>325000</v>
+      </c>
+      <c r="AG254" s="106">
+        <v>45806</v>
       </c>
       <c r="AH254" s="52">
-        <v>1000</v>
-      </c>
-      <c r="AI254" s="52" t="s">
-        <v>129</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="AI254" s="52"/>
       <c r="AJ254" s="52" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
     </row>
     <row r="255" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y255" s="62"/>
       <c r="Z255" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB255" s="63">
-        <v>1200</v>
-      </c>
-      <c r="AC255" s="62" t="s">
-        <v>309</v>
-      </c>
-      <c r="AD255" s="89">
-        <f>AD252-AD253</f>
-        <v>67242.81703999998</v>
-      </c>
+        <v>15300</v>
+      </c>
+      <c r="AC255" s="62"/>
+      <c r="AD255" s="64"/>
       <c r="AF255" s="71">
-        <v>514200</v>
-      </c>
-      <c r="AG255" s="107">
-        <v>45772</v>
+        <v>648000</v>
+      </c>
+      <c r="AG255" s="106">
+        <v>45786</v>
       </c>
       <c r="AH255" s="52">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="AI255" s="52" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AJ255" s="52" t="s">
         <v>16</v>
@@ -20181,77 +20685,82 @@
     <row r="256" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y256" s="62"/>
       <c r="Z256" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="AB256" s="63">
-        <v>12900</v>
+        <v>1200</v>
       </c>
       <c r="AC256" s="62" t="s">
-        <v>342</v>
+        <v>306</v>
       </c>
       <c r="AD256" s="89">
-        <v>50000</v>
+        <f>AD253-AD254</f>
+        <v>67242.81703999998</v>
       </c>
       <c r="AF256" s="71">
-        <v>325000</v>
-      </c>
-      <c r="AG256" s="107">
-        <v>45762</v>
+        <v>514200</v>
+      </c>
+      <c r="AG256" s="106">
+        <v>45772</v>
       </c>
       <c r="AH256" s="52">
-        <v>500</v>
-      </c>
-      <c r="AI256" s="52"/>
+        <v>800</v>
+      </c>
+      <c r="AI256" s="52" t="s">
+        <v>127</v>
+      </c>
       <c r="AJ256" s="52" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
     </row>
     <row r="257" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y257" s="62"/>
       <c r="Z257" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AB257" s="63">
-        <v>7000</v>
+        <v>12900</v>
       </c>
       <c r="AC257" s="62" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AD257" s="89">
-        <f>AD255-AD256</f>
-        <v>17242.81703999998</v>
+        <v>50000</v>
       </c>
       <c r="AF257" s="71">
-        <v>632000</v>
-      </c>
-      <c r="AG257" s="107">
-        <v>45749</v>
+        <v>325000</v>
+      </c>
+      <c r="AG257" s="106">
+        <v>45762</v>
       </c>
       <c r="AH257" s="52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI257" s="52"/>
       <c r="AJ257" s="52" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
     </row>
     <row r="258" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y258" s="62"/>
       <c r="Z258" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AB258" s="63">
-        <v>5000</v>
-      </c>
-      <c r="AC258" s="62"/>
-      <c r="AD258" s="64" t="s">
-        <v>194</v>
+        <v>7000</v>
+      </c>
+      <c r="AC258" s="62" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD258" s="89">
+        <f>AD256-AD257</f>
+        <v>17242.81703999998</v>
       </c>
       <c r="AF258" s="71">
         <v>632000</v>
       </c>
-      <c r="AG258" s="107">
-        <v>45736</v>
+      <c r="AG258" s="106">
+        <v>45749</v>
       </c>
       <c r="AH258" s="52">
         <v>1000</v>
@@ -20264,18 +20773,20 @@
     <row r="259" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y259" s="62"/>
       <c r="Z259" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AB259" s="63">
-        <v>10400</v>
+        <v>5000</v>
       </c>
       <c r="AC259" s="62"/>
-      <c r="AD259" s="64"/>
+      <c r="AD259" s="64" t="s">
+        <v>194</v>
+      </c>
       <c r="AF259" s="71">
         <v>632000</v>
       </c>
-      <c r="AG259" s="107">
-        <v>45721</v>
+      <c r="AG259" s="106">
+        <v>45736</v>
       </c>
       <c r="AH259" s="52">
         <v>1000</v>
@@ -20288,20 +20799,20 @@
     <row r="260" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y260" s="62"/>
       <c r="Z260" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AB260" s="63">
-        <v>5441</v>
+        <v>10400</v>
       </c>
       <c r="AC260" s="62"/>
       <c r="AD260" s="64"/>
       <c r="AF260" s="71">
         <v>632000</v>
       </c>
-      <c r="AG260" s="108">
-        <v>45706</v>
-      </c>
-      <c r="AH260" s="109">
+      <c r="AG260" s="106">
+        <v>45721</v>
+      </c>
+      <c r="AH260" s="52">
         <v>1000</v>
       </c>
       <c r="AI260" s="52"/>
@@ -20311,23 +20822,23 @@
     </row>
     <row r="261" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y261" s="62"/>
-      <c r="Z261" s="85" t="s">
-        <v>307</v>
-      </c>
-      <c r="AA261" s="85"/>
-      <c r="AB261" s="84">
-        <f>AB252-AB254+AB255-AB256-AB257+AB258+AB259-AB260</f>
-        <v>53543.625279999993</v>
+      <c r="Z261" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB261" s="63">
+        <v>5441</v>
       </c>
       <c r="AC261" s="62"/>
       <c r="AD261" s="64"/>
       <c r="AF261" s="71">
-        <v>21610</v>
-      </c>
-      <c r="AG261" s="108">
-        <v>45692</v>
-      </c>
-      <c r="AH261" s="52"/>
+        <v>632000</v>
+      </c>
+      <c r="AG261" s="107">
+        <v>45706</v>
+      </c>
+      <c r="AH261" s="108">
+        <v>1000</v>
+      </c>
       <c r="AI261" s="52"/>
       <c r="AJ261" s="52" t="s">
         <v>16</v>
@@ -20336,23 +20847,22 @@
     <row r="262" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y262" s="62"/>
       <c r="Z262" s="85" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="AA262" s="85"/>
       <c r="AB262" s="84">
-        <v>65000</v>
+        <f>AB253-AB255+AB256-AB257-AB258+AB259+AB260-AB261</f>
+        <v>53543.625279999993</v>
       </c>
       <c r="AC262" s="62"/>
       <c r="AD262" s="64"/>
       <c r="AF262" s="71">
-        <v>200000</v>
-      </c>
-      <c r="AG262" s="108">
-        <v>45687</v>
-      </c>
-      <c r="AH262" s="109">
-        <v>300</v>
-      </c>
+        <v>21610</v>
+      </c>
+      <c r="AG262" s="107">
+        <v>45692</v>
+      </c>
+      <c r="AH262" s="52"/>
       <c r="AI262" s="52"/>
       <c r="AJ262" s="52" t="s">
         <v>16</v>
@@ -20360,65 +20870,70 @@
     </row>
     <row r="263" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y263" s="62"/>
-      <c r="Z263" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB263" s="91">
-        <f>AB262-AB261</f>
-        <v>11456.374720000007</v>
+      <c r="Z263" s="85" t="s">
+        <v>275</v>
+      </c>
+      <c r="AA263" s="85"/>
+      <c r="AB263" s="84">
+        <v>65000</v>
       </c>
       <c r="AC263" s="62"/>
       <c r="AD263" s="64"/>
       <c r="AF263" s="71">
-        <v>50000</v>
-      </c>
-      <c r="AG263" s="108">
-        <v>45680</v>
-      </c>
-      <c r="AH263" s="101"/>
+        <v>200000</v>
+      </c>
+      <c r="AG263" s="107">
+        <v>45687</v>
+      </c>
+      <c r="AH263" s="108">
+        <v>300</v>
+      </c>
       <c r="AI263" s="52"/>
       <c r="AJ263" s="52" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="264" spans="18:36" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="R264" s="68"/>
-      <c r="S264" s="69"/>
-      <c r="T264" s="68"/>
-      <c r="U264" s="68"/>
-      <c r="Y264" s="65"/>
-      <c r="Z264" s="67"/>
-      <c r="AA264" s="67"/>
-      <c r="AB264" s="66"/>
-      <c r="AC264" s="65"/>
-      <c r="AD264" s="90"/>
+    <row r="264" spans="18:36" x14ac:dyDescent="0.2">
+      <c r="Y264" s="62"/>
+      <c r="Z264" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB264" s="91">
+        <f>AB263-AB262</f>
+        <v>11456.374720000007</v>
+      </c>
+      <c r="AC264" s="62"/>
+      <c r="AD264" s="64"/>
       <c r="AF264" s="71">
-        <v>300000</v>
-      </c>
-      <c r="AG264" s="108">
-        <v>45674</v>
-      </c>
-      <c r="AH264" s="110">
-        <v>500</v>
-      </c>
+        <v>50000</v>
+      </c>
+      <c r="AG264" s="107">
+        <v>45680</v>
+      </c>
+      <c r="AH264" s="100"/>
       <c r="AI264" s="52"/>
       <c r="AJ264" s="52" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="265" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="R265" s="70"/>
-      <c r="S265" s="70"/>
-      <c r="T265" s="70"/>
-      <c r="U265" s="70"/>
-      <c r="AB265" s="17"/>
+    <row r="265" spans="18:36" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="R265" s="68"/>
+      <c r="S265" s="69"/>
+      <c r="T265" s="68"/>
+      <c r="U265" s="68"/>
+      <c r="Y265" s="65"/>
+      <c r="Z265" s="67"/>
+      <c r="AA265" s="67"/>
+      <c r="AB265" s="66"/>
+      <c r="AC265" s="65"/>
+      <c r="AD265" s="90"/>
       <c r="AF265" s="71">
-        <v>332000</v>
-      </c>
-      <c r="AG265" s="108">
-        <v>45664</v>
-      </c>
-      <c r="AH265" s="110">
+        <v>300000</v>
+      </c>
+      <c r="AG265" s="107">
+        <v>45674</v>
+      </c>
+      <c r="AH265" s="109">
         <v>500</v>
       </c>
       <c r="AI265" s="52"/>
@@ -20431,13 +20946,14 @@
       <c r="S266" s="70"/>
       <c r="T266" s="70"/>
       <c r="U266" s="70"/>
+      <c r="AB266" s="17"/>
       <c r="AF266" s="71">
         <v>332000</v>
       </c>
-      <c r="AG266" s="108">
-        <v>45656</v>
-      </c>
-      <c r="AH266" s="110">
+      <c r="AG266" s="107">
+        <v>45664</v>
+      </c>
+      <c r="AH266" s="109">
         <v>500</v>
       </c>
       <c r="AI266" s="52"/>
@@ -20446,28 +20962,17 @@
       </c>
     </row>
     <row r="267" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="R267" s="43"/>
-      <c r="T267" s="43"/>
-      <c r="U267" s="43"/>
-      <c r="Y267" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z267" s="17">
-        <f>SUM(AC87)</f>
-        <v>1107210.2</v>
-      </c>
-      <c r="AA267" s="17"/>
-      <c r="AB267" s="17">
-        <f>AC88+AC89+AC90</f>
-        <v>1107782.96</v>
-      </c>
+      <c r="R267" s="70"/>
+      <c r="S267" s="70"/>
+      <c r="T267" s="70"/>
+      <c r="U267" s="70"/>
       <c r="AF267" s="71">
-        <v>339500</v>
-      </c>
-      <c r="AG267" s="108">
-        <v>45649</v>
-      </c>
-      <c r="AH267" s="110">
+        <v>332000</v>
+      </c>
+      <c r="AG267" s="107">
+        <v>45656</v>
+      </c>
+      <c r="AH267" s="109">
         <v>500</v>
       </c>
       <c r="AI267" s="52"/>
@@ -20476,26 +20981,29 @@
       </c>
     </row>
     <row r="268" spans="18:36" x14ac:dyDescent="0.2">
+      <c r="R268" s="43"/>
+      <c r="T268" s="43"/>
+      <c r="U268" s="43"/>
       <c r="Y268" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z268" s="15">
-        <f>72*O87</f>
-        <v>107728.56</v>
-      </c>
-      <c r="AA268" s="15"/>
+        <v>209</v>
+      </c>
+      <c r="Z268" s="17">
+        <f>SUM(AC87)</f>
+        <v>1107210.2</v>
+      </c>
+      <c r="AA268" s="17"/>
       <c r="AB268" s="17">
-        <f>72*O91</f>
-        <v>107784.288</v>
+        <f>AC88+AC89+AC90</f>
+        <v>1107782.96</v>
       </c>
       <c r="AF268" s="71">
-        <v>679000</v>
+        <v>339500</v>
       </c>
       <c r="AG268" s="107">
-        <v>45643</v>
-      </c>
-      <c r="AH268" s="52">
-        <v>1000</v>
+        <v>45649</v>
+      </c>
+      <c r="AH268" s="109">
+        <v>500</v>
       </c>
       <c r="AI268" s="52"/>
       <c r="AJ268" s="52" t="s">
@@ -20504,1084 +21012,1110 @@
     </row>
     <row r="269" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y269" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="Z269" s="43">
-        <f>Z268*0.25</f>
-        <v>26932.14</v>
-      </c>
-      <c r="AA269" s="43"/>
+        <v>211</v>
+      </c>
+      <c r="Z269" s="15">
+        <f>72*O87</f>
+        <v>107728.56</v>
+      </c>
+      <c r="AA269" s="15"/>
       <c r="AB269" s="17">
-        <f>AB268*0.25</f>
-        <v>26946.072</v>
+        <f>72*O91</f>
+        <v>107784.288</v>
+      </c>
+      <c r="AF269" s="71">
+        <v>679000</v>
+      </c>
+      <c r="AG269" s="106">
+        <v>45643</v>
+      </c>
+      <c r="AH269" s="52">
+        <v>1000</v>
+      </c>
+      <c r="AI269" s="52"/>
+      <c r="AJ269" s="52" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="270" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y270" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="Z270">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="AB270" s="82">
-        <v>18.309999999999999</v>
+        <v>210</v>
+      </c>
+      <c r="Z270" s="43">
+        <f>Z269*0.25</f>
+        <v>26932.14</v>
+      </c>
+      <c r="AA270" s="43"/>
+      <c r="AB270" s="17">
+        <f>AB269*0.25</f>
+        <v>26946.072</v>
       </c>
     </row>
     <row r="271" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y271" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z271" s="43">
-        <f>Z269*Z270</f>
-        <v>509017.44599999994</v>
-      </c>
-      <c r="AA271" s="43"/>
-      <c r="AB271" s="17">
-        <v>491765.81</v>
-      </c>
-      <c r="AD271" s="116" t="s">
-        <v>237</v>
-      </c>
-      <c r="AE271" s="116"/>
-      <c r="AF271" s="116"/>
-      <c r="AG271" s="116"/>
-      <c r="AH271" s="116"/>
+        <v>212</v>
+      </c>
+      <c r="Z271">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="AB271" s="82">
+        <v>18.309999999999999</v>
+      </c>
     </row>
     <row r="272" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y272" s="41" t="s">
-        <v>213</v>
+        <v>80</v>
       </c>
       <c r="Z272" s="43">
-        <f>Z271*0.05</f>
-        <v>25450.872299999999</v>
+        <f>Z270*Z271</f>
+        <v>509017.44599999994</v>
       </c>
       <c r="AA272" s="43"/>
       <c r="AB272" s="17">
-        <f>AB271*0.05</f>
-        <v>24588.290500000003</v>
-      </c>
-      <c r="AD272" s="52"/>
-      <c r="AE272" s="76" t="s">
-        <v>236</v>
-      </c>
-      <c r="AF272" s="76" t="s">
-        <v>234</v>
-      </c>
-      <c r="AG272" s="73"/>
-      <c r="AH272" s="73" t="s">
-        <v>235</v>
-      </c>
+        <v>491765.81</v>
+      </c>
+      <c r="AD272" s="115" t="s">
+        <v>237</v>
+      </c>
+      <c r="AE272" s="115"/>
+      <c r="AF272" s="115"/>
+      <c r="AG272" s="115"/>
+      <c r="AH272" s="115"/>
     </row>
     <row r="273" spans="24:40" x14ac:dyDescent="0.2">
       <c r="Y273" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z273" s="43">
+        <f>Z272*0.05</f>
+        <v>25450.872299999999</v>
+      </c>
+      <c r="AA273" s="43"/>
+      <c r="AB273" s="17">
+        <f>AB272*0.05</f>
+        <v>24588.290500000003</v>
+      </c>
+      <c r="AD273" s="52"/>
+      <c r="AE273" s="76" t="s">
+        <v>236</v>
+      </c>
+      <c r="AF273" s="76" t="s">
+        <v>234</v>
+      </c>
+      <c r="AG273" s="73"/>
+      <c r="AH273" s="73" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="274" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y274" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="Z273" s="97">
+      <c r="Z274" s="96">
         <f>O87</f>
         <v>1496.23</v>
       </c>
-      <c r="AA273" s="97"/>
-      <c r="AB273" s="97">
+      <c r="AA274" s="96"/>
+      <c r="AB274" s="96">
         <f>O91</f>
         <v>1497.0039999999999</v>
       </c>
-      <c r="AC273" s="98"/>
-      <c r="AD273" s="52" t="s">
+      <c r="AC274" s="97"/>
+      <c r="AD274" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="AE273" s="53">
+      <c r="AE274" s="53">
         <f>SUM(W66,W76,W87,W91,W101,W122)</f>
         <v>8571607.8409999982</v>
       </c>
-      <c r="AF273" s="77">
-        <f>SUMIF(AJ223:AJ268,"Arauco",AF223:AF268)</f>
+      <c r="AF274" s="77">
+        <f>SUMIF(AJ224:AJ269,"Arauco",AF224:AF269)</f>
         <v>8589229</v>
       </c>
-      <c r="AG273" s="52" t="s">
+      <c r="AG274" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="AH273" s="78">
-        <f>AE273-AF273</f>
+      <c r="AH274" s="78">
+        <f>AE274-AF274</f>
         <v>-17621.159000001848</v>
       </c>
     </row>
-    <row r="274" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="X274" s="98"/>
-      <c r="Y274" s="41" t="s">
+    <row r="275" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="X275" s="97"/>
+      <c r="Y275" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="Z274" s="94">
-        <f>Z271-Z272</f>
+      <c r="Z275" s="94">
+        <f>Z272-Z273</f>
         <v>483566.57369999995</v>
       </c>
-      <c r="AA274" s="94"/>
-      <c r="AB274" s="93">
-        <f>AB271-AB272</f>
+      <c r="AA275" s="94"/>
+      <c r="AB275" s="93">
+        <f>AB272-AB273</f>
         <v>467177.51949999999</v>
       </c>
-      <c r="AD274" s="52" t="s">
+      <c r="AD275" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="AE274" s="53">
+      <c r="AE275" s="53">
         <f>SUM(W83,W98,W109,W116,W118,W131,W143,W146,W153,W161,W169,W176,W183,W193,W206)</f>
         <v>5001187.9850000003</v>
       </c>
-      <c r="AF274" s="77">
-        <f>SUMIF(AJ222:AJ268,"CPP",AF222:AF268)</f>
+      <c r="AF275" s="77">
+        <f>SUMIF(AJ223:AJ269,"CPP",AF223:AF269)</f>
         <v>4920001</v>
       </c>
-      <c r="AG274" s="52" t="s">
+      <c r="AG275" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="AH274" s="78">
-        <f>AE274-AF274</f>
+      <c r="AH275" s="78">
+        <f>AE275-AF275</f>
         <v>81186.985000000335</v>
       </c>
     </row>
-    <row r="275" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y275" s="41"/>
-      <c r="Z275" t="s">
+    <row r="276" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y276" s="41"/>
+      <c r="Z276" t="s">
         <v>136</v>
       </c>
-      <c r="AB275" t="s">
+      <c r="AB276" t="s">
         <v>136</v>
       </c>
-      <c r="AD275" s="52" t="s">
+      <c r="AD276" s="52" t="s">
         <v>141</v>
       </c>
-      <c r="AE275" s="53">
-        <f>SUM(AE273:AE274)</f>
+      <c r="AE276" s="53">
+        <f>SUM(AE274:AE275)</f>
         <v>13572795.825999998</v>
       </c>
-      <c r="AF275" s="77">
-        <f>SUM(AF228:AF268)</f>
+      <c r="AF276" s="77">
+        <f>SUM(AF229:AF269)</f>
         <v>12180230</v>
       </c>
-      <c r="AG275" s="52" t="s">
+      <c r="AG276" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="AH275" s="78">
-        <f>SUM(AH273:AH274)</f>
+      <c r="AH276" s="78">
+        <f>SUM(AH274:AH275)</f>
         <v>63565.825999998488</v>
       </c>
     </row>
-    <row r="276" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y276" s="41" t="s">
+    <row r="277" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y277" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="Z276" s="17">
+      <c r="Z277" s="17">
         <f>AC101</f>
         <v>711470.40999999992</v>
       </c>
-      <c r="AA276" s="17"/>
-      <c r="AB276" s="17">
+      <c r="AA277" s="17"/>
+      <c r="AB277" s="17">
         <f>AC122</f>
         <v>1235394.02</v>
       </c>
     </row>
-    <row r="277" spans="24:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y277" s="41" t="s">
+    <row r="278" spans="24:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y278" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="Z277" s="17">
+      <c r="Z278" s="17">
         <f>73*O101</f>
         <v>73151.183000000005</v>
       </c>
-      <c r="AA277" s="17"/>
-      <c r="AB277" s="15">
+      <c r="AA278" s="17"/>
+      <c r="AB278" s="15">
         <f>73*O122</f>
         <v>145457.68299999999</v>
       </c>
-      <c r="AF277" s="117" t="s">
+      <c r="AF278" s="116" t="s">
         <v>142</v>
       </c>
-      <c r="AG277" s="117"/>
-      <c r="AI277" s="119" t="s">
+      <c r="AG278" s="116"/>
+      <c r="AI278" s="118" t="s">
         <v>164</v>
       </c>
-      <c r="AJ277" s="119"/>
-      <c r="AK277" s="119"/>
-      <c r="AL277" s="36"/>
-      <c r="AM277" s="117" t="s">
+      <c r="AJ278" s="118"/>
+      <c r="AK278" s="118"/>
+      <c r="AL278" s="36"/>
+      <c r="AM278" s="116" t="s">
         <v>146</v>
       </c>
-      <c r="AN277" s="117"/>
-    </row>
-    <row r="278" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y278" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="Z278" s="17">
-        <f>Z277*0.25</f>
-        <v>18287.795750000001</v>
-      </c>
-      <c r="AA278" s="17"/>
-      <c r="AB278" s="43">
-        <f>AB277*0.25</f>
-        <v>36364.420749999997</v>
-      </c>
-      <c r="AF278" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI278" s="49"/>
-      <c r="AJ278" s="49"/>
-      <c r="AK278" s="49"/>
-      <c r="AM278" s="41" t="s">
-        <v>143</v>
-      </c>
+      <c r="AN278" s="116"/>
     </row>
     <row r="279" spans="24:40" x14ac:dyDescent="0.2">
       <c r="Y279" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="Z279">
-        <v>18.2</v>
-      </c>
-      <c r="AB279" s="82">
-        <v>17.7</v>
-      </c>
-      <c r="AF279" t="s">
-        <v>137</v>
-      </c>
-      <c r="AG279">
-        <v>3300</v>
-      </c>
-      <c r="AI279" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="AJ279" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK279" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM279" t="s">
-        <v>137</v>
-      </c>
-      <c r="AN279">
-        <v>3300</v>
+        <v>210</v>
+      </c>
+      <c r="Z279" s="17">
+        <f>Z278*0.25</f>
+        <v>18287.795750000001</v>
+      </c>
+      <c r="AA279" s="17"/>
+      <c r="AB279" s="43">
+        <f>AB278*0.25</f>
+        <v>36364.420749999997</v>
+      </c>
+      <c r="AF279" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI279" s="49"/>
+      <c r="AJ279" s="49"/>
+      <c r="AK279" s="49"/>
+      <c r="AM279" s="41" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="280" spans="24:40" x14ac:dyDescent="0.2">
       <c r="Y280" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z280">
+        <v>18.2</v>
+      </c>
+      <c r="AB280" s="82">
+        <v>17.7</v>
+      </c>
+      <c r="AF280" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG280">
+        <v>3300</v>
+      </c>
+      <c r="AI280" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="AJ280" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="AK280" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM280" t="s">
+        <v>137</v>
+      </c>
+      <c r="AN280">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="281" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y281" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="Z280" s="17">
-        <f>Z278*Z279</f>
+      <c r="Z281" s="17">
+        <f>Z279*Z280</f>
         <v>332837.88264999999</v>
       </c>
-      <c r="AA280" s="17"/>
-      <c r="AB280" s="43">
-        <f>AB278*AB279</f>
+      <c r="AA281" s="17"/>
+      <c r="AB281" s="43">
+        <f>AB279*AB280</f>
         <v>643650.24727499997</v>
       </c>
-      <c r="AF280" t="s">
+      <c r="AF281" t="s">
         <v>138</v>
       </c>
-      <c r="AG280">
+      <c r="AG281">
         <f>O66</f>
         <v>3370.0310000000004</v>
       </c>
-      <c r="AI280" s="49">
-        <v>15</v>
-      </c>
-      <c r="AJ280" s="49">
-        <f>AG62</f>
-        <v>0</v>
-      </c>
-      <c r="AK280" s="50">
-        <f>AI280*AJ280</f>
-        <v>0</v>
-      </c>
-      <c r="AM280" t="s">
-        <v>138</v>
-      </c>
-      <c r="AN280">
-        <v>3370.0309999999999</v>
-      </c>
-    </row>
-    <row r="281" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y281" s="92" t="s">
-        <v>213</v>
-      </c>
-      <c r="Z281" s="17">
-        <f>Z280*0.05</f>
-        <v>16641.894132500001</v>
-      </c>
-      <c r="AA281" s="17"/>
-      <c r="AB281" s="43">
-        <f>AB280*0.05</f>
-        <v>32182.51236375</v>
-      </c>
-      <c r="AF281" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG281">
-        <f>AG280-AG279</f>
-        <v>70.031000000000404</v>
-      </c>
       <c r="AI281" s="49">
         <v>15</v>
       </c>
       <c r="AJ281" s="49">
+        <f>AG62</f>
+        <v>0</v>
+      </c>
+      <c r="AK281" s="50">
+        <f>AI281*AJ281</f>
+        <v>0</v>
+      </c>
+      <c r="AM281" t="s">
+        <v>138</v>
+      </c>
+      <c r="AN281">
+        <v>3370.0309999999999</v>
+      </c>
+    </row>
+    <row r="282" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y282" s="92" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z282" s="17">
+        <f>Z281*0.05</f>
+        <v>16641.894132500001</v>
+      </c>
+      <c r="AA282" s="17"/>
+      <c r="AB282" s="43">
+        <f>AB281*0.05</f>
+        <v>32182.51236375</v>
+      </c>
+      <c r="AF282" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG282">
+        <f>AG281-AG280</f>
+        <v>70.031000000000404</v>
+      </c>
+      <c r="AI282" s="49">
+        <v>15</v>
+      </c>
+      <c r="AJ282" s="49">
         <f>AG63</f>
         <v>0</v>
       </c>
-      <c r="AK281" s="50">
-        <f t="shared" ref="AK281:AK283" si="142">AI281*AJ281</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="X282" s="98"/>
-      <c r="Y282" s="41" t="s">
+      <c r="AK282" s="50">
+        <f t="shared" ref="AK282:AK284" si="146">AI282*AJ282</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="X283" s="97"/>
+      <c r="Y283" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="Z282" s="97">
+      <c r="Z283" s="96">
         <f>O101</f>
         <v>1002.071</v>
       </c>
-      <c r="AA282" s="97"/>
-      <c r="AB282" s="97">
+      <c r="AA283" s="96"/>
+      <c r="AB283" s="96">
         <f>O122</f>
         <v>1992.5709999999999</v>
       </c>
-      <c r="AF282" t="s">
+      <c r="AF283" t="s">
         <v>140</v>
       </c>
-      <c r="AG282" s="15">
+      <c r="AG283" s="15">
         <v>755</v>
-      </c>
-      <c r="AI282" s="49">
-        <v>15</v>
-      </c>
-      <c r="AJ282" s="49">
-        <f>AG64</f>
-        <v>0</v>
-      </c>
-      <c r="AK282" s="50">
-        <f t="shared" si="142"/>
-        <v>0</v>
-      </c>
-      <c r="AM282" t="s">
-        <v>136</v>
-      </c>
-      <c r="AN282" s="43">
-        <f>SUM(AF261:AF268)</f>
-        <v>2254110</v>
-      </c>
-    </row>
-    <row r="283" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y283" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z283" s="93">
-        <f>Z280-Z281</f>
-        <v>316195.98851749999</v>
-      </c>
-      <c r="AA283" s="93"/>
-      <c r="AB283" s="93">
-        <f>AB280-AB281</f>
-        <v>611467.73491124995</v>
-      </c>
-      <c r="AF283" t="s">
-        <v>159</v>
-      </c>
-      <c r="AG283" s="44">
-        <f>AG281*AG282</f>
-        <v>52873.405000000304</v>
       </c>
       <c r="AI283" s="49">
         <v>15</v>
       </c>
       <c r="AJ283" s="49">
+        <f>AG64</f>
+        <v>0</v>
+      </c>
+      <c r="AK283" s="50">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="AM283" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN283" s="43">
+        <f>SUM(AF262:AF269)</f>
+        <v>2254110</v>
+      </c>
+    </row>
+    <row r="284" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y284" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z284" s="93">
+        <f>Z281-Z282</f>
+        <v>316195.98851749999</v>
+      </c>
+      <c r="AA284" s="93"/>
+      <c r="AB284" s="93">
+        <f>AB281-AB282</f>
+        <v>611467.73491124995</v>
+      </c>
+      <c r="AF284" t="s">
+        <v>159</v>
+      </c>
+      <c r="AG284" s="44">
+        <f>AG282*AG283</f>
+        <v>52873.405000000304</v>
+      </c>
+      <c r="AI284" s="49">
+        <v>15</v>
+      </c>
+      <c r="AJ284" s="49">
         <f>AG65</f>
         <v>0</v>
       </c>
-      <c r="AK283" s="50">
-        <f t="shared" si="142"/>
-        <v>0</v>
-      </c>
-      <c r="AM283" t="s">
+      <c r="AK284" s="50">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="AM284" t="s">
         <v>147</v>
       </c>
-      <c r="AN283" s="17">
+      <c r="AN284" s="17">
         <f>W66</f>
         <v>2260662.449</v>
       </c>
     </row>
-    <row r="284" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Z284" t="s">
+    <row r="285" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Z285" t="s">
         <v>136</v>
       </c>
-      <c r="AB284" t="s">
+      <c r="AB285" t="s">
         <v>136</v>
       </c>
-      <c r="AI284" s="49"/>
-      <c r="AJ284" s="49"/>
-      <c r="AK284" s="50"/>
-      <c r="AM284" s="41" t="s">
+      <c r="AI285" s="49"/>
+      <c r="AJ285" s="49"/>
+      <c r="AK285" s="50"/>
+      <c r="AM285" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="AN284" s="45">
-        <f>AN282-AN283</f>
+      <c r="AN285" s="45">
+        <f>AN283-AN284</f>
         <v>-6552.4490000000224</v>
-      </c>
-    </row>
-    <row r="285" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y285" s="41"/>
-      <c r="AB285" s="98"/>
-      <c r="AF285" t="s">
-        <v>145</v>
-      </c>
-      <c r="AG285" s="17">
-        <v>2491500</v>
-      </c>
-      <c r="AI285" s="49"/>
-      <c r="AJ285" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK285" s="50">
-        <f>SUM(AK280:AK283)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="286" spans="24:40" x14ac:dyDescent="0.2">
       <c r="Y286" s="41"/>
+      <c r="AB286" s="97"/>
       <c r="AF286" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AG286" s="17">
-        <f>AC66</f>
-        <v>2544373.4050000003</v>
+        <v>2491500</v>
       </c>
       <c r="AI286" s="49"/>
       <c r="AJ286" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="AK286" s="51">
-        <f>AG287</f>
-        <v>52873.405000000261</v>
+        <v>17</v>
+      </c>
+      <c r="AK286" s="50">
+        <f>SUM(AK281:AK284)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="24:40" x14ac:dyDescent="0.2">
       <c r="Y287" s="41"/>
       <c r="AF287" t="s">
-        <v>159</v>
-      </c>
-      <c r="AG287" s="44">
-        <f>AG286-AG285</f>
-        <v>52873.405000000261</v>
+        <v>141</v>
+      </c>
+      <c r="AG287" s="17">
+        <f>AC66</f>
+        <v>2544373.4050000003</v>
       </c>
       <c r="AI287" s="49"/>
       <c r="AJ287" s="49" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AK287" s="51">
-        <f>+AK286-AK285</f>
+        <f>AG288</f>
         <v>52873.405000000261</v>
       </c>
     </row>
     <row r="288" spans="24:40" x14ac:dyDescent="0.2">
       <c r="Y288" s="41"/>
-    </row>
-    <row r="289" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF288" t="s">
+        <v>159</v>
+      </c>
+      <c r="AG288" s="44">
+        <f>AG287-AG286</f>
+        <v>52873.405000000261</v>
+      </c>
+      <c r="AI288" s="49"/>
+      <c r="AJ288" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="AK288" s="51">
+        <f>+AK287-AK286</f>
+        <v>52873.405000000261</v>
+      </c>
+    </row>
+    <row r="289" spans="25:39" x14ac:dyDescent="0.2">
       <c r="Y289" s="41"/>
-      <c r="AF289" t="s">
+    </row>
+    <row r="290" spans="25:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y290" s="41"/>
+      <c r="AF290" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="290" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y290" s="92"/>
-      <c r="AB290" s="43"/>
-      <c r="AF290" t="s">
+    <row r="291" spans="25:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y291" s="92"/>
+      <c r="AB291" s="43"/>
+      <c r="AF291" t="s">
         <v>155</v>
       </c>
-      <c r="AG290" t="s">
+      <c r="AG291" t="s">
         <v>156</v>
       </c>
-      <c r="AH290" t="s">
+      <c r="AH291" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="291" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y291" s="41"/>
-      <c r="AF291">
-        <f t="shared" ref="AF291:AF296" si="143">O59-500</f>
-        <v>10.76400000000001</v>
-      </c>
-      <c r="AG291" s="17">
-        <f t="shared" ref="AG291:AG297" si="144">X59-V59</f>
-        <v>76</v>
-      </c>
-      <c r="AH291" s="17">
-        <f>AG291*AF291</f>
-        <v>818.06400000000076</v>
-      </c>
-    </row>
-    <row r="292" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="25:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Y292" s="41"/>
       <c r="AF292">
-        <f t="shared" si="143"/>
+        <f t="shared" ref="AF292:AF297" si="147">O59-500</f>
+        <v>10.76400000000001</v>
+      </c>
+      <c r="AG292" s="17">
+        <f t="shared" ref="AG292:AG298" si="148">X59-V59</f>
+        <v>76</v>
+      </c>
+      <c r="AH292" s="17">
+        <f>AG292*AF292</f>
+        <v>818.06400000000076</v>
+      </c>
+    </row>
+    <row r="293" spans="25:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y293" s="41"/>
+      <c r="AF293">
+        <f t="shared" si="147"/>
         <v>10.338999999999999</v>
       </c>
-      <c r="AG292" s="17">
-        <f t="shared" si="144"/>
+      <c r="AG293" s="17">
+        <f t="shared" si="148"/>
         <v>76</v>
       </c>
-      <c r="AH292" s="17">
-        <f t="shared" ref="AH292:AH297" si="145">AG292*AF292</f>
+      <c r="AH293" s="17">
+        <f t="shared" ref="AH293:AH298" si="149">AG293*AF293</f>
         <v>785.7639999999999</v>
       </c>
     </row>
-    <row r="293" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AF293">
-        <f t="shared" si="143"/>
+    <row r="294" spans="25:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF294">
+        <f t="shared" si="147"/>
         <v>9.6879999999999882</v>
       </c>
-      <c r="AG293" s="17">
-        <f t="shared" si="144"/>
+      <c r="AG294" s="17">
+        <f t="shared" si="148"/>
         <v>76</v>
       </c>
-      <c r="AH293" s="17">
-        <f t="shared" si="145"/>
+      <c r="AH294" s="17">
+        <f t="shared" si="149"/>
         <v>736.2879999999991</v>
       </c>
     </row>
-    <row r="294" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AE294" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF294">
-        <f t="shared" si="143"/>
-        <v>10.899999999999977</v>
-      </c>
-      <c r="AG294" s="17">
-        <f t="shared" si="144"/>
-        <v>91</v>
-      </c>
-      <c r="AH294" s="17">
-        <f t="shared" si="145"/>
-        <v>991.89999999999793</v>
-      </c>
-    </row>
-    <row r="295" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="25:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AE295" t="s">
         <v>157</v>
       </c>
       <c r="AF295">
-        <f t="shared" si="143"/>
+        <f t="shared" si="147"/>
         <v>10.899999999999977</v>
       </c>
       <c r="AG295" s="17">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>91</v>
       </c>
       <c r="AH295" s="17">
-        <f t="shared" si="145"/>
+        <f t="shared" si="149"/>
         <v>991.89999999999793</v>
       </c>
     </row>
-    <row r="296" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="25:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AE296" t="s">
         <v>157</v>
       </c>
       <c r="AF296">
-        <f t="shared" si="143"/>
+        <f t="shared" si="147"/>
         <v>10.899999999999977</v>
       </c>
       <c r="AG296" s="17">
-        <f t="shared" si="144"/>
+        <f t="shared" si="148"/>
         <v>91</v>
       </c>
       <c r="AH296" s="17">
-        <f t="shared" si="145"/>
+        <f t="shared" si="149"/>
         <v>991.89999999999793</v>
       </c>
     </row>
-    <row r="297" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="25:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AE297" t="s">
         <v>157</v>
       </c>
       <c r="AF297">
+        <f t="shared" si="147"/>
+        <v>10.899999999999977</v>
+      </c>
+      <c r="AG297" s="17">
+        <f t="shared" si="148"/>
+        <v>91</v>
+      </c>
+      <c r="AH297" s="17">
+        <f t="shared" si="149"/>
+        <v>991.89999999999793</v>
+      </c>
+    </row>
+    <row r="298" spans="25:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE298" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF298">
         <f>O65-300</f>
         <v>6.5400000000000205</v>
       </c>
-      <c r="AG297" s="17">
-        <f t="shared" si="144"/>
+      <c r="AG298" s="17">
+        <f t="shared" si="148"/>
         <v>91</v>
       </c>
-      <c r="AH297" s="17">
-        <f t="shared" si="145"/>
+      <c r="AH298" s="17">
+        <f t="shared" si="149"/>
         <v>595.14000000000192</v>
       </c>
     </row>
-    <row r="298" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AF298" t="s">
+    <row r="299" spans="25:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF299" t="s">
         <v>17</v>
       </c>
-      <c r="AH298" s="17" t="s">
+      <c r="AH299" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="299" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF299">
-        <f>SUM(AF291:AF297)</f>
+    <row r="300" spans="25:39" x14ac:dyDescent="0.2">
+      <c r="AF300">
+        <f>SUM(AF292:AF298)</f>
         <v>70.030999999999949</v>
       </c>
-      <c r="AH299" s="47">
-        <f>SUM(AH291:AH297)</f>
+      <c r="AH300" s="47">
+        <f>SUM(AH292:AH298)</f>
         <v>5910.9559999999956</v>
       </c>
     </row>
-    <row r="300" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF300" s="118" t="s">
+    <row r="301" spans="25:39" x14ac:dyDescent="0.2">
+      <c r="AF301" s="117" t="s">
         <v>158</v>
       </c>
-      <c r="AG300" s="118"/>
-      <c r="AH300" s="118"/>
-    </row>
-    <row r="303" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF303" s="41" t="s">
+      <c r="AG301" s="117"/>
+      <c r="AH301" s="117"/>
+    </row>
+    <row r="304" spans="25:39" x14ac:dyDescent="0.2">
+      <c r="AF304" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="AM303" s="41" t="s">
+      <c r="AM304" s="41" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="304" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF304" t="s">
-        <v>137</v>
-      </c>
-      <c r="AG304">
-        <v>4300</v>
-      </c>
-      <c r="AM304" t="s">
-        <v>137</v>
-      </c>
-      <c r="AN304">
-        <v>4300</v>
       </c>
     </row>
     <row r="305" spans="32:40" x14ac:dyDescent="0.2">
       <c r="AF305" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG305">
+        <v>4300</v>
+      </c>
+      <c r="AM305" t="s">
+        <v>137</v>
+      </c>
+      <c r="AN305">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="306" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF306" t="s">
         <v>138</v>
       </c>
-      <c r="AG305">
+      <c r="AG306">
         <f>O76</f>
         <v>4248.7540000000008</v>
       </c>
-      <c r="AM305" t="s">
+      <c r="AM306" t="s">
         <v>138</v>
       </c>
-      <c r="AN305">
-        <f>AG305</f>
+      <c r="AN306">
+        <f>AG306</f>
         <v>4248.7540000000008</v>
-      </c>
-    </row>
-    <row r="306" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF306" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG306">
-        <f>AG305-AG304</f>
-        <v>-51.245999999999185</v>
       </c>
     </row>
     <row r="307" spans="32:40" x14ac:dyDescent="0.2">
       <c r="AF307" t="s">
-        <v>140</v>
-      </c>
-      <c r="AG307" s="15">
-        <v>705</v>
-      </c>
-      <c r="AM307" t="s">
-        <v>136</v>
-      </c>
-      <c r="AN307" s="43">
-        <f>SUM(AF257:AF260)+190000</f>
-        <v>2718000</v>
+        <v>139</v>
+      </c>
+      <c r="AG307">
+        <f>AG306-AG305</f>
+        <v>-51.245999999999185</v>
       </c>
     </row>
     <row r="308" spans="32:40" x14ac:dyDescent="0.2">
       <c r="AF308" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG308" s="15">
+        <v>705</v>
+      </c>
+      <c r="AM308" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN308" s="43">
+        <f>SUM(AF258:AF261)+190000</f>
+        <v>2718000</v>
+      </c>
+    </row>
+    <row r="309" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF309" t="s">
         <v>141</v>
       </c>
-      <c r="AG308" s="44">
-        <f>AG306*AG307</f>
+      <c r="AG309" s="44">
+        <f>AG307*AG308</f>
         <v>-36128.429999999425</v>
       </c>
-      <c r="AM308" t="s">
+      <c r="AM309" t="s">
         <v>147</v>
       </c>
-      <c r="AN308" s="17">
+      <c r="AN309" s="17">
         <f>W76</f>
         <v>2689678.5019999999</v>
       </c>
     </row>
-    <row r="309" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AM309" t="s">
+    <row r="310" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AM310" t="s">
         <v>148</v>
       </c>
-      <c r="AN309" s="45">
-        <f>AN307-AN308</f>
+      <c r="AN310" s="45">
+        <f>AN308-AN309</f>
         <v>28321.498000000138</v>
-      </c>
-    </row>
-    <row r="310" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF310" t="s">
-        <v>145</v>
-      </c>
-      <c r="AG310" s="15">
-        <v>3031500</v>
       </c>
     </row>
     <row r="311" spans="32:40" x14ac:dyDescent="0.2">
       <c r="AF311" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG311" s="15">
+        <v>3031500</v>
+      </c>
+    </row>
+    <row r="312" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF312" t="s">
         <v>141</v>
       </c>
-      <c r="AG311" s="17">
+      <c r="AG312" s="17">
         <f>AC76</f>
         <v>2995371.57</v>
       </c>
-      <c r="AM311" s="41" t="s">
+      <c r="AM312" s="41" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="312" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF312" t="s">
+    <row r="313" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF313" t="s">
         <v>139</v>
       </c>
-      <c r="AG312" s="44">
-        <f>AG311-AG310</f>
+      <c r="AG313" s="44">
+        <f>AG312-AG311</f>
         <v>-36128.430000000168</v>
       </c>
-      <c r="AM312" t="s">
+      <c r="AM313" t="s">
         <v>137</v>
       </c>
-      <c r="AN312">
+      <c r="AN313">
         <v>4300</v>
       </c>
     </row>
-    <row r="313" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AM313" t="s">
+    <row r="314" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AM314" t="s">
         <v>138</v>
       </c>
-      <c r="AN313">
-        <f>AN305</f>
+      <c r="AN314">
+        <f>AN306</f>
         <v>4248.7540000000008</v>
       </c>
     </row>
-    <row r="314" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF314" s="41" t="s">
+    <row r="315" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF315" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="AG314" s="47">
-        <f>AG287+AG312</f>
+      <c r="AG315" s="47">
+        <f>AG288+AG313</f>
         <v>16744.975000000093</v>
-      </c>
-    </row>
-    <row r="315" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AM315" t="s">
-        <v>136</v>
-      </c>
-      <c r="AN315" s="43">
-        <f>AN307</f>
-        <v>2718000</v>
       </c>
     </row>
     <row r="316" spans="32:40" x14ac:dyDescent="0.2">
       <c r="AM316" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN316" s="43">
+        <f>AN308</f>
+        <v>2718000</v>
+      </c>
+    </row>
+    <row r="317" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AM317" t="s">
         <v>147</v>
       </c>
-      <c r="AN316" s="17">
+      <c r="AN317" s="17">
         <f>W67+W68+W69+W70+W71+W72+W73+(O74*668)+(O75*668)</f>
         <v>2716213.4279999998</v>
       </c>
     </row>
-    <row r="317" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AM317" t="s">
+    <row r="318" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AM318" t="s">
         <v>148</v>
       </c>
-      <c r="AN317" s="45">
-        <f>AN315-AN316</f>
+      <c r="AN318" s="45">
+        <f>AN316-AN317</f>
         <v>1786.5720000001602</v>
-      </c>
-    </row>
-    <row r="319" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF319" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="320" spans="32:40" x14ac:dyDescent="0.2">
       <c r="AF320" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="321" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF321" t="s">
         <v>155</v>
       </c>
-      <c r="AG320" t="s">
+      <c r="AG321" t="s">
         <v>156</v>
       </c>
-      <c r="AH320" t="s">
+      <c r="AH321" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="321" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF321">
-        <f t="shared" ref="AF321:AF328" si="146">O67-500</f>
+    <row r="322" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF322">
+        <f t="shared" ref="AF322:AF329" si="150">O67-500</f>
         <v>11.160000000000025</v>
       </c>
-      <c r="AG321" s="17">
-        <f t="shared" ref="AG321:AG329" si="147">X67-V67</f>
+      <c r="AG322" s="17">
+        <f t="shared" ref="AG322:AG330" si="151">X67-V67</f>
         <v>73</v>
       </c>
-      <c r="AH321" s="17">
-        <f>AF321*AG321</f>
+      <c r="AH322" s="17">
+        <f>AF322*AG322</f>
         <v>814.68000000000188</v>
       </c>
     </row>
-    <row r="322" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF322">
-        <f t="shared" si="146"/>
+    <row r="323" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF323">
+        <f t="shared" si="150"/>
         <v>9.1940000000000168</v>
       </c>
-      <c r="AG322" s="17">
-        <f t="shared" si="147"/>
+      <c r="AG323" s="17">
+        <f t="shared" si="151"/>
         <v>73</v>
       </c>
-      <c r="AH322" s="17">
-        <f t="shared" ref="AH322:AH329" si="148">AF322*AG322</f>
+      <c r="AH323" s="17">
+        <f t="shared" ref="AH323:AH330" si="152">AF323*AG323</f>
         <v>671.16200000000117</v>
       </c>
     </row>
-    <row r="323" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF323">
-        <f t="shared" si="146"/>
+    <row r="324" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF324">
+        <f t="shared" si="150"/>
         <v>-14.966999999999985</v>
       </c>
-      <c r="AG323" s="17">
-        <f t="shared" si="147"/>
+      <c r="AG324" s="17">
+        <f t="shared" si="151"/>
         <v>73</v>
       </c>
-      <c r="AH323" s="17">
-        <f t="shared" si="148"/>
+      <c r="AH324" s="17">
+        <f t="shared" si="152"/>
         <v>-1092.590999999999</v>
       </c>
     </row>
-    <row r="324" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF324">
-        <f t="shared" si="146"/>
+    <row r="325" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF325">
+        <f t="shared" si="150"/>
         <v>10.379999999999995</v>
       </c>
-      <c r="AG324" s="17">
-        <f t="shared" si="147"/>
+      <c r="AG325" s="17">
+        <f t="shared" si="151"/>
         <v>73</v>
       </c>
-      <c r="AH324" s="17">
-        <f t="shared" si="148"/>
+      <c r="AH325" s="17">
+        <f t="shared" si="152"/>
         <v>757.73999999999967</v>
       </c>
     </row>
-    <row r="325" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF325">
-        <f t="shared" si="146"/>
+    <row r="326" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF326">
+        <f t="shared" si="150"/>
         <v>-15.939000000000021</v>
       </c>
-      <c r="AG325" s="17">
-        <f t="shared" si="147"/>
+      <c r="AG326" s="17">
+        <f t="shared" si="151"/>
         <v>71</v>
       </c>
-      <c r="AH325" s="17">
-        <f t="shared" si="148"/>
+      <c r="AH326" s="17">
+        <f t="shared" si="152"/>
         <v>-1131.6690000000015</v>
       </c>
     </row>
-    <row r="326" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF326">
-        <f t="shared" si="146"/>
+    <row r="327" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF327">
+        <f t="shared" si="150"/>
         <v>-15.386000000000024</v>
       </c>
-      <c r="AG326" s="17">
-        <f t="shared" si="147"/>
+      <c r="AG327" s="17">
+        <f t="shared" si="151"/>
         <v>71</v>
       </c>
-      <c r="AH326" s="17">
-        <f t="shared" si="148"/>
+      <c r="AH327" s="17">
+        <f t="shared" si="152"/>
         <v>-1092.4060000000018</v>
       </c>
     </row>
-    <row r="327" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF327">
-        <f t="shared" si="146"/>
+    <row r="328" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF328">
+        <f t="shared" si="150"/>
         <v>-16.12700000000001</v>
       </c>
-      <c r="AG327" s="17">
-        <f t="shared" si="147"/>
+      <c r="AG328" s="17">
+        <f t="shared" si="151"/>
         <v>71</v>
       </c>
-      <c r="AH327" s="17">
-        <f t="shared" si="148"/>
+      <c r="AH328" s="17">
+        <f t="shared" si="152"/>
         <v>-1145.0170000000007</v>
       </c>
     </row>
-    <row r="328" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF328">
-        <f t="shared" si="146"/>
+    <row r="329" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF329">
+        <f t="shared" si="150"/>
         <v>-17.918999999999983</v>
       </c>
-      <c r="AG328" s="17">
-        <f t="shared" si="147"/>
+      <c r="AG329" s="17">
+        <f t="shared" si="151"/>
         <v>71</v>
       </c>
-      <c r="AH328" s="17">
-        <f t="shared" si="148"/>
+      <c r="AH329" s="17">
+        <f t="shared" si="152"/>
         <v>-1272.2489999999989</v>
       </c>
     </row>
-    <row r="329" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF329">
+    <row r="330" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF330">
         <f>O75-300</f>
         <v>-1.6419999999999959</v>
       </c>
-      <c r="AG329" s="17">
-        <f t="shared" si="147"/>
+      <c r="AG330" s="17">
+        <f t="shared" si="151"/>
         <v>71</v>
       </c>
-      <c r="AH329" s="17">
-        <f t="shared" si="148"/>
+      <c r="AH330" s="17">
+        <f t="shared" si="152"/>
         <v>-116.58199999999971</v>
       </c>
     </row>
-    <row r="330" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF330" t="s">
+    <row r="331" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF331" t="s">
         <v>17</v>
       </c>
-      <c r="AH330" s="17" t="s">
+      <c r="AH331" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="331" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF331">
-        <f>SUM(AF321:AF329)</f>
+    <row r="332" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF332">
+        <f>SUM(AF322:AF330)</f>
         <v>-51.245999999999981</v>
       </c>
-      <c r="AH331" s="47">
-        <f>SUM(AH321:AH329)</f>
+      <c r="AH332" s="47">
+        <f>SUM(AH322:AH330)</f>
         <v>-3606.9319999999993</v>
       </c>
     </row>
-    <row r="332" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF332" s="118" t="s">
+    <row r="333" spans="32:34" x14ac:dyDescent="0.2">
+      <c r="AF333" s="117" t="s">
         <v>161</v>
       </c>
-      <c r="AG332" s="118"/>
-      <c r="AH332" s="118"/>
-    </row>
-    <row r="336" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF336" s="117" t="s">
+      <c r="AG333" s="117"/>
+      <c r="AH333" s="117"/>
+    </row>
+    <row r="337" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF337" s="116" t="s">
         <v>151</v>
       </c>
-      <c r="AG336" s="117"/>
-      <c r="AI336" s="118" t="s">
+      <c r="AG337" s="116"/>
+      <c r="AI337" s="117" t="s">
         <v>150</v>
       </c>
-      <c r="AJ336" s="118"/>
-      <c r="AK336" s="46"/>
-      <c r="AL336" s="46"/>
-    </row>
-    <row r="337" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF337" t="s">
+      <c r="AJ337" s="117"/>
+      <c r="AK337" s="46"/>
+      <c r="AL337" s="46"/>
+    </row>
+    <row r="338" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF338" t="s">
         <v>137</v>
       </c>
-      <c r="AG337">
+      <c r="AG338">
         <f>O83</f>
         <v>548.89300000000003</v>
       </c>
-      <c r="AI337" t="s">
+      <c r="AI338" t="s">
         <v>152</v>
       </c>
-      <c r="AJ337">
+      <c r="AJ338">
         <v>500</v>
       </c>
     </row>
-    <row r="338" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF338" t="s">
+    <row r="339" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF339" t="s">
         <v>138</v>
       </c>
-      <c r="AG338">
-        <f>AG337</f>
-        <v>548.89300000000003</v>
-      </c>
-      <c r="AI338" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ338">
+      <c r="AG339">
         <f>AG338</f>
         <v>548.89300000000003</v>
       </c>
-    </row>
-    <row r="339" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF339" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG339">
-        <v>0</v>
+      <c r="AI339" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ339">
+        <f>AG339</f>
+        <v>548.89300000000003</v>
       </c>
     </row>
     <row r="340" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF340" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG340">
-        <v>800</v>
-      </c>
-      <c r="AI340" t="s">
-        <v>136</v>
-      </c>
-      <c r="AJ340" s="43">
-        <f>AF256</f>
-        <v>325000</v>
-      </c>
-      <c r="AK340" s="43"/>
-      <c r="AL340" s="43"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="341" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF341" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG341">
+        <v>800</v>
+      </c>
+      <c r="AI341" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ341" s="43">
+        <f>AF257</f>
+        <v>325000</v>
+      </c>
+      <c r="AK341" s="43"/>
+      <c r="AL341" s="43"/>
+    </row>
+    <row r="342" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF342" t="s">
         <v>141</v>
       </c>
-      <c r="AG341" s="15">
-        <f>AG338*AG340</f>
+      <c r="AG342" s="15">
+        <f>AG339*AG341</f>
         <v>439114.4</v>
       </c>
-      <c r="AI341" t="s">
+      <c r="AI342" t="s">
         <v>153</v>
       </c>
-      <c r="AJ341" s="17">
+      <c r="AJ342" s="17">
         <f>W83</f>
         <v>356780.45</v>
       </c>
-      <c r="AK341" s="17"/>
-      <c r="AL341" s="17"/>
-    </row>
-    <row r="342" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AI342" t="s">
+      <c r="AK342" s="17"/>
+      <c r="AL342" s="17"/>
+    </row>
+    <row r="343" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AI343" t="s">
         <v>148</v>
       </c>
-      <c r="AJ342" s="45">
-        <f>AJ340-AJ341</f>
+      <c r="AJ343" s="45">
+        <f>AJ341-AJ342</f>
         <v>-31780.450000000012</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="AC209:AD209"/>
-    <mergeCell ref="AF221:AJ221"/>
-    <mergeCell ref="AF277:AG277"/>
-    <mergeCell ref="AM277:AN277"/>
-    <mergeCell ref="AI336:AJ336"/>
-    <mergeCell ref="AF336:AG336"/>
-    <mergeCell ref="AF300:AH300"/>
-    <mergeCell ref="AF332:AH332"/>
-    <mergeCell ref="AI277:AK277"/>
-    <mergeCell ref="AD271:AH271"/>
+  <mergeCells count="16">
+    <mergeCell ref="AF222:AJ222"/>
+    <mergeCell ref="AF278:AG278"/>
+    <mergeCell ref="AM278:AN278"/>
+    <mergeCell ref="AI337:AJ337"/>
+    <mergeCell ref="AF337:AG337"/>
+    <mergeCell ref="AF301:AH301"/>
+    <mergeCell ref="AF333:AH333"/>
+    <mergeCell ref="AI278:AK278"/>
+    <mergeCell ref="AD272:AH272"/>
     <mergeCell ref="L58:AD58"/>
     <mergeCell ref="AF61:AH61"/>
     <mergeCell ref="K39:K45"/>
@@ -21609,44 +22143,44 @@
   <sheetData>
     <row r="7" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D7">
         <v>635</v>
       </c>
       <c r="E7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D8">
         <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>344</v>
-      </c>
-      <c r="D9" s="99">
+        <v>341</v>
+      </c>
+      <c r="D9" s="98">
         <f>D7-D8</f>
         <v>600</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D10">
         <f>D9*0.03</f>
@@ -21661,12 +22195,12 @@
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="3:9" x14ac:dyDescent="0.2">
       <c r="E14" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="3:9" x14ac:dyDescent="0.2">
@@ -21678,46 +22212,46 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="116" t="s">
-        <v>354</v>
-      </c>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="116"/>
-      <c r="I18" s="116"/>
-      <c r="J18" s="116"/>
+      <c r="C18" s="115" t="s">
+        <v>351</v>
+      </c>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C19" s="73" t="s">
-        <v>349</v>
-      </c>
-      <c r="D19" s="102">
+        <v>346</v>
+      </c>
+      <c r="D19" s="101">
         <v>0.03</v>
       </c>
-      <c r="E19" s="102">
+      <c r="E19" s="101">
         <v>0.05</v>
       </c>
-      <c r="F19" s="103">
+      <c r="F19" s="102">
         <v>5.5E-2</v>
       </c>
-      <c r="G19" s="102">
+      <c r="G19" s="101">
         <v>0.06</v>
       </c>
-      <c r="H19" s="103">
+      <c r="H19" s="102">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="I19" s="102">
+      <c r="I19" s="101">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J19" s="102">
+      <c r="J19" s="101">
         <v>0.08</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C20" s="73" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D20" s="71">
         <v>550</v>
@@ -21743,7 +22277,7 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C21" s="73" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D21" s="71">
         <f>D20*0.03</f>
@@ -21776,7 +22310,7 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C22" s="73" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D22" s="71">
         <f>D20-D21</f>
@@ -21808,46 +22342,46 @@
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C24" s="116" t="s">
-        <v>355</v>
-      </c>
-      <c r="D24" s="116"/>
-      <c r="E24" s="116"/>
-      <c r="F24" s="116"/>
-      <c r="G24" s="116"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="116"/>
-      <c r="J24" s="116"/>
+      <c r="C24" s="115" t="s">
+        <v>352</v>
+      </c>
+      <c r="D24" s="115"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="115"/>
+      <c r="G24" s="115"/>
+      <c r="H24" s="115"/>
+      <c r="I24" s="115"/>
+      <c r="J24" s="115"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C25" s="73" t="s">
-        <v>349</v>
-      </c>
-      <c r="D25" s="102">
+        <v>346</v>
+      </c>
+      <c r="D25" s="101">
         <v>0.03</v>
       </c>
-      <c r="E25" s="102">
+      <c r="E25" s="101">
         <v>0.05</v>
       </c>
-      <c r="F25" s="103">
+      <c r="F25" s="102">
         <v>5.5E-2</v>
       </c>
-      <c r="G25" s="102">
+      <c r="G25" s="101">
         <v>0.06</v>
       </c>
-      <c r="H25" s="103">
+      <c r="H25" s="102">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="I25" s="102">
+      <c r="I25" s="101">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J25" s="102">
+      <c r="J25" s="101">
         <v>0.08</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C26" s="73" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D26" s="71">
         <v>530</v>
@@ -21873,7 +22407,7 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C27" s="73" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D27" s="71">
         <f>D26*0.03</f>
@@ -21906,7 +22440,7 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C28" s="73" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D28" s="71">
         <f>D26-D27</f>
@@ -21939,11 +22473,11 @@
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C32" s="100"/>
+      <c r="C32" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -21966,33 +22500,33 @@
   <sheetData>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" s="73" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C4" s="73" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D4" s="73" t="s">
+        <v>309</v>
+      </c>
+      <c r="E4" s="73" t="s">
+        <v>311</v>
+      </c>
+      <c r="F4" s="73" t="s">
         <v>312</v>
       </c>
-      <c r="E4" s="73" t="s">
-        <v>314</v>
-      </c>
-      <c r="F4" s="73" t="s">
-        <v>315</v>
-      </c>
       <c r="G4" s="73" t="s">
-        <v>313</v>
-      </c>
-      <c r="I4" s="96" t="s">
-        <v>330</v>
+        <v>310</v>
+      </c>
+      <c r="I4" s="95" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B5" s="52" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D5" s="52">
         <v>19</v>
@@ -22011,10 +22545,10 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B6" s="52" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D6" s="52">
         <v>19</v>
@@ -22033,10 +22567,10 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B7" s="52" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D7" s="52">
         <v>19</v>
@@ -22055,10 +22589,10 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B8" s="52" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D8" s="52">
         <v>19</v>
@@ -22077,43 +22611,43 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B10" s="73" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C10" s="73" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D10" s="73" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E10" s="73" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F10" s="73" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G10" s="73" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H10" s="73" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I10" s="43"/>
       <c r="K10" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="L10" s="41" t="s">
         <v>244</v>
       </c>
       <c r="M10" s="41" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B11" s="52" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D11" s="52">
         <v>19</v>
@@ -22151,10 +22685,10 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12" s="52" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D12" s="52">
         <v>19</v>
@@ -22192,10 +22726,10 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B13" s="52" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D13" s="52">
         <v>19</v>
@@ -22233,10 +22767,10 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B14" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="C14" s="52" t="s">
         <v>321</v>
-      </c>
-      <c r="C14" s="52" t="s">
-        <v>324</v>
       </c>
       <c r="D14" s="52">
         <v>19</v>
@@ -22279,35 +22813,35 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B16" s="73" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C16" s="73" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D16" s="73" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E16" s="73" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F16" s="73" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G16" s="73" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H16" s="73" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K16" s="43"/>
       <c r="M16" s="43"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17" s="52" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D17" s="52">
         <v>19</v>
@@ -22345,10 +22879,10 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18" s="52" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D18" s="52">
         <v>19</v>
@@ -22386,10 +22920,10 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19" s="52" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D19" s="52">
         <v>19</v>
@@ -22427,10 +22961,10 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20" s="52" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D20" s="52">
         <v>19</v>
@@ -22533,7 +23067,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C12">
         <v>0.36</v>
@@ -22561,7 +23095,7 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -22572,7 +23106,7 @@
         <v>421238.73167999997</v>
       </c>
       <c r="F17" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
@@ -22582,7 +23116,7 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E19">
         <v>15300</v>
@@ -22590,40 +23124,40 @@
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C20" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E20">
         <v>1200</v>
       </c>
       <c r="F20" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E21">
         <v>12900</v>
       </c>
       <c r="F21" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E22">
         <v>7000</v>
       </c>
       <c r="F22" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E23">
         <v>5000</v>
@@ -22631,7 +23165,7 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E24">
         <v>10400</v>
@@ -22639,7 +23173,7 @@
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E25">
         <v>5441</v>
@@ -22647,7 +23181,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E26">
         <v>397197.73167999997</v>
@@ -22655,7 +23189,7 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E27">
         <v>65000</v>
@@ -22670,8 +23204,8 @@
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B31" s="104" t="s">
-        <v>379</v>
+      <c r="B31" s="103" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
